--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -6004,7 +6004,7 @@
         <v>88</v>
       </c>
       <c r="U8" s="28">
-        <f t="shared" si="8"/>
+        <f>P8*U$3/1000*100</f>
         <v>1.5439999999999998</v>
       </c>
       <c r="V8" s="58">
@@ -6059,7 +6059,7 @@
         <v>6.2</v>
       </c>
       <c r="F9" s="28">
-        <f t="shared" si="4"/>
+        <f>AVERAGE(U9,AJ9)</f>
         <v>1.496</v>
       </c>
       <c r="G9" s="58">
@@ -6103,7 +6103,7 @@
         <v>62</v>
       </c>
       <c r="U9" s="28">
-        <f t="shared" si="8"/>
+        <f>P9*U$3/1000*100</f>
         <v>1.496</v>
       </c>
       <c r="V9" s="58">

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="648">
   <si>
     <t>f_feed</t>
   </si>
@@ -1981,6 +1981,29 @@
   <si>
     <t>Crop residues</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Setting this parameter too close to 100% may cause problems.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1989,7 +2012,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2177,6 +2200,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2773,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R154"/>
+  <dimension ref="A1:R153"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -3886,35 +3917,13 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" t="s">
-        <v>319</v>
-      </c>
-      <c r="I69" t="s">
-        <v>28</v>
-      </c>
-      <c r="M69" t="s">
-        <v>320</v>
-      </c>
-      <c r="N69" s="3">
-        <v>90</v>
-      </c>
-      <c r="O69" t="s">
-        <v>23</v>
-      </c>
-      <c r="P69" s="3"/>
+        <v>647</v>
+      </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>19</v>
       </c>
-      <c r="B70" t="s">
-        <v>314</v>
-      </c>
-      <c r="E70" t="s">
-        <v>315</v>
-      </c>
       <c r="H70" t="s">
         <v>319</v>
       </c>
@@ -3925,7 +3934,7 @@
         <v>320</v>
       </c>
       <c r="N70" s="3">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="O70" t="s">
         <v>23</v>
@@ -3940,7 +3949,7 @@
         <v>314</v>
       </c>
       <c r="E71" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H71" t="s">
         <v>319</v>
@@ -3963,8 +3972,11 @@
       <c r="A72" t="s">
         <v>19</v>
       </c>
+      <c r="B72" t="s">
+        <v>314</v>
+      </c>
       <c r="E72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H72" t="s">
         <v>319</v>
@@ -3976,7 +3988,7 @@
         <v>320</v>
       </c>
       <c r="N72" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O72" t="s">
         <v>23</v>
@@ -3987,11 +3999,8 @@
       <c r="A73" t="s">
         <v>19</v>
       </c>
-      <c r="B73" t="s">
-        <v>314</v>
-      </c>
       <c r="E73" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H73" t="s">
         <v>319</v>
@@ -4011,31 +4020,34 @@
       <c r="P73" s="3"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N74" s="3"/>
+      <c r="A74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" t="s">
+        <v>314</v>
+      </c>
+      <c r="E74" t="s">
+        <v>318</v>
+      </c>
+      <c r="H74" t="s">
+        <v>319</v>
+      </c>
+      <c r="I74" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74" t="s">
+        <v>320</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>23</v>
+      </c>
       <c r="P74" s="3"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>19</v>
-      </c>
-      <c r="H75" t="s">
-        <v>319</v>
-      </c>
-      <c r="I75" t="s">
-        <v>28</v>
-      </c>
-      <c r="L75">
-        <v>811</v>
-      </c>
-      <c r="M75" t="s">
-        <v>320</v>
-      </c>
-      <c r="N75" s="3">
-        <v>100</v>
-      </c>
-      <c r="O75" t="s">
-        <v>23</v>
-      </c>
+      <c r="N75" s="3"/>
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -4159,6 +4171,12 @@
       <c r="A80" t="s">
         <v>19</v>
       </c>
+      <c r="B80" t="s">
+        <v>314</v>
+      </c>
+      <c r="E80" t="s">
+        <v>315</v>
+      </c>
       <c r="H80" t="s">
         <v>319</v>
       </c>
@@ -4172,7 +4190,7 @@
         <v>320</v>
       </c>
       <c r="N80" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O80" t="s">
         <v>23</v>
@@ -4187,7 +4205,7 @@
         <v>314</v>
       </c>
       <c r="E81" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H81" t="s">
         <v>319</v>
@@ -4213,11 +4231,8 @@
       <c r="A82" t="s">
         <v>19</v>
       </c>
-      <c r="B82" t="s">
-        <v>314</v>
-      </c>
       <c r="E82" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H82" t="s">
         <v>319</v>
@@ -4232,7 +4247,7 @@
         <v>320</v>
       </c>
       <c r="N82" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
         <v>23</v>
@@ -4243,8 +4258,11 @@
       <c r="A83" t="s">
         <v>19</v>
       </c>
+      <c r="B83" t="s">
+        <v>314</v>
+      </c>
       <c r="E83" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H83" t="s">
         <v>319</v>
@@ -4267,88 +4285,72 @@
       <c r="P83" s="3"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>19</v>
-      </c>
-      <c r="B84" t="s">
-        <v>314</v>
-      </c>
-      <c r="E84" t="s">
-        <v>318</v>
-      </c>
-      <c r="H84" t="s">
+      <c r="N84" s="3"/>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>377</v>
+      </c>
+      <c r="H85" t="s">
         <v>319</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I85" t="s">
         <v>28</v>
       </c>
-      <c r="L84">
-        <v>812</v>
-      </c>
-      <c r="M84" t="s">
+      <c r="M85" t="s">
         <v>320</v>
       </c>
-      <c r="N84" s="3">
-        <v>0</v>
-      </c>
-      <c r="O84" t="s">
+      <c r="N85" s="3">
+        <v>10</v>
+      </c>
+      <c r="O85" t="s">
         <v>23</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N85" s="3"/>
       <c r="P85" s="3"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>377</v>
-      </c>
-      <c r="H86" t="s">
-        <v>319</v>
-      </c>
-      <c r="I86" t="s">
-        <v>28</v>
-      </c>
-      <c r="M86" t="s">
-        <v>320</v>
-      </c>
-      <c r="N86" s="3">
-        <v>10</v>
-      </c>
-      <c r="O86" t="s">
+      <c r="N86" s="3"/>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M88" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="N88" s="6">
+        <v>0</v>
+      </c>
+      <c r="O88" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N87" s="3"/>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
+      <c r="P88" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M89" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N89" s="6">
         <v>0</v>
@@ -4361,29 +4363,39 @@
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M90" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="N90" s="6">
-        <v>0</v>
-      </c>
-      <c r="O90" s="6" t="s">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" t="s">
+        <v>314</v>
+      </c>
+      <c r="E90" t="s">
+        <v>315</v>
+      </c>
+      <c r="G90" t="s">
+        <v>632</v>
+      </c>
+      <c r="M90" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="N90" s="21">
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O90" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P90" s="6" t="s">
-        <v>29</v>
+      <c r="P90" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>19</v>
       </c>
-      <c r="B91" t="s">
-        <v>314</v>
-      </c>
-      <c r="E91" t="s">
-        <v>315</v>
-      </c>
       <c r="G91" t="s">
         <v>632</v>
       </c>
@@ -4391,14 +4403,14 @@
         <v>378</v>
       </c>
       <c r="N91" s="21">
-        <f>(0.8*20+0.2*2)</f>
-        <v>16.399999999999999</v>
+        <f>(0.6*20+0.4*2)</f>
+        <v>12.8</v>
       </c>
       <c r="O91" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P91" s="21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q91" t="s">
         <v>639</v>
@@ -4406,7 +4418,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="G92" t="s">
         <v>632</v>
@@ -4415,14 +4427,13 @@
         <v>378</v>
       </c>
       <c r="N92" s="21">
-        <f>(0.6*20+0.4*2)</f>
-        <v>12.8</v>
+        <v>2</v>
       </c>
       <c r="O92" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P92" s="21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q92" t="s">
         <v>639</v>
@@ -4430,7 +4441,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G93" t="s">
         <v>632</v>
@@ -4453,22 +4464,28 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>377</v>
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>314</v>
+      </c>
+      <c r="E94" t="s">
+        <v>315</v>
       </c>
       <c r="G94" t="s">
         <v>632</v>
       </c>
       <c r="M94" s="21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N94" s="21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O94" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P94" s="21" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q94" t="s">
         <v>639</v>
@@ -4478,11 +4495,8 @@
       <c r="A95" t="s">
         <v>19</v>
       </c>
-      <c r="B95" t="s">
-        <v>314</v>
-      </c>
       <c r="E95" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G95" t="s">
         <v>632</v>
@@ -4507,9 +4521,6 @@
       <c r="A96" t="s">
         <v>19</v>
       </c>
-      <c r="E96" t="s">
-        <v>317</v>
-      </c>
       <c r="G96" t="s">
         <v>632</v>
       </c>
@@ -4517,13 +4528,14 @@
         <v>379</v>
       </c>
       <c r="N96" s="21">
-        <v>5</v>
+        <f>0.9*5+0.1*15</f>
+        <v>6</v>
       </c>
       <c r="O96" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P96" s="21" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q96" t="s">
         <v>639</v>
@@ -4531,7 +4543,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="G97" t="s">
         <v>632</v>
@@ -4540,22 +4552,19 @@
         <v>379</v>
       </c>
       <c r="N97" s="21">
-        <f>0.9*5+0.1*15</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O97" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P97" s="21" t="s">
-        <v>386</v>
-      </c>
+      <c r="P97" s="21"/>
       <c r="Q97" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G98" t="s">
         <v>632</v>
@@ -4575,17 +4584,17 @@
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>377</v>
-      </c>
+      <c r="A99" s="22"/>
+      <c r="B99" s="22"/>
+      <c r="E99" s="22"/>
       <c r="G99" t="s">
-        <v>632</v>
+        <v>301</v>
       </c>
       <c r="M99" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N99" s="21">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O99" s="21" t="s">
         <v>23</v>
@@ -4596,44 +4605,56 @@
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="22"/>
-      <c r="B100" s="22"/>
-      <c r="E100" s="22"/>
+      <c r="A100" s="22" t="str">
+        <f>A94</f>
+        <v>cattle</v>
+      </c>
+      <c r="B100" s="22" t="str">
+        <f>B94</f>
+        <v>dairy</v>
+      </c>
+      <c r="E100" s="22" t="str">
+        <f t="shared" ref="E100:E101" si="0">E94</f>
+        <v>cows</v>
+      </c>
       <c r="G100" t="s">
         <v>301</v>
       </c>
-      <c r="M100" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N100" s="21">
+      <c r="M100" s="22" t="str">
+        <f t="shared" ref="M100:Q104" si="1">M94</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N100" s="22">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="O100" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P100" s="21"/>
-      <c r="Q100" t="s">
-        <v>639</v>
+      <c r="O100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="str">
-        <f>A95</f>
+        <f t="shared" ref="A101:A104" si="2">A95</f>
         <v>cattle</v>
       </c>
-      <c r="B101" s="22" t="str">
-        <f>B95</f>
-        <v>dairy</v>
-      </c>
       <c r="E101" s="22" t="str">
-        <f t="shared" ref="E101:E102" si="0">E95</f>
-        <v>cows</v>
+        <f t="shared" si="0"/>
+        <v>bulls</v>
       </c>
       <c r="G101" t="s">
         <v>301</v>
       </c>
       <c r="M101" s="22" t="str">
-        <f t="shared" ref="M101:Q105" si="1">M95</f>
+        <f t="shared" si="1"/>
         <v>feeding_losses</v>
       </c>
       <c r="N101" s="22">
@@ -4655,12 +4676,8 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="22" t="str">
-        <f t="shared" ref="A102:A105" si="2">A96</f>
+        <f t="shared" si="2"/>
         <v>cattle</v>
-      </c>
-      <c r="E102" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>bulls</v>
       </c>
       <c r="G102" t="s">
         <v>301</v>
@@ -4671,7 +4688,7 @@
       </c>
       <c r="N102" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O102" s="22" t="str">
         <f t="shared" si="1"/>
@@ -4679,7 +4696,7 @@
       </c>
       <c r="P102" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
+        <v>10% feeding on pasture</v>
       </c>
       <c r="Q102" s="22" t="str">
         <f t="shared" si="1"/>
@@ -4689,7 +4706,7 @@
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>cattle</v>
+        <v>sheep</v>
       </c>
       <c r="G103" t="s">
         <v>301</v>
@@ -4700,16 +4717,13 @@
       </c>
       <c r="N103" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O103" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P103" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
-      </c>
+      <c r="P103" s="22"/>
       <c r="Q103" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
@@ -4718,7 +4732,7 @@
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>sheep</v>
+        <v>horses</v>
       </c>
       <c r="G104" t="s">
         <v>301</v>
@@ -4742,67 +4756,74 @@
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>horses</v>
-      </c>
       <c r="G105" t="s">
-        <v>301</v>
-      </c>
-      <c r="M105" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N105" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="O105" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P105" s="22"/>
-      <c r="Q105" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
+        <v>633</v>
+      </c>
+      <c r="M105" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="N105" s="21">
+        <v>5</v>
+      </c>
+      <c r="O105" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P105" s="21"/>
+      <c r="Q105" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="22" t="str">
+        <f>A94</f>
+        <v>cattle</v>
+      </c>
+      <c r="B106" s="22" t="str">
+        <f>B94</f>
+        <v>dairy</v>
+      </c>
+      <c r="E106" s="22" t="str">
+        <f t="shared" ref="E106:E107" si="3">E94</f>
+        <v>cows</v>
+      </c>
       <c r="G106" t="s">
         <v>633</v>
       </c>
-      <c r="M106" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N106" s="21">
+      <c r="M106" s="22" t="str">
+        <f t="shared" ref="M106:Q110" si="4">M94</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N106" s="22">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O106" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P106" s="21"/>
-      <c r="Q106" t="s">
-        <v>639</v>
+      <c r="O106" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P106" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q106" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="22" t="str">
-        <f>A95</f>
+        <f t="shared" ref="A107:A110" si="5">A95</f>
         <v>cattle</v>
       </c>
-      <c r="B107" s="22" t="str">
-        <f>B95</f>
-        <v>dairy</v>
-      </c>
       <c r="E107" s="22" t="str">
-        <f t="shared" ref="E107:E108" si="3">E95</f>
-        <v>cows</v>
+        <f t="shared" si="3"/>
+        <v>bulls</v>
       </c>
       <c r="G107" t="s">
         <v>633</v>
       </c>
       <c r="M107" s="22" t="str">
-        <f t="shared" ref="M107:Q111" si="4">M95</f>
+        <f t="shared" si="4"/>
         <v>feeding_losses</v>
       </c>
       <c r="N107" s="22">
@@ -4824,12 +4845,8 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="str">
-        <f t="shared" ref="A108:A111" si="5">A96</f>
+        <f t="shared" si="5"/>
         <v>cattle</v>
-      </c>
-      <c r="E108" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
       </c>
       <c r="G108" t="s">
         <v>633</v>
@@ -4840,7 +4857,7 @@
       </c>
       <c r="N108" s="22">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O108" s="22" t="str">
         <f t="shared" si="4"/>
@@ -4848,7 +4865,7 @@
       </c>
       <c r="P108" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
+        <v>10% feeding on pasture</v>
       </c>
       <c r="Q108" s="22" t="str">
         <f t="shared" si="4"/>
@@ -4858,7 +4875,7 @@
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="str">
         <f t="shared" si="5"/>
-        <v>cattle</v>
+        <v>sheep</v>
       </c>
       <c r="G109" t="s">
         <v>633</v>
@@ -4869,25 +4886,22 @@
       </c>
       <c r="N109" s="22">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O109" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
-      </c>
+      <c r="P109" s="21"/>
       <c r="Q109" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="Q109:Q110" si="6">Q97</f>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="22" t="str">
         <f t="shared" si="5"/>
-        <v>sheep</v>
+        <v>horses</v>
       </c>
       <c r="G110" t="s">
         <v>633</v>
@@ -4906,39 +4920,26 @@
       </c>
       <c r="P110" s="21"/>
       <c r="Q110" s="22" t="str">
-        <f t="shared" ref="Q110:Q111" si="6">Q98</f>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>horses</v>
-      </c>
-      <c r="G111" t="s">
-        <v>633</v>
-      </c>
-      <c r="M111" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N111" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O111" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P111" s="21"/>
-      <c r="Q111" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N111" s="3"/>
+      <c r="P111" s="21"/>
+    </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N112" s="3"/>
-      <c r="P112" s="21"/>
+      <c r="A112" s="3"/>
+      <c r="G112" t="s">
+        <v>634</v>
+      </c>
+      <c r="M112" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="N112" s="21"/>
+      <c r="P112" s="3" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
@@ -4946,32 +4947,32 @@
         <v>634</v>
       </c>
       <c r="M113" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N113" s="21"/>
+        <v>379</v>
+      </c>
+      <c r="N113" s="21">
+        <v>2</v>
+      </c>
+      <c r="O113" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="P113" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="G114" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M114" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="N114" s="21">
-        <v>2</v>
-      </c>
-      <c r="O114" s="21" t="s">
-        <v>23</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N114" s="21"/>
       <c r="P114" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -4980,67 +4981,82 @@
         <v>635</v>
       </c>
       <c r="M115" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N115" s="21"/>
+        <v>379</v>
+      </c>
+      <c r="N115" s="21">
+        <v>3</v>
+      </c>
+      <c r="O115" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="P115" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="3"/>
-      <c r="G116" t="s">
-        <v>635</v>
-      </c>
-      <c r="M116" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="N116" s="21">
-        <v>3</v>
-      </c>
-      <c r="O116" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P116" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>638</v>
-      </c>
+      <c r="N116" s="3"/>
+      <c r="P116" s="21"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N117" s="3"/>
-      <c r="P117" s="21"/>
+      <c r="A117" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="2"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
-      <c r="L118" s="2"/>
-      <c r="M118" s="2"/>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" s="2"/>
-      <c r="Q118" s="2"/>
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="N118" s="21"/>
+      <c r="P118" s="21" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>19</v>
-      </c>
-      <c r="N119" s="21"/>
-      <c r="P119" s="21" t="s">
-        <v>601</v>
-      </c>
+      <c r="A119" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N119" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="P119" s="3"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
@@ -5049,9 +5065,7 @@
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
-      <c r="E120" s="3" t="s">
-        <v>485</v>
-      </c>
+      <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
@@ -5063,7 +5077,7 @@
         <v>486</v>
       </c>
       <c r="N120" s="3">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="O120" s="3" t="s">
         <v>487</v>
@@ -5071,40 +5085,32 @@
       <c r="P120" s="3"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="3"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3"/>
-      <c r="L121" s="3"/>
-      <c r="M121" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="N121" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="O121" s="3" t="s">
-        <v>487</v>
+      <c r="A121" t="s">
+        <v>377</v>
+      </c>
+      <c r="M121" t="s">
+        <v>488</v>
+      </c>
+      <c r="N121" s="21">
+        <v>18</v>
+      </c>
+      <c r="O121" t="s">
+        <v>489</v>
       </c>
       <c r="P121" s="3"/>
+      <c r="Q121" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
       <c r="M122" t="s">
         <v>488</v>
       </c>
       <c r="N122" s="21">
-        <v>18</v>
+        <v>1.5</v>
       </c>
       <c r="O122" t="s">
         <v>489</v>
@@ -5116,13 +5122,13 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="M123" t="s">
         <v>488</v>
       </c>
       <c r="N123" s="21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O123" t="s">
         <v>489</v>
@@ -5133,28 +5139,28 @@
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>374</v>
-      </c>
-      <c r="M124" t="s">
-        <v>488</v>
-      </c>
-      <c r="N124" s="21">
-        <v>0</v>
-      </c>
-      <c r="O124" t="s">
-        <v>489</v>
-      </c>
+      <c r="N124" s="21"/>
       <c r="P124" s="3"/>
-      <c r="Q124" t="s">
-        <v>490</v>
-      </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N125" s="21"/>
-      <c r="P125" s="3"/>
+      <c r="M125" t="s">
+        <v>602</v>
+      </c>
+      <c r="N125" s="21">
+        <v>1</v>
+      </c>
+      <c r="O125" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="P125" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q125" s="21"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
       <c r="M126" t="s">
         <v>602</v>
       </c>
@@ -5164,15 +5170,19 @@
       <c r="O126" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="P126" s="21" t="s">
-        <v>604</v>
-      </c>
+      <c r="P126" s="21"/>
       <c r="Q126" s="21"/>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>19</v>
       </c>
+      <c r="B127" t="s">
+        <v>314</v>
+      </c>
+      <c r="E127" t="s">
+        <v>315</v>
+      </c>
       <c r="M127" t="s">
         <v>602</v>
       </c>
@@ -5193,7 +5203,7 @@
         <v>314</v>
       </c>
       <c r="E128" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M128" t="s">
         <v>602</v>
@@ -5212,7 +5222,7 @@
         <v>19</v>
       </c>
       <c r="B129" t="s">
-        <v>314</v>
+        <v>605</v>
       </c>
       <c r="E129" t="s">
         <v>317</v>
@@ -5230,86 +5240,72 @@
       <c r="Q129" s="21"/>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>19</v>
-      </c>
-      <c r="B130" t="s">
-        <v>605</v>
-      </c>
-      <c r="E130" t="s">
-        <v>317</v>
-      </c>
-      <c r="M130" t="s">
-        <v>602</v>
-      </c>
-      <c r="N130" s="21">
-        <v>1</v>
-      </c>
-      <c r="O130" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="P130" s="21"/>
-      <c r="Q130" s="21"/>
+      <c r="N130" s="3"/>
+      <c r="P130" s="3"/>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N131" s="3"/>
-      <c r="P131" s="3"/>
+      <c r="A131" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q131" s="2"/>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2"/>
-      <c r="M132" s="2"/>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q132" s="2"/>
+      <c r="L132" s="103" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L133" s="103" t="s">
-        <v>617</v>
-      </c>
+      <c r="M133" t="s">
+        <v>375</v>
+      </c>
+      <c r="N133" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="O133" t="s">
+        <v>598</v>
+      </c>
+      <c r="P133" s="3"/>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M134" t="s">
-        <v>375</v>
+        <v>476</v>
       </c>
       <c r="N134" s="21" t="s">
         <v>614</v>
       </c>
       <c r="O134" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="P134" s="3"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M135" t="s">
-        <v>476</v>
+      <c r="M135" s="37" t="s">
+        <v>608</v>
       </c>
       <c r="N135" s="21" t="s">
         <v>614</v>
       </c>
-      <c r="O135" t="s">
-        <v>597</v>
-      </c>
-      <c r="P135" s="3"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M136" s="37" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N136" s="21" t="s">
         <v>614</v>
@@ -5317,7 +5313,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M137" s="37" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N137" s="21" t="s">
         <v>614</v>
@@ -5325,175 +5321,167 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M138" s="37" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N138" s="21" t="s">
         <v>614</v>
       </c>
+      <c r="P138" s="3"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M139" s="37" t="s">
-        <v>611</v>
-      </c>
-      <c r="N139" s="21" t="s">
-        <v>614</v>
-      </c>
-      <c r="P139" s="3"/>
+      <c r="L139" s="103" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L140" s="103" t="s">
-        <v>616</v>
+      <c r="M140" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="O140" t="s">
+        <v>622</v>
+      </c>
+      <c r="P140" s="21" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M141" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="N141" s="21" t="s">
         <v>615</v>
       </c>
       <c r="O141" t="s">
-        <v>622</v>
-      </c>
-      <c r="P141" s="21" t="s">
-        <v>595</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="P141" s="3"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M142" t="s">
-        <v>588</v>
+        <v>477</v>
       </c>
       <c r="N142" s="21" t="s">
         <v>615</v>
       </c>
       <c r="O142" t="s">
-        <v>596</v>
-      </c>
-      <c r="P142" s="3"/>
+        <v>478</v>
+      </c>
+      <c r="P142" s="21" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M143" t="s">
-        <v>477</v>
-      </c>
-      <c r="N143" s="21" t="s">
-        <v>615</v>
-      </c>
-      <c r="O143" t="s">
-        <v>478</v>
-      </c>
-      <c r="P143" s="21" t="s">
-        <v>479</v>
+      <c r="L143" s="103" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L144" s="103" t="s">
-        <v>618</v>
+      <c r="M144" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="O144" t="s">
+        <v>622</v>
+      </c>
+      <c r="P144" s="21" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="145" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M145" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="N145" s="21" t="s">
         <v>625</v>
       </c>
       <c r="O145" t="s">
+        <v>596</v>
+      </c>
+      <c r="P145" s="3"/>
+    </row>
+    <row r="146" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L146" s="103" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="147" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M147" t="s">
+        <v>17</v>
+      </c>
+      <c r="N147" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="O147" t="s">
         <v>622</v>
       </c>
-      <c r="P145" s="21" t="s">
+      <c r="P147" s="21" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="146" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M146" t="s">
-        <v>588</v>
-      </c>
-      <c r="N146" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="O146" t="s">
-        <v>596</v>
-      </c>
-      <c r="P146" s="3"/>
-    </row>
-    <row r="147" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L147" s="103" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="148" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M148" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="N148" s="21" t="s">
         <v>626</v>
       </c>
       <c r="O148" t="s">
-        <v>622</v>
-      </c>
-      <c r="P148" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="P148" s="3"/>
+    </row>
+    <row r="149" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L149" s="103" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="150" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M150" t="s">
+        <v>17</v>
+      </c>
+      <c r="N150" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="O150" t="s">
+        <v>623</v>
+      </c>
+      <c r="P150" s="21" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="149" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M149" t="s">
-        <v>588</v>
-      </c>
-      <c r="N149" s="21" t="s">
-        <v>626</v>
-      </c>
-      <c r="O149" t="s">
-        <v>596</v>
-      </c>
-      <c r="P149" s="3"/>
-    </row>
-    <row r="150" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L150" s="103" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="151" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M151" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="N151" s="21" t="s">
         <v>627</v>
       </c>
       <c r="O151" t="s">
-        <v>623</v>
-      </c>
-      <c r="P151" s="21" t="s">
-        <v>595</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="P151" s="3"/>
     </row>
     <row r="152" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M152" t="s">
-        <v>588</v>
-      </c>
-      <c r="N152" s="21" t="s">
-        <v>627</v>
-      </c>
-      <c r="O152" t="s">
-        <v>596</v>
-      </c>
-      <c r="P152" s="3"/>
+      <c r="L152" s="103" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="153" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L153" s="103" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="154" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M154" t="s">
+      <c r="M153" t="s">
         <v>613</v>
       </c>
-      <c r="N154" s="21" t="s">
+      <c r="N153" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="O154" t="s">
+      <c r="O153" t="s">
         <v>624</v>
       </c>
-      <c r="P154" s="21"/>
+      <c r="P153" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="648">
   <si>
     <t>f_feed</t>
   </si>
@@ -2804,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R153"/>
+  <dimension ref="A1:R158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -4310,47 +4310,54 @@
       <c r="P85" s="3"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N86" s="3"/>
+      <c r="A86" t="s">
+        <v>381</v>
+      </c>
+      <c r="H86" t="s">
+        <v>319</v>
+      </c>
+      <c r="I86" t="s">
+        <v>28</v>
+      </c>
+      <c r="M86" t="s">
+        <v>320</v>
+      </c>
+      <c r="N86" s="3">
+        <v>90</v>
+      </c>
+      <c r="O86" t="s">
+        <v>23</v>
+      </c>
       <c r="P86" s="3"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="N87" s="3"/>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M88" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="N88" s="6">
-        <v>0</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="2"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M89" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N89" s="6">
         <v>0</v>
@@ -4363,39 +4370,29 @@
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>19</v>
-      </c>
-      <c r="B90" t="s">
-        <v>314</v>
-      </c>
-      <c r="E90" t="s">
-        <v>315</v>
-      </c>
-      <c r="G90" t="s">
-        <v>632</v>
-      </c>
-      <c r="M90" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N90" s="21">
-        <f>(0.8*20+0.2*2)</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="O90" s="21" t="s">
+      <c r="M90" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="N90" s="6">
+        <v>0</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P90" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>639</v>
+      <c r="P90" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>19</v>
       </c>
+      <c r="B91" t="s">
+        <v>314</v>
+      </c>
+      <c r="E91" t="s">
+        <v>315</v>
+      </c>
       <c r="G91" t="s">
         <v>632</v>
       </c>
@@ -4403,37 +4400,38 @@
         <v>378</v>
       </c>
       <c r="N91" s="21">
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O91" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P91" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" t="s">
+        <v>632</v>
+      </c>
+      <c r="M92" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="N92" s="21">
         <f>(0.6*20+0.4*2)</f>
         <v>12.8</v>
       </c>
-      <c r="O91" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P91" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>381</v>
-      </c>
-      <c r="G92" t="s">
-        <v>632</v>
-      </c>
-      <c r="M92" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N92" s="21">
-        <v>2</v>
-      </c>
       <c r="O92" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P92" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q92" t="s">
         <v>639</v>
@@ -4441,7 +4439,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G93" t="s">
         <v>632</v>
@@ -4464,63 +4462,43 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B94" t="s">
-        <v>314</v>
-      </c>
-      <c r="E94" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="G94" t="s">
         <v>632</v>
       </c>
       <c r="M94" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N94" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O94" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P94" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q94" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" t="s">
-        <v>317</v>
-      </c>
-      <c r="G95" t="s">
-        <v>632</v>
-      </c>
-      <c r="M95" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="N95" s="21">
-        <v>5</v>
-      </c>
-      <c r="O95" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P95" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>639</v>
-      </c>
+      <c r="M95" s="21"/>
+      <c r="N95" s="21"/>
+      <c r="O95" s="21"/>
+      <c r="P95" s="21"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>19</v>
       </c>
+      <c r="B96" t="s">
+        <v>314</v>
+      </c>
+      <c r="E96" t="s">
+        <v>315</v>
+      </c>
       <c r="G96" t="s">
         <v>632</v>
       </c>
@@ -4528,73 +4506,80 @@
         <v>379</v>
       </c>
       <c r="N96" s="21">
+        <v>5</v>
+      </c>
+      <c r="O96" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P96" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" t="s">
+        <v>317</v>
+      </c>
+      <c r="G97" t="s">
+        <v>632</v>
+      </c>
+      <c r="M97" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="N97" s="21">
+        <v>5</v>
+      </c>
+      <c r="O97" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P97" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" t="s">
+        <v>632</v>
+      </c>
+      <c r="M98" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="N98" s="21">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="O96" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P96" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>381</v>
-      </c>
-      <c r="G97" t="s">
-        <v>632</v>
-      </c>
-      <c r="M97" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="N97" s="21">
-        <v>15</v>
-      </c>
-      <c r="O97" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P97" s="21"/>
-      <c r="Q97" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>377</v>
-      </c>
-      <c r="G98" t="s">
-        <v>632</v>
-      </c>
-      <c r="M98" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="N98" s="21">
-        <v>15</v>
-      </c>
       <c r="O98" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P98" s="21"/>
+      <c r="P98" s="21" t="s">
+        <v>386</v>
+      </c>
       <c r="Q98" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" s="22"/>
-      <c r="B99" s="22"/>
-      <c r="E99" s="22"/>
+      <c r="A99" t="s">
+        <v>381</v>
+      </c>
       <c r="G99" t="s">
-        <v>301</v>
+        <v>632</v>
       </c>
       <c r="M99" s="21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N99" s="21">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O99" s="21" t="s">
         <v>23</v>
@@ -4605,125 +4590,85 @@
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="22" t="str">
-        <f>A94</f>
+      <c r="A100" t="s">
+        <v>377</v>
+      </c>
+      <c r="G100" t="s">
+        <v>632</v>
+      </c>
+      <c r="M100" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="N100" s="21">
+        <v>15</v>
+      </c>
+      <c r="O100" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P100" s="21"/>
+      <c r="Q100" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
+      <c r="O101" s="21"/>
+      <c r="P101" s="21"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="22"/>
+      <c r="B102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="G102" t="s">
+        <v>301</v>
+      </c>
+      <c r="M102" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="N102" s="21">
+        <v>5</v>
+      </c>
+      <c r="O102" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P102" s="21"/>
+      <c r="Q102" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="22" t="str">
+        <f>A96</f>
         <v>cattle</v>
       </c>
-      <c r="B100" s="22" t="str">
-        <f>B94</f>
+      <c r="B103" s="22" t="str">
+        <f>B96</f>
         <v>dairy</v>
       </c>
-      <c r="E100" s="22" t="str">
-        <f t="shared" ref="E100:E101" si="0">E94</f>
+      <c r="E103" s="22" t="str">
+        <f t="shared" ref="E103:E104" si="0">E96</f>
         <v>cows</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G103" t="s">
         <v>301</v>
       </c>
-      <c r="M100" s="22" t="str">
-        <f t="shared" ref="M100:Q104" si="1">M94</f>
+      <c r="M103" s="22" t="str">
+        <f t="shared" ref="M103:Q107" si="1">M96</f>
         <v>feeding_losses</v>
       </c>
-      <c r="N100" s="22">
+      <c r="N103" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
-      </c>
-      <c r="O100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="22" t="str">
-        <f t="shared" ref="A101:A104" si="2">A95</f>
-        <v>cattle</v>
-      </c>
-      <c r="E101" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>bulls</v>
-      </c>
-      <c r="G101" t="s">
-        <v>301</v>
-      </c>
-      <c r="M101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N101" s="22">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="O101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>cattle</v>
-      </c>
-      <c r="G102" t="s">
-        <v>301</v>
-      </c>
-      <c r="M102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N102" s="22">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="O102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="Q102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>sheep</v>
-      </c>
-      <c r="G103" t="s">
-        <v>301</v>
-      </c>
-      <c r="M103" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N103" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
       </c>
       <c r="O103" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P103" s="22"/>
+      <c r="P103" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q103" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
@@ -4731,8 +4676,12 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>horses</v>
+        <f t="shared" ref="A104:A107" si="2">A97</f>
+        <v>cattle</v>
+      </c>
+      <c r="E104" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>bulls</v>
       </c>
       <c r="G104" t="s">
         <v>301</v>
@@ -4743,745 +4692,844 @@
       </c>
       <c r="N104" s="22">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O104" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P104" s="22"/>
+      <c r="P104" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q104" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>cattle</v>
+      </c>
       <c r="G105" t="s">
-        <v>633</v>
-      </c>
-      <c r="M105" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="N105" s="21">
-        <v>5</v>
-      </c>
-      <c r="O105" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P105" s="21"/>
-      <c r="Q105" t="s">
-        <v>639</v>
+        <v>301</v>
+      </c>
+      <c r="M105" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N105" s="22">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O105" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P105" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="Q105" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="22" t="str">
-        <f>A94</f>
+        <f t="shared" si="2"/>
+        <v>sheep</v>
+      </c>
+      <c r="G106" t="s">
+        <v>301</v>
+      </c>
+      <c r="M106" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N106" s="22">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O106" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P106" s="22"/>
+      <c r="Q106" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>horses</v>
+      </c>
+      <c r="G107" t="s">
+        <v>301</v>
+      </c>
+      <c r="M107" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N107" s="22">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O107" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P107" s="22"/>
+      <c r="Q107" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" s="22"/>
+      <c r="M108" s="22"/>
+      <c r="N108" s="22"/>
+      <c r="O108" s="22"/>
+      <c r="P108" s="22"/>
+      <c r="Q108" s="22"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G109" t="s">
+        <v>633</v>
+      </c>
+      <c r="M109" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="N109" s="21">
+        <v>5</v>
+      </c>
+      <c r="O109" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P109" s="21"/>
+      <c r="Q109" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="str">
+        <f>A96</f>
         <v>cattle</v>
       </c>
-      <c r="B106" s="22" t="str">
-        <f>B94</f>
+      <c r="B110" s="22" t="str">
+        <f>B96</f>
         <v>dairy</v>
       </c>
-      <c r="E106" s="22" t="str">
-        <f t="shared" ref="E106:E107" si="3">E94</f>
+      <c r="E110" s="22" t="str">
+        <f t="shared" ref="E110:E111" si="3">E96</f>
         <v>cows</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G110" t="s">
         <v>633</v>
       </c>
-      <c r="M106" s="22" t="str">
-        <f t="shared" ref="M106:Q110" si="4">M94</f>
+      <c r="M110" s="22" t="str">
+        <f t="shared" ref="M110:Q114" si="4">M96</f>
         <v>feeding_losses</v>
       </c>
-      <c r="N106" s="22">
+      <c r="N110" s="22">
         <f t="shared" si="4"/>
         <v>5</v>
-      </c>
-      <c r="O106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107" s="22" t="str">
-        <f t="shared" ref="A107:A110" si="5">A95</f>
-        <v>cattle</v>
-      </c>
-      <c r="E107" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
-      </c>
-      <c r="G107" t="s">
-        <v>633</v>
-      </c>
-      <c r="M107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N107" s="22">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>cattle</v>
-      </c>
-      <c r="G108" t="s">
-        <v>633</v>
-      </c>
-      <c r="M108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N108" s="22">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="O108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="Q108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>sheep</v>
-      </c>
-      <c r="G109" t="s">
-        <v>633</v>
-      </c>
-      <c r="M109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N109" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P109" s="21"/>
-      <c r="Q109" s="22" t="str">
-        <f t="shared" ref="Q109:Q110" si="6">Q97</f>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>horses</v>
-      </c>
-      <c r="G110" t="s">
-        <v>633</v>
-      </c>
-      <c r="M110" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N110" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
       </c>
       <c r="O110" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P110" s="21"/>
+      <c r="P110" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q110" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="22" t="str">
+        <f t="shared" ref="A111:A114" si="5">A97</f>
+        <v>cattle</v>
+      </c>
+      <c r="E111" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
+      </c>
+      <c r="G111" t="s">
+        <v>633</v>
+      </c>
+      <c r="M111" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N111" s="22">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="O111" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P111" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q111" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>cattle</v>
+      </c>
+      <c r="G112" t="s">
+        <v>633</v>
+      </c>
+      <c r="M112" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N112" s="22">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="O112" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P112" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="Q112" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>sheep</v>
+      </c>
+      <c r="G113" t="s">
+        <v>633</v>
+      </c>
+      <c r="M113" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N113" s="22">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="O113" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P113" s="21"/>
+      <c r="Q113" s="22" t="str">
+        <f t="shared" ref="Q113:Q114" si="6">Q99</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>horses</v>
+      </c>
+      <c r="G114" t="s">
+        <v>633</v>
+      </c>
+      <c r="M114" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N114" s="22">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="O114" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P114" s="21"/>
+      <c r="Q114" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N111" s="3"/>
-      <c r="P111" s="21"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112" s="3"/>
-      <c r="G112" t="s">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N115" s="3"/>
+      <c r="P115" s="21"/>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+      <c r="G116" t="s">
         <v>634</v>
       </c>
-      <c r="M112" s="21" t="s">
+      <c r="M116" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="N112" s="21"/>
-      <c r="P112" s="3" t="s">
+      <c r="N116" s="21"/>
+      <c r="P116" s="3" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113" s="3"/>
-      <c r="G113" t="s">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+      <c r="G117" t="s">
         <v>634</v>
       </c>
-      <c r="M113" s="21" t="s">
+      <c r="M117" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="N113" s="21">
+      <c r="N117" s="21">
         <v>2</v>
       </c>
-      <c r="O113" s="21" t="s">
+      <c r="O117" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P113" s="3" t="s">
+      <c r="P117" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="Q113" t="s">
+      <c r="Q117" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114" s="3"/>
-      <c r="G114" t="s">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+      <c r="M118" s="21"/>
+      <c r="N118" s="21"/>
+      <c r="O118" s="21"/>
+      <c r="P118" s="3"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="3"/>
+      <c r="G119" t="s">
         <v>635</v>
       </c>
-      <c r="M114" s="21" t="s">
+      <c r="M119" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="N114" s="21"/>
-      <c r="P114" s="3" t="s">
+      <c r="N119" s="21"/>
+      <c r="P119" s="3" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
-      <c r="G115" t="s">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="3"/>
+      <c r="G120" t="s">
         <v>635</v>
       </c>
-      <c r="M115" s="21" t="s">
+      <c r="M120" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="N115" s="21">
+      <c r="N120" s="21">
         <v>3</v>
       </c>
-      <c r="O115" s="21" t="s">
+      <c r="O120" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P115" s="3" t="s">
+      <c r="P120" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="Q115" t="s">
+      <c r="Q120" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N116" s="3"/>
-      <c r="P116" s="21"/>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N121" s="3"/>
+      <c r="P121" s="21"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
-      <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" s="2"/>
-      <c r="Q117" s="2"/>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>19</v>
-      </c>
-      <c r="N118" s="21"/>
-      <c r="P118" s="21" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="N119" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="O119" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P119" s="3"/>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="N120" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="O120" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P120" s="3"/>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>377</v>
-      </c>
-      <c r="M121" t="s">
-        <v>488</v>
-      </c>
-      <c r="N121" s="21">
-        <v>18</v>
-      </c>
-      <c r="O121" t="s">
-        <v>489</v>
-      </c>
-      <c r="P121" s="3"/>
-      <c r="Q121" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>20</v>
-      </c>
-      <c r="M122" t="s">
-        <v>488</v>
-      </c>
-      <c r="N122" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="O122" t="s">
-        <v>489</v>
-      </c>
-      <c r="P122" s="3"/>
-      <c r="Q122" t="s">
-        <v>490</v>
-      </c>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>374</v>
-      </c>
-      <c r="M123" t="s">
-        <v>488</v>
-      </c>
-      <c r="N123" s="21">
-        <v>0</v>
-      </c>
-      <c r="O123" t="s">
-        <v>489</v>
-      </c>
-      <c r="P123" s="3"/>
-      <c r="Q123" t="s">
-        <v>490</v>
+        <v>19</v>
+      </c>
+      <c r="N123" s="21"/>
+      <c r="P123" s="21" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N124" s="21"/>
+      <c r="A124" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N124" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>487</v>
+      </c>
       <c r="P124" s="3"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M125" t="s">
-        <v>602</v>
-      </c>
-      <c r="N125" s="21">
-        <v>1</v>
-      </c>
-      <c r="O125" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="P125" s="21" t="s">
-        <v>604</v>
-      </c>
-      <c r="Q125" s="21"/>
+      <c r="A125" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N125" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O125" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="P125" s="3"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>19</v>
+        <v>377</v>
       </c>
       <c r="M126" t="s">
-        <v>602</v>
+        <v>488</v>
       </c>
       <c r="N126" s="21">
-        <v>1</v>
-      </c>
-      <c r="O126" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="P126" s="21"/>
-      <c r="Q126" s="21"/>
+        <v>18</v>
+      </c>
+      <c r="O126" t="s">
+        <v>489</v>
+      </c>
+      <c r="P126" s="3"/>
+      <c r="Q126" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>19</v>
-      </c>
-      <c r="B127" t="s">
-        <v>314</v>
-      </c>
-      <c r="E127" t="s">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="M127" t="s">
-        <v>602</v>
+        <v>488</v>
       </c>
       <c r="N127" s="21">
-        <v>1</v>
-      </c>
-      <c r="O127" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="P127" s="21"/>
-      <c r="Q127" s="21"/>
+        <v>1.5</v>
+      </c>
+      <c r="O127" t="s">
+        <v>489</v>
+      </c>
+      <c r="P127" s="3"/>
+      <c r="Q127" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>374</v>
+      </c>
+      <c r="M128" t="s">
+        <v>488</v>
+      </c>
+      <c r="N128" s="21">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
+        <v>489</v>
+      </c>
+      <c r="P128" s="3"/>
+      <c r="Q128" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N129" s="21"/>
+      <c r="P129" s="3"/>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M130" t="s">
+        <v>602</v>
+      </c>
+      <c r="N130" s="21">
+        <v>1</v>
+      </c>
+      <c r="O130" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="P130" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q130" s="21"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>19</v>
       </c>
-      <c r="B128" t="s">
+      <c r="M131" t="s">
+        <v>602</v>
+      </c>
+      <c r="N131" s="21">
+        <v>1</v>
+      </c>
+      <c r="O131" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="P131" s="21"/>
+      <c r="Q131" s="21"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>19</v>
+      </c>
+      <c r="B132" t="s">
         <v>314</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E132" t="s">
+        <v>315</v>
+      </c>
+      <c r="M132" t="s">
+        <v>602</v>
+      </c>
+      <c r="N132" s="21">
+        <v>1</v>
+      </c>
+      <c r="O132" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="P132" s="21"/>
+      <c r="Q132" s="21"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" t="s">
+        <v>314</v>
+      </c>
+      <c r="E133" t="s">
         <v>317</v>
       </c>
-      <c r="M128" t="s">
+      <c r="M133" t="s">
         <v>602</v>
       </c>
-      <c r="N128" s="21">
+      <c r="N133" s="21">
         <v>1</v>
       </c>
-      <c r="O128" s="21" t="s">
+      <c r="O133" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="P128" s="21"/>
-      <c r="Q128" s="21"/>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="P133" s="21"/>
+      <c r="Q133" s="21"/>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>19</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B134" t="s">
         <v>605</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E134" t="s">
         <v>317</v>
       </c>
-      <c r="M129" t="s">
+      <c r="M134" t="s">
         <v>602</v>
       </c>
-      <c r="N129" s="21">
+      <c r="N134" s="21">
         <v>1</v>
       </c>
-      <c r="O129" s="21" t="s">
+      <c r="O134" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="P129" s="21"/>
-      <c r="Q129" s="21"/>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N130" s="3"/>
-      <c r="P130" s="3"/>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
+      <c r="P134" s="21"/>
+      <c r="Q134" s="21"/>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N135" s="3"/>
+      <c r="P135" s="3"/>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
-      <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2" t="s">
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="Q131" s="2"/>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L132" s="103" t="s">
+      <c r="Q136" s="2"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L137" s="103" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M133" t="s">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M138" t="s">
         <v>375</v>
-      </c>
-      <c r="N133" s="21" t="s">
-        <v>614</v>
-      </c>
-      <c r="O133" t="s">
-        <v>598</v>
-      </c>
-      <c r="P133" s="3"/>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M134" t="s">
-        <v>476</v>
-      </c>
-      <c r="N134" s="21" t="s">
-        <v>614</v>
-      </c>
-      <c r="O134" t="s">
-        <v>597</v>
-      </c>
-      <c r="P134" s="3"/>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M135" s="37" t="s">
-        <v>608</v>
-      </c>
-      <c r="N135" s="21" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M136" s="37" t="s">
-        <v>609</v>
-      </c>
-      <c r="N136" s="21" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M137" s="37" t="s">
-        <v>610</v>
-      </c>
-      <c r="N137" s="21" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M138" s="37" t="s">
-        <v>611</v>
       </c>
       <c r="N138" s="21" t="s">
         <v>614</v>
       </c>
+      <c r="O138" t="s">
+        <v>598</v>
+      </c>
       <c r="P138" s="3"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L139" s="103" t="s">
+      <c r="M139" t="s">
+        <v>476</v>
+      </c>
+      <c r="N139" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="O139" t="s">
+        <v>597</v>
+      </c>
+      <c r="P139" s="3"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M140" s="37" t="s">
+        <v>608</v>
+      </c>
+      <c r="N140" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M141" s="37" t="s">
+        <v>609</v>
+      </c>
+      <c r="N141" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M142" s="37" t="s">
+        <v>610</v>
+      </c>
+      <c r="N142" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M143" s="37" t="s">
+        <v>611</v>
+      </c>
+      <c r="N143" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="P143" s="3"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L144" s="103" t="s">
         <v>616</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M140" t="s">
-        <v>17</v>
-      </c>
-      <c r="N140" s="21" t="s">
-        <v>615</v>
-      </c>
-      <c r="O140" t="s">
-        <v>622</v>
-      </c>
-      <c r="P140" s="21" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M141" t="s">
-        <v>588</v>
-      </c>
-      <c r="N141" s="21" t="s">
-        <v>615</v>
-      </c>
-      <c r="O141" t="s">
-        <v>596</v>
-      </c>
-      <c r="P141" s="3"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M142" t="s">
-        <v>477</v>
-      </c>
-      <c r="N142" s="21" t="s">
-        <v>615</v>
-      </c>
-      <c r="O142" t="s">
-        <v>478</v>
-      </c>
-      <c r="P142" s="21" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L143" s="103" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M144" t="s">
-        <v>17</v>
-      </c>
-      <c r="N144" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="O144" t="s">
-        <v>622</v>
-      </c>
-      <c r="P144" s="21" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="145" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="O145" t="s">
+        <v>622</v>
+      </c>
+      <c r="P145" s="21" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="146" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M146" t="s">
         <v>588</v>
       </c>
-      <c r="N145" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="O145" t="s">
+      <c r="N146" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="O146" t="s">
         <v>596</v>
       </c>
-      <c r="P145" s="3"/>
-    </row>
-    <row r="146" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L146" s="103" t="s">
-        <v>619</v>
-      </c>
+      <c r="P146" s="3"/>
     </row>
     <row r="147" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M147" t="s">
+        <v>477</v>
+      </c>
+      <c r="N147" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="O147" t="s">
+        <v>478</v>
+      </c>
+      <c r="P147" s="21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="148" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L148" s="103" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="149" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M149" t="s">
         <v>17</v>
       </c>
-      <c r="N147" s="21" t="s">
-        <v>626</v>
-      </c>
-      <c r="O147" t="s">
+      <c r="N149" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="O149" t="s">
         <v>622</v>
       </c>
-      <c r="P147" s="21" t="s">
+      <c r="P149" s="21" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="148" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M148" t="s">
-        <v>588</v>
-      </c>
-      <c r="N148" s="21" t="s">
-        <v>626</v>
-      </c>
-      <c r="O148" t="s">
-        <v>596</v>
-      </c>
-      <c r="P148" s="3"/>
-    </row>
-    <row r="149" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L149" s="103" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="150" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M150" t="s">
+        <v>588</v>
+      </c>
+      <c r="N150" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="O150" t="s">
+        <v>596</v>
+      </c>
+      <c r="P150" s="3"/>
+    </row>
+    <row r="151" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L151" s="103" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="152" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M152" t="s">
         <v>17</v>
       </c>
-      <c r="N150" s="21" t="s">
-        <v>627</v>
-      </c>
-      <c r="O150" t="s">
-        <v>623</v>
-      </c>
-      <c r="P150" s="21" t="s">
+      <c r="N152" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="O152" t="s">
+        <v>622</v>
+      </c>
+      <c r="P152" s="21" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="151" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M151" t="s">
-        <v>588</v>
-      </c>
-      <c r="N151" s="21" t="s">
-        <v>627</v>
-      </c>
-      <c r="O151" t="s">
-        <v>596</v>
-      </c>
-      <c r="P151" s="3"/>
-    </row>
-    <row r="152" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L152" s="103" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="153" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M153" t="s">
+        <v>588</v>
+      </c>
+      <c r="N153" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="O153" t="s">
+        <v>596</v>
+      </c>
+      <c r="P153" s="3"/>
+    </row>
+    <row r="154" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L154" s="103" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="155" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M155" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="O155" t="s">
+        <v>623</v>
+      </c>
+      <c r="P155" s="21" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="156" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M156" t="s">
+        <v>588</v>
+      </c>
+      <c r="N156" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="O156" t="s">
+        <v>596</v>
+      </c>
+      <c r="P156" s="3"/>
+    </row>
+    <row r="157" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L157" s="103" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="158" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M158" t="s">
         <v>613</v>
       </c>
-      <c r="N153" s="21" t="s">
+      <c r="N158" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="O153" t="s">
+      <c r="O158" t="s">
         <v>624</v>
       </c>
-      <c r="P153" s="21"/>
+      <c r="P158" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="default" sheetId="1" r:id="rId1"/>
-    <sheet name="references" sheetId="9" r:id="rId2"/>
+    <sheet name="references" sheetId="9" r:id="rId1"/>
+    <sheet name="default" sheetId="1" r:id="rId2"/>
     <sheet name="feed pars" sheetId="2" r:id="rId3"/>
     <sheet name="feed pars csv" sheetId="8" r:id="rId4"/>
-    <sheet name="pigs" sheetId="3" r:id="rId5"/>
-    <sheet name="ruminants" sheetId="4" r:id="rId6"/>
-    <sheet name="ruminants, roughage" sheetId="6" r:id="rId7"/>
-    <sheet name="horses" sheetId="7" r:id="rId8"/>
-    <sheet name="poultry" sheetId="5" r:id="rId9"/>
+    <sheet name="max SNG" sheetId="10" r:id="rId5"/>
+    <sheet name="pigs" sheetId="3" r:id="rId6"/>
+    <sheet name="ruminants" sheetId="4" r:id="rId7"/>
+    <sheet name="ruminants, roughage" sheetId="6" r:id="rId8"/>
+    <sheet name="horses" sheetId="7" r:id="rId9"/>
+    <sheet name="poultry" sheetId="5" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="651">
   <si>
     <t>f_feed</t>
   </si>
@@ -2003,6 +2004,15 @@
       </rPr>
       <t xml:space="preserve"> Setting this parameter too close to 100% may cause problems.</t>
     </r>
+  </si>
+  <si>
+    <t>milling by-products from wheat, barley or rye</t>
+  </si>
+  <si>
+    <t>milling by-products from oats</t>
+  </si>
+  <si>
+    <t>add as crop product?</t>
   </si>
 </sst>
 </file>
@@ -2804,6 +2814,2624 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D1">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>2</v>
+      </c>
+      <c r="F1">
+        <v>3</v>
+      </c>
+      <c r="G1">
+        <v>4</v>
+      </c>
+      <c r="H1">
+        <v>5</v>
+      </c>
+      <c r="I1">
+        <v>6</v>
+      </c>
+      <c r="J1">
+        <v>7</v>
+      </c>
+      <c r="K1">
+        <v>8</v>
+      </c>
+      <c r="L1">
+        <v>9</v>
+      </c>
+      <c r="M1">
+        <v>10</v>
+      </c>
+      <c r="N1">
+        <v>11</v>
+      </c>
+      <c r="O1">
+        <v>12</v>
+      </c>
+      <c r="P1">
+        <v>13</v>
+      </c>
+      <c r="Q1">
+        <v>14</v>
+      </c>
+      <c r="R1">
+        <v>15</v>
+      </c>
+      <c r="S1">
+        <v>16</v>
+      </c>
+      <c r="T1">
+        <v>17</v>
+      </c>
+      <c r="U1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" s="10">
+        <v>99</v>
+      </c>
+      <c r="E3" s="10">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>965</v>
+      </c>
+      <c r="K3" s="10">
+        <v>170</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>0</v>
+      </c>
+      <c r="S3" s="10">
+        <v>0</v>
+      </c>
+      <c r="T3" s="10">
+        <v>0</v>
+      </c>
+      <c r="U3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B4" s="11">
+        <v>2</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="13">
+        <v>99</v>
+      </c>
+      <c r="E4" s="13">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F4" s="13">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
+        <v>975</v>
+      </c>
+      <c r="K4" s="13">
+        <v>300</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
+        <v>0</v>
+      </c>
+      <c r="O4" s="13">
+        <v>0</v>
+      </c>
+      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
+        <v>0</v>
+      </c>
+      <c r="T4" s="13">
+        <v>0</v>
+      </c>
+      <c r="U4" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B5" s="8">
+        <v>3</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D5" s="10">
+        <v>100</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10">
+        <v>213</v>
+      </c>
+      <c r="P5" s="10">
+        <v>187</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>165</v>
+      </c>
+      <c r="R5" s="10">
+        <v>1</v>
+      </c>
+      <c r="S5" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="T5" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="U5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B6" s="11">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D6" s="13">
+        <v>100</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
+      <c r="N6" s="13">
+        <v>0</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13">
+        <v>208</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>208</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
+        <v>310</v>
+      </c>
+      <c r="T6" s="13">
+        <v>0</v>
+      </c>
+      <c r="U6" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B7" s="8">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="10">
+        <v>100</v>
+      </c>
+      <c r="E7" s="10">
+        <v>15.4</v>
+      </c>
+      <c r="F7" s="10">
+        <v>587</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>980</v>
+      </c>
+      <c r="I7" s="10">
+        <v>980</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="11">
+        <v>6</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" s="13">
+        <v>92</v>
+      </c>
+      <c r="E8" s="13">
+        <v>12.6</v>
+      </c>
+      <c r="F8" s="13">
+        <v>621</v>
+      </c>
+      <c r="G8" s="13">
+        <v>48.1</v>
+      </c>
+      <c r="H8" s="13">
+        <v>17.7</v>
+      </c>
+      <c r="I8" s="13">
+        <v>23.4</v>
+      </c>
+      <c r="J8" s="13">
+        <v>50</v>
+      </c>
+      <c r="K8" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
+        <v>0</v>
+      </c>
+      <c r="O8" s="13">
+        <v>41</v>
+      </c>
+      <c r="P8" s="13">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>21</v>
+      </c>
+      <c r="R8" s="13">
+        <v>9</v>
+      </c>
+      <c r="S8" s="13">
+        <v>6</v>
+      </c>
+      <c r="T8" s="13">
+        <v>9</v>
+      </c>
+      <c r="U8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B9" s="8">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="10">
+        <v>92</v>
+      </c>
+      <c r="E9" s="10">
+        <v>10.8</v>
+      </c>
+      <c r="F9" s="10">
+        <v>653</v>
+      </c>
+      <c r="G9" s="10">
+        <v>50.1</v>
+      </c>
+      <c r="H9" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I9" s="10">
+        <v>24.2</v>
+      </c>
+      <c r="J9" s="10">
+        <v>18</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <v>41</v>
+      </c>
+      <c r="P9" s="10">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>21</v>
+      </c>
+      <c r="R9" s="10">
+        <v>9</v>
+      </c>
+      <c r="S9" s="10">
+        <v>6</v>
+      </c>
+      <c r="T9" s="10">
+        <v>9</v>
+      </c>
+      <c r="U9" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="11">
+        <v>8</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="D10" s="13">
+        <v>92</v>
+      </c>
+      <c r="E10" s="13">
+        <v>13.6</v>
+      </c>
+      <c r="F10" s="13">
+        <v>661</v>
+      </c>
+      <c r="G10" s="13">
+        <v>51.5</v>
+      </c>
+      <c r="H10" s="13">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="I10" s="13">
+        <v>24.9</v>
+      </c>
+      <c r="J10" s="13">
+        <v>100</v>
+      </c>
+      <c r="K10" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
+        <v>41</v>
+      </c>
+      <c r="P10" s="13">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>21</v>
+      </c>
+      <c r="R10" s="13">
+        <v>9</v>
+      </c>
+      <c r="S10" s="13">
+        <v>6</v>
+      </c>
+      <c r="T10" s="13">
+        <v>9</v>
+      </c>
+      <c r="U10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B11" s="8">
+        <v>9</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="D11" s="10">
+        <v>100</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10">
+        <v>375</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="S11" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="T11" s="10">
+        <v>0</v>
+      </c>
+      <c r="U11" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="11">
+        <v>10</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="D12" s="13">
+        <v>87</v>
+      </c>
+      <c r="E12" s="13">
+        <v>10.7</v>
+      </c>
+      <c r="F12" s="13">
+        <v>104</v>
+      </c>
+      <c r="G12" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="I12" s="13">
+        <v>4.8</v>
+      </c>
+      <c r="J12" s="13">
+        <v>52</v>
+      </c>
+      <c r="K12" s="13">
+        <v>21</v>
+      </c>
+      <c r="L12" s="13">
+        <v>400</v>
+      </c>
+      <c r="M12" s="13">
+        <v>10</v>
+      </c>
+      <c r="N12" s="13">
+        <v>87</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="P12" s="13">
+        <v>3.4</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="R12" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="S12" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="T12" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B13" s="8">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D13" s="10">
+        <v>87</v>
+      </c>
+      <c r="E13" s="10">
+        <v>13.8</v>
+      </c>
+      <c r="F13" s="10">
+        <v>132</v>
+      </c>
+      <c r="G13" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="H13" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I13" s="10">
+        <v>6</v>
+      </c>
+      <c r="J13" s="10">
+        <v>65</v>
+      </c>
+      <c r="K13" s="10">
+        <v>25</v>
+      </c>
+      <c r="L13" s="10">
+        <v>400</v>
+      </c>
+      <c r="M13" s="10">
+        <v>10</v>
+      </c>
+      <c r="N13" s="10">
+        <v>25</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="P13" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="R13" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="S13" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="T13" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U13" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="11">
+        <v>12</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D14" s="13">
+        <v>87</v>
+      </c>
+      <c r="E14" s="13">
+        <v>10</v>
+      </c>
+      <c r="F14" s="13">
+        <v>100</v>
+      </c>
+      <c r="G14" s="13">
+        <v>3.7</v>
+      </c>
+      <c r="H14" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="I14" s="13">
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="13">
+        <v>52</v>
+      </c>
+      <c r="K14" s="13">
+        <v>21</v>
+      </c>
+      <c r="L14" s="13">
+        <v>380</v>
+      </c>
+      <c r="M14" s="13">
+        <v>8</v>
+      </c>
+      <c r="N14" s="13">
+        <v>104</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="P14" s="13">
+        <v>3.4</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="R14" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="S14" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="T14" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="8">
+        <v>13</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="D15" s="10">
+        <v>87</v>
+      </c>
+      <c r="E15" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="F15" s="10">
+        <v>109</v>
+      </c>
+      <c r="G15" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="I15" s="10">
+        <v>5</v>
+      </c>
+      <c r="J15" s="10">
+        <v>52</v>
+      </c>
+      <c r="K15" s="10">
+        <v>21</v>
+      </c>
+      <c r="L15" s="10">
+        <v>420</v>
+      </c>
+      <c r="M15" s="10">
+        <v>12</v>
+      </c>
+      <c r="N15" s="10">
+        <v>78</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="P15" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="R15" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="S15" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="T15" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U15" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <v>14</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="13">
+        <v>87</v>
+      </c>
+      <c r="E16" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="F16" s="13">
+        <v>46</v>
+      </c>
+      <c r="G16" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0.7</v>
+      </c>
+      <c r="I16" s="13">
+        <v>1.3</v>
+      </c>
+      <c r="J16" s="13">
+        <v>14</v>
+      </c>
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13">
+        <v>287</v>
+      </c>
+      <c r="O16" s="13">
+        <v>1.3</v>
+      </c>
+      <c r="P16" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="S16" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="T16" s="13">
+        <v>1</v>
+      </c>
+      <c r="U16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="8">
+        <v>15</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" s="10">
+        <v>100</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>3</v>
+      </c>
+      <c r="P17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>0</v>
+      </c>
+      <c r="R17" s="10">
+        <v>0</v>
+      </c>
+      <c r="S17" s="10">
+        <v>390</v>
+      </c>
+      <c r="T17" s="10">
+        <v>600</v>
+      </c>
+      <c r="U17" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="11">
+        <v>16</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="13">
+        <v>87</v>
+      </c>
+      <c r="E18" s="13">
+        <v>11.8</v>
+      </c>
+      <c r="F18" s="13">
+        <v>104</v>
+      </c>
+      <c r="G18" s="13">
+        <v>3.8</v>
+      </c>
+      <c r="H18" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="I18" s="13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J18" s="13">
+        <v>25</v>
+      </c>
+      <c r="K18" s="13">
+        <v>10</v>
+      </c>
+      <c r="L18" s="13">
+        <v>490</v>
+      </c>
+      <c r="M18" s="13">
+        <v>26</v>
+      </c>
+      <c r="N18" s="13">
+        <v>41</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="P18" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="R18" s="13">
+        <v>4.8</v>
+      </c>
+      <c r="S18" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="T18" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="U18" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="8">
+        <v>17</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" s="10">
+        <v>87</v>
+      </c>
+      <c r="E19" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="F19" s="10">
+        <v>100</v>
+      </c>
+      <c r="G19" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="H19" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="I19" s="10">
+        <v>4</v>
+      </c>
+      <c r="J19" s="10">
+        <v>25</v>
+      </c>
+      <c r="K19" s="10">
+        <v>10</v>
+      </c>
+      <c r="L19" s="10">
+        <v>450</v>
+      </c>
+      <c r="M19" s="10">
+        <v>22</v>
+      </c>
+      <c r="N19" s="10">
+        <v>71</v>
+      </c>
+      <c r="O19" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="P19" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="R19" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="S19" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="T19" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="U19" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="D20" s="13">
+        <v>87</v>
+      </c>
+      <c r="E20" s="13">
+        <v>12.2</v>
+      </c>
+      <c r="F20" s="13">
+        <v>117</v>
+      </c>
+      <c r="G20" s="13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H20" s="13">
+        <v>2</v>
+      </c>
+      <c r="I20" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="J20" s="13">
+        <v>25</v>
+      </c>
+      <c r="K20" s="13">
+        <v>10</v>
+      </c>
+      <c r="L20" s="13">
+        <v>517</v>
+      </c>
+      <c r="M20" s="13">
+        <v>28</v>
+      </c>
+      <c r="N20" s="13">
+        <v>37</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="R20" s="13">
+        <v>4.8</v>
+      </c>
+      <c r="S20" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="T20" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="U20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="8">
+        <v>19</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D21" s="10">
+        <v>95</v>
+      </c>
+      <c r="E21" s="10">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F21" s="10">
+        <v>530</v>
+      </c>
+      <c r="G21" s="10">
+        <v>29</v>
+      </c>
+      <c r="H21" s="10">
+        <v>8.1</v>
+      </c>
+      <c r="I21" s="10">
+        <v>13.9</v>
+      </c>
+      <c r="J21" s="10">
+        <v>104</v>
+      </c>
+      <c r="K21" s="10">
+        <v>15</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10">
+        <v>100</v>
+      </c>
+      <c r="P21" s="10">
+        <v>45</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>36</v>
+      </c>
+      <c r="R21" s="10">
+        <v>6</v>
+      </c>
+      <c r="S21" s="10">
+        <v>7</v>
+      </c>
+      <c r="T21" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="U21" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="11">
+        <v>20</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="13">
+        <v>93</v>
+      </c>
+      <c r="E22" s="13">
+        <v>11</v>
+      </c>
+      <c r="F22" s="13">
+        <v>590</v>
+      </c>
+      <c r="G22" s="13">
+        <v>30</v>
+      </c>
+      <c r="H22" s="13">
+        <v>8.4</v>
+      </c>
+      <c r="I22" s="13">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="J22" s="13">
+        <v>79</v>
+      </c>
+      <c r="K22" s="13">
+        <v>12</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
+        <v>80</v>
+      </c>
+      <c r="P22" s="13">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>30</v>
+      </c>
+      <c r="R22" s="13">
+        <v>5</v>
+      </c>
+      <c r="S22" s="13">
+        <v>6</v>
+      </c>
+      <c r="T22" s="13">
+        <v>7</v>
+      </c>
+      <c r="U22" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="8">
+        <v>21</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D23" s="10">
+        <v>93</v>
+      </c>
+      <c r="E23" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="F23" s="10">
+        <v>648</v>
+      </c>
+      <c r="G23" s="10">
+        <v>37</v>
+      </c>
+      <c r="H23" s="10">
+        <v>10.4</v>
+      </c>
+      <c r="I23" s="10">
+        <v>17.8</v>
+      </c>
+      <c r="J23" s="10">
+        <v>100</v>
+      </c>
+      <c r="K23" s="10">
+        <v>15</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10">
+        <v>76</v>
+      </c>
+      <c r="P23" s="10">
+        <v>40</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>30</v>
+      </c>
+      <c r="R23" s="10">
+        <v>10</v>
+      </c>
+      <c r="S23" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="T23" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="U23" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="11">
+        <v>22</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D24" s="13">
+        <v>90</v>
+      </c>
+      <c r="E24" s="13">
+        <v>6.67</v>
+      </c>
+      <c r="F24" s="13">
+        <v>193</v>
+      </c>
+      <c r="G24" s="13">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H24" s="13">
+        <v>2.9</v>
+      </c>
+      <c r="I24" s="13">
+        <v>5.4</v>
+      </c>
+      <c r="J24" s="13">
+        <v>36</v>
+      </c>
+      <c r="K24" s="13">
+        <v>5</v>
+      </c>
+      <c r="L24" s="13">
+        <v>45</v>
+      </c>
+      <c r="M24" s="13">
+        <v>51</v>
+      </c>
+      <c r="N24" s="13">
+        <v>193</v>
+      </c>
+      <c r="O24" s="13">
+        <v>14</v>
+      </c>
+      <c r="P24" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R24" s="13">
+        <v>22</v>
+      </c>
+      <c r="S24" s="13">
+        <v>1.3</v>
+      </c>
+      <c r="T24" s="13">
+        <v>4.7</v>
+      </c>
+      <c r="U24" s="13">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B25" s="8">
+        <v>23</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" s="10">
+        <v>100</v>
+      </c>
+      <c r="E25" s="10">
+        <v>16.7</v>
+      </c>
+      <c r="F25" s="10">
+        <v>934</v>
+      </c>
+      <c r="G25" s="10">
+        <v>780</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10">
+        <v>0</v>
+      </c>
+      <c r="J25" s="10">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0</v>
+      </c>
+      <c r="M25" s="10">
+        <v>0</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10">
+        <v>0</v>
+      </c>
+      <c r="P25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>0</v>
+      </c>
+      <c r="R25" s="10">
+        <v>0</v>
+      </c>
+      <c r="S25" s="10">
+        <v>0</v>
+      </c>
+      <c r="T25" s="10">
+        <v>0</v>
+      </c>
+      <c r="U25" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="11">
+        <v>24</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="D26" s="13">
+        <v>87</v>
+      </c>
+      <c r="E26" s="13">
+        <v>13.8</v>
+      </c>
+      <c r="F26" s="13">
+        <v>87</v>
+      </c>
+      <c r="G26" s="13">
+        <v>2.4</v>
+      </c>
+      <c r="H26" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="I26" s="13">
+        <v>3.8</v>
+      </c>
+      <c r="J26" s="13">
+        <v>40</v>
+      </c>
+      <c r="K26" s="13">
+        <v>32</v>
+      </c>
+      <c r="L26" s="13">
+        <v>650</v>
+      </c>
+      <c r="M26" s="13">
+        <v>16.3</v>
+      </c>
+      <c r="N26" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="O26" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="P26" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>3.3</v>
+      </c>
+      <c r="R26" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="S26" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="T26" s="13">
+        <v>50</v>
+      </c>
+      <c r="U26" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>373</v>
+      </c>
+      <c r="B27" s="8">
+        <v>25</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D27" s="10">
+        <v>87</v>
+      </c>
+      <c r="E27" s="10">
+        <v>14.2</v>
+      </c>
+      <c r="F27" s="10">
+        <v>644</v>
+      </c>
+      <c r="G27" s="10">
+        <v>10.8</v>
+      </c>
+      <c r="H27" s="10">
+        <v>15.2</v>
+      </c>
+      <c r="I27" s="10">
+        <v>26.8</v>
+      </c>
+      <c r="J27" s="10">
+        <v>39</v>
+      </c>
+      <c r="K27" s="10">
+        <v>20</v>
+      </c>
+      <c r="L27" s="10">
+        <v>123</v>
+      </c>
+      <c r="M27" s="10">
+        <v>6</v>
+      </c>
+      <c r="N27" s="10">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="O27" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="P27" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="R27" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="S27" s="10">
+        <v>2</v>
+      </c>
+      <c r="T27" s="10">
+        <v>5</v>
+      </c>
+      <c r="U27" s="10">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B28" s="11">
+        <v>26</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="D28" s="13">
+        <v>100</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13">
+        <v>160</v>
+      </c>
+      <c r="P28" s="13">
+        <v>210</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>190</v>
+      </c>
+      <c r="R28" s="13">
+        <v>0.7</v>
+      </c>
+      <c r="S28" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="T28" s="13">
+        <v>0</v>
+      </c>
+      <c r="U28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B29" s="8">
+        <v>27</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D29" s="10">
+        <v>100</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0</v>
+      </c>
+      <c r="F29" s="10">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0</v>
+      </c>
+      <c r="J29" s="10">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10">
+        <v>0</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10">
+        <v>0</v>
+      </c>
+      <c r="P29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>0</v>
+      </c>
+      <c r="R29" s="10">
+        <v>0</v>
+      </c>
+      <c r="S29" s="10">
+        <v>270</v>
+      </c>
+      <c r="T29" s="10">
+        <v>0</v>
+      </c>
+      <c r="U29" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="11">
+        <v>28</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D30" s="13">
+        <v>90</v>
+      </c>
+      <c r="E30" s="13">
+        <v>14.4</v>
+      </c>
+      <c r="F30" s="13">
+        <v>790</v>
+      </c>
+      <c r="G30" s="13">
+        <v>64</v>
+      </c>
+      <c r="H30" s="13">
+        <v>18</v>
+      </c>
+      <c r="I30" s="13">
+        <v>31</v>
+      </c>
+      <c r="J30" s="13">
+        <v>40</v>
+      </c>
+      <c r="K30" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="13">
+        <v>0</v>
+      </c>
+      <c r="N30" s="13">
+        <v>0</v>
+      </c>
+      <c r="O30" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="P30" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>2</v>
+      </c>
+      <c r="R30" s="13">
+        <v>1</v>
+      </c>
+      <c r="S30" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="T30" s="13">
+        <v>2.1</v>
+      </c>
+      <c r="U30" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="8">
+        <v>29</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D31" s="10">
+        <v>90</v>
+      </c>
+      <c r="E31" s="10">
+        <v>7.6</v>
+      </c>
+      <c r="F31" s="10">
+        <v>348</v>
+      </c>
+      <c r="G31" s="10">
+        <v>19.5</v>
+      </c>
+      <c r="H31" s="10">
+        <v>7.1</v>
+      </c>
+      <c r="I31" s="10">
+        <v>15.9</v>
+      </c>
+      <c r="J31" s="10">
+        <v>23</v>
+      </c>
+      <c r="K31" s="10">
+        <v>7</v>
+      </c>
+      <c r="L31" s="10">
+        <v>40</v>
+      </c>
+      <c r="M31" s="10">
+        <v>78</v>
+      </c>
+      <c r="N31" s="10">
+        <v>120</v>
+      </c>
+      <c r="O31" s="10">
+        <v>5</v>
+      </c>
+      <c r="P31" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="R31" s="10">
+        <v>14</v>
+      </c>
+      <c r="S31" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="T31" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="U31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" s="11">
+        <v>30</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="D32" s="13">
+        <v>87</v>
+      </c>
+      <c r="E32" s="13">
+        <v>11.2</v>
+      </c>
+      <c r="F32" s="13">
+        <v>96</v>
+      </c>
+      <c r="G32" s="13">
+        <v>3.9</v>
+      </c>
+      <c r="H32" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="I32" s="13">
+        <v>4.2</v>
+      </c>
+      <c r="J32" s="13">
+        <v>16</v>
+      </c>
+      <c r="K32" s="13">
+        <v>7</v>
+      </c>
+      <c r="L32" s="13">
+        <v>568</v>
+      </c>
+      <c r="M32" s="13">
+        <v>55</v>
+      </c>
+      <c r="N32" s="13">
+        <v>26</v>
+      </c>
+      <c r="O32" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="P32" s="13">
+        <v>3.3</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="R32" s="13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S32" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="T32" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="U32" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="8">
+        <v>31</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D33" s="10">
+        <v>89</v>
+      </c>
+      <c r="E33" s="10">
+        <v>13</v>
+      </c>
+      <c r="F33" s="10">
+        <v>115</v>
+      </c>
+      <c r="G33" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="H33" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="I33" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="J33" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K33" s="10">
+        <v>8</v>
+      </c>
+      <c r="L33" s="10">
+        <v>550</v>
+      </c>
+      <c r="M33" s="10">
+        <v>60</v>
+      </c>
+      <c r="N33" s="10">
+        <v>21</v>
+      </c>
+      <c r="O33" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="P33" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>0</v>
+      </c>
+      <c r="R33" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="S33" s="10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T33" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="U33" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <v>32</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="D34" s="13">
+        <v>99</v>
+      </c>
+      <c r="E34" s="13">
+        <v>34</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13">
+        <v>990</v>
+      </c>
+      <c r="K34" s="13">
+        <v>40</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13">
+        <v>0</v>
+      </c>
+      <c r="N34" s="13">
+        <v>0</v>
+      </c>
+      <c r="O34" s="13">
+        <v>0</v>
+      </c>
+      <c r="P34" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13">
+        <v>0</v>
+      </c>
+      <c r="R34" s="13">
+        <v>0</v>
+      </c>
+      <c r="S34" s="13">
+        <v>0</v>
+      </c>
+      <c r="T34" s="13">
+        <v>0</v>
+      </c>
+      <c r="U34" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="8">
+        <v>33</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" s="10">
+        <v>87</v>
+      </c>
+      <c r="E35" s="10">
+        <v>9.1</v>
+      </c>
+      <c r="F35" s="10">
+        <v>440</v>
+      </c>
+      <c r="G35" s="10">
+        <v>27.5</v>
+      </c>
+      <c r="H35" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="I35" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="J35" s="10">
+        <v>13</v>
+      </c>
+      <c r="K35" s="10">
+        <v>6</v>
+      </c>
+      <c r="L35" s="10">
+        <v>64</v>
+      </c>
+      <c r="M35" s="10">
+        <v>93</v>
+      </c>
+      <c r="N35" s="10">
+        <v>60</v>
+      </c>
+      <c r="O35" s="10">
+        <v>2</v>
+      </c>
+      <c r="P35" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="R35" s="10">
+        <v>20</v>
+      </c>
+      <c r="S35" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="T35" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="U35" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B36" s="11">
+        <v>34</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="D36" s="13">
+        <v>99</v>
+      </c>
+      <c r="E36" s="13">
+        <v>36</v>
+      </c>
+      <c r="F36" s="13">
+        <v>0</v>
+      </c>
+      <c r="G36" s="13">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13">
+        <v>990</v>
+      </c>
+      <c r="K36" s="13">
+        <v>524</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13">
+        <v>0</v>
+      </c>
+      <c r="O36" s="13">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="13">
+        <v>0</v>
+      </c>
+      <c r="R36" s="13">
+        <v>0</v>
+      </c>
+      <c r="S36" s="13">
+        <v>0</v>
+      </c>
+      <c r="T36" s="13">
+        <v>0</v>
+      </c>
+      <c r="U36" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="8">
+        <v>35</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D37" s="10">
+        <v>87</v>
+      </c>
+      <c r="E37" s="10">
+        <v>12.8</v>
+      </c>
+      <c r="F37" s="10">
+        <v>113</v>
+      </c>
+      <c r="G37" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="H37" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="I37" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="10">
+        <v>19</v>
+      </c>
+      <c r="K37" s="10">
+        <v>8</v>
+      </c>
+      <c r="L37" s="10">
+        <v>580</v>
+      </c>
+      <c r="M37" s="10">
+        <v>78</v>
+      </c>
+      <c r="N37" s="10">
+        <v>21</v>
+      </c>
+      <c r="O37" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="P37" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="R37" s="10">
+        <v>4</v>
+      </c>
+      <c r="S37" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="T37" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="U37" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="11">
+        <v>36</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="D38" s="13">
+        <v>87</v>
+      </c>
+      <c r="E38" s="13">
+        <v>12.2</v>
+      </c>
+      <c r="F38" s="13">
+        <v>169</v>
+      </c>
+      <c r="G38" s="13">
+        <v>5.9</v>
+      </c>
+      <c r="H38" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="I38" s="13">
+        <v>6.3</v>
+      </c>
+      <c r="J38" s="13">
+        <v>44</v>
+      </c>
+      <c r="K38" s="13">
+        <v>15</v>
+      </c>
+      <c r="L38" s="13">
+        <v>419</v>
+      </c>
+      <c r="M38" s="13">
+        <v>60</v>
+      </c>
+      <c r="N38" s="13">
+        <v>26</v>
+      </c>
+      <c r="O38" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="P38" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="R38" s="13">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S38" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="T38" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="U38" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B39" s="8">
+        <v>37</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D39" s="10">
+        <v>87</v>
+      </c>
+      <c r="E39" s="10">
+        <v>9.4</v>
+      </c>
+      <c r="F39" s="10">
+        <v>157</v>
+      </c>
+      <c r="G39" s="10">
+        <v>5.7</v>
+      </c>
+      <c r="H39" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="I39" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="J39" s="10">
+        <v>39</v>
+      </c>
+      <c r="K39" s="10">
+        <v>12</v>
+      </c>
+      <c r="L39" s="10">
+        <v>270</v>
+      </c>
+      <c r="M39" s="10">
+        <v>66</v>
+      </c>
+      <c r="N39" s="10">
+        <v>65</v>
+      </c>
+      <c r="O39" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="P39" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="R39" s="10">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S39" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="T39" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="U39" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="11">
+        <v>38</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D40" s="13">
+        <v>87</v>
+      </c>
+      <c r="E40" s="13">
+        <v>6.8</v>
+      </c>
+      <c r="F40" s="13">
+        <v>157</v>
+      </c>
+      <c r="G40" s="13">
+        <v>6.4</v>
+      </c>
+      <c r="H40" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="I40" s="13">
+        <v>5.8</v>
+      </c>
+      <c r="J40" s="13">
+        <v>45</v>
+      </c>
+      <c r="K40" s="13">
+        <v>12</v>
+      </c>
+      <c r="L40" s="13">
+        <v>135</v>
+      </c>
+      <c r="M40" s="13">
+        <v>55</v>
+      </c>
+      <c r="N40" s="13">
+        <v>100</v>
+      </c>
+      <c r="O40" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="P40" s="13">
+        <v>11.5</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>6</v>
+      </c>
+      <c r="R40" s="13">
+        <v>9.9</v>
+      </c>
+      <c r="S40" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="T40" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="U40" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="8">
+        <v>39</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="D41" s="10">
+        <v>87</v>
+      </c>
+      <c r="E41" s="10">
+        <v>11</v>
+      </c>
+      <c r="F41" s="10">
+        <v>226</v>
+      </c>
+      <c r="G41" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="H41" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I41" s="10">
+        <v>5.6</v>
+      </c>
+      <c r="J41" s="10">
+        <v>13</v>
+      </c>
+      <c r="K41" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="L41" s="10">
+        <v>416</v>
+      </c>
+      <c r="M41" s="10">
+        <v>56</v>
+      </c>
+      <c r="N41" s="10">
+        <v>61</v>
+      </c>
+      <c r="O41" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="P41" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="R41" s="10">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="S41" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="T41" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="U41" s="10">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3343,14 +5971,16 @@
         <v>1.1111111111111112</v>
       </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
         <v>43</v>
       </c>
       <c r="J31" t="s">
-        <v>43</v>
+        <v>648</v>
       </c>
       <c r="M31" t="s">
         <v>27</v>
@@ -3365,7 +5995,7 @@
         <v>44</v>
       </c>
       <c r="J32" t="s">
-        <v>43</v>
+        <v>648</v>
       </c>
       <c r="M32" t="s">
         <v>27</v>
@@ -3380,7 +6010,7 @@
         <v>586</v>
       </c>
       <c r="J33" t="s">
-        <v>586</v>
+        <v>649</v>
       </c>
       <c r="M33" t="s">
         <v>27</v>
@@ -3395,7 +6025,7 @@
         <v>587</v>
       </c>
       <c r="J34" t="s">
-        <v>587</v>
+        <v>649</v>
       </c>
       <c r="M34" t="s">
         <v>27</v>
@@ -3410,7 +6040,7 @@
         <v>630</v>
       </c>
       <c r="J35" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="M35" t="s">
         <v>27</v>
@@ -5534,26 +8164,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -16713,6 +19323,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24046,7 +26665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34836,7 +37455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AE61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39729,7 +42348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:N56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -41981,2602 +44600,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D1">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>2</v>
-      </c>
-      <c r="F1">
-        <v>3</v>
-      </c>
-      <c r="G1">
-        <v>4</v>
-      </c>
-      <c r="H1">
-        <v>5</v>
-      </c>
-      <c r="I1">
-        <v>6</v>
-      </c>
-      <c r="J1">
-        <v>7</v>
-      </c>
-      <c r="K1">
-        <v>8</v>
-      </c>
-      <c r="L1">
-        <v>9</v>
-      </c>
-      <c r="M1">
-        <v>10</v>
-      </c>
-      <c r="N1">
-        <v>11</v>
-      </c>
-      <c r="O1">
-        <v>12</v>
-      </c>
-      <c r="P1">
-        <v>13</v>
-      </c>
-      <c r="Q1">
-        <v>14</v>
-      </c>
-      <c r="R1">
-        <v>15</v>
-      </c>
-      <c r="S1">
-        <v>16</v>
-      </c>
-      <c r="T1">
-        <v>17</v>
-      </c>
-      <c r="U1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>325</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B3" s="8">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="D3" s="10">
-        <v>99</v>
-      </c>
-      <c r="E3" s="10">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>965</v>
-      </c>
-      <c r="K3" s="10">
-        <v>170</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10">
-        <v>0</v>
-      </c>
-      <c r="O3" s="10">
-        <v>0</v>
-      </c>
-      <c r="P3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>0</v>
-      </c>
-      <c r="S3" s="10">
-        <v>0</v>
-      </c>
-      <c r="T3" s="10">
-        <v>0</v>
-      </c>
-      <c r="U3" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
-        <v>2</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D4" s="13">
-        <v>99</v>
-      </c>
-      <c r="E4" s="13">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
-        <v>0</v>
-      </c>
-      <c r="I4" s="13">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
-        <v>975</v>
-      </c>
-      <c r="K4" s="13">
-        <v>300</v>
-      </c>
-      <c r="L4" s="13">
-        <v>0</v>
-      </c>
-      <c r="M4" s="13">
-        <v>0</v>
-      </c>
-      <c r="N4" s="13">
-        <v>0</v>
-      </c>
-      <c r="O4" s="13">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <v>0</v>
-      </c>
-      <c r="T4" s="13">
-        <v>0</v>
-      </c>
-      <c r="U4" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
-        <v>3</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="D5" s="10">
-        <v>100</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0</v>
-      </c>
-      <c r="J5" s="10">
-        <v>0</v>
-      </c>
-      <c r="K5" s="10">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10">
-        <v>0</v>
-      </c>
-      <c r="M5" s="10">
-        <v>0</v>
-      </c>
-      <c r="N5" s="10">
-        <v>0</v>
-      </c>
-      <c r="O5" s="10">
-        <v>213</v>
-      </c>
-      <c r="P5" s="10">
-        <v>187</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>165</v>
-      </c>
-      <c r="R5" s="10">
-        <v>1</v>
-      </c>
-      <c r="S5" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="T5" s="10">
-        <v>0.13</v>
-      </c>
-      <c r="U5" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B6" s="11">
-        <v>4</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" s="13">
-        <v>100</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
-        <v>0</v>
-      </c>
-      <c r="K6" s="13">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <v>0</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="13">
-        <v>0</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
-        <v>208</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>208</v>
-      </c>
-      <c r="R6" s="13">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <v>310</v>
-      </c>
-      <c r="T6" s="13">
-        <v>0</v>
-      </c>
-      <c r="U6" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="D7" s="10">
-        <v>100</v>
-      </c>
-      <c r="E7" s="10">
-        <v>15.4</v>
-      </c>
-      <c r="F7" s="10">
-        <v>587</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>980</v>
-      </c>
-      <c r="I7" s="10">
-        <v>980</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>0</v>
-      </c>
-      <c r="R7" s="10">
-        <v>0</v>
-      </c>
-      <c r="S7" s="10">
-        <v>0</v>
-      </c>
-      <c r="T7" s="10">
-        <v>0</v>
-      </c>
-      <c r="U7" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="11">
-        <v>6</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="D8" s="13">
-        <v>92</v>
-      </c>
-      <c r="E8" s="13">
-        <v>12.6</v>
-      </c>
-      <c r="F8" s="13">
-        <v>621</v>
-      </c>
-      <c r="G8" s="13">
-        <v>48.1</v>
-      </c>
-      <c r="H8" s="13">
-        <v>17.7</v>
-      </c>
-      <c r="I8" s="13">
-        <v>23.4</v>
-      </c>
-      <c r="J8" s="13">
-        <v>50</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="L8" s="13">
-        <v>0</v>
-      </c>
-      <c r="M8" s="13">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13">
-        <v>41</v>
-      </c>
-      <c r="P8" s="13">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>21</v>
-      </c>
-      <c r="R8" s="13">
-        <v>9</v>
-      </c>
-      <c r="S8" s="13">
-        <v>6</v>
-      </c>
-      <c r="T8" s="13">
-        <v>9</v>
-      </c>
-      <c r="U8" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B9" s="8">
-        <v>7</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="D9" s="10">
-        <v>92</v>
-      </c>
-      <c r="E9" s="10">
-        <v>10.8</v>
-      </c>
-      <c r="F9" s="10">
-        <v>653</v>
-      </c>
-      <c r="G9" s="10">
-        <v>50.1</v>
-      </c>
-      <c r="H9" s="10">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="I9" s="10">
-        <v>24.2</v>
-      </c>
-      <c r="J9" s="10">
-        <v>18</v>
-      </c>
-      <c r="K9" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10">
-        <v>0</v>
-      </c>
-      <c r="O9" s="10">
-        <v>41</v>
-      </c>
-      <c r="P9" s="10">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>21</v>
-      </c>
-      <c r="R9" s="10">
-        <v>9</v>
-      </c>
-      <c r="S9" s="10">
-        <v>6</v>
-      </c>
-      <c r="T9" s="10">
-        <v>9</v>
-      </c>
-      <c r="U9" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B10" s="11">
-        <v>8</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="D10" s="13">
-        <v>92</v>
-      </c>
-      <c r="E10" s="13">
-        <v>13.6</v>
-      </c>
-      <c r="F10" s="13">
-        <v>661</v>
-      </c>
-      <c r="G10" s="13">
-        <v>51.5</v>
-      </c>
-      <c r="H10" s="13">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="I10" s="13">
-        <v>24.9</v>
-      </c>
-      <c r="J10" s="13">
-        <v>100</v>
-      </c>
-      <c r="K10" s="13">
-        <v>1.2</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
-      </c>
-      <c r="N10" s="13">
-        <v>0</v>
-      </c>
-      <c r="O10" s="13">
-        <v>41</v>
-      </c>
-      <c r="P10" s="13">
-        <v>26</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>21</v>
-      </c>
-      <c r="R10" s="13">
-        <v>9</v>
-      </c>
-      <c r="S10" s="13">
-        <v>6</v>
-      </c>
-      <c r="T10" s="13">
-        <v>9</v>
-      </c>
-      <c r="U10" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B11" s="8">
-        <v>9</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="D11" s="10">
-        <v>100</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10">
-        <v>375</v>
-      </c>
-      <c r="P11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="S11" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="11">
-        <v>10</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="D12" s="13">
-        <v>87</v>
-      </c>
-      <c r="E12" s="13">
-        <v>10.7</v>
-      </c>
-      <c r="F12" s="13">
-        <v>104</v>
-      </c>
-      <c r="G12" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="H12" s="13">
-        <v>1.8</v>
-      </c>
-      <c r="I12" s="13">
-        <v>4.8</v>
-      </c>
-      <c r="J12" s="13">
-        <v>52</v>
-      </c>
-      <c r="K12" s="13">
-        <v>21</v>
-      </c>
-      <c r="L12" s="13">
-        <v>400</v>
-      </c>
-      <c r="M12" s="13">
-        <v>10</v>
-      </c>
-      <c r="N12" s="13">
-        <v>87</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="P12" s="13">
-        <v>3.4</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="R12" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="S12" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="T12" s="13">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U12" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="D13" s="10">
-        <v>87</v>
-      </c>
-      <c r="E13" s="10">
-        <v>13.8</v>
-      </c>
-      <c r="F13" s="10">
-        <v>132</v>
-      </c>
-      <c r="G13" s="10">
-        <v>5.5</v>
-      </c>
-      <c r="H13" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I13" s="10">
-        <v>6</v>
-      </c>
-      <c r="J13" s="10">
-        <v>65</v>
-      </c>
-      <c r="K13" s="10">
-        <v>25</v>
-      </c>
-      <c r="L13" s="10">
-        <v>400</v>
-      </c>
-      <c r="M13" s="10">
-        <v>10</v>
-      </c>
-      <c r="N13" s="10">
-        <v>25</v>
-      </c>
-      <c r="O13" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="P13" s="10">
-        <v>3.6</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="R13" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="S13" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="T13" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U13" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B14" s="11">
-        <v>12</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="D14" s="13">
-        <v>87</v>
-      </c>
-      <c r="E14" s="13">
-        <v>10</v>
-      </c>
-      <c r="F14" s="13">
-        <v>100</v>
-      </c>
-      <c r="G14" s="13">
-        <v>3.7</v>
-      </c>
-      <c r="H14" s="13">
-        <v>1.8</v>
-      </c>
-      <c r="I14" s="13">
-        <v>4.3</v>
-      </c>
-      <c r="J14" s="13">
-        <v>52</v>
-      </c>
-      <c r="K14" s="13">
-        <v>21</v>
-      </c>
-      <c r="L14" s="13">
-        <v>380</v>
-      </c>
-      <c r="M14" s="13">
-        <v>8</v>
-      </c>
-      <c r="N14" s="13">
-        <v>104</v>
-      </c>
-      <c r="O14" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="P14" s="13">
-        <v>3.4</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="R14" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="S14" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="T14" s="13">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U14" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B15" s="8">
-        <v>13</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="D15" s="10">
-        <v>87</v>
-      </c>
-      <c r="E15" s="10">
-        <v>11.1</v>
-      </c>
-      <c r="F15" s="10">
-        <v>109</v>
-      </c>
-      <c r="G15" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="H15" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="I15" s="10">
-        <v>5</v>
-      </c>
-      <c r="J15" s="10">
-        <v>52</v>
-      </c>
-      <c r="K15" s="10">
-        <v>21</v>
-      </c>
-      <c r="L15" s="10">
-        <v>420</v>
-      </c>
-      <c r="M15" s="10">
-        <v>12</v>
-      </c>
-      <c r="N15" s="10">
-        <v>78</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="P15" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="R15" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="S15" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="T15" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U15" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B16" s="11">
-        <v>14</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="D16" s="13">
-        <v>87</v>
-      </c>
-      <c r="E16" s="13">
-        <v>1.7</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46</v>
-      </c>
-      <c r="G16" s="13">
-        <v>1.4</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="I16" s="13">
-        <v>1.3</v>
-      </c>
-      <c r="J16" s="13">
-        <v>14</v>
-      </c>
-      <c r="K16" s="13">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="13">
-        <v>287</v>
-      </c>
-      <c r="O16" s="13">
-        <v>1.3</v>
-      </c>
-      <c r="P16" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>5.3</v>
-      </c>
-      <c r="S16" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="T16" s="13">
-        <v>1</v>
-      </c>
-      <c r="U16" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
-        <v>15</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="D17" s="10">
-        <v>100</v>
-      </c>
-      <c r="E17" s="10">
-        <v>0</v>
-      </c>
-      <c r="F17" s="10">
-        <v>0</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0</v>
-      </c>
-      <c r="I17" s="10">
-        <v>0</v>
-      </c>
-      <c r="J17" s="10">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10">
-        <v>0</v>
-      </c>
-      <c r="L17" s="10">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10">
-        <v>0</v>
-      </c>
-      <c r="N17" s="10">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <v>3</v>
-      </c>
-      <c r="P17" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>0</v>
-      </c>
-      <c r="R17" s="10">
-        <v>0</v>
-      </c>
-      <c r="S17" s="10">
-        <v>390</v>
-      </c>
-      <c r="T17" s="10">
-        <v>600</v>
-      </c>
-      <c r="U17" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="11">
-        <v>16</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="D18" s="13">
-        <v>87</v>
-      </c>
-      <c r="E18" s="13">
-        <v>11.8</v>
-      </c>
-      <c r="F18" s="13">
-        <v>104</v>
-      </c>
-      <c r="G18" s="13">
-        <v>3.8</v>
-      </c>
-      <c r="H18" s="13">
-        <v>1.8</v>
-      </c>
-      <c r="I18" s="13">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J18" s="13">
-        <v>25</v>
-      </c>
-      <c r="K18" s="13">
-        <v>10</v>
-      </c>
-      <c r="L18" s="13">
-        <v>490</v>
-      </c>
-      <c r="M18" s="13">
-        <v>26</v>
-      </c>
-      <c r="N18" s="13">
-        <v>41</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="P18" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>1.7</v>
-      </c>
-      <c r="R18" s="13">
-        <v>4.8</v>
-      </c>
-      <c r="S18" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="T18" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="U18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="8">
-        <v>17</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="D19" s="10">
-        <v>87</v>
-      </c>
-      <c r="E19" s="10">
-        <v>11.1</v>
-      </c>
-      <c r="F19" s="10">
-        <v>100</v>
-      </c>
-      <c r="G19" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="H19" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="I19" s="10">
-        <v>4</v>
-      </c>
-      <c r="J19" s="10">
-        <v>25</v>
-      </c>
-      <c r="K19" s="10">
-        <v>10</v>
-      </c>
-      <c r="L19" s="10">
-        <v>450</v>
-      </c>
-      <c r="M19" s="10">
-        <v>22</v>
-      </c>
-      <c r="N19" s="10">
-        <v>71</v>
-      </c>
-      <c r="O19" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="P19" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="R19" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="S19" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="T19" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="U19" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B20" s="11">
-        <v>18</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="D20" s="13">
-        <v>87</v>
-      </c>
-      <c r="E20" s="13">
-        <v>12.2</v>
-      </c>
-      <c r="F20" s="13">
-        <v>117</v>
-      </c>
-      <c r="G20" s="13">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H20" s="13">
-        <v>2</v>
-      </c>
-      <c r="I20" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="J20" s="13">
-        <v>25</v>
-      </c>
-      <c r="K20" s="13">
-        <v>10</v>
-      </c>
-      <c r="L20" s="13">
-        <v>517</v>
-      </c>
-      <c r="M20" s="13">
-        <v>28</v>
-      </c>
-      <c r="N20" s="13">
-        <v>37</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="P20" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>1.7</v>
-      </c>
-      <c r="R20" s="13">
-        <v>4.8</v>
-      </c>
-      <c r="S20" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="T20" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="U20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="8">
-        <v>19</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="D21" s="10">
-        <v>95</v>
-      </c>
-      <c r="E21" s="10">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="F21" s="10">
-        <v>530</v>
-      </c>
-      <c r="G21" s="10">
-        <v>29</v>
-      </c>
-      <c r="H21" s="10">
-        <v>8.1</v>
-      </c>
-      <c r="I21" s="10">
-        <v>13.9</v>
-      </c>
-      <c r="J21" s="10">
-        <v>104</v>
-      </c>
-      <c r="K21" s="10">
-        <v>15</v>
-      </c>
-      <c r="L21" s="10">
-        <v>0</v>
-      </c>
-      <c r="M21" s="10">
-        <v>0</v>
-      </c>
-      <c r="N21" s="10">
-        <v>0</v>
-      </c>
-      <c r="O21" s="10">
-        <v>100</v>
-      </c>
-      <c r="P21" s="10">
-        <v>45</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>36</v>
-      </c>
-      <c r="R21" s="10">
-        <v>6</v>
-      </c>
-      <c r="S21" s="10">
-        <v>7</v>
-      </c>
-      <c r="T21" s="10">
-        <v>7.5</v>
-      </c>
-      <c r="U21" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="11">
-        <v>20</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="D22" s="13">
-        <v>93</v>
-      </c>
-      <c r="E22" s="13">
-        <v>11</v>
-      </c>
-      <c r="F22" s="13">
-        <v>590</v>
-      </c>
-      <c r="G22" s="13">
-        <v>30</v>
-      </c>
-      <c r="H22" s="13">
-        <v>8.4</v>
-      </c>
-      <c r="I22" s="13">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="J22" s="13">
-        <v>79</v>
-      </c>
-      <c r="K22" s="13">
-        <v>12</v>
-      </c>
-      <c r="L22" s="13">
-        <v>0</v>
-      </c>
-      <c r="M22" s="13">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13">
-        <v>0</v>
-      </c>
-      <c r="O22" s="13">
-        <v>80</v>
-      </c>
-      <c r="P22" s="13">
-        <v>37</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>30</v>
-      </c>
-      <c r="R22" s="13">
-        <v>5</v>
-      </c>
-      <c r="S22" s="13">
-        <v>6</v>
-      </c>
-      <c r="T22" s="13">
-        <v>7</v>
-      </c>
-      <c r="U22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="8">
-        <v>21</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="D23" s="10">
-        <v>93</v>
-      </c>
-      <c r="E23" s="10">
-        <v>11.4</v>
-      </c>
-      <c r="F23" s="10">
-        <v>648</v>
-      </c>
-      <c r="G23" s="10">
-        <v>37</v>
-      </c>
-      <c r="H23" s="10">
-        <v>10.4</v>
-      </c>
-      <c r="I23" s="10">
-        <v>17.8</v>
-      </c>
-      <c r="J23" s="10">
-        <v>100</v>
-      </c>
-      <c r="K23" s="10">
-        <v>15</v>
-      </c>
-      <c r="L23" s="10">
-        <v>0</v>
-      </c>
-      <c r="M23" s="10">
-        <v>0</v>
-      </c>
-      <c r="N23" s="10">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10">
-        <v>76</v>
-      </c>
-      <c r="P23" s="10">
-        <v>40</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>30</v>
-      </c>
-      <c r="R23" s="10">
-        <v>10</v>
-      </c>
-      <c r="S23" s="10">
-        <v>7.2</v>
-      </c>
-      <c r="T23" s="10">
-        <v>7.4</v>
-      </c>
-      <c r="U23" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B24" s="11">
-        <v>22</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="D24" s="13">
-        <v>90</v>
-      </c>
-      <c r="E24" s="13">
-        <v>6.67</v>
-      </c>
-      <c r="F24" s="13">
-        <v>193</v>
-      </c>
-      <c r="G24" s="13">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H24" s="13">
-        <v>2.9</v>
-      </c>
-      <c r="I24" s="13">
-        <v>5.4</v>
-      </c>
-      <c r="J24" s="13">
-        <v>36</v>
-      </c>
-      <c r="K24" s="13">
-        <v>5</v>
-      </c>
-      <c r="L24" s="13">
-        <v>45</v>
-      </c>
-      <c r="M24" s="13">
-        <v>51</v>
-      </c>
-      <c r="N24" s="13">
-        <v>193</v>
-      </c>
-      <c r="O24" s="13">
-        <v>14</v>
-      </c>
-      <c r="P24" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="R24" s="13">
-        <v>22</v>
-      </c>
-      <c r="S24" s="13">
-        <v>1.3</v>
-      </c>
-      <c r="T24" s="13">
-        <v>4.7</v>
-      </c>
-      <c r="U24" s="13">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B25" s="8">
-        <v>23</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="D25" s="10">
-        <v>100</v>
-      </c>
-      <c r="E25" s="10">
-        <v>16.7</v>
-      </c>
-      <c r="F25" s="10">
-        <v>934</v>
-      </c>
-      <c r="G25" s="10">
-        <v>780</v>
-      </c>
-      <c r="H25" s="10">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10">
-        <v>0</v>
-      </c>
-      <c r="J25" s="10">
-        <v>0</v>
-      </c>
-      <c r="K25" s="10">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10">
-        <v>0</v>
-      </c>
-      <c r="M25" s="10">
-        <v>0</v>
-      </c>
-      <c r="N25" s="10">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10">
-        <v>0</v>
-      </c>
-      <c r="P25" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>0</v>
-      </c>
-      <c r="R25" s="10">
-        <v>0</v>
-      </c>
-      <c r="S25" s="10">
-        <v>0</v>
-      </c>
-      <c r="T25" s="10">
-        <v>0</v>
-      </c>
-      <c r="U25" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="11">
-        <v>24</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="D26" s="13">
-        <v>87</v>
-      </c>
-      <c r="E26" s="13">
-        <v>13.8</v>
-      </c>
-      <c r="F26" s="13">
-        <v>87</v>
-      </c>
-      <c r="G26" s="13">
-        <v>2.4</v>
-      </c>
-      <c r="H26" s="13">
-        <v>1.8</v>
-      </c>
-      <c r="I26" s="13">
-        <v>3.8</v>
-      </c>
-      <c r="J26" s="13">
-        <v>40</v>
-      </c>
-      <c r="K26" s="13">
-        <v>32</v>
-      </c>
-      <c r="L26" s="13">
-        <v>650</v>
-      </c>
-      <c r="M26" s="13">
-        <v>16.3</v>
-      </c>
-      <c r="N26" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="O26" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="P26" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>3.3</v>
-      </c>
-      <c r="R26" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="S26" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="T26" s="13">
-        <v>50</v>
-      </c>
-      <c r="U26" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>373</v>
-      </c>
-      <c r="B27" s="8">
-        <v>25</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="D27" s="10">
-        <v>87</v>
-      </c>
-      <c r="E27" s="10">
-        <v>14.2</v>
-      </c>
-      <c r="F27" s="10">
-        <v>644</v>
-      </c>
-      <c r="G27" s="10">
-        <v>10.8</v>
-      </c>
-      <c r="H27" s="10">
-        <v>15.2</v>
-      </c>
-      <c r="I27" s="10">
-        <v>26.8</v>
-      </c>
-      <c r="J27" s="10">
-        <v>39</v>
-      </c>
-      <c r="K27" s="10">
-        <v>20</v>
-      </c>
-      <c r="L27" s="10">
-        <v>123</v>
-      </c>
-      <c r="M27" s="10">
-        <v>6</v>
-      </c>
-      <c r="N27" s="10">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="O27" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="P27" s="10">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>1.9</v>
-      </c>
-      <c r="R27" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="S27" s="10">
-        <v>2</v>
-      </c>
-      <c r="T27" s="10">
-        <v>5</v>
-      </c>
-      <c r="U27" s="10">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B28" s="11">
-        <v>26</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="D28" s="13">
-        <v>100</v>
-      </c>
-      <c r="E28" s="13">
-        <v>0</v>
-      </c>
-      <c r="F28" s="13">
-        <v>0</v>
-      </c>
-      <c r="G28" s="13">
-        <v>0</v>
-      </c>
-      <c r="H28" s="13">
-        <v>0</v>
-      </c>
-      <c r="I28" s="13">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13">
-        <v>0</v>
-      </c>
-      <c r="K28" s="13">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13">
-        <v>0</v>
-      </c>
-      <c r="M28" s="13">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13">
-        <v>0</v>
-      </c>
-      <c r="O28" s="13">
-        <v>160</v>
-      </c>
-      <c r="P28" s="13">
-        <v>210</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>190</v>
-      </c>
-      <c r="R28" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="S28" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="T28" s="13">
-        <v>0</v>
-      </c>
-      <c r="U28" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B29" s="8">
-        <v>27</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="D29" s="10">
-        <v>100</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10">
-        <v>0</v>
-      </c>
-      <c r="I29" s="10">
-        <v>0</v>
-      </c>
-      <c r="J29" s="10">
-        <v>0</v>
-      </c>
-      <c r="K29" s="10">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10">
-        <v>0</v>
-      </c>
-      <c r="M29" s="10">
-        <v>0</v>
-      </c>
-      <c r="N29" s="10">
-        <v>0</v>
-      </c>
-      <c r="O29" s="10">
-        <v>0</v>
-      </c>
-      <c r="P29" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>0</v>
-      </c>
-      <c r="R29" s="10">
-        <v>0</v>
-      </c>
-      <c r="S29" s="10">
-        <v>270</v>
-      </c>
-      <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="11">
-        <v>28</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="D30" s="13">
-        <v>90</v>
-      </c>
-      <c r="E30" s="13">
-        <v>14.4</v>
-      </c>
-      <c r="F30" s="13">
-        <v>790</v>
-      </c>
-      <c r="G30" s="13">
-        <v>64</v>
-      </c>
-      <c r="H30" s="13">
-        <v>18</v>
-      </c>
-      <c r="I30" s="13">
-        <v>31</v>
-      </c>
-      <c r="J30" s="13">
-        <v>40</v>
-      </c>
-      <c r="K30" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="L30" s="13">
-        <v>0</v>
-      </c>
-      <c r="M30" s="13">
-        <v>0</v>
-      </c>
-      <c r="N30" s="13">
-        <v>0</v>
-      </c>
-      <c r="O30" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="P30" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>2</v>
-      </c>
-      <c r="R30" s="13">
-        <v>1</v>
-      </c>
-      <c r="S30" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="T30" s="13">
-        <v>2.1</v>
-      </c>
-      <c r="U30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="8">
-        <v>29</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="D31" s="10">
-        <v>90</v>
-      </c>
-      <c r="E31" s="10">
-        <v>7.6</v>
-      </c>
-      <c r="F31" s="10">
-        <v>348</v>
-      </c>
-      <c r="G31" s="10">
-        <v>19.5</v>
-      </c>
-      <c r="H31" s="10">
-        <v>7.1</v>
-      </c>
-      <c r="I31" s="10">
-        <v>15.9</v>
-      </c>
-      <c r="J31" s="10">
-        <v>23</v>
-      </c>
-      <c r="K31" s="10">
-        <v>7</v>
-      </c>
-      <c r="L31" s="10">
-        <v>40</v>
-      </c>
-      <c r="M31" s="10">
-        <v>78</v>
-      </c>
-      <c r="N31" s="10">
-        <v>120</v>
-      </c>
-      <c r="O31" s="10">
-        <v>5</v>
-      </c>
-      <c r="P31" s="10">
-        <v>10</v>
-      </c>
-      <c r="Q31" s="10">
-        <v>2.8</v>
-      </c>
-      <c r="R31" s="10">
-        <v>14</v>
-      </c>
-      <c r="S31" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="T31" s="10">
-        <v>0.13</v>
-      </c>
-      <c r="U31" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>305</v>
-      </c>
-      <c r="B32" s="11">
-        <v>30</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="D32" s="13">
-        <v>87</v>
-      </c>
-      <c r="E32" s="13">
-        <v>11.2</v>
-      </c>
-      <c r="F32" s="13">
-        <v>96</v>
-      </c>
-      <c r="G32" s="13">
-        <v>3.9</v>
-      </c>
-      <c r="H32" s="13">
-        <v>1.7</v>
-      </c>
-      <c r="I32" s="13">
-        <v>4.2</v>
-      </c>
-      <c r="J32" s="13">
-        <v>16</v>
-      </c>
-      <c r="K32" s="13">
-        <v>7</v>
-      </c>
-      <c r="L32" s="13">
-        <v>568</v>
-      </c>
-      <c r="M32" s="13">
-        <v>55</v>
-      </c>
-      <c r="N32" s="13">
-        <v>26</v>
-      </c>
-      <c r="O32" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="P32" s="13">
-        <v>3.3</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>1.7</v>
-      </c>
-      <c r="R32" s="13">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="S32" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="T32" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="U32" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="8">
-        <v>31</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D33" s="10">
-        <v>89</v>
-      </c>
-      <c r="E33" s="10">
-        <v>13</v>
-      </c>
-      <c r="F33" s="10">
-        <v>115</v>
-      </c>
-      <c r="G33" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="H33" s="10">
-        <v>2.8</v>
-      </c>
-      <c r="I33" s="10">
-        <v>2.1</v>
-      </c>
-      <c r="J33" s="10">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K33" s="10">
-        <v>8</v>
-      </c>
-      <c r="L33" s="10">
-        <v>550</v>
-      </c>
-      <c r="M33" s="10">
-        <v>60</v>
-      </c>
-      <c r="N33" s="10">
-        <v>21</v>
-      </c>
-      <c r="O33" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="P33" s="10">
-        <v>3.3</v>
-      </c>
-      <c r="Q33" s="10">
-        <v>0</v>
-      </c>
-      <c r="R33" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="S33" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="T33" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="U33" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B34" s="11">
-        <v>32</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="D34" s="13">
-        <v>99</v>
-      </c>
-      <c r="E34" s="13">
-        <v>34</v>
-      </c>
-      <c r="F34" s="13">
-        <v>0</v>
-      </c>
-      <c r="G34" s="13">
-        <v>0</v>
-      </c>
-      <c r="H34" s="13">
-        <v>0</v>
-      </c>
-      <c r="I34" s="13">
-        <v>0</v>
-      </c>
-      <c r="J34" s="13">
-        <v>990</v>
-      </c>
-      <c r="K34" s="13">
-        <v>40</v>
-      </c>
-      <c r="L34" s="13">
-        <v>0</v>
-      </c>
-      <c r="M34" s="13">
-        <v>0</v>
-      </c>
-      <c r="N34" s="13">
-        <v>0</v>
-      </c>
-      <c r="O34" s="13">
-        <v>0</v>
-      </c>
-      <c r="P34" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13">
-        <v>0</v>
-      </c>
-      <c r="R34" s="13">
-        <v>0</v>
-      </c>
-      <c r="S34" s="13">
-        <v>0</v>
-      </c>
-      <c r="T34" s="13">
-        <v>0</v>
-      </c>
-      <c r="U34" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="8">
-        <v>33</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D35" s="10">
-        <v>87</v>
-      </c>
-      <c r="E35" s="10">
-        <v>9.1</v>
-      </c>
-      <c r="F35" s="10">
-        <v>440</v>
-      </c>
-      <c r="G35" s="10">
-        <v>27.5</v>
-      </c>
-      <c r="H35" s="10">
-        <v>6.4</v>
-      </c>
-      <c r="I35" s="10">
-        <v>13.1</v>
-      </c>
-      <c r="J35" s="10">
-        <v>13</v>
-      </c>
-      <c r="K35" s="10">
-        <v>6</v>
-      </c>
-      <c r="L35" s="10">
-        <v>64</v>
-      </c>
-      <c r="M35" s="10">
-        <v>93</v>
-      </c>
-      <c r="N35" s="10">
-        <v>60</v>
-      </c>
-      <c r="O35" s="10">
-        <v>2</v>
-      </c>
-      <c r="P35" s="10">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="R35" s="10">
-        <v>20</v>
-      </c>
-      <c r="S35" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="T35" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="U35" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B36" s="11">
-        <v>34</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="D36" s="13">
-        <v>99</v>
-      </c>
-      <c r="E36" s="13">
-        <v>36</v>
-      </c>
-      <c r="F36" s="13">
-        <v>0</v>
-      </c>
-      <c r="G36" s="13">
-        <v>0</v>
-      </c>
-      <c r="H36" s="13">
-        <v>0</v>
-      </c>
-      <c r="I36" s="13">
-        <v>0</v>
-      </c>
-      <c r="J36" s="13">
-        <v>990</v>
-      </c>
-      <c r="K36" s="13">
-        <v>524</v>
-      </c>
-      <c r="L36" s="13">
-        <v>0</v>
-      </c>
-      <c r="M36" s="13">
-        <v>0</v>
-      </c>
-      <c r="N36" s="13">
-        <v>0</v>
-      </c>
-      <c r="O36" s="13">
-        <v>0</v>
-      </c>
-      <c r="P36" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="13">
-        <v>0</v>
-      </c>
-      <c r="R36" s="13">
-        <v>0</v>
-      </c>
-      <c r="S36" s="13">
-        <v>0</v>
-      </c>
-      <c r="T36" s="13">
-        <v>0</v>
-      </c>
-      <c r="U36" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="8">
-        <v>35</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="D37" s="10">
-        <v>87</v>
-      </c>
-      <c r="E37" s="10">
-        <v>12.8</v>
-      </c>
-      <c r="F37" s="10">
-        <v>113</v>
-      </c>
-      <c r="G37" s="10">
-        <v>3.1</v>
-      </c>
-      <c r="H37" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="I37" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="J37" s="10">
-        <v>19</v>
-      </c>
-      <c r="K37" s="10">
-        <v>8</v>
-      </c>
-      <c r="L37" s="10">
-        <v>580</v>
-      </c>
-      <c r="M37" s="10">
-        <v>78</v>
-      </c>
-      <c r="N37" s="10">
-        <v>21</v>
-      </c>
-      <c r="O37" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="P37" s="10">
-        <v>3.3</v>
-      </c>
-      <c r="Q37" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="R37" s="10">
-        <v>4</v>
-      </c>
-      <c r="S37" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="T37" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="U37" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="11">
-        <v>36</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="D38" s="13">
-        <v>87</v>
-      </c>
-      <c r="E38" s="13">
-        <v>12.2</v>
-      </c>
-      <c r="F38" s="13">
-        <v>169</v>
-      </c>
-      <c r="G38" s="13">
-        <v>5.9</v>
-      </c>
-      <c r="H38" s="13">
-        <v>2.8</v>
-      </c>
-      <c r="I38" s="13">
-        <v>6.3</v>
-      </c>
-      <c r="J38" s="13">
-        <v>44</v>
-      </c>
-      <c r="K38" s="13">
-        <v>15</v>
-      </c>
-      <c r="L38" s="13">
-        <v>419</v>
-      </c>
-      <c r="M38" s="13">
-        <v>60</v>
-      </c>
-      <c r="N38" s="13">
-        <v>26</v>
-      </c>
-      <c r="O38" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="P38" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q38" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="R38" s="13">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="S38" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="T38" s="13">
-        <v>1.4</v>
-      </c>
-      <c r="U38" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B39" s="8">
-        <v>37</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="D39" s="10">
-        <v>87</v>
-      </c>
-      <c r="E39" s="10">
-        <v>9.4</v>
-      </c>
-      <c r="F39" s="10">
-        <v>157</v>
-      </c>
-      <c r="G39" s="10">
-        <v>5.7</v>
-      </c>
-      <c r="H39" s="10">
-        <v>2.6</v>
-      </c>
-      <c r="I39" s="10">
-        <v>5.8</v>
-      </c>
-      <c r="J39" s="10">
-        <v>39</v>
-      </c>
-      <c r="K39" s="10">
-        <v>12</v>
-      </c>
-      <c r="L39" s="10">
-        <v>270</v>
-      </c>
-      <c r="M39" s="10">
-        <v>66</v>
-      </c>
-      <c r="N39" s="10">
-        <v>65</v>
-      </c>
-      <c r="O39" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="P39" s="10">
-        <v>4</v>
-      </c>
-      <c r="Q39" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="R39" s="10">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="S39" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="T39" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="U39" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="11">
-        <v>38</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="D40" s="13">
-        <v>87</v>
-      </c>
-      <c r="E40" s="13">
-        <v>6.8</v>
-      </c>
-      <c r="F40" s="13">
-        <v>157</v>
-      </c>
-      <c r="G40" s="13">
-        <v>6.4</v>
-      </c>
-      <c r="H40" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="I40" s="13">
-        <v>5.8</v>
-      </c>
-      <c r="J40" s="13">
-        <v>45</v>
-      </c>
-      <c r="K40" s="13">
-        <v>12</v>
-      </c>
-      <c r="L40" s="13">
-        <v>135</v>
-      </c>
-      <c r="M40" s="13">
-        <v>55</v>
-      </c>
-      <c r="N40" s="13">
-        <v>100</v>
-      </c>
-      <c r="O40" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="P40" s="13">
-        <v>11.5</v>
-      </c>
-      <c r="Q40" s="13">
-        <v>6</v>
-      </c>
-      <c r="R40" s="13">
-        <v>9.9</v>
-      </c>
-      <c r="S40" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="T40" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="U40" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="8">
-        <v>39</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="D41" s="10">
-        <v>87</v>
-      </c>
-      <c r="E41" s="10">
-        <v>11</v>
-      </c>
-      <c r="F41" s="10">
-        <v>226</v>
-      </c>
-      <c r="G41" s="10">
-        <v>15.8</v>
-      </c>
-      <c r="H41" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I41" s="10">
-        <v>5.6</v>
-      </c>
-      <c r="J41" s="10">
-        <v>13</v>
-      </c>
-      <c r="K41" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="L41" s="10">
-        <v>416</v>
-      </c>
-      <c r="M41" s="10">
-        <v>56</v>
-      </c>
-      <c r="N41" s="10">
-        <v>61</v>
-      </c>
-      <c r="O41" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="P41" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="Q41" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="R41" s="10">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="S41" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="T41" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="U41" s="10">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -969,9 +969,6 @@
     <t>minerals</t>
   </si>
   <si>
-    <t>f_crop</t>
-  </si>
-  <si>
     <t>dairy</t>
   </si>
   <si>
@@ -2013,6 +2010,9 @@
   </si>
   <si>
     <t>add as crop product?</t>
+  </si>
+  <si>
+    <t>f_crop_group</t>
   </si>
 </sst>
 </file>
@@ -2819,12 +2819,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -2908,28 +2908,28 @@
         <v>120</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>328</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>329</v>
       </c>
       <c r="L2" s="15" t="s">
         <v>125</v>
@@ -2944,10 +2944,10 @@
         <v>143</v>
       </c>
       <c r="P2" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q2" s="15" t="s">
         <v>330</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>331</v>
       </c>
       <c r="R2" s="15" t="s">
         <v>146</v>
@@ -2956,10 +2956,10 @@
         <v>147</v>
       </c>
       <c r="T2" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="U2" s="15" t="s">
         <v>332</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D3" s="10">
         <v>99</v>
@@ -3032,7 +3032,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D4" s="13">
         <v>99</v>
@@ -3094,7 +3094,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D5" s="10">
         <v>100</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D6" s="13">
         <v>100</v>
@@ -3218,7 +3218,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" s="10">
         <v>100</v>
@@ -3283,7 +3283,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D8" s="13">
         <v>92</v>
@@ -3345,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D9" s="10">
         <v>92</v>
@@ -3407,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D10" s="13">
         <v>92</v>
@@ -3469,7 +3469,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D11" s="10">
         <v>100</v>
@@ -3534,7 +3534,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D12" s="13">
         <v>87</v>
@@ -3596,7 +3596,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D13" s="10">
         <v>87</v>
@@ -3658,7 +3658,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D14" s="13">
         <v>87</v>
@@ -3720,7 +3720,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D15" s="10">
         <v>87</v>
@@ -3782,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D16" s="13">
         <v>87</v>
@@ -3844,7 +3844,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D17" s="10">
         <v>100</v>
@@ -3909,7 +3909,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D18" s="13">
         <v>87</v>
@@ -3971,7 +3971,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D19" s="10">
         <v>87</v>
@@ -4033,7 +4033,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D20" s="13">
         <v>87</v>
@@ -4095,7 +4095,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D21" s="10">
         <v>95</v>
@@ -4157,7 +4157,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D22" s="13">
         <v>93</v>
@@ -4219,7 +4219,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D23" s="10">
         <v>93</v>
@@ -4281,7 +4281,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D24" s="13">
         <v>90</v>
@@ -4343,7 +4343,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D25" s="10">
         <v>100</v>
@@ -4408,7 +4408,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D26" s="13">
         <v>87</v>
@@ -4467,13 +4467,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B27" s="8">
         <v>25</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D27" s="10">
         <v>87</v>
@@ -4535,7 +4535,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D28" s="13">
         <v>100</v>
@@ -4597,7 +4597,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D29" s="10">
         <v>100</v>
@@ -4662,7 +4662,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D30" s="13">
         <v>90</v>
@@ -4727,7 +4727,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D31" s="10">
         <v>90</v>
@@ -4792,7 +4792,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D32" s="13">
         <v>87</v>
@@ -4857,7 +4857,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D33" s="10">
         <v>89</v>
@@ -4919,7 +4919,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D34" s="13">
         <v>99</v>
@@ -4984,7 +4984,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D35" s="10">
         <v>87</v>
@@ -5046,7 +5046,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D36" s="13">
         <v>99</v>
@@ -5111,7 +5111,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D37" s="10">
         <v>87</v>
@@ -5176,7 +5176,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D38" s="13">
         <v>87</v>
@@ -5238,7 +5238,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D39" s="10">
         <v>87</v>
@@ -5303,7 +5303,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D40" s="13">
         <v>87</v>
@@ -5368,7 +5368,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D41" s="10">
         <v>87</v>
@@ -5467,10 +5467,10 @@
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>313</v>
+        <v>650</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>1</v>
@@ -5479,10 +5479,10 @@
         <v>8</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>3</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5518,7 +5518,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P2" s="20" t="s">
         <v>298</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="103" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="17"/>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="103" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -5980,7 +5980,7 @@
         <v>43</v>
       </c>
       <c r="J31" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M31" t="s">
         <v>27</v>
@@ -5995,7 +5995,7 @@
         <v>44</v>
       </c>
       <c r="J32" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M32" t="s">
         <v>27</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J33" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M33" t="s">
         <v>27</v>
@@ -6022,10 +6022,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J34" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M34" t="s">
         <v>27</v>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J35" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M35" t="s">
         <v>27</v>
@@ -6172,10 +6172,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F44" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J44" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="M44" t="s">
         <v>27</v>
@@ -6205,7 +6205,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="103" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N47" s="18"/>
     </row>
@@ -6323,7 +6323,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I56" t="s">
         <v>32</v>
@@ -6359,7 +6359,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I58" t="s">
         <v>16</v>
@@ -6395,7 +6395,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I60" t="s">
         <v>33</v>
@@ -6521,12 +6521,12 @@
         <v>23</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6547,7 +6547,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -6555,13 +6555,13 @@
         <v>19</v>
       </c>
       <c r="H70" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I70" t="s">
         <v>28</v>
       </c>
       <c r="M70" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N70" s="3">
         <v>90</v>
@@ -6576,19 +6576,19 @@
         <v>19</v>
       </c>
       <c r="B71" t="s">
+        <v>313</v>
+      </c>
+      <c r="E71" t="s">
         <v>314</v>
       </c>
-      <c r="E71" t="s">
-        <v>315</v>
-      </c>
       <c r="H71" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I71" t="s">
         <v>28</v>
       </c>
       <c r="M71" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N71" s="3">
         <v>5</v>
@@ -6603,19 +6603,19 @@
         <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E72" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I72" t="s">
         <v>28</v>
       </c>
       <c r="M72" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N72" s="3">
         <v>5</v>
@@ -6630,16 +6630,16 @@
         <v>19</v>
       </c>
       <c r="E73" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H73" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I73" t="s">
         <v>28</v>
       </c>
       <c r="M73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N73" s="3">
         <v>0</v>
@@ -6654,19 +6654,19 @@
         <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E74" t="s">
+        <v>317</v>
+      </c>
+      <c r="H74" t="s">
         <v>318</v>
-      </c>
-      <c r="H74" t="s">
-        <v>319</v>
       </c>
       <c r="I74" t="s">
         <v>28</v>
       </c>
       <c r="M74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N74" s="3">
         <v>0</v>
@@ -6685,13 +6685,13 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
+        <v>313</v>
+      </c>
+      <c r="E76" t="s">
         <v>314</v>
       </c>
-      <c r="E76" t="s">
-        <v>315</v>
-      </c>
       <c r="H76" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I76" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>811</v>
       </c>
       <c r="M76" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N76" s="3">
         <v>50</v>
@@ -6715,13 +6715,13 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E77" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H77" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I77" t="s">
         <v>28</v>
@@ -6730,7 +6730,7 @@
         <v>811</v>
       </c>
       <c r="M77" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N77" s="3">
         <v>50</v>
@@ -6745,10 +6745,10 @@
         <v>19</v>
       </c>
       <c r="E78" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H78" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I78" t="s">
         <v>28</v>
@@ -6757,7 +6757,7 @@
         <v>811</v>
       </c>
       <c r="M78" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N78" s="3">
         <v>0</v>
@@ -6772,13 +6772,13 @@
         <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E79" t="s">
+        <v>317</v>
+      </c>
+      <c r="H79" t="s">
         <v>318</v>
-      </c>
-      <c r="H79" t="s">
-        <v>319</v>
       </c>
       <c r="I79" t="s">
         <v>28</v>
@@ -6787,7 +6787,7 @@
         <v>811</v>
       </c>
       <c r="M79" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N79" s="3">
         <v>0</v>
@@ -6802,13 +6802,13 @@
         <v>19</v>
       </c>
       <c r="B80" t="s">
+        <v>313</v>
+      </c>
+      <c r="E80" t="s">
         <v>314</v>
       </c>
-      <c r="E80" t="s">
-        <v>315</v>
-      </c>
       <c r="H80" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I80" t="s">
         <v>28</v>
@@ -6817,7 +6817,7 @@
         <v>812</v>
       </c>
       <c r="M80" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N80" s="3">
         <v>50</v>
@@ -6832,13 +6832,13 @@
         <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E81" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H81" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I81" t="s">
         <v>28</v>
@@ -6847,7 +6847,7 @@
         <v>812</v>
       </c>
       <c r="M81" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N81" s="3">
         <v>50</v>
@@ -6862,10 +6862,10 @@
         <v>19</v>
       </c>
       <c r="E82" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H82" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I82" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>812</v>
       </c>
       <c r="M82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N82" s="3">
         <v>0</v>
@@ -6889,13 +6889,13 @@
         <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E83" t="s">
+        <v>317</v>
+      </c>
+      <c r="H83" t="s">
         <v>318</v>
-      </c>
-      <c r="H83" t="s">
-        <v>319</v>
       </c>
       <c r="I83" t="s">
         <v>28</v>
@@ -6904,7 +6904,7 @@
         <v>812</v>
       </c>
       <c r="M83" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6920,16 +6920,16 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H85" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I85" t="s">
         <v>28</v>
       </c>
       <c r="M85" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N85" s="3">
         <v>10</v>
@@ -6941,16 +6941,16 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I86" t="s">
         <v>28</v>
       </c>
       <c r="M86" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N86" s="3">
         <v>90</v>
@@ -6966,7 +6966,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -6987,7 +6987,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M89" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N89" s="6">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M90" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N90" s="6">
         <v>0</v>
@@ -7018,16 +7018,16 @@
         <v>19</v>
       </c>
       <c r="B91" t="s">
+        <v>313</v>
+      </c>
+      <c r="E91" t="s">
         <v>314</v>
       </c>
-      <c r="E91" t="s">
-        <v>315</v>
-      </c>
       <c r="G91" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M91" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N91" s="21">
         <f>(0.8*20+0.2*2)</f>
@@ -7037,10 +7037,10 @@
         <v>23</v>
       </c>
       <c r="P91" s="21" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q91" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -7048,10 +7048,10 @@
         <v>19</v>
       </c>
       <c r="G92" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M92" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N92" s="21">
         <f>(0.6*20+0.4*2)</f>
@@ -7061,21 +7061,21 @@
         <v>23</v>
       </c>
       <c r="P92" s="21" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q92" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G93" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M93" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N93" s="21">
         <v>2</v>
@@ -7084,21 +7084,21 @@
         <v>23</v>
       </c>
       <c r="P93" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q93" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>376</v>
+      </c>
+      <c r="G94" t="s">
+        <v>631</v>
+      </c>
+      <c r="M94" s="21" t="s">
         <v>377</v>
-      </c>
-      <c r="G94" t="s">
-        <v>632</v>
-      </c>
-      <c r="M94" s="21" t="s">
-        <v>378</v>
       </c>
       <c r="N94" s="21">
         <v>2</v>
@@ -7107,10 +7107,10 @@
         <v>23</v>
       </c>
       <c r="P94" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q94" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -7124,16 +7124,16 @@
         <v>19</v>
       </c>
       <c r="B96" t="s">
+        <v>313</v>
+      </c>
+      <c r="E96" t="s">
         <v>314</v>
       </c>
-      <c r="E96" t="s">
-        <v>315</v>
-      </c>
       <c r="G96" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M96" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N96" s="21">
         <v>5</v>
@@ -7142,10 +7142,10 @@
         <v>23</v>
       </c>
       <c r="P96" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q96" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -7153,13 +7153,13 @@
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G97" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M97" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N97" s="21">
         <v>5</v>
@@ -7168,10 +7168,10 @@
         <v>23</v>
       </c>
       <c r="P97" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q97" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -7179,10 +7179,10 @@
         <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M98" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N98" s="21">
         <f>0.9*5+0.1*15</f>
@@ -7192,21 +7192,21 @@
         <v>23</v>
       </c>
       <c r="P98" s="21" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q98" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G99" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M99" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N99" s="21">
         <v>15</v>
@@ -7216,18 +7216,18 @@
       </c>
       <c r="P99" s="21"/>
       <c r="Q99" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G100" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M100" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N100" s="21">
         <v>15</v>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="P100" s="21"/>
       <c r="Q100" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -7254,7 +7254,7 @@
         <v>301</v>
       </c>
       <c r="M102" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N102" s="21">
         <v>5</v>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P102" s="21"/>
       <c r="Q102" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -7428,10 +7428,10 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G109" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M109" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N109" s="21">
         <v>5</v>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="P109" s="21"/>
       <c r="Q109" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -7458,7 +7458,7 @@
         <v>cows</v>
       </c>
       <c r="G110" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M110" s="22" t="str">
         <f t="shared" ref="M110:Q114" si="4">M96</f>
@@ -7491,7 +7491,7 @@
         <v>bulls</v>
       </c>
       <c r="G111" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M111" s="22" t="str">
         <f t="shared" si="4"/>
@@ -7520,7 +7520,7 @@
         <v>cattle</v>
       </c>
       <c r="G112" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M112" s="22" t="str">
         <f t="shared" si="4"/>
@@ -7549,7 +7549,7 @@
         <v>sheep</v>
       </c>
       <c r="G113" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M113" s="22" t="str">
         <f t="shared" si="4"/>
@@ -7575,7 +7575,7 @@
         <v>horses</v>
       </c>
       <c r="G114" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M114" s="22" t="str">
         <f t="shared" si="4"/>
@@ -7602,23 +7602,23 @@
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
       <c r="G116" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M116" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N116" s="21"/>
       <c r="P116" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="G117" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M117" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N117" s="21">
         <v>2</v>
@@ -7627,10 +7627,10 @@
         <v>23</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="Q117" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -7643,23 +7643,23 @@
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="G119" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M119" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N119" s="21"/>
       <c r="P119" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="G120" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M120" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N120" s="21">
         <v>3</v>
@@ -7668,10 +7668,10 @@
         <v>23</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="Q120" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -7680,7 +7680,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7705,18 +7705,18 @@
       </c>
       <c r="N123" s="21"/>
       <c r="P123" s="21" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
@@ -7726,19 +7726,19 @@
       <c r="K124" s="3"/>
       <c r="L124" s="3"/>
       <c r="M124" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N124" s="3">
         <v>4.5</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P124" s="3"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -7752,32 +7752,32 @@
       <c r="K125" s="3"/>
       <c r="L125" s="3"/>
       <c r="M125" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N125" s="3">
         <v>6.5</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P125" s="3"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M126" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N126" s="21">
         <v>18</v>
       </c>
       <c r="O126" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P126" s="3"/>
       <c r="Q126" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -7785,35 +7785,35 @@
         <v>20</v>
       </c>
       <c r="M127" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N127" s="21">
         <v>1.5</v>
       </c>
       <c r="O127" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P127" s="3"/>
       <c r="Q127" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M128" t="s">
+        <v>487</v>
+      </c>
+      <c r="N128" s="21">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
         <v>488</v>
-      </c>
-      <c r="N128" s="21">
-        <v>0</v>
-      </c>
-      <c r="O128" t="s">
-        <v>489</v>
       </c>
       <c r="P128" s="3"/>
       <c r="Q128" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -7822,16 +7822,16 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M130" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N130" s="21">
         <v>1</v>
       </c>
       <c r="O130" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="P130" s="21" t="s">
         <v>603</v>
-      </c>
-      <c r="P130" s="21" t="s">
-        <v>604</v>
       </c>
       <c r="Q130" s="21"/>
     </row>
@@ -7840,13 +7840,13 @@
         <v>19</v>
       </c>
       <c r="M131" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N131" s="21">
         <v>1</v>
       </c>
       <c r="O131" s="21" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="P131" s="21"/>
       <c r="Q131" s="21"/>
@@ -7856,19 +7856,19 @@
         <v>19</v>
       </c>
       <c r="B132" t="s">
+        <v>313</v>
+      </c>
+      <c r="E132" t="s">
         <v>314</v>
       </c>
-      <c r="E132" t="s">
-        <v>315</v>
-      </c>
       <c r="M132" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N132" s="21">
         <v>1</v>
       </c>
       <c r="O132" s="21" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="P132" s="21"/>
       <c r="Q132" s="21"/>
@@ -7878,19 +7878,19 @@
         <v>19</v>
       </c>
       <c r="B133" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E133" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M133" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N133" s="21">
         <v>1</v>
       </c>
       <c r="O133" s="21" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="P133" s="21"/>
       <c r="Q133" s="21"/>
@@ -7900,19 +7900,19 @@
         <v>19</v>
       </c>
       <c r="B134" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E134" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M134" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N134" s="21">
         <v>1</v>
       </c>
       <c r="O134" s="21" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="P134" s="21"/>
       <c r="Q134" s="21"/>
@@ -7946,69 +7946,69 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="L137" s="103" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M138" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N138" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="O138" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="P138" s="3"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M139" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N139" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="O139" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P139" s="3"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M140" s="37" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="N140" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M141" s="37" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N141" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M142" s="37" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="N142" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M143" s="37" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="N143" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P143" s="3"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="L144" s="103" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="145" spans="12:16" x14ac:dyDescent="0.25">
@@ -8016,44 +8016,44 @@
         <v>17</v>
       </c>
       <c r="N145" s="21" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O145" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P145" s="21" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="146" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M146" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N146" s="21" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O146" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P146" s="3"/>
     </row>
     <row r="147" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M147" t="s">
+        <v>476</v>
+      </c>
+      <c r="N147" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="O147" t="s">
         <v>477</v>
       </c>
-      <c r="N147" s="21" t="s">
-        <v>615</v>
-      </c>
-      <c r="O147" t="s">
+      <c r="P147" s="21" t="s">
         <v>478</v>
-      </c>
-      <c r="P147" s="21" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="148" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L148" s="103" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="149" spans="12:16" x14ac:dyDescent="0.25">
@@ -8061,30 +8061,30 @@
         <v>17</v>
       </c>
       <c r="N149" s="21" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="O149" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P149" s="21" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="150" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M150" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N150" s="21" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="O150" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P150" s="3"/>
     </row>
     <row r="151" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L151" s="103" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="152" spans="12:16" x14ac:dyDescent="0.25">
@@ -8092,30 +8092,30 @@
         <v>17</v>
       </c>
       <c r="N152" s="21" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="O152" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P152" s="21" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="153" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M153" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N153" s="21" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="O153" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P153" s="3"/>
     </row>
     <row r="154" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L154" s="103" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="155" spans="12:16" x14ac:dyDescent="0.25">
@@ -8123,41 +8123,41 @@
         <v>17</v>
       </c>
       <c r="N155" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O155" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P155" s="21" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="156" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M156" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N156" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O156" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P156" s="3"/>
     </row>
     <row r="157" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L157" s="103" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="158" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M158" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N158" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="O158" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="P158" s="21"/>
     </row>
@@ -8180,7 +8180,7 @@
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>113</v>
@@ -8204,7 +8204,7 @@
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="K3" s="41" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
@@ -8215,7 +8215,7 @@
       <c r="R3" s="42"/>
       <c r="S3" s="42"/>
       <c r="T3" s="56" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="U3" s="42">
         <f>1/6.25</f>
@@ -8235,7 +8235,7 @@
       <c r="AG3" s="42"/>
       <c r="AH3" s="42"/>
       <c r="AI3" s="56" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AJ3" s="42">
         <f>1/6.25</f>
@@ -8244,7 +8244,7 @@
       <c r="AK3" s="42"/>
       <c r="AL3" s="42"/>
       <c r="AP3" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AQ3" s="42"/>
       <c r="AR3" s="42"/>
@@ -8263,7 +8263,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="N4" s="46">
         <v>2</v>
@@ -8302,10 +8302,10 @@
         <v>1</v>
       </c>
       <c r="AB4" s="46" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AC4" s="46" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AD4" s="46">
         <v>2</v>
@@ -8351,22 +8351,22 @@
         <v>54</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F5" s="48" t="s">
+        <v>479</v>
+      </c>
+      <c r="G5" s="48" t="s">
         <v>480</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="H5" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="H5" s="49" t="s">
-        <v>482</v>
-      </c>
       <c r="I5" s="51" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K5" s="45" t="s">
         <v>290</v>
@@ -8375,40 +8375,40 @@
         <v>54</v>
       </c>
       <c r="M5" s="48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O5" s="48" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P5" s="47" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q5" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="Q5" s="48" t="s">
+      <c r="R5" s="48" t="s">
         <v>391</v>
-      </c>
-      <c r="R5" s="48" t="s">
-        <v>392</v>
       </c>
       <c r="S5" s="48" t="s">
         <v>277</v>
       </c>
       <c r="T5" s="49" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="U5" s="48" t="s">
+        <v>479</v>
+      </c>
+      <c r="V5" s="48" t="s">
         <v>480</v>
       </c>
-      <c r="V5" s="48" t="s">
+      <c r="W5" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="W5" s="49" t="s">
-        <v>482</v>
-      </c>
       <c r="X5" s="77" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Z5" s="45" t="s">
         <v>290</v>
@@ -8417,10 +8417,10 @@
         <v>54</v>
       </c>
       <c r="AB5" s="48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AC5" s="71" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AD5" s="48" t="s">
         <v>116</v>
@@ -8429,31 +8429,31 @@
         <v>115</v>
       </c>
       <c r="AF5" s="47" t="s">
+        <v>389</v>
+      </c>
+      <c r="AG5" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="AG5" s="48" t="s">
-        <v>391</v>
-      </c>
       <c r="AH5" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AI5" s="49" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AJ5" s="48" t="s">
+        <v>479</v>
+      </c>
+      <c r="AK5" s="48" t="s">
         <v>480</v>
       </c>
-      <c r="AK5" s="48" t="s">
+      <c r="AL5" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="AL5" s="49" t="s">
-        <v>482</v>
-      </c>
       <c r="AM5" s="77" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN5" s="70" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AO5" s="4"/>
       <c r="AP5" s="45" t="s">
@@ -8463,10 +8463,10 @@
         <v>54</v>
       </c>
       <c r="AR5" s="94" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AS5" s="51" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
@@ -8557,7 +8557,7 @@
       <c r="AL6" s="32"/>
       <c r="AM6" s="78"/>
       <c r="AO6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP6" s="45"/>
       <c r="AQ6" s="96"/>
@@ -8651,7 +8651,7 @@
       <c r="AL7" s="32"/>
       <c r="AM7" s="78"/>
       <c r="AO7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP7" s="45"/>
       <c r="AQ7" s="27"/>
@@ -8731,10 +8731,10 @@
         <v>2.35</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Y8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z8" s="45"/>
       <c r="AA8" s="27"/>
@@ -8751,7 +8751,7 @@
       <c r="AL8" s="35"/>
       <c r="AM8" s="78"/>
       <c r="AO8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP8" s="45"/>
       <c r="AQ8" s="27"/>
@@ -8845,7 +8845,7 @@
       <c r="AL9" s="32"/>
       <c r="AM9" s="78"/>
       <c r="AO9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP9" s="45"/>
       <c r="AQ9" s="27"/>
@@ -8923,10 +8923,10 @@
         <v>1.03</v>
       </c>
       <c r="X10" s="79" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z10" s="45"/>
       <c r="AA10" s="27"/>
@@ -8943,7 +8943,7 @@
       <c r="AL10" s="32"/>
       <c r="AM10" s="78"/>
       <c r="AO10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP10" s="45"/>
       <c r="AQ10" s="27"/>
@@ -9037,7 +9037,7 @@
       <c r="AL11" s="32"/>
       <c r="AM11" s="78"/>
       <c r="AO11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP11" s="45"/>
       <c r="AQ11" s="27"/>
@@ -9072,7 +9072,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J12" s="62"/>
       <c r="K12" s="45">
@@ -9182,10 +9182,10 @@
       </c>
       <c r="AM12" s="78"/>
       <c r="AN12" s="75" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AO12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP12" s="45">
         <f>MATCH($B12,poultry!$A$3:$A$41,0)</f>
@@ -9229,7 +9229,7 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="I13" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="45">
@@ -9339,10 +9339,10 @@
       </c>
       <c r="AM13" s="78"/>
       <c r="AN13" s="75" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AO13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP13" s="45">
         <f>MATCH($B13,poultry!$A$3:$A$41,0)</f>
@@ -9386,7 +9386,7 @@
         <v>0.54</v>
       </c>
       <c r="I14" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="45">
@@ -9496,10 +9496,10 @@
       </c>
       <c r="AM14" s="78"/>
       <c r="AN14" s="75" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AO14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP14" s="45">
         <f>MATCH($B14,poultry!$A$3:$A$41,0)</f>
@@ -9543,7 +9543,7 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="I15" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="45">
@@ -9653,10 +9653,10 @@
       </c>
       <c r="AM15" s="78"/>
       <c r="AN15" s="75" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AO15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP15" s="45">
         <f>MATCH($B15,poultry!$A$3:$A$41,0)</f>
@@ -9700,7 +9700,7 @@
         <v>0.55499999999999994</v>
       </c>
       <c r="I16" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="45">
@@ -9809,7 +9809,7 @@
       <c r="AM16" s="78"/>
       <c r="AN16" s="74"/>
       <c r="AO16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP16" s="45">
         <f>MATCH($B16,poultry!$A$3:$A$41,0)</f>
@@ -9853,7 +9853,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="45">
@@ -9963,10 +9963,10 @@
       </c>
       <c r="AM17" s="78"/>
       <c r="AN17" s="75" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AO17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP17" s="45">
         <f>MATCH($B17,poultry!$A$3:$A$41,0)</f>
@@ -10010,7 +10010,7 @@
         <v>1.155</v>
       </c>
       <c r="I18" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="45">
@@ -10119,10 +10119,10 @@
       </c>
       <c r="AM18" s="78"/>
       <c r="AN18" s="75" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AO18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP18" s="45">
         <f>MATCH($B18,poultry!$A$3:$A$41,0)</f>
@@ -10166,7 +10166,7 @@
         <v>1.375</v>
       </c>
       <c r="I19" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="45"/>
@@ -10216,7 +10216,7 @@
         <v>310</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z19" s="45">
         <f>MATCH($B19,pigs!$A$3:$A$60,0)</f>
@@ -10274,7 +10274,7 @@
         <v>310</v>
       </c>
       <c r="AO19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP19" s="45"/>
       <c r="AQ19" s="27"/>
@@ -10309,7 +10309,7 @@
         <v>0.90999999999999992</v>
       </c>
       <c r="I20" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="45">
@@ -10418,10 +10418,10 @@
       </c>
       <c r="AM20" s="78"/>
       <c r="AN20" s="75" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AO20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP20" s="45"/>
       <c r="AQ20" s="27"/>
@@ -10429,7 +10429,7 @@
         <v>16.8</v>
       </c>
       <c r="AS20" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="21" spans="2:45" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <v>0.89500000000000002</v>
       </c>
       <c r="I21" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="45">
@@ -10570,10 +10570,10 @@
       </c>
       <c r="AM21" s="78"/>
       <c r="AN21" s="75" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AO21" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP21" s="45"/>
       <c r="AQ21" s="27"/>
@@ -10653,7 +10653,7 @@
         <v>311</v>
       </c>
       <c r="Y22" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z22" s="45">
         <f>MATCH($B22,pigs!$A$3:$A$60,0)</f>
@@ -10711,7 +10711,7 @@
         <v>311</v>
       </c>
       <c r="AO22" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP22" s="45">
         <f>MATCH($B22,poultry!$A$3:$A$41,0)</f>
@@ -10825,7 +10825,7 @@
       <c r="AM23" s="78"/>
       <c r="AN23" s="75"/>
       <c r="AO23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP23" s="45"/>
       <c r="AQ23" s="27"/>
@@ -10930,7 +10930,7 @@
       <c r="AM24" s="78"/>
       <c r="AN24" s="75"/>
       <c r="AO24" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP24" s="45"/>
       <c r="AQ24" s="27"/>
@@ -10938,7 +10938,7 @@
         <v>16</v>
       </c>
       <c r="AS24" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" spans="2:45" x14ac:dyDescent="0.25">
@@ -11077,10 +11077,10 @@
       </c>
       <c r="AM25" s="78"/>
       <c r="AN25" s="75" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AO25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP25" s="45">
         <f>MATCH($B25,poultry!$A$3:$A$41,0)</f>
@@ -11169,10 +11169,10 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="X26" s="79" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Y26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z26" s="45">
         <f>MATCH($B26,pigs!$A$3:$A$60,0)</f>
@@ -11227,10 +11227,10 @@
       </c>
       <c r="AM26" s="78"/>
       <c r="AN26" s="75" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AO26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP26" s="45"/>
       <c r="AQ26" s="27"/>
@@ -11372,10 +11372,10 @@
       </c>
       <c r="AM27" s="78"/>
       <c r="AN27" s="75" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AO27" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP27" s="45">
         <f>MATCH($B27,poultry!$A$3:$A$41,0)</f>
@@ -11526,10 +11526,10 @@
       </c>
       <c r="AM28" s="78"/>
       <c r="AN28" s="75" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AO28" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP28" s="45"/>
       <c r="AQ28" s="27"/>
@@ -11537,7 +11537,7 @@
         <v>8.6</v>
       </c>
       <c r="AS28" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.25">
@@ -11677,7 +11677,7 @@
       <c r="AM29" s="78"/>
       <c r="AN29" s="75"/>
       <c r="AO29" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP29" s="45"/>
       <c r="AQ29" s="27"/>
@@ -11759,7 +11759,7 @@
         <v>308</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z30" s="45"/>
       <c r="AA30" s="27"/>
@@ -11777,7 +11777,7 @@
       <c r="AM30" s="78"/>
       <c r="AN30" s="75"/>
       <c r="AO30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP30" s="45"/>
       <c r="AQ30" s="27"/>
@@ -11919,10 +11919,10 @@
       </c>
       <c r="AM31" s="78"/>
       <c r="AN31" s="75" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AO31" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP31" s="45">
         <f>MATCH($B31,poultry!$A$3:$A$41,0)</f>
@@ -12011,10 +12011,10 @@
         <v>0.62</v>
       </c>
       <c r="X32" s="79" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Y32" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z32" s="45">
         <f>MATCH($B32,pigs!$A$3:$A$60,0)</f>
@@ -12069,10 +12069,10 @@
       </c>
       <c r="AM32" s="78"/>
       <c r="AN32" s="75" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AO32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP32" s="45">
         <f>MATCH($B32,poultry!$A$3:$A$41,0)</f>
@@ -12089,7 +12089,7 @@
     </row>
     <row r="33" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C33" s="44">
         <f t="shared" ref="C33:C35" si="31">AVERAGE(AA33,L33)</f>
@@ -12191,7 +12191,7 @@
     </row>
     <row r="34" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C34" s="44">
         <f>AVERAGE(AA34,L34)</f>
@@ -12293,7 +12293,7 @@
     </row>
     <row r="35" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C35" s="44">
         <f t="shared" si="31"/>
@@ -12529,10 +12529,10 @@
       </c>
       <c r="AM36" s="78"/>
       <c r="AN36" s="75" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AO36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP36" s="45"/>
       <c r="AQ36" s="27"/>
@@ -12637,7 +12637,7 @@
       <c r="AM37" s="78"/>
       <c r="AN37" s="75"/>
       <c r="AO37" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP37" s="45"/>
       <c r="AQ37" s="27"/>
@@ -12770,13 +12770,13 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AM38" s="79" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AN38" s="75" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AO38" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP38" s="45"/>
       <c r="AQ38" s="27"/>
@@ -12784,7 +12784,7 @@
     </row>
     <row r="39" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C39" s="44">
         <f>AVERAGE(AA39,L39,AQ39)</f>
@@ -12918,10 +12918,10 @@
       </c>
       <c r="AM39" s="79"/>
       <c r="AN39" s="75" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AO39" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP39" s="45">
         <f>MATCH($B39,poultry!$A$3:$A$41,0)</f>
@@ -13072,10 +13072,10 @@
       </c>
       <c r="AM40" s="78"/>
       <c r="AN40" s="75" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO40" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP40" s="45"/>
       <c r="AQ40" s="27"/>
@@ -13217,10 +13217,10 @@
       </c>
       <c r="AM41" s="78"/>
       <c r="AN41" s="75" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AO41" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP41" s="45"/>
       <c r="AQ41" s="27"/>
@@ -13364,7 +13364,7 @@
       <c r="AM42" s="78"/>
       <c r="AN42" s="75"/>
       <c r="AO42" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP42" s="45"/>
       <c r="AQ42" s="27"/>
@@ -13444,10 +13444,10 @@
         <v>2.1</v>
       </c>
       <c r="X43" s="79" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Y43" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z43" s="45">
         <f>MATCH($B43,pigs!$A$3:$A$60,0)</f>
@@ -13502,10 +13502,10 @@
       </c>
       <c r="AM43" s="78"/>
       <c r="AN43" s="75" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AO43" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP43" s="45"/>
       <c r="AQ43" s="27"/>
@@ -13647,10 +13647,10 @@
       </c>
       <c r="AM44" s="78"/>
       <c r="AN44" s="75" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AO44" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP44" s="45">
         <f>MATCH($B44,poultry!$A$3:$A$41,0)</f>
@@ -13667,7 +13667,7 @@
     </row>
     <row r="45" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C45" s="44">
         <f t="shared" ref="C45" si="44">AVERAGE(AA45,L45)</f>
@@ -13840,10 +13840,10 @@
         <v>1.1900000000000002</v>
       </c>
       <c r="X46" s="79" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Y46" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z46" s="45">
         <f>MATCH($B46,pigs!$A$3:$A$60,0)</f>
@@ -13899,10 +13899,10 @@
       </c>
       <c r="AM46" s="78"/>
       <c r="AN46" s="75" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AO46" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AP46" s="45">
         <f>MATCH($B46,poultry!$A$3:$A$41,0)</f>
@@ -14001,7 +14001,7 @@
     </row>
     <row r="49" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D49" s="64" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E49" s="98"/>
       <c r="F49" s="65"/>
@@ -14013,7 +14013,7 @@
     </row>
     <row r="50" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D50" s="27" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E50" s="37"/>
       <c r="F50" s="37"/>
@@ -14025,7 +14025,7 @@
     </row>
     <row r="51" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D51" s="67" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E51" s="99"/>
       <c r="F51" s="37"/>
@@ -14037,7 +14037,7 @@
     </row>
     <row r="52" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D52" s="68" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E52" s="100"/>
       <c r="F52" s="36"/>
@@ -14104,25 +14104,25 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="P1" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="AJ1" s="4" t="s">
-        <v>594</v>
-      </c>
       <c r="AP1" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -14130,22 +14130,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D2" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>608</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="F2" s="36" t="s">
         <v>609</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="G2" s="36" t="s">
         <v>610</v>
-      </c>
-      <c r="G2" s="36" t="s">
-        <v>611</v>
       </c>
       <c r="H2" s="37"/>
       <c r="I2" s="36" t="s">
@@ -14158,13 +14158,13 @@
         <v>15</v>
       </c>
       <c r="L2" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M2" s="36" t="s">
         <v>17</v>
       </c>
       <c r="N2" s="36" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P2" s="36" t="s">
         <v>0</v>
@@ -14176,13 +14176,13 @@
         <v>15</v>
       </c>
       <c r="S2" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="T2" s="36" t="s">
         <v>17</v>
       </c>
       <c r="U2" s="36" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="W2" s="36" t="s">
         <v>0</v>
@@ -14194,13 +14194,13 @@
         <v>15</v>
       </c>
       <c r="Z2" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AA2" s="36" t="s">
         <v>17</v>
       </c>
       <c r="AB2" s="36" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AD2" s="36" t="s">
         <v>0</v>
@@ -14212,7 +14212,7 @@
         <v>15</v>
       </c>
       <c r="AG2" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AH2" s="36" t="s">
         <v>17</v>
@@ -14227,7 +14227,7 @@
         <v>15</v>
       </c>
       <c r="AM2" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN2" s="36" t="s">
         <v>17</v>
@@ -14242,7 +14242,7 @@
         <v>15</v>
       </c>
       <c r="AS2" s="102" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
@@ -14299,7 +14299,7 @@
         <v>ley silage, 1st cut</v>
       </c>
       <c r="Q3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S3" s="65">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A3,'feed pars'!$B$6:$B$47,0))</f>
@@ -14318,7 +14318,7 @@
         <v>ley silage, 1st cut</v>
       </c>
       <c r="X3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z3" s="65">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A3,'feed pars'!$B$6:$B$47,0))</f>
@@ -14358,7 +14358,7 @@
         <v>ley silage, 1st cut</v>
       </c>
       <c r="AQ3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
@@ -14415,7 +14415,7 @@
         <v>ley silage, regrowth</v>
       </c>
       <c r="Q4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S4" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A4,'feed pars'!$B$6:$B$47,0))</f>
@@ -14434,7 +14434,7 @@
         <v>ley silage, regrowth</v>
       </c>
       <c r="X4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z4" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A4,'feed pars'!$B$6:$B$47,0))</f>
@@ -14474,7 +14474,7 @@
         <v>ley silage, regrowth</v>
       </c>
       <c r="AQ4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
@@ -14531,7 +14531,7 @@
         <v>other silage</v>
       </c>
       <c r="Q5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S5" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A5,'feed pars'!$B$6:$B$47,0))</f>
@@ -14550,7 +14550,7 @@
         <v>other silage</v>
       </c>
       <c r="X5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z5" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A5,'feed pars'!$B$6:$B$47,0))</f>
@@ -14590,7 +14590,7 @@
         <v>other silage</v>
       </c>
       <c r="AQ5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
@@ -14647,7 +14647,7 @@
         <v>hay</v>
       </c>
       <c r="Q6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S6" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A6,'feed pars'!$B$6:$B$47,0))</f>
@@ -14666,7 +14666,7 @@
         <v>hay</v>
       </c>
       <c r="X6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z6" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A6,'feed pars'!$B$6:$B$47,0))</f>
@@ -14706,7 +14706,7 @@
         <v>hay</v>
       </c>
       <c r="AQ6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
@@ -14763,7 +14763,7 @@
         <v>maize silage</v>
       </c>
       <c r="Q7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S7" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A7,'feed pars'!$B$6:$B$47,0))</f>
@@ -14782,7 +14782,7 @@
         <v>maize silage</v>
       </c>
       <c r="X7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z7" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A7,'feed pars'!$B$6:$B$47,0))</f>
@@ -14822,7 +14822,7 @@
         <v>maize silage</v>
       </c>
       <c r="AQ7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
@@ -14879,7 +14879,7 @@
         <v>grazing</v>
       </c>
       <c r="Q8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S8" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A8,'feed pars'!$B$6:$B$47,0))</f>
@@ -14898,7 +14898,7 @@
         <v>grazing</v>
       </c>
       <c r="X8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z8" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A8,'feed pars'!$B$6:$B$47,0))</f>
@@ -14938,7 +14938,7 @@
         <v>grazing</v>
       </c>
       <c r="AQ8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
@@ -14995,7 +14995,7 @@
         <v>wheat</v>
       </c>
       <c r="Q9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S9" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A9,'feed pars'!$B$6:$B$47,0))</f>
@@ -15014,7 +15014,7 @@
         <v>wheat</v>
       </c>
       <c r="X9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z9" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A9,'feed pars'!$B$6:$B$47,0))</f>
@@ -15064,7 +15064,7 @@
         <v>wheat</v>
       </c>
       <c r="AQ9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS9" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A9,'feed pars'!$B$6:$B$47,0))</f>
@@ -15125,7 +15125,7 @@
         <v>barley</v>
       </c>
       <c r="Q10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S10" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A10,'feed pars'!$B$6:$B$47,0))</f>
@@ -15144,7 +15144,7 @@
         <v>barley</v>
       </c>
       <c r="X10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z10" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A10,'feed pars'!$B$6:$B$47,0))</f>
@@ -15194,7 +15194,7 @@
         <v>barley</v>
       </c>
       <c r="AQ10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS10" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A10,'feed pars'!$B$6:$B$47,0))</f>
@@ -15255,7 +15255,7 @@
         <v>oats</v>
       </c>
       <c r="Q11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S11" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A11,'feed pars'!$B$6:$B$47,0))</f>
@@ -15274,7 +15274,7 @@
         <v>oats</v>
       </c>
       <c r="X11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z11" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A11,'feed pars'!$B$6:$B$47,0))</f>
@@ -15324,7 +15324,7 @@
         <v>oats</v>
       </c>
       <c r="AQ11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS11" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A11,'feed pars'!$B$6:$B$47,0))</f>
@@ -15385,7 +15385,7 @@
         <v>triticale</v>
       </c>
       <c r="Q12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S12" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A12,'feed pars'!$B$6:$B$47,0))</f>
@@ -15404,7 +15404,7 @@
         <v>triticale</v>
       </c>
       <c r="X12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z12" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A12,'feed pars'!$B$6:$B$47,0))</f>
@@ -15454,7 +15454,7 @@
         <v>triticale</v>
       </c>
       <c r="AQ12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS12" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A12,'feed pars'!$B$6:$B$47,0))</f>
@@ -15515,7 +15515,7 @@
         <v>rye</v>
       </c>
       <c r="Q13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S13" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A13,'feed pars'!$B$6:$B$47,0))</f>
@@ -15534,7 +15534,7 @@
         <v>rye</v>
       </c>
       <c r="X13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z13" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A13,'feed pars'!$B$6:$B$47,0))</f>
@@ -15584,7 +15584,7 @@
         <v>rye</v>
       </c>
       <c r="AQ13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS13" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A13,'feed pars'!$B$6:$B$47,0))</f>
@@ -15645,7 +15645,7 @@
         <v>maize</v>
       </c>
       <c r="Q14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S14" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A14,'feed pars'!$B$6:$B$47,0))</f>
@@ -15664,7 +15664,7 @@
         <v>maize</v>
       </c>
       <c r="X14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z14" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A14,'feed pars'!$B$6:$B$47,0))</f>
@@ -15714,7 +15714,7 @@
         <v>maize</v>
       </c>
       <c r="AQ14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS14" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A14,'feed pars'!$B$6:$B$47,0))</f>
@@ -15775,7 +15775,7 @@
         <v>peas</v>
       </c>
       <c r="Q15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S15" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A15,'feed pars'!$B$6:$B$47,0))</f>
@@ -15794,7 +15794,7 @@
         <v>peas</v>
       </c>
       <c r="X15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z15" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A15,'feed pars'!$B$6:$B$47,0))</f>
@@ -15844,7 +15844,7 @@
         <v>peas</v>
       </c>
       <c r="AQ15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS15" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A15,'feed pars'!$B$6:$B$47,0))</f>
@@ -15905,7 +15905,7 @@
         <v>broad beans</v>
       </c>
       <c r="Q16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S16" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A16,'feed pars'!$B$6:$B$47,0))</f>
@@ -15924,7 +15924,7 @@
         <v>broad beans</v>
       </c>
       <c r="X16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z16" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A16,'feed pars'!$B$6:$B$47,0))</f>
@@ -15974,7 +15974,7 @@
         <v>broad beans</v>
       </c>
       <c r="AQ16" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS16" s="28"/>
     </row>
@@ -16032,7 +16032,7 @@
         <v>rapeseed</v>
       </c>
       <c r="Q17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S17" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A17,'feed pars'!$B$6:$B$47,0))</f>
@@ -16051,7 +16051,7 @@
         <v>rapeseed</v>
       </c>
       <c r="X17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z17" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A17,'feed pars'!$B$6:$B$47,0))</f>
@@ -16101,7 +16101,7 @@
         <v>rapeseed</v>
       </c>
       <c r="AQ17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS17" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A17,'feed pars'!$B$6:$B$47,0))</f>
@@ -16162,7 +16162,7 @@
         <v>linseed</v>
       </c>
       <c r="Q18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S18" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A18,'feed pars'!$B$6:$B$47,0))</f>
@@ -16181,7 +16181,7 @@
         <v>linseed</v>
       </c>
       <c r="X18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z18" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A18,'feed pars'!$B$6:$B$47,0))</f>
@@ -16231,7 +16231,7 @@
         <v>linseed</v>
       </c>
       <c r="AQ18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS18" s="28"/>
     </row>
@@ -16289,7 +16289,7 @@
         <v>vegetable oils</v>
       </c>
       <c r="Q19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S19" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A19,'feed pars'!$B$6:$B$47,0))</f>
@@ -16308,7 +16308,7 @@
         <v>vegetable oils</v>
       </c>
       <c r="X19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z19" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A19,'feed pars'!$B$6:$B$47,0))</f>
@@ -16358,7 +16358,7 @@
         <v>vegetable oils</v>
       </c>
       <c r="AQ19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS19" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A19,'feed pars'!$B$6:$B$47,0))</f>
@@ -16419,7 +16419,7 @@
         <v>straw</v>
       </c>
       <c r="Q20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S20" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A20,'feed pars'!$B$6:$B$47,0))</f>
@@ -16438,7 +16438,7 @@
         <v>straw</v>
       </c>
       <c r="X20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z20" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A20,'feed pars'!$B$6:$B$47,0))</f>
@@ -16479,7 +16479,7 @@
         <v>straw</v>
       </c>
       <c r="AQ20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS20" s="28"/>
     </row>
@@ -16537,7 +16537,7 @@
         <v>soybeans</v>
       </c>
       <c r="Q21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S21" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A21,'feed pars'!$B$6:$B$47,0))</f>
@@ -16556,7 +16556,7 @@
         <v>soybeans</v>
       </c>
       <c r="X21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z21" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A21,'feed pars'!$B$6:$B$47,0))</f>
@@ -16597,7 +16597,7 @@
         <v>soybeans</v>
       </c>
       <c r="AQ21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS21" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A21,'feed pars'!$B$6:$B$47,0))</f>
@@ -16658,7 +16658,7 @@
         <v>soybean meal</v>
       </c>
       <c r="Q22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S22" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A22,'feed pars'!$B$6:$B$47,0))</f>
@@ -16677,7 +16677,7 @@
         <v>soybean meal</v>
       </c>
       <c r="X22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z22" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A22,'feed pars'!$B$6:$B$47,0))</f>
@@ -16727,7 +16727,7 @@
         <v>soybean meal</v>
       </c>
       <c r="AQ22" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS22" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A22,'feed pars'!$B$6:$B$47,0))</f>
@@ -16788,7 +16788,7 @@
         <v>soybean protein concentrate</v>
       </c>
       <c r="Q23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S23" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A23,'feed pars'!$B$6:$B$47,0))</f>
@@ -16807,7 +16807,7 @@
         <v>soybean protein concentrate</v>
       </c>
       <c r="X23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z23" s="37"/>
       <c r="AA23" s="37"/>
@@ -16848,7 +16848,7 @@
         <v>soybean protein concentrate</v>
       </c>
       <c r="AQ23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS23" s="28"/>
     </row>
@@ -16906,7 +16906,7 @@
         <v>rapeseed meal</v>
       </c>
       <c r="Q24" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S24" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A24,'feed pars'!$B$6:$B$47,0))</f>
@@ -16925,7 +16925,7 @@
         <v>rapeseed meal</v>
       </c>
       <c r="X24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z24" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A24,'feed pars'!$B$6:$B$47,0))</f>
@@ -16975,7 +16975,7 @@
         <v>rapeseed meal</v>
       </c>
       <c r="AQ24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS24" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A24,'feed pars'!$B$6:$B$47,0))</f>
@@ -17036,7 +17036,7 @@
         <v>sunflower seed meal</v>
       </c>
       <c r="Q25" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S25" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A25,'feed pars'!$B$6:$B$47,0))</f>
@@ -17055,7 +17055,7 @@
         <v>sunflower seed meal</v>
       </c>
       <c r="X25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z25" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A25,'feed pars'!$B$6:$B$47,0))</f>
@@ -17105,7 +17105,7 @@
         <v>sunflower seed meal</v>
       </c>
       <c r="AQ25" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS25" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A25,'feed pars'!$B$6:$B$47,0))</f>
@@ -17166,7 +17166,7 @@
         <v>palm kernel expeller</v>
       </c>
       <c r="Q26" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S26" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A26,'feed pars'!$B$6:$B$47,0))</f>
@@ -17185,7 +17185,7 @@
         <v>palm kernel expeller</v>
       </c>
       <c r="X26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z26" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A26,'feed pars'!$B$6:$B$47,0))</f>
@@ -17235,7 +17235,7 @@
         <v>palm kernel expeller</v>
       </c>
       <c r="AQ26" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS26" s="28"/>
     </row>
@@ -17293,7 +17293,7 @@
         <v>luzern meal</v>
       </c>
       <c r="Q27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S27" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A27,'feed pars'!$B$6:$B$47,0))</f>
@@ -17312,7 +17312,7 @@
         <v>luzern meal</v>
       </c>
       <c r="X27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z27" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A27,'feed pars'!$B$6:$B$47,0))</f>
@@ -17353,7 +17353,7 @@
         <v>luzern meal</v>
       </c>
       <c r="AQ27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS27" s="28"/>
     </row>
@@ -17411,7 +17411,7 @@
         <v>wheat bran</v>
       </c>
       <c r="Q28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S28" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A28,'feed pars'!$B$6:$B$47,0))</f>
@@ -17430,7 +17430,7 @@
         <v>wheat bran</v>
       </c>
       <c r="X28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z28" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A28,'feed pars'!$B$6:$B$47,0))</f>
@@ -17480,7 +17480,7 @@
         <v>wheat bran</v>
       </c>
       <c r="AQ28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS28" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A28,'feed pars'!$B$6:$B$47,0))</f>
@@ -17541,7 +17541,7 @@
         <v>wheat bran, fine</v>
       </c>
       <c r="Q29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S29" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A29,'feed pars'!$B$6:$B$47,0))</f>
@@ -17560,7 +17560,7 @@
         <v>wheat bran, fine</v>
       </c>
       <c r="X29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z29" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A29,'feed pars'!$B$6:$B$47,0))</f>
@@ -17610,7 +17610,7 @@
         <v>wheat bran, fine</v>
       </c>
       <c r="AQ29" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS29" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A29,'feed pars'!$B$6:$B$47,0))</f>
@@ -17671,7 +17671,7 @@
         <v>oat hulls</v>
       </c>
       <c r="Q30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S30" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A30,'feed pars'!$B$6:$B$47,0))</f>
@@ -17690,7 +17690,7 @@
         <v>oat hulls</v>
       </c>
       <c r="X30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z30" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A30,'feed pars'!$B$6:$B$47,0))</f>
@@ -17731,7 +17731,7 @@
         <v>oat hulls</v>
       </c>
       <c r="AQ30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS30" s="28"/>
     </row>
@@ -17789,7 +17789,7 @@
         <v>oat bran</v>
       </c>
       <c r="Q31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S31" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A31,'feed pars'!$B$6:$B$47,0))</f>
@@ -17808,7 +17808,7 @@
         <v>oat bran</v>
       </c>
       <c r="X31" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z31" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A31,'feed pars'!$B$6:$B$47,0))</f>
@@ -17849,7 +17849,7 @@
         <v>oat bran</v>
       </c>
       <c r="AQ31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS31" s="28"/>
     </row>
@@ -17906,7 +17906,7 @@
         <v>rye bran</v>
       </c>
       <c r="Q32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S32" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A32,'feed pars'!$B$6:$B$47,0))</f>
@@ -17925,7 +17925,7 @@
         <v>rye bran</v>
       </c>
       <c r="X32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z32" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A32,'feed pars'!$B$6:$B$47,0))</f>
@@ -17994,7 +17994,7 @@
         <v>wheat distillers grain, dry</v>
       </c>
       <c r="Q33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S33" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A33,'feed pars'!$B$6:$B$47,0))</f>
@@ -18013,7 +18013,7 @@
         <v>wheat distillers grain, dry</v>
       </c>
       <c r="X33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z33" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A33,'feed pars'!$B$6:$B$47,0))</f>
@@ -18063,7 +18063,7 @@
         <v>wheat distillers grain, dry</v>
       </c>
       <c r="AQ33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS33" s="28"/>
     </row>
@@ -18112,7 +18112,7 @@
         <v>wheat distillers grain, wet</v>
       </c>
       <c r="Q34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S34" s="37"/>
       <c r="T34" s="37"/>
@@ -18122,7 +18122,7 @@
         <v>wheat distillers grain, wet</v>
       </c>
       <c r="X34" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z34" s="37"/>
       <c r="AA34" s="37"/>
@@ -18163,7 +18163,7 @@
         <v>wheat distillers grain, wet</v>
       </c>
       <c r="AQ34" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS34" s="28"/>
     </row>
@@ -18221,7 +18221,7 @@
         <v>barley brewers grain</v>
       </c>
       <c r="Q35" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S35" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A35,'feed pars'!$B$6:$B$47,0))</f>
@@ -18240,7 +18240,7 @@
         <v>barley brewers grain</v>
       </c>
       <c r="X35" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z35" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A35,'feed pars'!$B$6:$B$47,0))</f>
@@ -18290,7 +18290,7 @@
         <v>barley brewers grain</v>
       </c>
       <c r="AQ35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS35" s="28"/>
     </row>
@@ -18348,7 +18348,7 @@
         <v>maize gluten meal</v>
       </c>
       <c r="Q36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S36" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A36,'feed pars'!$B$6:$B$47,0))</f>
@@ -18367,7 +18367,7 @@
         <v>maize gluten meal</v>
       </c>
       <c r="X36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z36" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A36,'feed pars'!$B$6:$B$47,0))</f>
@@ -18417,7 +18417,7 @@
         <v>maize gluten meal</v>
       </c>
       <c r="AQ36" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS36" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A36,'feed pars'!$B$6:$B$47,0))</f>
@@ -18478,7 +18478,7 @@
         <v>sugar beet molasses</v>
       </c>
       <c r="Q37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S37" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A37,'feed pars'!$B$6:$B$47,0))</f>
@@ -18497,7 +18497,7 @@
         <v>sugar beet molasses</v>
       </c>
       <c r="X37" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z37" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A37,'feed pars'!$B$6:$B$47,0))</f>
@@ -18547,7 +18547,7 @@
         <v>sugar beet molasses</v>
       </c>
       <c r="AQ37" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS37" s="28"/>
     </row>
@@ -18605,7 +18605,7 @@
         <v>sugar beet pulp</v>
       </c>
       <c r="Q38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S38" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A38,'feed pars'!$B$6:$B$47,0))</f>
@@ -18624,7 +18624,7 @@
         <v>sugar beet pulp</v>
       </c>
       <c r="X38" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z38" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A38,'feed pars'!$B$6:$B$47,0))</f>
@@ -18674,7 +18674,7 @@
         <v>sugar beet pulp</v>
       </c>
       <c r="AQ38" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS38" s="28"/>
     </row>
@@ -18732,7 +18732,7 @@
         <v>whey</v>
       </c>
       <c r="Q39" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S39" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A39,'feed pars'!$B$6:$B$47,0))</f>
@@ -18751,7 +18751,7 @@
         <v>whey</v>
       </c>
       <c r="X39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z39" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A39,'feed pars'!$B$6:$B$47,0))</f>
@@ -18801,7 +18801,7 @@
         <v>whey</v>
       </c>
       <c r="AQ39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS39" s="28"/>
     </row>
@@ -18859,7 +18859,7 @@
         <v>whey powder</v>
       </c>
       <c r="Q40" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S40" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A40,'feed pars'!$B$6:$B$47,0))</f>
@@ -18878,7 +18878,7 @@
         <v>whey powder</v>
       </c>
       <c r="X40" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z40" s="37"/>
       <c r="AA40" s="37"/>
@@ -18919,7 +18919,7 @@
         <v>whey powder</v>
       </c>
       <c r="AQ40" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS40" s="28"/>
     </row>
@@ -18977,7 +18977,7 @@
         <v>potatoe protein</v>
       </c>
       <c r="Q41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S41" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A41,'feed pars'!$B$6:$B$47,0))</f>
@@ -18996,7 +18996,7 @@
         <v>potatoe protein</v>
       </c>
       <c r="X41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z41" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A41,'feed pars'!$B$6:$B$47,0))</f>
@@ -19046,7 +19046,7 @@
         <v>potatoe protein</v>
       </c>
       <c r="AQ41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AS41" s="28">
         <f>INDEX('feed pars'!$AR$6:$AR$47,MATCH($A41,'feed pars'!$B$6:$B$47,0))</f>
@@ -19109,7 +19109,7 @@
         <v>fish meal</v>
       </c>
       <c r="Q42" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="37">
@@ -19130,7 +19130,7 @@
         <v>fish meal</v>
       </c>
       <c r="X42" s="37" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y42" s="37"/>
       <c r="Z42" s="37"/>
@@ -19174,7 +19174,7 @@
         <v>fish meal</v>
       </c>
       <c r="AQ42" s="37" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AR42" s="37"/>
       <c r="AS42" s="28">
@@ -19237,7 +19237,7 @@
         <v>minerals</v>
       </c>
       <c r="Q43" s="36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R43" s="36"/>
       <c r="S43" s="36">
@@ -19257,7 +19257,7 @@
         <v>minerals</v>
       </c>
       <c r="X43" s="36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y43" s="36"/>
       <c r="Z43" s="36">
@@ -19308,7 +19308,7 @@
         <v>minerals</v>
       </c>
       <c r="AQ43" s="36" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AR43" s="36"/>
       <c r="AS43" s="57">
@@ -22087,7 +22087,7 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B24" s="11">
         <v>22</v>
@@ -29098,7 +29098,7 @@
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B29" s="8">
         <v>27</v>
@@ -29284,7 +29284,7 @@
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B31" s="8">
         <v>29</v>
@@ -31207,7 +31207,7 @@
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B52" s="11">
         <v>50</v>
@@ -32445,7 +32445,7 @@
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B65" s="8">
         <v>63</v>
@@ -33667,7 +33667,7 @@
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B78" s="11">
         <v>76</v>
@@ -37473,7 +37473,7 @@
         <v>120</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E2" s="15" t="s">
         <v>272</v>
@@ -37482,52 +37482,52 @@
         <v>273</v>
       </c>
       <c r="G2" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="O2" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="P2" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="Q2" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="R2" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="S2" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="T2" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>406</v>
       </c>
       <c r="U2" s="15" t="s">
         <v>118</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="W2" s="15" t="s">
         <v>143</v>
@@ -37553,7 +37553,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D3" s="10">
         <v>9.4</v>
@@ -37622,7 +37622,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D4" s="13">
         <v>9.4</v>
@@ -37691,7 +37691,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D5" s="10">
         <v>6.1</v>
@@ -37760,7 +37760,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" s="13">
         <v>9.4</v>
@@ -37829,7 +37829,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D7" s="10">
         <v>10.5</v>
@@ -37898,7 +37898,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D8" s="13">
         <v>11.1</v>
@@ -37967,7 +37967,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D9" s="10">
         <v>11</v>
@@ -38041,7 +38041,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D10" s="13">
         <v>10.1</v>
@@ -38113,7 +38113,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D11" s="10">
         <v>9.5</v>
@@ -38181,7 +38181,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D12" s="13">
         <v>10.5</v>
@@ -38257,7 +38257,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D13" s="10">
         <v>10.8</v>
@@ -38331,7 +38331,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D14" s="13">
         <v>11.5</v>
@@ -38405,7 +38405,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D15" s="10">
         <v>9.8000000000000007</v>
@@ -38492,7 +38492,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D16" s="13">
         <v>9.8000000000000007</v>
@@ -38579,7 +38579,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D17" s="10">
         <v>9.3000000000000007</v>
@@ -38664,7 +38664,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D18" s="13">
         <v>9.3000000000000007</v>
@@ -38749,7 +38749,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D19" s="10">
         <v>10.199999999999999</v>
@@ -38834,7 +38834,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D20" s="13">
         <v>10.199999999999999</v>
@@ -38919,7 +38919,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D21" s="10">
         <v>10.9</v>
@@ -39002,7 +39002,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D22" s="13">
         <v>11.7</v>
@@ -39083,7 +39083,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D23" s="10">
         <v>8</v>
@@ -39162,7 +39162,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D24" s="13">
         <v>9.1999999999999993</v>
@@ -39245,7 +39245,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D25" s="10">
         <v>10.1</v>
@@ -39328,7 +39328,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D26" s="13">
         <v>10.3</v>
@@ -39411,7 +39411,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D27" s="10">
         <v>10.3</v>
@@ -39494,7 +39494,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D28" s="13">
         <v>10.1</v>
@@ -39575,7 +39575,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D29" s="10">
         <v>10.199999999999999</v>
@@ -39656,7 +39656,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D30" s="13">
         <v>10.1</v>
@@ -39737,7 +39737,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D31" s="10">
         <v>10.199999999999999</v>
@@ -39820,7 +39820,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D32" s="13">
         <v>9.9</v>
@@ -39901,7 +39901,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D33" s="10">
         <v>9.1</v>
@@ -39982,7 +39982,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D34" s="13">
         <v>9.3000000000000007</v>
@@ -40063,7 +40063,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D35" s="10">
         <v>9.1999999999999993</v>
@@ -40144,7 +40144,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D36" s="13">
         <v>9.4</v>
@@ -40217,7 +40217,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D37" s="10">
         <v>10.199999999999999</v>
@@ -40304,7 +40304,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D38" s="13">
         <v>10.199999999999999</v>
@@ -40391,7 +40391,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D39" s="10">
         <v>9.8000000000000007</v>
@@ -40476,7 +40476,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D40" s="13">
         <v>9.8000000000000007</v>
@@ -40561,7 +40561,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D41" s="10">
         <v>10.7</v>
@@ -40646,7 +40646,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D42" s="13">
         <v>10.7</v>
@@ -40731,7 +40731,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D43" s="10">
         <v>9.9</v>
@@ -40816,7 +40816,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D44" s="13">
         <v>9.9</v>
@@ -40901,7 +40901,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D45" s="10">
         <v>9.5</v>
@@ -40986,7 +40986,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D46" s="13">
         <v>9.3000000000000007</v>
@@ -41071,7 +41071,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D47" s="10">
         <v>10.4</v>
@@ -41156,7 +41156,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D48" s="13">
         <v>10.4</v>
@@ -41241,7 +41241,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D49" s="10">
         <v>10.199999999999999</v>
@@ -41328,7 +41328,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D50" s="13">
         <v>10.199999999999999</v>
@@ -41415,7 +41415,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D51" s="10">
         <v>9.5</v>
@@ -41500,7 +41500,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D52" s="13">
         <v>9.5</v>
@@ -41585,7 +41585,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D53" s="10">
         <v>11</v>
@@ -41670,7 +41670,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D54" s="13">
         <v>11</v>
@@ -41755,7 +41755,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D55" s="10">
         <v>10.6</v>
@@ -41840,7 +41840,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D56" s="13">
         <v>10.6</v>
@@ -41925,7 +41925,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D57" s="10">
         <v>10.199999999999999</v>
@@ -42010,7 +42010,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D58" s="13">
         <v>10.199999999999999</v>
@@ -42095,7 +42095,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D59" s="10">
         <v>11</v>
@@ -42180,7 +42180,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D60" s="13">
         <v>11</v>
@@ -42265,7 +42265,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D61" s="10">
         <v>10.5</v>
@@ -42364,40 +42364,40 @@
         <v>117</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>501</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>503</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>504</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -42405,7 +42405,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D3" s="10">
         <v>50</v>
@@ -42444,7 +42444,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D4" s="13">
         <v>85</v>
@@ -42483,7 +42483,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D5" s="10">
         <v>90</v>
@@ -42524,7 +42524,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D6" s="13">
         <v>90</v>
@@ -42606,7 +42606,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" s="13">
         <v>90</v>
@@ -42647,7 +42647,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D9" s="10">
         <v>8</v>
@@ -42688,7 +42688,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D10" s="13">
         <v>91</v>
@@ -42729,7 +42729,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D11" s="10">
         <v>94</v>
@@ -42770,7 +42770,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D12" s="13">
         <v>91</v>
@@ -42811,7 +42811,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D13" s="10">
         <v>90</v>
@@ -42852,7 +42852,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D14" s="13">
         <v>87</v>
@@ -42891,7 +42891,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D15" s="10">
         <v>87</v>
@@ -42932,7 +42932,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D16" s="13">
         <v>87</v>
@@ -43012,7 +43012,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D18" s="13">
         <v>87</v>
@@ -43047,7 +43047,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D19" s="10">
         <v>87</v>
@@ -43088,7 +43088,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D20" s="13">
         <v>93</v>
@@ -43129,7 +43129,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D21" s="10">
         <v>90</v>
@@ -43170,7 +43170,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D22" s="13">
         <v>87</v>
@@ -43211,7 +43211,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D23" s="10">
         <v>87</v>
@@ -43252,7 +43252,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D24" s="13">
         <v>92</v>
@@ -43293,7 +43293,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D25" s="10">
         <v>9</v>
@@ -43334,7 +43334,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D26" s="13">
         <v>12</v>
@@ -43375,7 +43375,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D27" s="10">
         <v>91</v>
@@ -43457,7 +43457,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D29" s="10">
         <v>94</v>
@@ -43498,7 +43498,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D30" s="13">
         <v>94</v>
@@ -43539,7 +43539,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D31" s="10">
         <v>93</v>
@@ -43580,7 +43580,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D32" s="13">
         <v>87</v>
@@ -43621,7 +43621,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D33" s="10">
         <v>89</v>
@@ -43662,7 +43662,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D34" s="13">
         <v>87</v>
@@ -43703,7 +43703,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D35" s="10">
         <v>87</v>
@@ -43744,7 +43744,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D36" s="13">
         <v>87</v>
@@ -43785,7 +43785,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D37" s="10">
         <v>78</v>
@@ -43826,7 +43826,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D38" s="13">
         <v>75</v>
@@ -43867,7 +43867,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D39" s="10">
         <v>91</v>
@@ -43908,7 +43908,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D40" s="13">
         <v>90</v>
@@ -43949,7 +43949,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D41" s="10">
         <v>87</v>
@@ -43990,7 +43990,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D42" s="13">
         <v>87</v>
@@ -44031,7 +44031,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D43" s="10">
         <v>92</v>
@@ -44072,7 +44072,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D44" s="13">
         <v>92</v>
@@ -44113,7 +44113,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D45" s="10">
         <v>87</v>
@@ -44154,7 +44154,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D46" s="13">
         <v>90</v>
@@ -44195,7 +44195,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D47" s="10">
         <v>90</v>
@@ -44236,7 +44236,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D48" s="13">
         <v>88</v>
@@ -44277,7 +44277,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D49" s="10">
         <v>89</v>
@@ -44316,7 +44316,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D50" s="13">
         <v>100</v>
@@ -44357,7 +44357,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D51" s="10">
         <v>87</v>
@@ -44398,7 +44398,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D52" s="13">
         <v>87</v>
@@ -44439,7 +44439,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D53" s="10">
         <v>87</v>
@@ -44480,7 +44480,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D54" s="13">
         <v>87</v>
@@ -44519,7 +44519,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D55" s="10">
         <v>87</v>
@@ -44560,7 +44560,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D56" s="13">
         <v>87</v>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="658">
   <si>
     <t>f_feed</t>
   </si>
@@ -5491,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R153"/>
+  <dimension ref="A1:R151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -6589,92 +6589,121 @@
       <c r="P70" s="6"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J71" t="s">
-        <v>38</v>
+      <c r="I71" t="s">
+        <v>37</v>
       </c>
       <c r="M71" t="s">
         <v>25</v>
       </c>
-      <c r="N71" s="21">
+      <c r="N71" s="3">
         <v>100</v>
       </c>
-      <c r="O71" s="21" t="s">
+      <c r="O71" t="s">
         <v>23</v>
       </c>
-      <c r="P71" s="6"/>
+      <c r="P71" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J72" t="s">
-        <v>30</v>
+      <c r="I72" t="s">
+        <v>34</v>
       </c>
       <c r="M72" t="s">
         <v>25</v>
       </c>
-      <c r="N72" s="21">
-        <v>61</v>
+      <c r="N72" s="3">
+        <v>50</v>
       </c>
       <c r="O72" t="s">
         <v>23</v>
       </c>
+      <c r="P72" s="3" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I73" t="s">
-        <v>37</v>
-      </c>
-      <c r="M73" t="s">
-        <v>25</v>
-      </c>
-      <c r="N73" s="3">
-        <v>100</v>
-      </c>
-      <c r="O73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>315</v>
+      </c>
+      <c r="I75" t="s">
+        <v>27</v>
+      </c>
+      <c r="M75" t="s">
+        <v>316</v>
+      </c>
+      <c r="N75" s="21">
+        <v>85</v>
+      </c>
+      <c r="O75" t="s">
         <v>23</v>
       </c>
-      <c r="P73" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I74" t="s">
-        <v>34</v>
-      </c>
-      <c r="M74" t="s">
-        <v>25</v>
-      </c>
-      <c r="N74" s="3">
-        <v>50</v>
-      </c>
-      <c r="O74" t="s">
+      <c r="P75" s="21" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" t="s">
+        <v>312</v>
+      </c>
+      <c r="E76" t="s">
+        <v>313</v>
+      </c>
+      <c r="H76" t="s">
+        <v>315</v>
+      </c>
+      <c r="I76" t="s">
+        <v>27</v>
+      </c>
+      <c r="M76" t="s">
+        <v>316</v>
+      </c>
+      <c r="N76" s="21">
+        <v>20</v>
+      </c>
+      <c r="O76" t="s">
         <v>23</v>
       </c>
-      <c r="P74" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
+      <c r="P76" s="21" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="H77" t="s">
         <v>315</v>
@@ -6686,27 +6715,19 @@
         <v>316</v>
       </c>
       <c r="N77" s="21">
-        <v>85</v>
+        <v>14.5</v>
       </c>
       <c r="O77" t="s">
         <v>23</v>
       </c>
-      <c r="P77" s="21" t="s">
-        <v>656</v>
-      </c>
+      <c r="P77" s="3"/>
       <c r="Q77" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>19</v>
-      </c>
-      <c r="B78" t="s">
-        <v>312</v>
-      </c>
-      <c r="E78" t="s">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="H78" t="s">
         <v>315</v>
@@ -6718,21 +6739,25 @@
         <v>316</v>
       </c>
       <c r="N78" s="21">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O78" t="s">
         <v>23</v>
       </c>
-      <c r="P78" s="21" t="s">
-        <v>657</v>
-      </c>
+      <c r="P78" s="3"/>
       <c r="Q78" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>373</v>
+        <v>377</v>
+      </c>
+      <c r="D79" t="s">
+        <v>647</v>
+      </c>
+      <c r="E79" t="s">
+        <v>481</v>
       </c>
       <c r="H79" t="s">
         <v>315</v>
@@ -6744,132 +6769,126 @@
         <v>316</v>
       </c>
       <c r="N79" s="21">
-        <v>14.5</v>
+        <v>69</v>
       </c>
       <c r="O79" t="s">
         <v>23</v>
       </c>
       <c r="P79" s="3"/>
       <c r="Q79" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N80" s="3"/>
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M82" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="N82" s="6">
+        <v>0</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M83" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="N83" s="6">
+        <v>0</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" t="s">
+        <v>312</v>
+      </c>
+      <c r="E84" t="s">
+        <v>313</v>
+      </c>
+      <c r="G84" t="s">
+        <v>628</v>
+      </c>
+      <c r="M84" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N84" s="21">
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O84" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P84" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q84" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>377</v>
-      </c>
-      <c r="H80" t="s">
-        <v>315</v>
-      </c>
-      <c r="I80" t="s">
-        <v>27</v>
-      </c>
-      <c r="M80" t="s">
-        <v>316</v>
-      </c>
-      <c r="N80" s="21">
-        <v>100</v>
-      </c>
-      <c r="O80" t="s">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" t="s">
+        <v>628</v>
+      </c>
+      <c r="M85" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N85" s="21">
+        <f>(0.6*20+0.4*2)</f>
+        <v>12.8</v>
+      </c>
+      <c r="O85" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P80" s="3"/>
-      <c r="Q80" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>377</v>
-      </c>
-      <c r="D81" t="s">
-        <v>647</v>
-      </c>
-      <c r="E81" t="s">
-        <v>481</v>
-      </c>
-      <c r="H81" t="s">
-        <v>315</v>
-      </c>
-      <c r="I81" t="s">
-        <v>27</v>
-      </c>
-      <c r="M81" t="s">
-        <v>316</v>
-      </c>
-      <c r="N81" s="21">
-        <v>69</v>
-      </c>
-      <c r="O81" t="s">
-        <v>23</v>
-      </c>
-      <c r="P81" s="3"/>
-      <c r="Q81" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N82" s="3"/>
-      <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
-      <c r="Q83" s="2"/>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M84" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="N84" s="6">
-        <v>0</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M85" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="N85" s="6">
-        <v>0</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>28</v>
+      <c r="P85" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>19</v>
-      </c>
-      <c r="B86" t="s">
-        <v>312</v>
-      </c>
-      <c r="E86" t="s">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="G86" t="s">
         <v>628</v>
@@ -6878,14 +6897,13 @@
         <v>374</v>
       </c>
       <c r="N86" s="21">
-        <f>(0.8*20+0.2*2)</f>
-        <v>16.399999999999999</v>
+        <v>2</v>
       </c>
       <c r="O86" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P86" s="21" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q86" t="s">
         <v>635</v>
@@ -6893,7 +6911,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="G87" t="s">
         <v>628</v>
@@ -6902,81 +6920,83 @@
         <v>374</v>
       </c>
       <c r="N87" s="21">
-        <f>(0.6*20+0.4*2)</f>
-        <v>12.8</v>
+        <v>2</v>
       </c>
       <c r="O87" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P87" s="21" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q87" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>377</v>
-      </c>
-      <c r="G88" t="s">
-        <v>628</v>
-      </c>
-      <c r="M88" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N88" s="21">
-        <v>2</v>
-      </c>
-      <c r="O88" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P88" s="21" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>635</v>
-      </c>
+      <c r="M88" s="21"/>
+      <c r="N88" s="21"/>
+      <c r="O88" s="21"/>
+      <c r="P88" s="21"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>373</v>
+        <v>19</v>
+      </c>
+      <c r="B89" t="s">
+        <v>312</v>
+      </c>
+      <c r="E89" t="s">
+        <v>313</v>
       </c>
       <c r="G89" t="s">
         <v>628</v>
       </c>
       <c r="M89" s="21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N89" s="21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O89" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P89" s="21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q89" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M90" s="21"/>
-      <c r="N90" s="21"/>
-      <c r="O90" s="21"/>
-      <c r="P90" s="21"/>
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" t="s">
+        <v>314</v>
+      </c>
+      <c r="G90" t="s">
+        <v>628</v>
+      </c>
+      <c r="M90" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="N90" s="21">
+        <v>5</v>
+      </c>
+      <c r="O90" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P90" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>19</v>
       </c>
-      <c r="B91" t="s">
-        <v>312</v>
-      </c>
-      <c r="E91" t="s">
-        <v>313</v>
-      </c>
       <c r="G91" t="s">
         <v>628</v>
       </c>
@@ -6984,13 +7004,14 @@
         <v>375</v>
       </c>
       <c r="N91" s="21">
-        <v>5</v>
+        <f>0.9*5+0.1*15</f>
+        <v>6</v>
       </c>
       <c r="O91" s="21" t="s">
         <v>23</v>
       </c>
       <c r="P91" s="21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q91" t="s">
         <v>635</v>
@@ -6998,10 +7019,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="G92" t="s">
         <v>628</v>
@@ -7010,21 +7028,19 @@
         <v>375</v>
       </c>
       <c r="N92" s="21">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O92" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P92" s="21" t="s">
-        <v>381</v>
-      </c>
+      <c r="P92" s="21"/>
       <c r="Q92" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="G93" t="s">
         <v>628</v>
@@ -7033,52 +7049,34 @@
         <v>375</v>
       </c>
       <c r="N93" s="21">
-        <f>0.9*5+0.1*15</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O93" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="P93" s="21" t="s">
-        <v>382</v>
-      </c>
+      <c r="P93" s="21"/>
       <c r="Q93" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>377</v>
-      </c>
-      <c r="G94" t="s">
-        <v>628</v>
-      </c>
-      <c r="M94" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="N94" s="21">
-        <v>15</v>
-      </c>
-      <c r="O94" s="21" t="s">
-        <v>23</v>
-      </c>
+      <c r="M94" s="21"/>
+      <c r="N94" s="21"/>
+      <c r="O94" s="21"/>
       <c r="P94" s="21"/>
-      <c r="Q94" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>373</v>
-      </c>
+      <c r="A95" s="22"/>
+      <c r="B95" s="22"/>
+      <c r="E95" s="22"/>
       <c r="G95" t="s">
-        <v>628</v>
+        <v>300</v>
       </c>
       <c r="M95" s="21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N95" s="21">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O95" s="21" t="s">
         <v>23</v>
@@ -7089,55 +7087,90 @@
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M96" s="21"/>
-      <c r="N96" s="21"/>
-      <c r="O96" s="21"/>
-      <c r="P96" s="21"/>
+      <c r="A96" s="22" t="str">
+        <f>A89</f>
+        <v>cattle</v>
+      </c>
+      <c r="B96" s="22" t="str">
+        <f>B89</f>
+        <v>dairy</v>
+      </c>
+      <c r="E96" s="22" t="str">
+        <f t="shared" ref="E96:E97" si="0">E89</f>
+        <v>cows</v>
+      </c>
+      <c r="G96" t="s">
+        <v>300</v>
+      </c>
+      <c r="M96" s="22" t="str">
+        <f t="shared" ref="M96:Q100" si="1">M89</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N96" s="22">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O96" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P96" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q96" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" s="22"/>
-      <c r="B97" s="22"/>
-      <c r="E97" s="22"/>
+      <c r="A97" s="22" t="str">
+        <f t="shared" ref="A97:A100" si="2">A90</f>
+        <v>cattle</v>
+      </c>
+      <c r="E97" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>bulls</v>
+      </c>
       <c r="G97" t="s">
         <v>300</v>
       </c>
-      <c r="M97" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N97" s="21">
+      <c r="M97" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N97" s="22">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="O97" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P97" s="21"/>
-      <c r="Q97" t="s">
-        <v>635</v>
+      <c r="O97" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P97" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q97" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="str">
-        <f>A91</f>
+        <f t="shared" si="2"/>
         <v>cattle</v>
-      </c>
-      <c r="B98" s="22" t="str">
-        <f>B91</f>
-        <v>dairy</v>
-      </c>
-      <c r="E98" s="22" t="str">
-        <f t="shared" ref="E98:E99" si="0">E91</f>
-        <v>cows</v>
       </c>
       <c r="G98" t="s">
         <v>300</v>
       </c>
       <c r="M98" s="22" t="str">
-        <f t="shared" ref="M98:Q102" si="1">M91</f>
+        <f t="shared" si="1"/>
         <v>feeding_losses</v>
       </c>
       <c r="N98" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O98" s="22" t="str">
         <f t="shared" si="1"/>
@@ -7145,7 +7178,7 @@
       </c>
       <c r="P98" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
+        <v>10% feeding on pasture</v>
       </c>
       <c r="Q98" s="22" t="str">
         <f t="shared" si="1"/>
@@ -7154,12 +7187,8 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="str">
-        <f t="shared" ref="A99:A102" si="2">A92</f>
-        <v>cattle</v>
-      </c>
-      <c r="E99" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>bulls</v>
+        <f t="shared" si="2"/>
+        <v>sheep</v>
       </c>
       <c r="G99" t="s">
         <v>300</v>
@@ -7170,16 +7199,13 @@
       </c>
       <c r="N99" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O99" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
+      <c r="P99" s="22"/>
       <c r="Q99" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
@@ -7188,7 +7214,7 @@
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>cattle</v>
+        <v>horses</v>
       </c>
       <c r="G100" t="s">
         <v>300</v>
@@ -7199,122 +7225,129 @@
       </c>
       <c r="N100" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O100" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
-      </c>
+      <c r="P100" s="22"/>
       <c r="Q100" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>sheep</v>
-      </c>
-      <c r="G101" t="s">
-        <v>300</v>
-      </c>
-      <c r="M101" s="22" t="str">
-        <f t="shared" si="1"/>
+      <c r="A101" s="22"/>
+      <c r="M101" s="22"/>
+      <c r="N101" s="22"/>
+      <c r="O101" s="22"/>
+      <c r="P101" s="22"/>
+      <c r="Q101" s="22"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G102" t="s">
+        <v>629</v>
+      </c>
+      <c r="M102" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N102" s="21">
+        <v>5</v>
+      </c>
+      <c r="O102" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P102" s="21"/>
+      <c r="Q102" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="22" t="str">
+        <f>A89</f>
+        <v>cattle</v>
+      </c>
+      <c r="B103" s="22" t="str">
+        <f>B89</f>
+        <v>dairy</v>
+      </c>
+      <c r="E103" s="22" t="str">
+        <f t="shared" ref="E103:E104" si="3">E89</f>
+        <v>cows</v>
+      </c>
+      <c r="G103" t="s">
+        <v>629</v>
+      </c>
+      <c r="M103" s="22" t="str">
+        <f t="shared" ref="M103:Q107" si="4">M89</f>
         <v>feeding_losses</v>
       </c>
-      <c r="N101" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="O101" s="22" t="str">
-        <f t="shared" si="1"/>
+      <c r="N103" s="22">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="O103" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P101" s="22"/>
-      <c r="Q101" s="22" t="str">
-        <f t="shared" si="1"/>
+      <c r="P103" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q103" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>horses</v>
-      </c>
-      <c r="G102" t="s">
-        <v>300</v>
-      </c>
-      <c r="M102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N102" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="O102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P102" s="22"/>
-      <c r="Q102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103" s="22"/>
-      <c r="M103" s="22"/>
-      <c r="N103" s="22"/>
-      <c r="O103" s="22"/>
-      <c r="P103" s="22"/>
-      <c r="Q103" s="22"/>
-    </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="22" t="str">
+        <f t="shared" ref="A104:A107" si="5">A90</f>
+        <v>cattle</v>
+      </c>
+      <c r="E104" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
+      </c>
       <c r="G104" t="s">
         <v>629</v>
       </c>
-      <c r="M104" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N104" s="21">
+      <c r="M104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N104" s="22">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O104" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P104" s="21"/>
-      <c r="Q104" t="s">
-        <v>635</v>
+      <c r="O104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="22" t="str">
-        <f>A91</f>
+        <f t="shared" si="5"/>
         <v>cattle</v>
-      </c>
-      <c r="B105" s="22" t="str">
-        <f>B91</f>
-        <v>dairy</v>
-      </c>
-      <c r="E105" s="22" t="str">
-        <f t="shared" ref="E105:E106" si="3">E91</f>
-        <v>cows</v>
       </c>
       <c r="G105" t="s">
         <v>629</v>
       </c>
       <c r="M105" s="22" t="str">
-        <f t="shared" ref="M105:Q109" si="4">M91</f>
+        <f t="shared" si="4"/>
         <v>feeding_losses</v>
       </c>
       <c r="N105" s="22">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O105" s="22" t="str">
         <f t="shared" si="4"/>
@@ -7322,7 +7355,7 @@
       </c>
       <c r="P105" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
+        <v>10% feeding on pasture</v>
       </c>
       <c r="Q105" s="22" t="str">
         <f t="shared" si="4"/>
@@ -7331,12 +7364,8 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="22" t="str">
-        <f t="shared" ref="A106:A109" si="5">A92</f>
-        <v>cattle</v>
-      </c>
-      <c r="E106" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
+        <f t="shared" si="5"/>
+        <v>sheep</v>
       </c>
       <c r="G106" t="s">
         <v>629</v>
@@ -7347,25 +7376,22 @@
       </c>
       <c r="N106" s="22">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O106" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
+      <c r="P106" s="21"/>
       <c r="Q106" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="Q106:Q107" si="6">Q92</f>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="22" t="str">
         <f t="shared" si="5"/>
-        <v>cattle</v>
+        <v>horses</v>
       </c>
       <c r="G107" t="s">
         <v>629</v>
@@ -7376,249 +7402,230 @@
       </c>
       <c r="N107" s="22">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O107" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
-      </c>
+      <c r="P107" s="21"/>
       <c r="Q107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>sheep</v>
-      </c>
-      <c r="G108" t="s">
-        <v>629</v>
-      </c>
-      <c r="M108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N108" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P108" s="21"/>
-      <c r="Q108" s="22" t="str">
-        <f t="shared" ref="Q108:Q109" si="6">Q94</f>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>horses</v>
-      </c>
-      <c r="G109" t="s">
-        <v>629</v>
-      </c>
-      <c r="M109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N109" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P109" s="21"/>
-      <c r="Q109" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N108" s="3"/>
+      <c r="P108" s="21"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+      <c r="G109" t="s">
+        <v>630</v>
+      </c>
+      <c r="M109" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N109" s="21"/>
+      <c r="P109" s="3" t="s">
+        <v>632</v>
+      </c>
+    </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N110" s="3"/>
-      <c r="P110" s="21"/>
+      <c r="A110" s="3"/>
+      <c r="G110" t="s">
+        <v>630</v>
+      </c>
+      <c r="M110" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="N110" s="21">
+        <v>2</v>
+      </c>
+      <c r="O110" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P110" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
-      <c r="G111" t="s">
-        <v>630</v>
-      </c>
-      <c r="M111" s="21" t="s">
-        <v>374</v>
-      </c>
+      <c r="M111" s="21"/>
       <c r="N111" s="21"/>
-      <c r="P111" s="3" t="s">
-        <v>632</v>
-      </c>
+      <c r="O111" s="21"/>
+      <c r="P111" s="3"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="G112" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M112" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="N112" s="21">
-        <v>2</v>
-      </c>
-      <c r="O112" s="21" t="s">
-        <v>23</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N112" s="21"/>
       <c r="P112" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
-      <c r="M113" s="21"/>
-      <c r="N113" s="21"/>
-      <c r="O113" s="21"/>
-      <c r="P113" s="3"/>
+      <c r="G113" t="s">
+        <v>631</v>
+      </c>
+      <c r="M113" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="N113" s="21">
+        <v>3</v>
+      </c>
+      <c r="O113" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P113" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114" s="3"/>
-      <c r="G114" t="s">
-        <v>631</v>
-      </c>
-      <c r="M114" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N114" s="21"/>
-      <c r="P114" s="3" t="s">
-        <v>632</v>
-      </c>
+      <c r="N114" s="3"/>
+      <c r="P114" s="21"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
-      <c r="G115" t="s">
-        <v>631</v>
-      </c>
-      <c r="M115" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="N115" s="21">
-        <v>3</v>
-      </c>
-      <c r="O115" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P115" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>634</v>
-      </c>
+      <c r="A115" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" s="2"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N116" s="3"/>
-      <c r="P116" s="21"/>
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="N116" s="21"/>
+      <c r="P116" s="21" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
-      <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" s="2"/>
-      <c r="Q117" s="2"/>
+      <c r="A117" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="3"/>
+      <c r="M117" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="N117" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="P117" s="3"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>19</v>
-      </c>
-      <c r="N118" s="21"/>
-      <c r="P118" s="21" t="s">
-        <v>597</v>
-      </c>
+      <c r="A118" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="N118" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="P118" s="3"/>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="N119" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="O119" s="3" t="s">
-        <v>483</v>
+      <c r="A119" t="s">
+        <v>373</v>
+      </c>
+      <c r="M119" t="s">
+        <v>484</v>
+      </c>
+      <c r="N119" s="21">
+        <v>18</v>
+      </c>
+      <c r="O119" t="s">
+        <v>485</v>
       </c>
       <c r="P119" s="3"/>
+      <c r="Q119" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="N120" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="O120" s="3" t="s">
-        <v>483</v>
+      <c r="A120" t="s">
+        <v>20</v>
+      </c>
+      <c r="M120" t="s">
+        <v>484</v>
+      </c>
+      <c r="N120" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="O120" t="s">
+        <v>485</v>
       </c>
       <c r="P120" s="3"/>
+      <c r="Q120" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="M121" t="s">
         <v>484</v>
       </c>
       <c r="N121" s="21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O121" t="s">
         <v>485</v>
@@ -7629,46 +7636,50 @@
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>20</v>
-      </c>
-      <c r="M122" t="s">
-        <v>484</v>
-      </c>
-      <c r="N122" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="O122" t="s">
-        <v>485</v>
-      </c>
+      <c r="N122" s="21"/>
       <c r="P122" s="3"/>
-      <c r="Q122" t="s">
-        <v>486</v>
-      </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>370</v>
-      </c>
       <c r="M123" t="s">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="N123" s="21">
-        <v>0</v>
-      </c>
-      <c r="O123" t="s">
-        <v>485</v>
-      </c>
-      <c r="P123" s="3"/>
-      <c r="Q123" t="s">
-        <v>486</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O123" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="P123" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q123" s="21"/>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N124" s="21"/>
-      <c r="P124" s="3"/>
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="M124" t="s">
+        <v>598</v>
+      </c>
+      <c r="N124" s="21">
+        <v>1</v>
+      </c>
+      <c r="O124" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="P124" s="21"/>
+      <c r="Q124" s="21"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" t="s">
+        <v>312</v>
+      </c>
+      <c r="E125" t="s">
+        <v>313</v>
+      </c>
       <c r="M125" t="s">
         <v>598</v>
       </c>
@@ -7678,15 +7689,19 @@
       <c r="O125" s="21" t="s">
         <v>599</v>
       </c>
-      <c r="P125" s="21" t="s">
-        <v>600</v>
-      </c>
+      <c r="P125" s="21"/>
       <c r="Q125" s="21"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>19</v>
       </c>
+      <c r="B126" t="s">
+        <v>312</v>
+      </c>
+      <c r="E126" t="s">
+        <v>314</v>
+      </c>
       <c r="M126" t="s">
         <v>598</v>
       </c>
@@ -7704,10 +7719,10 @@
         <v>19</v>
       </c>
       <c r="B127" t="s">
-        <v>312</v>
+        <v>601</v>
       </c>
       <c r="E127" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M127" t="s">
         <v>598</v>
@@ -7722,108 +7737,80 @@
       <c r="Q127" s="21"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>19</v>
-      </c>
-      <c r="B128" t="s">
-        <v>312</v>
-      </c>
-      <c r="E128" t="s">
-        <v>314</v>
-      </c>
-      <c r="M128" t="s">
-        <v>598</v>
-      </c>
-      <c r="N128" s="21">
-        <v>1</v>
-      </c>
-      <c r="O128" s="21" t="s">
-        <v>599</v>
-      </c>
-      <c r="P128" s="21"/>
-      <c r="Q128" s="21"/>
+      <c r="N128" s="3"/>
+      <c r="P128" s="3"/>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>19</v>
-      </c>
-      <c r="B129" t="s">
-        <v>601</v>
-      </c>
-      <c r="E129" t="s">
-        <v>314</v>
-      </c>
-      <c r="M129" t="s">
-        <v>598</v>
-      </c>
-      <c r="N129" s="21">
-        <v>1</v>
-      </c>
-      <c r="O129" s="21" t="s">
-        <v>599</v>
-      </c>
-      <c r="P129" s="21"/>
-      <c r="Q129" s="21"/>
+      <c r="A129" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+      <c r="M129" s="2"/>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q129" s="2"/>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N130" s="3"/>
-      <c r="P130" s="3"/>
+      <c r="L130" s="103" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
-      <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q131" s="2"/>
+      <c r="M131" t="s">
+        <v>371</v>
+      </c>
+      <c r="N131" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="O131" t="s">
+        <v>594</v>
+      </c>
+      <c r="P131" s="3"/>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L132" s="103" t="s">
-        <v>613</v>
-      </c>
+      <c r="M132" t="s">
+        <v>472</v>
+      </c>
+      <c r="N132" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="O132" t="s">
+        <v>593</v>
+      </c>
+      <c r="P132" s="3"/>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M133" t="s">
-        <v>371</v>
+      <c r="M133" s="37" t="s">
+        <v>604</v>
       </c>
       <c r="N133" s="21" t="s">
         <v>610</v>
       </c>
-      <c r="O133" t="s">
-        <v>594</v>
-      </c>
-      <c r="P133" s="3"/>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M134" t="s">
-        <v>472</v>
+      <c r="M134" s="37" t="s">
+        <v>605</v>
       </c>
       <c r="N134" s="21" t="s">
         <v>610</v>
       </c>
-      <c r="O134" t="s">
-        <v>593</v>
-      </c>
-      <c r="P134" s="3"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M135" s="37" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N135" s="21" t="s">
         <v>610</v>
@@ -7831,183 +7818,167 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M136" s="37" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N136" s="21" t="s">
         <v>610</v>
       </c>
+      <c r="P136" s="3"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M137" s="37" t="s">
-        <v>606</v>
-      </c>
-      <c r="N137" s="21" t="s">
-        <v>610</v>
+      <c r="L137" s="103" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M138" s="37" t="s">
-        <v>607</v>
+      <c r="M138" t="s">
+        <v>17</v>
       </c>
       <c r="N138" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="P138" s="3"/>
+        <v>611</v>
+      </c>
+      <c r="O138" t="s">
+        <v>618</v>
+      </c>
+      <c r="P138" s="21" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L139" s="103" t="s">
-        <v>612</v>
-      </c>
+      <c r="M139" t="s">
+        <v>584</v>
+      </c>
+      <c r="N139" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="O139" t="s">
+        <v>592</v>
+      </c>
+      <c r="P139" s="3"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M140" t="s">
-        <v>17</v>
+        <v>473</v>
       </c>
       <c r="N140" s="21" t="s">
         <v>611</v>
       </c>
       <c r="O140" t="s">
-        <v>618</v>
+        <v>474</v>
       </c>
       <c r="P140" s="21" t="s">
-        <v>591</v>
+        <v>475</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M141" t="s">
-        <v>584</v>
-      </c>
-      <c r="N141" s="21" t="s">
-        <v>611</v>
-      </c>
-      <c r="O141" t="s">
-        <v>592</v>
-      </c>
-      <c r="P141" s="3"/>
+      <c r="L141" s="103" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M142" t="s">
-        <v>473</v>
+        <v>17</v>
       </c>
       <c r="N142" s="21" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="O142" t="s">
-        <v>474</v>
+        <v>618</v>
       </c>
       <c r="P142" s="21" t="s">
-        <v>475</v>
+        <v>591</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L143" s="103" t="s">
-        <v>614</v>
-      </c>
+      <c r="M143" t="s">
+        <v>584</v>
+      </c>
+      <c r="N143" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="O143" t="s">
+        <v>592</v>
+      </c>
+      <c r="P143" s="3"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M144" t="s">
-        <v>17</v>
-      </c>
-      <c r="N144" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="O144" t="s">
-        <v>618</v>
-      </c>
-      <c r="P144" s="21" t="s">
-        <v>591</v>
+      <c r="L144" s="103" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="145" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="O145" t="s">
+        <v>618</v>
+      </c>
+      <c r="P145" s="21" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="146" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M146" t="s">
         <v>584</v>
       </c>
-      <c r="N145" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="O145" t="s">
+      <c r="N146" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="O146" t="s">
         <v>592</v>
       </c>
-      <c r="P145" s="3"/>
-    </row>
-    <row r="146" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L146" s="103" t="s">
-        <v>615</v>
-      </c>
+      <c r="P146" s="3"/>
     </row>
     <row r="147" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M147" t="s">
-        <v>17</v>
-      </c>
-      <c r="N147" s="21" t="s">
-        <v>622</v>
-      </c>
-      <c r="O147" t="s">
-        <v>618</v>
-      </c>
-      <c r="P147" s="21" t="s">
-        <v>591</v>
+      <c r="L147" s="103" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="148" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M148" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="O148" t="s">
+        <v>619</v>
+      </c>
+      <c r="P148" s="21" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="149" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="M149" t="s">
         <v>584</v>
       </c>
-      <c r="N148" s="21" t="s">
-        <v>622</v>
-      </c>
-      <c r="O148" t="s">
+      <c r="N149" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="O149" t="s">
         <v>592</v>
       </c>
-      <c r="P148" s="3"/>
-    </row>
-    <row r="149" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L149" s="103" t="s">
-        <v>616</v>
-      </c>
+      <c r="P149" s="3"/>
     </row>
     <row r="150" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M150" t="s">
-        <v>17</v>
-      </c>
-      <c r="N150" s="21" t="s">
-        <v>623</v>
-      </c>
-      <c r="O150" t="s">
-        <v>619</v>
-      </c>
-      <c r="P150" s="21" t="s">
-        <v>591</v>
+      <c r="L150" s="103" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="151" spans="12:16" x14ac:dyDescent="0.25">
       <c r="M151" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="N151" s="21" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O151" t="s">
-        <v>592</v>
-      </c>
-      <c r="P151" s="3"/>
-    </row>
-    <row r="152" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="L152" s="103" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="153" spans="12:16" x14ac:dyDescent="0.25">
-      <c r="M153" t="s">
-        <v>609</v>
-      </c>
-      <c r="N153" s="21" t="s">
-        <v>624</v>
-      </c>
-      <c r="O153" t="s">
         <v>620</v>
       </c>
-      <c r="P153" s="21"/>
+      <c r="P151" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="9" r:id="rId1"/>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="677">
   <si>
     <t>f_feed</t>
   </si>
@@ -2195,9 +2195,6 @@
   </si>
   <si>
     <t>GE</t>
-  </si>
-  <si>
-    <t>DM</t>
   </si>
   <si>
     <t>ASH</t>
@@ -5912,10 +5909,10 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M153" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="N153" s="108" t="s">
         <v>676</v>
-      </c>
-      <c r="N153" s="108" t="s">
-        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -12548,119 +12545,115 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AV46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="25" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="24" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
         <v>584</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
       <c r="D1" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="2">
-        <v>5</v>
-      </c>
-      <c r="I1" s="2">
         <v>6</v>
       </c>
-      <c r="K1" s="40" t="s">
+      <c r="J1" s="40" t="s">
         <v>585</v>
       </c>
+      <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
       <c r="N1" s="2">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>17</v>
+      </c>
+      <c r="S1" s="40" t="s">
+        <v>587</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2">
         <v>12</v>
       </c>
-      <c r="O1" s="2">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2">
+      <c r="W1" s="2">
         <v>15</v>
       </c>
-      <c r="R1" s="2">
+      <c r="X1" s="2">
         <v>17</v>
       </c>
-      <c r="T1" s="40" t="s">
-        <v>587</v>
-      </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2">
+      <c r="Z1" s="40" t="s">
+        <v>586</v>
+      </c>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2">
         <v>12</v>
       </c>
-      <c r="X1" s="2">
+      <c r="AD1" s="2">
         <v>15</v>
       </c>
-      <c r="Y1" s="2">
+      <c r="AE1" s="2">
         <v>17</v>
       </c>
-      <c r="AA1" s="40" t="s">
-        <v>586</v>
-      </c>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2">
-        <v>12</v>
-      </c>
-      <c r="AE1" s="2">
-        <v>15</v>
-      </c>
-      <c r="AF1" s="2">
-        <v>17</v>
-      </c>
-      <c r="AH1" s="40" t="s">
+      <c r="AG1" s="40" t="s">
         <v>588</v>
       </c>
+      <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
+      <c r="AJ1" s="2">
+        <v>30</v>
+      </c>
       <c r="AK1" s="2">
-        <v>30</v>
-      </c>
-      <c r="AL1" s="2">
         <v>29</v>
       </c>
-      <c r="AN1" s="40" t="s">
+      <c r="AM1" s="40" t="s">
         <v>589</v>
       </c>
+      <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2">
+      <c r="AP1" s="2">
         <v>31</v>
       </c>
-      <c r="AR1" s="2"/>
-      <c r="AT1" s="40" t="s">
+      <c r="AQ1" s="2"/>
+      <c r="AS1" s="40" t="s">
         <v>607</v>
       </c>
+      <c r="AT1" s="2"/>
       <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2">
+      <c r="AV1" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
         <v>0</v>
       </c>
@@ -12671,10 +12664,10 @@
         <v>15</v>
       </c>
       <c r="D2" s="36" t="s">
+        <v>663</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>664</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>663</v>
       </c>
       <c r="F2" s="36" t="s">
         <v>665</v>
@@ -12685,18 +12678,18 @@
       <c r="H2" s="36" t="s">
         <v>667</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="37"/>
+      <c r="J2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="36" t="s">
         <v>668</v>
-      </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="36" t="s">
-        <v>15</v>
       </c>
       <c r="N2" s="36" t="s">
         <v>669</v>
@@ -12705,2124 +12698,2065 @@
         <v>670</v>
       </c>
       <c r="P2" s="36" t="s">
+        <v>673</v>
+      </c>
+      <c r="Q2" s="36" t="s">
         <v>671</v>
       </c>
-      <c r="Q2" s="36" t="s">
-        <v>674</v>
-      </c>
-      <c r="R2" s="36" t="s">
+      <c r="S2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="36" t="s">
+        <v>668</v>
+      </c>
+      <c r="W2" s="36" t="s">
+        <v>673</v>
+      </c>
+      <c r="X2" s="36" t="s">
+        <v>671</v>
+      </c>
+      <c r="Z2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB2" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC2" s="36" t="s">
+        <v>668</v>
+      </c>
+      <c r="AD2" s="36" t="s">
+        <v>673</v>
+      </c>
+      <c r="AE2" s="36" t="s">
+        <v>671</v>
+      </c>
+      <c r="AG2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI2" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ2" s="36" t="s">
         <v>672</v>
-      </c>
-      <c r="T2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="U2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="V2" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="W2" s="36" t="s">
-        <v>669</v>
-      </c>
-      <c r="X2" s="36" t="s">
-        <v>674</v>
-      </c>
-      <c r="Y2" s="36" t="s">
-        <v>672</v>
-      </c>
-      <c r="AA2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC2" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD2" s="36" t="s">
-        <v>669</v>
-      </c>
-      <c r="AE2" s="36" t="s">
-        <v>674</v>
-      </c>
-      <c r="AF2" s="36" t="s">
-        <v>672</v>
-      </c>
-      <c r="AH2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ2" s="36" t="s">
-        <v>15</v>
       </c>
       <c r="AK2" s="36" t="s">
         <v>673</v>
       </c>
-      <c r="AL2" s="36" t="s">
-        <v>674</v>
+      <c r="AM2" s="36" t="s">
+        <v>0</v>
       </c>
       <c r="AN2" s="36" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO2" s="36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP2" s="36" t="s">
-        <v>15</v>
+        <v>672</v>
       </c>
       <c r="AQ2" s="36" t="s">
         <v>673</v>
       </c>
-      <c r="AR2" s="36" t="s">
+      <c r="AS2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="AU2" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="AV2" s="101" t="s">
         <v>674</v>
       </c>
-      <c r="AT2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="AV2" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="AW2" s="101" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
       <c r="D3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>17.316948400000001</v>
       </c>
       <c r="E3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.316948400000001</v>
+        <v>7.55</v>
       </c>
       <c r="F3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.55</v>
+        <v>2.4239999999999999</v>
       </c>
       <c r="G3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.4239999999999999</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="H3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="I3" s="79">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.4250000000000003</v>
       </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28" t="str">
+      <c r="I3" s="28"/>
+      <c r="J3" s="28" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
-      <c r="L3" t="s">
+      <c r="K3" t="s">
         <v>19</v>
+      </c>
+      <c r="M3" s="79">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11.3</v>
       </c>
       <c r="N3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11.3</v>
+        <v>72</v>
       </c>
       <c r="O3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>72</v>
+        <v>26.5</v>
       </c>
       <c r="P3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>26.5</v>
+        <v>13.35</v>
       </c>
       <c r="Q3" s="79">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>13.35</v>
-      </c>
-      <c r="R3" s="79">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T3" s="28" t="str">
+      <c r="S3" s="28" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
-      <c r="U3" t="s">
+      <c r="T3" t="s">
         <v>376</v>
+      </c>
+      <c r="V3" s="65">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11.3</v>
       </c>
       <c r="W3" s="65">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11.3</v>
+        <v>13.35</v>
       </c>
       <c r="X3" s="65">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>13.35</v>
-      </c>
-      <c r="Y3" s="65">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA3" s="28" t="str">
+      <c r="Z3" s="28" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AA3" t="s">
         <v>372</v>
+      </c>
+      <c r="AC3" s="65">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11.3</v>
       </c>
       <c r="AD3" s="65">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11.3</v>
+        <v>13.35</v>
       </c>
       <c r="AE3" s="65">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>13.35</v>
-      </c>
-      <c r="AF3" s="65">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH3" s="28" t="str">
+      <c r="AG3" s="28" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AH3" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ3" s="65" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK3" s="65" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL3" s="65" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN3" s="28" t="str">
+      <c r="AM3" s="28" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
+      <c r="AN3" t="s">
+        <v>20</v>
+      </c>
       <c r="AO3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP3" t="s">
         <v>289</v>
+      </c>
+      <c r="AP3" s="65" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ3" s="65" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR3" s="65" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT3" s="28" t="str">
+      <c r="AS3" s="28" t="str">
         <f>'feed pars'!$B6</f>
         <v>ley silage, 1st cut</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AT3" t="s">
         <v>369</v>
       </c>
-      <c r="AW3" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV3" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
       <c r="D4" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>17.150216</v>
       </c>
       <c r="E4" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.150216</v>
+        <v>7.8</v>
       </c>
       <c r="F4" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.8</v>
+        <v>2.1280000000000001</v>
       </c>
       <c r="G4" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.1280000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H4" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.27</v>
-      </c>
-      <c r="I4" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.34</v>
       </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28" t="str">
+      <c r="I4" s="28"/>
+      <c r="J4" s="28" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
-      <c r="L4" t="s">
+      <c r="K4" t="s">
         <v>19</v>
+      </c>
+      <c r="M4" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>10.1</v>
       </c>
       <c r="N4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>10.1</v>
+        <v>69</v>
       </c>
       <c r="O4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="P4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>14</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="Q4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>11.899999999999999</v>
-      </c>
-      <c r="R4" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T4" s="28" t="str">
+      <c r="S4" s="28" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
-      <c r="U4" t="s">
+      <c r="T4" t="s">
         <v>376</v>
+      </c>
+      <c r="V4" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>10.1</v>
       </c>
       <c r="W4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>10.1</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="X4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>11.899999999999999</v>
-      </c>
-      <c r="Y4" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA4" s="28" t="str">
+      <c r="Z4" s="28" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AA4" t="s">
         <v>372</v>
+      </c>
+      <c r="AC4" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>10.1</v>
       </c>
       <c r="AD4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>10.1</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="AE4" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>11.899999999999999</v>
-      </c>
-      <c r="AF4" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH4" s="28" t="str">
+      <c r="AG4" s="28" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AH4" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ4" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK4" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL4" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN4" s="28" t="str">
+      <c r="AM4" s="28" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
+      <c r="AN4" t="s">
+        <v>20</v>
+      </c>
       <c r="AO4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP4" t="s">
         <v>289</v>
+      </c>
+      <c r="AP4" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ4" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR4" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT4" s="28" t="str">
+      <c r="AS4" s="28" t="str">
         <f>'feed pars'!$B7</f>
         <v>ley silage, regrowth</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AT4" t="s">
         <v>369</v>
       </c>
-      <c r="AW4" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV4" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
       <c r="D5" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>16.789764399999999</v>
       </c>
       <c r="E5" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.789764399999999</v>
+        <v>8.7999999999999989</v>
       </c>
       <c r="F5" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>8.7999999999999989</v>
+        <v>1.5439999999999998</v>
       </c>
       <c r="G5" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.5439999999999998</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H5" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="I5" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.35</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28" t="str">
+      <c r="I5" s="28"/>
+      <c r="J5" s="28" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
-      <c r="L5" t="s">
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="37">
+      <c r="M5" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>8.5</v>
+      </c>
+      <c r="N5" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>8.5</v>
+        <v/>
       </c>
       <c r="O5" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
         <v/>
       </c>
-      <c r="P5" s="37" t="str">
+      <c r="P5" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v/>
+        <v>10.75</v>
       </c>
       <c r="Q5" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>10.75</v>
-      </c>
-      <c r="R5" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>22.5</v>
       </c>
-      <c r="T5" s="28" t="str">
+      <c r="S5" s="28" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
-      <c r="U5" t="s">
+      <c r="T5" t="s">
         <v>376</v>
+      </c>
+      <c r="V5" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>8.5</v>
       </c>
       <c r="W5" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>8.5</v>
+        <v>10.75</v>
       </c>
       <c r="X5" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>10.75</v>
-      </c>
-      <c r="Y5" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>22.5</v>
       </c>
-      <c r="AA5" s="28" t="str">
+      <c r="Z5" s="28" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AA5" t="s">
         <v>372</v>
+      </c>
+      <c r="AC5" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>8.5</v>
       </c>
       <c r="AD5" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>8.5</v>
+        <v>10.75</v>
       </c>
       <c r="AE5" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>10.75</v>
-      </c>
-      <c r="AF5" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>22.5</v>
       </c>
-      <c r="AH5" s="28" t="str">
+      <c r="AG5" s="28" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AH5" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ5" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK5" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL5" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN5" s="28" t="str">
+      <c r="AM5" s="28" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
+      <c r="AN5" t="s">
+        <v>20</v>
+      </c>
       <c r="AO5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP5" t="s">
         <v>289</v>
+      </c>
+      <c r="AP5" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ5" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR5" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT5" s="28" t="str">
+      <c r="AS5" s="28" t="str">
         <f>'feed pars'!$B8</f>
         <v>other silage</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AT5" t="s">
         <v>369</v>
       </c>
-      <c r="AW5" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV5" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
       <c r="D6" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>17.160257599999998</v>
       </c>
       <c r="E6" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.160257599999998</v>
+        <v>6.2</v>
       </c>
       <c r="F6" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>6.2</v>
+        <v>1.496</v>
       </c>
       <c r="G6" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.496</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H6" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="I6" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.81</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28" t="str">
+      <c r="I6" s="28"/>
+      <c r="J6" s="28" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
-      <c r="L6" t="s">
+      <c r="K6" t="s">
         <v>19</v>
+      </c>
+      <c r="M6" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>9.1</v>
       </c>
       <c r="N6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>9.1</v>
+        <v>66</v>
       </c>
       <c r="O6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>66</v>
+        <v>-19</v>
       </c>
       <c r="P6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-19</v>
+        <v>11.8</v>
       </c>
       <c r="Q6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>11.8</v>
-      </c>
-      <c r="R6" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T6" s="28" t="str">
+      <c r="S6" s="28" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
-      <c r="U6" t="s">
+      <c r="T6" t="s">
         <v>376</v>
+      </c>
+      <c r="V6" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>9.1</v>
       </c>
       <c r="W6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>9.1</v>
+        <v>11.8</v>
       </c>
       <c r="X6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>11.8</v>
-      </c>
-      <c r="Y6" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA6" s="28" t="str">
+      <c r="Z6" s="28" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AA6" t="s">
         <v>372</v>
+      </c>
+      <c r="AC6" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>9.1</v>
       </c>
       <c r="AD6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>9.1</v>
+        <v>11.8</v>
       </c>
       <c r="AE6" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>11.8</v>
-      </c>
-      <c r="AF6" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH6" s="28" t="str">
+      <c r="AG6" s="28" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AH6" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ6" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK6" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL6" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN6" s="28" t="str">
+      <c r="AM6" s="28" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
+      <c r="AN6" t="s">
+        <v>20</v>
+      </c>
       <c r="AO6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP6" t="s">
         <v>289</v>
+      </c>
+      <c r="AP6" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ6" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR6" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT6" s="28" t="str">
+      <c r="AS6" s="28" t="str">
         <f>'feed pars'!$B9</f>
         <v>hay</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AT6" t="s">
         <v>369</v>
       </c>
-      <c r="AW6" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV6" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
       <c r="D7" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>17.6573168</v>
       </c>
       <c r="E7" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.6573168</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F7" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>3.5999999999999996</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="G7" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.0880000000000001</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="H7" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="I7" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.03</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28" t="str">
+      <c r="I7" s="28"/>
+      <c r="J7" s="28" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
-      <c r="L7" t="s">
+      <c r="K7" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="37">
+      <c r="M7" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11</v>
+      </c>
+      <c r="N7" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="O7" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
         <v/>
       </c>
-      <c r="P7" s="37" t="str">
+      <c r="P7" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v/>
+        <v>12.3</v>
       </c>
       <c r="Q7" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>12.3</v>
-      </c>
-      <c r="R7" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>30</v>
       </c>
-      <c r="T7" s="28" t="str">
+      <c r="S7" s="28" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
-      <c r="U7" t="s">
+      <c r="T7" t="s">
         <v>376</v>
+      </c>
+      <c r="V7" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11</v>
       </c>
       <c r="W7" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="X7" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>12.3</v>
-      </c>
-      <c r="Y7" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>30</v>
       </c>
-      <c r="AA7" s="28" t="str">
+      <c r="Z7" s="28" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AA7" t="s">
         <v>372</v>
+      </c>
+      <c r="AC7" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11</v>
       </c>
       <c r="AD7" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="AE7" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>12.3</v>
-      </c>
-      <c r="AF7" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>30</v>
       </c>
-      <c r="AH7" s="28" t="str">
+      <c r="AG7" s="28" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AH7" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ7" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK7" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL7" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN7" s="28" t="str">
+      <c r="AM7" s="28" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
+      <c r="AN7" t="s">
+        <v>20</v>
+      </c>
       <c r="AO7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP7" t="s">
         <v>289</v>
+      </c>
+      <c r="AP7" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ7" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR7" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT7" s="28" t="str">
+      <c r="AS7" s="28" t="str">
         <f>'feed pars'!$B10</f>
         <v>maize silage</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AT7" t="s">
         <v>369</v>
       </c>
-      <c r="AW7" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV7" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
       <c r="D8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>17.411437066666668</v>
       </c>
       <c r="E8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.411437066666668</v>
+        <v>6.5666666666666647</v>
       </c>
       <c r="F8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>6.5666666666666647</v>
+        <v>2.2466666666666666</v>
       </c>
       <c r="G8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.2466666666666666</v>
+        <v>0.27</v>
       </c>
       <c r="H8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.27</v>
-      </c>
-      <c r="I8" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.34</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28" t="str">
+      <c r="I8" s="28"/>
+      <c r="J8" s="28" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
-      <c r="L8" t="s">
+      <c r="K8" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="37">
+      <c r="M8" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>9.9416666666666664</v>
+      </c>
+      <c r="N8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>9.9416666666666664</v>
+        <v>74.333333333333329</v>
       </c>
       <c r="O8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>74.333333333333329</v>
+        <v>12.25</v>
       </c>
       <c r="P8" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>12.25</v>
-      </c>
-      <c r="Q8" s="28">
+        <v>12.4</v>
+      </c>
+      <c r="Q8" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>12.4</v>
-      </c>
-      <c r="R8" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T8" s="28" t="str">
+      <c r="S8" s="28" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
-      <c r="U8" t="s">
+      <c r="T8" t="s">
         <v>376</v>
+      </c>
+      <c r="V8" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>9.9416666666666664</v>
       </c>
       <c r="W8" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>9.9416666666666664</v>
+        <v>12.4</v>
       </c>
       <c r="X8" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>12.4</v>
-      </c>
-      <c r="Y8" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA8" s="28" t="str">
+      <c r="Z8" s="28" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AA8" t="s">
         <v>372</v>
+      </c>
+      <c r="AC8" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>9.9416666666666664</v>
       </c>
       <c r="AD8" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>9.9416666666666664</v>
+        <v>12.4</v>
       </c>
       <c r="AE8" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>12.4</v>
-      </c>
-      <c r="AF8" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH8" s="28" t="str">
+      <c r="AG8" s="28" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AH8" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ8" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK8" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL8" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN8" s="28" t="str">
+      <c r="AM8" s="28" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
+      <c r="AN8" t="s">
+        <v>20</v>
+      </c>
       <c r="AO8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP8" t="s">
         <v>289</v>
+      </c>
+      <c r="AP8" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ8" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR8" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT8" s="28" t="str">
+      <c r="AS8" s="28" t="str">
         <f>'feed pars'!$B11</f>
         <v>grazing</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AT8" t="s">
         <v>369</v>
       </c>
-      <c r="AW8" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV8" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
       <c r="D9" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>86</v>
+        <v>18.210023200000002</v>
       </c>
       <c r="E9" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.210023200000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F9" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>1.7999999999999998</v>
+        <v>1.9359999999999999</v>
       </c>
       <c r="G9" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.9359999999999999</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="H9" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="I9" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.52500000000000002</v>
       </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28" t="str">
+      <c r="I9" s="28"/>
+      <c r="J9" s="28" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
-      <c r="L9" t="s">
+      <c r="K9" t="s">
         <v>19</v>
+      </c>
+      <c r="M9" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>14.1</v>
       </c>
       <c r="N9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>14.1</v>
+        <v>95</v>
       </c>
       <c r="O9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>95</v>
+        <v>-33</v>
       </c>
       <c r="P9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-33</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>16</v>
-      </c>
-      <c r="R9" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>25</v>
       </c>
-      <c r="T9" s="28" t="str">
+      <c r="S9" s="28" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
-      <c r="U9" t="s">
+      <c r="T9" t="s">
         <v>376</v>
+      </c>
+      <c r="V9" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>14.1</v>
       </c>
       <c r="W9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="X9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>16</v>
-      </c>
-      <c r="Y9" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>25</v>
       </c>
-      <c r="AA9" s="28" t="str">
+      <c r="Z9" s="28" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AA9" t="s">
         <v>372</v>
+      </c>
+      <c r="AC9" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>14.1</v>
       </c>
       <c r="AD9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="AE9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>16</v>
-      </c>
-      <c r="AF9" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>25</v>
       </c>
-      <c r="AH9" s="28" t="str">
+      <c r="AG9" s="28" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AH9" t="s">
         <v>20</v>
       </c>
-      <c r="AJ9" s="37"/>
+      <c r="AI9" s="37"/>
+      <c r="AJ9" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>12.1</v>
+      </c>
       <c r="AK9" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>12.1</v>
-      </c>
-      <c r="AL9" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>15.9</v>
       </c>
-      <c r="AN9" s="28" t="str">
+      <c r="AM9" s="28" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
+      <c r="AN9" t="s">
+        <v>20</v>
+      </c>
       <c r="AO9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP9" t="s">
         <v>289</v>
       </c>
-      <c r="AQ9" s="37">
+      <c r="AP9" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>12.3</v>
+      </c>
+      <c r="AQ9" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>12.3</v>
-      </c>
-      <c r="AR9" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT9" s="28" t="str">
+      <c r="AS9" s="28" t="str">
         <f>'feed pars'!$B12</f>
         <v>wheat</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AT9" t="s">
         <v>369</v>
       </c>
-      <c r="AW9" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV9" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>14.712643678160921</v>
       </c>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
       <c r="D10" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>86</v>
+        <v>18.089524000000001</v>
       </c>
       <c r="E10" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.089524000000001</v>
+        <v>2.7</v>
       </c>
       <c r="F10" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>2.7</v>
+        <v>1.9039999999999999</v>
       </c>
       <c r="G10" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.9039999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="H10" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.375</v>
-      </c>
-      <c r="I10" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.58000000000000007</v>
       </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28" t="str">
+      <c r="I10" s="28"/>
+      <c r="J10" s="28" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
-      <c r="L10" t="s">
+      <c r="K10" t="s">
         <v>19</v>
+      </c>
+      <c r="M10" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.2</v>
       </c>
       <c r="N10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.2</v>
+        <v>90</v>
       </c>
       <c r="O10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>90</v>
+        <v>-29</v>
       </c>
       <c r="P10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-29</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15</v>
-      </c>
-      <c r="R10" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>27</v>
       </c>
-      <c r="T10" s="28" t="str">
+      <c r="S10" s="28" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
-      <c r="U10" t="s">
+      <c r="T10" t="s">
         <v>376</v>
+      </c>
+      <c r="V10" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.2</v>
       </c>
       <c r="W10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="X10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15</v>
-      </c>
-      <c r="Y10" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>27</v>
       </c>
-      <c r="AA10" s="28" t="str">
+      <c r="Z10" s="28" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AA10" t="s">
         <v>372</v>
+      </c>
+      <c r="AC10" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.2</v>
       </c>
       <c r="AD10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="AE10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15</v>
-      </c>
-      <c r="AF10" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>27</v>
       </c>
-      <c r="AH10" s="28" t="str">
+      <c r="AG10" s="28" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="AH10" t="s">
         <v>20</v>
       </c>
-      <c r="AJ10" s="37"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>11</v>
+      </c>
       <c r="AK10" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>11</v>
-      </c>
-      <c r="AL10" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>14.8</v>
       </c>
-      <c r="AN10" s="28" t="str">
+      <c r="AM10" s="28" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
+      <c r="AN10" t="s">
+        <v>20</v>
+      </c>
       <c r="AO10" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP10" t="s">
         <v>289</v>
       </c>
-      <c r="AQ10" s="37">
+      <c r="AP10" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>11.2</v>
+      </c>
+      <c r="AQ10" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>11.2</v>
-      </c>
-      <c r="AR10" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT10" s="28" t="str">
+      <c r="AS10" s="28" t="str">
         <f>'feed pars'!$B13</f>
         <v>barley</v>
       </c>
-      <c r="AU10" t="s">
+      <c r="AT10" t="s">
         <v>369</v>
       </c>
-      <c r="AW10" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV10" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>13.563218390804598</v>
       </c>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
       <c r="D11" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>86</v>
+        <v>18.6602216</v>
       </c>
       <c r="E11" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.6602216</v>
+        <v>3.2</v>
       </c>
       <c r="F11" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>3.2</v>
+        <v>1.7680000000000002</v>
       </c>
       <c r="G11" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.7680000000000002</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H11" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="I11" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.54</v>
       </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28" t="str">
+      <c r="I11" s="28"/>
+      <c r="J11" s="28" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
-      <c r="L11" t="s">
+      <c r="K11" t="s">
         <v>19</v>
+      </c>
+      <c r="M11" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11.7</v>
       </c>
       <c r="N11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11.7</v>
+        <v>67</v>
       </c>
       <c r="O11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>67</v>
+        <v>-2</v>
       </c>
       <c r="P11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-2</v>
+        <v>13.3</v>
       </c>
       <c r="Q11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>13.3</v>
-      </c>
-      <c r="R11" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>61</v>
       </c>
-      <c r="T11" s="28" t="str">
+      <c r="S11" s="28" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
-      <c r="U11" t="s">
+      <c r="T11" t="s">
         <v>376</v>
+      </c>
+      <c r="V11" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11.7</v>
       </c>
       <c r="W11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="X11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>13.3</v>
-      </c>
-      <c r="Y11" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>61</v>
       </c>
-      <c r="AA11" s="28" t="str">
+      <c r="Z11" s="28" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AA11" t="s">
         <v>372</v>
+      </c>
+      <c r="AC11" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11.7</v>
       </c>
       <c r="AD11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="AE11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>13.3</v>
-      </c>
-      <c r="AF11" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>61</v>
       </c>
-      <c r="AH11" s="28" t="str">
+      <c r="AG11" s="28" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
-      <c r="AI11" t="s">
+      <c r="AH11" t="s">
         <v>20</v>
       </c>
-      <c r="AJ11" s="37"/>
+      <c r="AI11" s="37"/>
+      <c r="AJ11" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>9</v>
+      </c>
       <c r="AK11" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>9</v>
-      </c>
-      <c r="AL11" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>12.7</v>
       </c>
-      <c r="AN11" s="28" t="str">
+      <c r="AM11" s="28" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
+      <c r="AN11" t="s">
+        <v>20</v>
+      </c>
       <c r="AO11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP11" t="s">
         <v>289</v>
       </c>
-      <c r="AQ11" s="37">
+      <c r="AP11" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>9.4</v>
+      </c>
+      <c r="AQ11" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>9.4</v>
-      </c>
-      <c r="AR11" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT11" s="28" t="str">
+      <c r="AS11" s="28" t="str">
         <f>'feed pars'!$B14</f>
         <v>oats</v>
       </c>
-      <c r="AU11" t="s">
+      <c r="AT11" t="s">
         <v>369</v>
       </c>
-      <c r="AW11" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV11" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>12.298850574712644</v>
       </c>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
       <c r="D12" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>86</v>
+        <v>18.2284328</v>
       </c>
       <c r="E12" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.2284328</v>
+        <v>2.0500000000000003</v>
       </c>
       <c r="F12" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>2.0500000000000003</v>
+        <v>1.8639999999999999</v>
       </c>
       <c r="G12" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.8639999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="H12" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.38</v>
-      </c>
-      <c r="I12" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.58000000000000007</v>
       </c>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28" t="str">
+      <c r="I12" s="28"/>
+      <c r="J12" s="28" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
-      <c r="L12" t="s">
+      <c r="K12" t="s">
         <v>19</v>
+      </c>
+      <c r="M12" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>14</v>
       </c>
       <c r="N12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="O12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>95</v>
+        <v>-31</v>
       </c>
       <c r="P12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-31</v>
+        <v>15.8</v>
       </c>
       <c r="Q12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15.8</v>
-      </c>
-      <c r="R12" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>26</v>
       </c>
-      <c r="T12" s="28" t="str">
+      <c r="S12" s="28" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
-      <c r="U12" t="s">
+      <c r="T12" t="s">
         <v>376</v>
+      </c>
+      <c r="V12" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>14</v>
       </c>
       <c r="W12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>14</v>
+        <v>15.8</v>
       </c>
       <c r="X12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15.8</v>
-      </c>
-      <c r="Y12" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>26</v>
       </c>
-      <c r="AA12" s="28" t="str">
+      <c r="Z12" s="28" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AA12" t="s">
         <v>372</v>
+      </c>
+      <c r="AC12" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>14</v>
       </c>
       <c r="AD12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>14</v>
+        <v>15.8</v>
       </c>
       <c r="AE12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15.8</v>
-      </c>
-      <c r="AF12" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>26</v>
       </c>
-      <c r="AH12" s="28" t="str">
+      <c r="AG12" s="28" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
-      <c r="AI12" t="s">
+      <c r="AH12" t="s">
         <v>20</v>
       </c>
-      <c r="AJ12" s="37"/>
+      <c r="AI12" s="37"/>
+      <c r="AJ12" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>11.9</v>
+      </c>
       <c r="AK12" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>11.9</v>
-      </c>
-      <c r="AL12" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>15.6</v>
       </c>
-      <c r="AN12" s="28" t="str">
+      <c r="AM12" s="28" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
+      <c r="AN12" t="s">
+        <v>20</v>
+      </c>
       <c r="AO12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP12" t="s">
         <v>289</v>
       </c>
-      <c r="AQ12" s="37">
+      <c r="AP12" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>12</v>
+      </c>
+      <c r="AQ12" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>12</v>
-      </c>
-      <c r="AR12" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT12" s="28" t="str">
+      <c r="AS12" s="28" t="str">
         <f>'feed pars'!$B15</f>
         <v>triticale</v>
       </c>
-      <c r="AU12" t="s">
+      <c r="AT12" t="s">
         <v>369</v>
       </c>
-      <c r="AW12" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV12" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>14.606741573033707</v>
       </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
       <c r="D13" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>86</v>
+        <v>17.924256</v>
       </c>
       <c r="E13" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.924256</v>
+        <v>2.0500000000000003</v>
       </c>
       <c r="F13" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>2.0500000000000003</v>
+        <v>1.6240000000000001</v>
       </c>
       <c r="G13" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.6240000000000001</v>
+        <v>0.32999999999999996</v>
       </c>
       <c r="H13" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="I13" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.55499999999999994</v>
       </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28" t="str">
+      <c r="I13" s="28"/>
+      <c r="J13" s="28" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
-      <c r="L13" t="s">
+      <c r="K13" t="s">
         <v>19</v>
+      </c>
+      <c r="M13" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.9</v>
       </c>
       <c r="N13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.9</v>
+        <v>95</v>
       </c>
       <c r="O13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>95</v>
+        <v>-57</v>
       </c>
       <c r="P13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-57</v>
+        <v>15.8</v>
       </c>
       <c r="Q13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15.8</v>
-      </c>
-      <c r="R13" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T13" s="28" t="str">
+      <c r="S13" s="28" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
-      <c r="U13" t="s">
+      <c r="T13" t="s">
         <v>376</v>
+      </c>
+      <c r="V13" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.9</v>
       </c>
       <c r="W13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.9</v>
+        <v>15.8</v>
       </c>
       <c r="X13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15.8</v>
-      </c>
-      <c r="Y13" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA13" s="28" t="str">
+      <c r="Z13" s="28" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AA13" t="s">
         <v>372</v>
+      </c>
+      <c r="AC13" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.9</v>
       </c>
       <c r="AD13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.9</v>
+        <v>15.8</v>
       </c>
       <c r="AE13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15.8</v>
-      </c>
-      <c r="AF13" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH13" s="28" t="str">
+      <c r="AG13" s="28" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
-      <c r="AI13" t="s">
+      <c r="AH13" t="s">
         <v>20</v>
       </c>
-      <c r="AJ13" s="37"/>
+      <c r="AI13" s="37"/>
+      <c r="AJ13" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>11.3</v>
+      </c>
       <c r="AK13" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>11.3</v>
-      </c>
-      <c r="AL13" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>15.1</v>
       </c>
-      <c r="AN13" s="28" t="str">
+      <c r="AM13" s="28" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
+      <c r="AN13" t="s">
+        <v>20</v>
+      </c>
       <c r="AO13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP13" t="s">
         <v>289</v>
       </c>
-      <c r="AQ13" s="37">
+      <c r="AP13" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>11.5</v>
+      </c>
+      <c r="AQ13" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>11.5</v>
-      </c>
-      <c r="AR13" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT13" s="28" t="str">
+      <c r="AS13" s="28" t="str">
         <f>'feed pars'!$B16</f>
         <v>rye</v>
       </c>
-      <c r="AU13" t="s">
+      <c r="AT13" t="s">
         <v>369</v>
       </c>
-      <c r="AW13" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV13" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>12.873563218390803</v>
       </c>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
       <c r="D14" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>86</v>
+        <v>18.3899352</v>
       </c>
       <c r="E14" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.3899352</v>
+        <v>1.8499999999999999</v>
       </c>
       <c r="F14" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>1.8499999999999999</v>
+        <v>1.6400000000000001</v>
       </c>
       <c r="G14" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.6400000000000001</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="H14" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="I14" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.46500000000000002</v>
       </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28" t="str">
+      <c r="I14" s="28"/>
+      <c r="J14" s="28" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
-      <c r="L14" t="s">
+      <c r="K14" t="s">
         <v>19</v>
+      </c>
+      <c r="M14" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>12.8</v>
       </c>
       <c r="N14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>12.8</v>
+        <v>81</v>
       </c>
       <c r="O14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>81</v>
+        <v>-30</v>
       </c>
       <c r="P14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-30</v>
+        <v>14.5</v>
       </c>
       <c r="Q14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>14.5</v>
-      </c>
-      <c r="R14" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>40</v>
       </c>
-      <c r="T14" s="28" t="str">
+      <c r="S14" s="28" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
-      <c r="U14" t="s">
+      <c r="T14" t="s">
         <v>376</v>
+      </c>
+      <c r="V14" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>12.8</v>
       </c>
       <c r="W14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="X14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>14.5</v>
-      </c>
-      <c r="Y14" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>40</v>
       </c>
-      <c r="AA14" s="28" t="str">
+      <c r="Z14" s="28" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AA14" t="s">
         <v>372</v>
+      </c>
+      <c r="AC14" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>12.8</v>
       </c>
       <c r="AD14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="AE14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>14.5</v>
-      </c>
-      <c r="AF14" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>40</v>
       </c>
-      <c r="AH14" s="28" t="str">
+      <c r="AG14" s="28" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
-      <c r="AI14" t="s">
+      <c r="AH14" t="s">
         <v>20</v>
       </c>
-      <c r="AJ14" s="37"/>
+      <c r="AI14" s="37"/>
+      <c r="AJ14" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>12.8</v>
+      </c>
       <c r="AK14" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>12.8</v>
-      </c>
-      <c r="AL14" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>16.5</v>
       </c>
-      <c r="AN14" s="28" t="str">
+      <c r="AM14" s="28" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
+      <c r="AN14" t="s">
+        <v>20</v>
+      </c>
       <c r="AO14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP14" t="s">
         <v>289</v>
       </c>
-      <c r="AQ14" s="37">
+      <c r="AP14" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>13.2</v>
+      </c>
+      <c r="AQ14" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>13.2</v>
-      </c>
-      <c r="AR14" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT14" s="28" t="str">
+      <c r="AS14" s="28" t="str">
         <f>'feed pars'!$B17</f>
         <v>maize</v>
       </c>
-      <c r="AU14" t="s">
+      <c r="AT14" t="s">
         <v>369</v>
       </c>
-      <c r="AW14" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV14" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>15.862068965517242</v>
       </c>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
       <c r="D15" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>85</v>
+        <v>18.478217600000001</v>
       </c>
       <c r="E15" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.478217600000001</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="F15" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>3.4000000000000004</v>
+        <v>3.7200000000000006</v>
       </c>
       <c r="G15" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>3.7200000000000006</v>
+        <v>0.44499999999999995</v>
       </c>
       <c r="H15" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.44499999999999995</v>
-      </c>
-      <c r="I15" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.155</v>
       </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28" t="str">
+      <c r="I15" s="28"/>
+      <c r="J15" s="28" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
-      <c r="L15" t="s">
+      <c r="K15" t="s">
         <v>19</v>
+      </c>
+      <c r="M15" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.8</v>
       </c>
       <c r="N15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.8</v>
+        <v>97</v>
       </c>
       <c r="O15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="P15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>16</v>
-      </c>
-      <c r="R15" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>17</v>
       </c>
-      <c r="T15" s="28" t="str">
+      <c r="S15" s="28" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
-      <c r="U15" t="s">
+      <c r="T15" t="s">
         <v>376</v>
+      </c>
+      <c r="V15" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.8</v>
       </c>
       <c r="W15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.8</v>
+        <v>16</v>
       </c>
       <c r="X15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>16</v>
-      </c>
-      <c r="Y15" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>17</v>
       </c>
-      <c r="AA15" s="28" t="str">
+      <c r="Z15" s="28" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AA15" t="s">
         <v>372</v>
+      </c>
+      <c r="AC15" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.8</v>
       </c>
       <c r="AD15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.8</v>
+        <v>16</v>
       </c>
       <c r="AE15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>16</v>
-      </c>
-      <c r="AF15" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>17</v>
       </c>
-      <c r="AH15" s="28" t="str">
+      <c r="AG15" s="28" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
-      <c r="AI15" t="s">
+      <c r="AH15" t="s">
         <v>20</v>
       </c>
-      <c r="AJ15" s="37"/>
+      <c r="AI15" s="37"/>
+      <c r="AJ15" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>11.2</v>
+      </c>
       <c r="AK15" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>11.2</v>
-      </c>
-      <c r="AL15" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>16.100000000000001</v>
       </c>
-      <c r="AN15" s="28" t="str">
+      <c r="AM15" s="28" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
+      <c r="AN15" t="s">
+        <v>20</v>
+      </c>
       <c r="AO15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP15" t="s">
         <v>289</v>
       </c>
-      <c r="AQ15" s="37">
+      <c r="AP15" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>11.5</v>
+      </c>
+      <c r="AQ15" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>11.5</v>
-      </c>
-      <c r="AR15" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT15" s="28" t="str">
+      <c r="AS15" s="28" t="str">
         <f>'feed pars'!$B18</f>
         <v>peas</v>
       </c>
-      <c r="AU15" t="s">
+      <c r="AT15" t="s">
         <v>369</v>
       </c>
-      <c r="AW15" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV15" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>12.64367816091954</v>
       </c>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
       <c r="D16" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>85</v>
+        <v>18.737207199999997</v>
       </c>
       <c r="E16" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.737207199999997</v>
+        <v>4</v>
       </c>
       <c r="F16" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>4</v>
+        <v>4.8079999999999998</v>
       </c>
       <c r="G16" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>4.8079999999999998</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="H16" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="I16" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.375</v>
       </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28" t="str">
+      <c r="I16" s="28"/>
+      <c r="J16" s="28" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
-      <c r="L16" t="s">
+      <c r="K16" t="s">
         <v>19</v>
+      </c>
+      <c r="M16" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="N16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.3</v>
+        <v>71</v>
       </c>
       <c r="O16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="P16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="Q16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>12.6</v>
-      </c>
-      <c r="R16" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>14</v>
       </c>
-      <c r="T16" s="28" t="str">
+      <c r="S16" s="28" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
-      <c r="U16" t="s">
+      <c r="T16" t="s">
         <v>376</v>
+      </c>
+      <c r="V16" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="W16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="X16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>12.6</v>
-      </c>
-      <c r="Y16" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>14</v>
       </c>
-      <c r="AA16" s="28" t="str">
+      <c r="Z16" s="28" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AA16" t="s">
         <v>372</v>
+      </c>
+      <c r="AC16" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="AD16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="AE16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>12.6</v>
-      </c>
-      <c r="AF16" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>14</v>
       </c>
-      <c r="AH16" s="28" t="str">
+      <c r="AG16" s="28" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
-      <c r="AI16" t="s">
+      <c r="AH16" t="s">
         <v>20</v>
       </c>
-      <c r="AJ16" s="37"/>
+      <c r="AI16" s="37"/>
+      <c r="AJ16" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>10.7</v>
+      </c>
       <c r="AK16" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>10.7</v>
-      </c>
-      <c r="AL16" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>15.5</v>
       </c>
-      <c r="AN16" s="28" t="str">
+      <c r="AM16" s="28" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
+      <c r="AN16" t="s">
+        <v>20</v>
+      </c>
       <c r="AO16" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP16" t="s">
         <v>289</v>
       </c>
-      <c r="AQ16" s="37">
+      <c r="AP16" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>10.9</v>
+      </c>
+      <c r="AQ16" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>10.9</v>
-      </c>
-      <c r="AR16" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT16" s="28" t="str">
+      <c r="AS16" s="28" t="str">
         <f>'feed pars'!$B19</f>
         <v>broad beans</v>
       </c>
-      <c r="AU16" t="s">
+      <c r="AT16" t="s">
         <v>369</v>
       </c>
-      <c r="AW16" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV16" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
       <c r="D17" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>91</v>
+        <v>27.903096000000001</v>
       </c>
       <c r="E17" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>27.903096000000001</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="F17" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>4.6500000000000004</v>
+        <v>3.3360000000000003</v>
       </c>
       <c r="G17" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>3.3360000000000003</v>
+        <v>0.81</v>
       </c>
       <c r="H17" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.81</v>
-      </c>
-      <c r="I17" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.90999999999999992</v>
       </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28" t="str">
+      <c r="I17" s="28"/>
+      <c r="J17" s="28" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
-      <c r="L17" t="s">
+      <c r="K17" t="s">
         <v>19</v>
+      </c>
+      <c r="M17" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>22.1</v>
       </c>
       <c r="N17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>22.1</v>
+        <v>56</v>
       </c>
       <c r="O17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="P17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>111</v>
+        <v>22.1</v>
       </c>
       <c r="Q17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>22.1</v>
-      </c>
-      <c r="R17" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>460</v>
       </c>
-      <c r="T17" s="28" t="str">
+      <c r="S17" s="28" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
-      <c r="U17" t="s">
+      <c r="T17" t="s">
         <v>376</v>
+      </c>
+      <c r="V17" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>22.1</v>
       </c>
       <c r="W17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
@@ -14830,18 +14764,18 @@
       </c>
       <c r="X17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>22.1</v>
-      </c>
-      <c r="Y17" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>460</v>
       </c>
-      <c r="AA17" s="28" t="str">
+      <c r="Z17" s="28" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AA17" t="s">
         <v>372</v>
+      </c>
+      <c r="AC17" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>22.1</v>
       </c>
       <c r="AD17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
@@ -14849,211 +14783,203 @@
       </c>
       <c r="AE17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>22.1</v>
-      </c>
-      <c r="AF17" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>460</v>
       </c>
-      <c r="AH17" s="28" t="str">
+      <c r="AG17" s="28" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
-      <c r="AI17" t="s">
+      <c r="AH17" t="s">
         <v>20</v>
       </c>
-      <c r="AJ17" s="37"/>
+      <c r="AI17" s="37"/>
+      <c r="AJ17" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>18</v>
+      </c>
       <c r="AK17" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>18</v>
-      </c>
-      <c r="AL17" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>23.5</v>
       </c>
-      <c r="AN17" s="28" t="str">
+      <c r="AM17" s="28" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
+      <c r="AN17" t="s">
+        <v>20</v>
+      </c>
       <c r="AO17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP17" t="s">
         <v>289</v>
       </c>
-      <c r="AQ17" s="37">
+      <c r="AP17" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>18.5</v>
+      </c>
+      <c r="AQ17" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>18.5</v>
-      </c>
-      <c r="AR17" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT17" s="28" t="str">
+      <c r="AS17" s="28" t="str">
         <f>'feed pars'!$B20</f>
         <v>rapeseed</v>
       </c>
-      <c r="AU17" t="s">
+      <c r="AT17" t="s">
         <v>369</v>
       </c>
-      <c r="AW17" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV17" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>16.8</v>
       </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
       <c r="D18" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>91</v>
+        <v>26.501456000000001</v>
       </c>
       <c r="E18" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>26.501456000000001</v>
+        <v>3.9</v>
       </c>
       <c r="F18" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>3.9</v>
+        <v>3.7359999999999998</v>
       </c>
       <c r="G18" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>3.7359999999999998</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="H18" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="I18" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.89500000000000002</v>
       </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28" t="str">
+      <c r="I18" s="28"/>
+      <c r="J18" s="28" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
-      <c r="L18" t="s">
+      <c r="K18" t="s">
         <v>19</v>
+      </c>
+      <c r="M18" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>20.100000000000001</v>
       </c>
       <c r="N18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>20.100000000000001</v>
+        <v>51</v>
       </c>
       <c r="O18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="P18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>154</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>20.8</v>
-      </c>
-      <c r="R18" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>380</v>
       </c>
-      <c r="T18" s="28" t="str">
+      <c r="S18" s="28" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
-      <c r="U18" t="s">
+      <c r="T18" t="s">
         <v>376</v>
+      </c>
+      <c r="V18" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>20.100000000000001</v>
       </c>
       <c r="W18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>20.100000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>20.8</v>
-      </c>
-      <c r="Y18" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>380</v>
       </c>
-      <c r="AA18" s="28" t="str">
+      <c r="Z18" s="28" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AA18" t="s">
         <v>372</v>
+      </c>
+      <c r="AC18" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>20.100000000000001</v>
       </c>
       <c r="AD18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>20.100000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="AE18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>20.8</v>
-      </c>
-      <c r="AF18" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>380</v>
       </c>
-      <c r="AH18" s="28" t="str">
+      <c r="AG18" s="28" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
-      <c r="AI18" t="s">
+      <c r="AH18" t="s">
         <v>20</v>
       </c>
-      <c r="AJ18" s="37"/>
+      <c r="AI18" s="37"/>
+      <c r="AJ18" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>17.3</v>
+      </c>
       <c r="AK18" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>17.3</v>
-      </c>
-      <c r="AL18" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>20.9</v>
       </c>
-      <c r="AN18" s="28" t="str">
+      <c r="AM18" s="28" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
+      <c r="AN18" t="s">
+        <v>20</v>
+      </c>
       <c r="AO18" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP18" t="s">
         <v>289</v>
       </c>
-      <c r="AQ18" s="37">
+      <c r="AP18" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>17.5</v>
+      </c>
+      <c r="AQ18" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>17.5</v>
-      </c>
-      <c r="AR18" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT18" s="28" t="str">
+      <c r="AS18" s="28" t="str">
         <f>'feed pars'!$B21</f>
         <v>linseed</v>
       </c>
-      <c r="AU18" t="s">
+      <c r="AT18" t="s">
         <v>369</v>
       </c>
-      <c r="AW18" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV18" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
       <c r="D19" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>39.329599999999999</v>
       </c>
       <c r="E19" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>39.329599999999999</v>
+        <v>0</v>
       </c>
       <c r="F19" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
@@ -15067,44 +14993,44 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28" t="str">
+      <c r="I19" s="28"/>
+      <c r="J19" s="28" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
-      <c r="L19" t="s">
+      <c r="K19" t="s">
         <v>19</v>
+      </c>
+      <c r="M19" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>36.6</v>
       </c>
       <c r="N19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>36.6</v>
+        <v>47</v>
       </c>
       <c r="O19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>47</v>
+        <v>-35</v>
       </c>
       <c r="P19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-35</v>
+        <v>36.6</v>
       </c>
       <c r="Q19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>36.6</v>
-      </c>
-      <c r="R19" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>1000</v>
       </c>
-      <c r="T19" s="28" t="str">
+      <c r="S19" s="28" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
-      <c r="U19" t="s">
+      <c r="T19" t="s">
         <v>376</v>
+      </c>
+      <c r="V19" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>36.6</v>
       </c>
       <c r="W19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
@@ -15112,18 +15038,18 @@
       </c>
       <c r="X19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>36.6</v>
-      </c>
-      <c r="Y19" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>1000</v>
       </c>
-      <c r="AA19" s="28" t="str">
+      <c r="Z19" s="28" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AA19" t="s">
         <v>372</v>
+      </c>
+      <c r="AC19" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>36.6</v>
       </c>
       <c r="AD19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
@@ -15131,2207 +15057,2143 @@
       </c>
       <c r="AE19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>36.6</v>
-      </c>
-      <c r="AF19" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>1000</v>
       </c>
-      <c r="AH19" s="28" t="str">
+      <c r="AG19" s="28" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
-      <c r="AI19" t="s">
+      <c r="AH19" t="s">
         <v>20</v>
       </c>
-      <c r="AJ19" s="37"/>
+      <c r="AI19" s="37"/>
+      <c r="AJ19" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>29.8</v>
+      </c>
       <c r="AK19" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>29.8</v>
-      </c>
-      <c r="AL19" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>34.5</v>
       </c>
-      <c r="AN19" s="28" t="str">
+      <c r="AM19" s="28" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
+      <c r="AN19" t="s">
+        <v>20</v>
+      </c>
       <c r="AO19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP19" t="s">
         <v>289</v>
       </c>
-      <c r="AQ19" s="37">
+      <c r="AP19" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>29.8</v>
+      </c>
+      <c r="AQ19" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>29.8</v>
-      </c>
-      <c r="AR19" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT19" s="28" t="str">
+      <c r="AS19" s="28" t="str">
         <f>'feed pars'!$B22</f>
         <v>vegetable oils</v>
       </c>
-      <c r="AU19" t="s">
+      <c r="AT19" t="s">
         <v>369</v>
       </c>
-      <c r="AW19" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV19" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>38.080808080808083</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
       <c r="D20" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>85</v>
+        <v>16.927627199999996</v>
       </c>
       <c r="E20" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.927627199999996</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="F20" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>6.6000000000000005</v>
+        <v>1.1040000000000001</v>
       </c>
       <c r="G20" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.1040000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H20" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.26</v>
-      </c>
-      <c r="I20" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28" t="str">
+      <c r="I20" s="28"/>
+      <c r="J20" s="28" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
-      <c r="L20" t="s">
+      <c r="K20" t="s">
         <v>19</v>
+      </c>
+      <c r="M20" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>6.6</v>
       </c>
       <c r="N20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>6.6</v>
+        <v>45</v>
       </c>
       <c r="O20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>45</v>
+        <v>-60</v>
       </c>
       <c r="P20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-60</v>
+        <v>7.6</v>
       </c>
       <c r="Q20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>7.6</v>
-      </c>
-      <c r="R20" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T20" s="28" t="str">
+      <c r="S20" s="28" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
-      <c r="U20" t="s">
+      <c r="T20" t="s">
         <v>376</v>
+      </c>
+      <c r="V20" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>6.6</v>
       </c>
       <c r="W20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="X20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>7.6</v>
-      </c>
-      <c r="Y20" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA20" s="28" t="str">
+      <c r="Z20" s="28" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AA20" t="s">
         <v>372</v>
+      </c>
+      <c r="AC20" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>6.6</v>
       </c>
       <c r="AD20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AE20" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>7.6</v>
-      </c>
-      <c r="AF20" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH20" s="28" t="str">
+      <c r="AG20" s="28" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
-      <c r="AI20" t="s">
+      <c r="AH20" t="s">
         <v>20</v>
       </c>
-      <c r="AJ20" s="37"/>
+      <c r="AI20" s="37"/>
+      <c r="AJ20" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
+      </c>
       <c r="AK20" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL20" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN20" s="28" t="str">
+      <c r="AM20" s="28" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
+      <c r="AN20" t="s">
+        <v>20</v>
+      </c>
       <c r="AO20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP20" t="s">
         <v>289</v>
+      </c>
+      <c r="AP20" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ20" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR20" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT20" s="28" t="str">
+      <c r="AS20" s="28" t="str">
         <f>'feed pars'!$B23</f>
         <v>straw</v>
       </c>
-      <c r="AU20" t="s">
+      <c r="AT20" t="s">
         <v>369</v>
       </c>
-      <c r="AW20" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV20" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
       <c r="D21" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87</v>
+        <v>22.965976000000001</v>
       </c>
       <c r="E21" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>22.965976000000001</v>
+        <v>5</v>
       </c>
       <c r="F21" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="G21" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>6.4</v>
+        <v>0.63</v>
       </c>
       <c r="H21" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.63</v>
-      </c>
-      <c r="I21" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.9</v>
       </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28" t="str">
+      <c r="I21" s="28"/>
+      <c r="J21" s="28" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
-      <c r="L21" t="s">
+      <c r="K21" t="s">
         <v>19</v>
+      </c>
+      <c r="M21" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>16.399999999999999</v>
       </c>
       <c r="N21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>16.399999999999999</v>
+        <v>69</v>
       </c>
       <c r="O21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>69</v>
+        <v>273</v>
       </c>
       <c r="P21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>273</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="Q21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="R21" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>180</v>
       </c>
-      <c r="T21" s="28" t="str">
+      <c r="S21" s="28" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
-      <c r="U21" t="s">
+      <c r="T21" t="s">
         <v>376</v>
+      </c>
+      <c r="V21" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>16.399999999999999</v>
       </c>
       <c r="W21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>16.399999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="X21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="Y21" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>180</v>
       </c>
-      <c r="AA21" s="28" t="str">
+      <c r="Z21" s="28" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AA21" t="s">
         <v>372</v>
+      </c>
+      <c r="AC21" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>16.399999999999999</v>
       </c>
       <c r="AD21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>16.399999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AE21" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="AF21" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>180</v>
       </c>
-      <c r="AH21" s="28" t="str">
+      <c r="AG21" s="28" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
-      <c r="AI21" t="s">
+      <c r="AH21" t="s">
         <v>20</v>
       </c>
-      <c r="AJ21" s="37"/>
+      <c r="AI21" s="37"/>
+      <c r="AJ21" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
+      </c>
       <c r="AK21" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL21" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN21" s="28" t="str">
+      <c r="AM21" s="28" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
+      <c r="AN21" t="s">
+        <v>20</v>
+      </c>
       <c r="AO21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP21" t="s">
         <v>289</v>
+      </c>
+      <c r="AP21" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ21" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR21" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT21" s="28" t="str">
+      <c r="AS21" s="28" t="str">
         <f>'feed pars'!$B24</f>
         <v>soybeans</v>
       </c>
-      <c r="AU21" t="s">
+      <c r="AT21" t="s">
         <v>369</v>
       </c>
-      <c r="AW21" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV21" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
       <c r="D22" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87.5</v>
+        <v>19.589487999999999</v>
       </c>
       <c r="E22" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>19.589487999999999</v>
+        <v>7.1499999999999995</v>
       </c>
       <c r="F22" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.1499999999999995</v>
+        <v>8.2080000000000002</v>
       </c>
       <c r="G22" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>8.2080000000000002</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="H22" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="I22" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.3499999999999996</v>
       </c>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28" t="str">
+      <c r="I22" s="28"/>
+      <c r="J22" s="28" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
-      <c r="L22" t="s">
+      <c r="K22" t="s">
         <v>19</v>
+      </c>
+      <c r="M22" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>14.6</v>
       </c>
       <c r="N22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>14.6</v>
+        <v>182</v>
       </c>
       <c r="O22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="P22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>261</v>
+        <v>17.8</v>
       </c>
       <c r="Q22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>17.8</v>
-      </c>
-      <c r="R22" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>10</v>
       </c>
-      <c r="T22" s="28" t="str">
+      <c r="S22" s="28" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
-      <c r="U22" t="s">
+      <c r="T22" t="s">
         <v>376</v>
+      </c>
+      <c r="V22" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>14.6</v>
       </c>
       <c r="W22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>14.6</v>
+        <v>17.8</v>
       </c>
       <c r="X22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>17.8</v>
-      </c>
-      <c r="Y22" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AA22" s="28" t="str">
+      <c r="Z22" s="28" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AA22" t="s">
         <v>372</v>
+      </c>
+      <c r="AC22" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>14.6</v>
       </c>
       <c r="AD22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>14.6</v>
+        <v>17.8</v>
       </c>
       <c r="AE22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>17.8</v>
-      </c>
-      <c r="AF22" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AH22" s="28" t="str">
+      <c r="AG22" s="28" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
-      <c r="AI22" t="s">
+      <c r="AH22" t="s">
         <v>20</v>
       </c>
-      <c r="AJ22" s="37"/>
+      <c r="AI22" s="37"/>
+      <c r="AJ22" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>9.3000000000000007</v>
+      </c>
       <c r="AK22" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="AL22" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>16.8</v>
       </c>
-      <c r="AN22" s="28" t="str">
+      <c r="AM22" s="28" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
+      <c r="AN22" t="s">
+        <v>20</v>
+      </c>
       <c r="AO22" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP22" t="s">
         <v>289</v>
       </c>
-      <c r="AQ22" s="37">
+      <c r="AP22" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>9.9</v>
+      </c>
+      <c r="AQ22" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>9.9</v>
-      </c>
-      <c r="AR22" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT22" s="28" t="str">
+      <c r="AS22" s="28" t="str">
         <f>'feed pars'!$B25</f>
         <v>soybean meal</v>
       </c>
-      <c r="AU22" t="s">
+      <c r="AT22" t="s">
         <v>369</v>
       </c>
-      <c r="AW22" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV22" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>10.459770114942529</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
       <c r="D23" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87.5</v>
+        <v>20.560594400000003</v>
       </c>
       <c r="E23" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>20.560594400000003</v>
+        <v>7.35</v>
       </c>
       <c r="F23" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.35</v>
+        <v>9.2880000000000003</v>
       </c>
       <c r="G23" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>9.2880000000000003</v>
+        <v>0.78999999999999992</v>
       </c>
       <c r="H23" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.78999999999999992</v>
-      </c>
-      <c r="I23" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.4649999999999999</v>
       </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28" t="str">
+      <c r="I23" s="28"/>
+      <c r="J23" s="28" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
-      <c r="L23" t="s">
+      <c r="K23" t="s">
         <v>19</v>
       </c>
-      <c r="N23" s="28">
+      <c r="M23" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.4</v>
+      </c>
+      <c r="N23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.4</v>
+        <v>59</v>
       </c>
       <c r="O23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="P23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-67</v>
+        <v>18.196692976000001</v>
       </c>
       <c r="Q23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>18.196692976000001</v>
-      </c>
-      <c r="R23" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>17</v>
       </c>
-      <c r="T23" s="28" t="str">
+      <c r="S23" s="28" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
-      <c r="U23" t="s">
+      <c r="T23" t="s">
         <v>376</v>
+      </c>
+      <c r="V23" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.4</v>
       </c>
       <c r="W23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.4</v>
+        <v>18.196692976000001</v>
       </c>
       <c r="X23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>18.196692976000001</v>
-      </c>
-      <c r="Y23" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>17</v>
       </c>
-      <c r="AA23" s="28" t="str">
+      <c r="Z23" s="28" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AA23" t="s">
         <v>372</v>
+      </c>
+      <c r="AC23" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.4</v>
       </c>
       <c r="AD23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.4</v>
+        <v>18.196692976000001</v>
       </c>
       <c r="AE23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>18.196692976000001</v>
-      </c>
-      <c r="AF23" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>17</v>
       </c>
-      <c r="AH23" s="28" t="str">
+      <c r="AG23" s="28" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
-      <c r="AI23" t="s">
+      <c r="AH23" t="s">
         <v>20</v>
       </c>
-      <c r="AJ23" s="37"/>
+      <c r="AI23" s="37"/>
+      <c r="AJ23" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>9.6999999999999993</v>
+      </c>
       <c r="AK23" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="AL23" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>17.3</v>
       </c>
-      <c r="AN23" s="28" t="str">
+      <c r="AM23" s="28" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
+      <c r="AN23" t="s">
+        <v>20</v>
+      </c>
       <c r="AO23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP23" t="s">
         <v>289</v>
       </c>
-      <c r="AQ23" s="37">
+      <c r="AP23" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>10.3</v>
+      </c>
+      <c r="AQ23" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>10.3</v>
-      </c>
-      <c r="AR23" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT23" s="28" t="str">
+      <c r="AS23" s="28" t="str">
         <f>'feed pars'!$B26</f>
         <v>soybean protein concentrate</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AT23" t="s">
         <v>369</v>
       </c>
-      <c r="AW23" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV23" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
       <c r="D24" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>89.5</v>
+        <v>19.4920008</v>
       </c>
       <c r="E24" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>19.4920008</v>
+        <v>7.7</v>
       </c>
       <c r="F24" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.7</v>
+        <v>6.152000000000001</v>
       </c>
       <c r="G24" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>6.152000000000001</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="H24" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>1.2450000000000001</v>
-      </c>
-      <c r="I24" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.55</v>
       </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28" t="str">
+      <c r="I24" s="28"/>
+      <c r="J24" s="28" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
-      <c r="L24" t="s">
+      <c r="K24" t="s">
         <v>19</v>
+      </c>
+      <c r="M24" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>12.2</v>
       </c>
       <c r="N24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>12.2</v>
+        <v>221</v>
       </c>
       <c r="O24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="P24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>79</v>
+        <v>14.6</v>
       </c>
       <c r="Q24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>14.6</v>
-      </c>
-      <c r="R24" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>46</v>
       </c>
-      <c r="T24" s="28" t="str">
+      <c r="S24" s="28" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
-      <c r="U24" t="s">
+      <c r="T24" t="s">
         <v>376</v>
+      </c>
+      <c r="V24" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>12.2</v>
       </c>
       <c r="W24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>12.2</v>
+        <v>14.6</v>
       </c>
       <c r="X24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>14.6</v>
-      </c>
-      <c r="Y24" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>46</v>
       </c>
-      <c r="AA24" s="28" t="str">
+      <c r="Z24" s="28" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AA24" t="s">
         <v>372</v>
+      </c>
+      <c r="AC24" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>12.2</v>
       </c>
       <c r="AD24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>12.2</v>
+        <v>14.6</v>
       </c>
       <c r="AE24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>14.6</v>
-      </c>
-      <c r="AF24" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>46</v>
       </c>
-      <c r="AH24" s="28" t="str">
+      <c r="AG24" s="28" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
-      <c r="AI24" t="s">
+      <c r="AH24" t="s">
         <v>20</v>
       </c>
-      <c r="AJ24" s="37"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>7.1</v>
+      </c>
       <c r="AK24" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>7.1</v>
-      </c>
-      <c r="AL24" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>13.3</v>
       </c>
-      <c r="AN24" s="28" t="str">
+      <c r="AM24" s="28" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
+      <c r="AN24" t="s">
+        <v>20</v>
+      </c>
       <c r="AO24" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP24" t="s">
         <v>289</v>
       </c>
-      <c r="AQ24" s="37">
+      <c r="AP24" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>7.7</v>
+      </c>
+      <c r="AQ24" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>7.7</v>
-      </c>
-      <c r="AR24" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT24" s="28" t="str">
+      <c r="AS24" s="28" t="str">
         <f>'feed pars'!$B27</f>
         <v>rapeseed meal</v>
       </c>
-      <c r="AU24" t="s">
+      <c r="AT24" t="s">
         <v>369</v>
       </c>
-      <c r="AW24" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV24" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>8.4444444444444446</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
       <c r="D25" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>91.5</v>
+        <v>21.972276000000001</v>
       </c>
       <c r="E25" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>21.972276000000001</v>
+        <v>6.75</v>
       </c>
       <c r="F25" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>6.75</v>
+        <v>5.1680000000000001</v>
       </c>
       <c r="G25" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>5.1680000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="H25" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I25" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.3250000000000002</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28" t="str">
+      <c r="I25" s="28"/>
+      <c r="J25" s="28" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
-      <c r="L25" t="s">
+      <c r="K25" t="s">
         <v>19</v>
+      </c>
+      <c r="M25" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>15.6</v>
       </c>
       <c r="N25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>15.6</v>
+        <v>80</v>
       </c>
       <c r="O25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="P25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>180</v>
+        <v>17.3</v>
       </c>
       <c r="Q25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>17.3</v>
-      </c>
-      <c r="R25" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>174</v>
       </c>
-      <c r="T25" s="28" t="str">
+      <c r="S25" s="28" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
-      <c r="U25" t="s">
+      <c r="T25" t="s">
         <v>376</v>
+      </c>
+      <c r="V25" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>15.6</v>
       </c>
       <c r="W25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>15.6</v>
+        <v>17.3</v>
       </c>
       <c r="X25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>17.3</v>
-      </c>
-      <c r="Y25" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>174</v>
       </c>
-      <c r="AA25" s="28" t="str">
+      <c r="Z25" s="28" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AA25" t="s">
         <v>372</v>
+      </c>
+      <c r="AC25" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>15.6</v>
       </c>
       <c r="AD25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>15.6</v>
+        <v>17.3</v>
       </c>
       <c r="AE25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>17.3</v>
-      </c>
-      <c r="AF25" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>174</v>
       </c>
-      <c r="AH25" s="28" t="str">
+      <c r="AG25" s="28" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
-      <c r="AI25" t="s">
+      <c r="AH25" t="s">
         <v>20</v>
       </c>
-      <c r="AJ25" s="37"/>
+      <c r="AI25" s="37"/>
+      <c r="AJ25" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>9.6999999999999993</v>
+      </c>
       <c r="AK25" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="AL25" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>14.3</v>
       </c>
-      <c r="AN25" s="28" t="str">
+      <c r="AM25" s="28" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
+      <c r="AN25" t="s">
+        <v>20</v>
+      </c>
       <c r="AO25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP25" t="s">
         <v>289</v>
       </c>
-      <c r="AQ25" s="37">
+      <c r="AP25" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="AQ25" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>10.199999999999999</v>
-      </c>
-      <c r="AR25" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT25" s="28" t="str">
+      <c r="AS25" s="28" t="str">
         <f>'feed pars'!$B28</f>
         <v>rapeseed cake</v>
       </c>
-      <c r="AU25" t="s">
+      <c r="AT25" t="s">
         <v>369</v>
       </c>
-      <c r="AW25" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV25" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
       <c r="D26" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>91</v>
+        <v>19.083224000000001</v>
       </c>
       <c r="E26" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>19.083224000000001</v>
+        <v>7.75</v>
       </c>
       <c r="F26" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.75</v>
+        <v>6.6640000000000006</v>
       </c>
       <c r="G26" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>6.6640000000000006</v>
+        <v>1.3050000000000002</v>
       </c>
       <c r="H26" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>1.3050000000000002</v>
-      </c>
-      <c r="I26" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.75</v>
       </c>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28" t="str">
+      <c r="I26" s="28"/>
+      <c r="J26" s="28" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
-      <c r="L26" t="s">
+      <c r="K26" t="s">
         <v>19</v>
+      </c>
+      <c r="M26" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11.4</v>
       </c>
       <c r="N26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11.4</v>
+        <v>109</v>
       </c>
       <c r="O26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>109</v>
+        <v>301</v>
       </c>
       <c r="P26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>301</v>
+        <v>14.1</v>
       </c>
       <c r="Q26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>14.1</v>
-      </c>
-      <c r="R26" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>10</v>
       </c>
-      <c r="T26" s="28" t="str">
+      <c r="S26" s="28" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
-      <c r="U26" t="s">
+      <c r="T26" t="s">
         <v>376</v>
+      </c>
+      <c r="V26" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11.4</v>
       </c>
       <c r="W26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="X26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>14.1</v>
-      </c>
-      <c r="Y26" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AA26" s="28" t="str">
+      <c r="Z26" s="28" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AA26" t="s">
         <v>372</v>
+      </c>
+      <c r="AC26" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11.4</v>
       </c>
       <c r="AD26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="AE26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>14.1</v>
-      </c>
-      <c r="AF26" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AH26" s="28" t="str">
+      <c r="AG26" s="28" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
-      <c r="AI26" t="s">
+      <c r="AH26" t="s">
         <v>20</v>
       </c>
-      <c r="AJ26" s="37"/>
+      <c r="AI26" s="37"/>
+      <c r="AJ26" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>5.9</v>
+      </c>
       <c r="AK26" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>5.9</v>
-      </c>
-      <c r="AL26" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>10.3</v>
       </c>
-      <c r="AN26" s="28" t="str">
+      <c r="AM26" s="28" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
+      <c r="AN26" t="s">
+        <v>20</v>
+      </c>
       <c r="AO26" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP26" t="s">
         <v>289</v>
       </c>
-      <c r="AQ26" s="37">
+      <c r="AP26" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>6.5</v>
+      </c>
+      <c r="AQ26" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>6.5</v>
-      </c>
-      <c r="AR26" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT26" s="28" t="str">
+      <c r="AS26" s="28" t="str">
         <f>'feed pars'!$B29</f>
         <v>sunflower seed meal</v>
       </c>
-      <c r="AU26" t="s">
+      <c r="AT26" t="s">
         <v>369</v>
       </c>
-      <c r="AW26" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV26" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>8.6</v>
       </c>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
       <c r="D27" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>91</v>
+        <v>19.581538399999999</v>
       </c>
       <c r="E27" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>19.581538399999999</v>
+        <v>4.5</v>
       </c>
       <c r="F27" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>4.5</v>
+        <v>2.5360000000000005</v>
       </c>
       <c r="G27" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.5360000000000005</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="H27" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="I27" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.77500000000000002</v>
       </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28" t="str">
+      <c r="I27" s="28"/>
+      <c r="J27" s="28" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
-      <c r="L27" t="s">
+      <c r="K27" t="s">
         <v>19</v>
+      </c>
+      <c r="M27" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.4</v>
       </c>
       <c r="N27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.4</v>
+        <v>115</v>
       </c>
       <c r="O27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>115</v>
+        <v>-35</v>
       </c>
       <c r="P27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-35</v>
+        <v>15</v>
       </c>
       <c r="Q27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15</v>
-      </c>
-      <c r="R27" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>97</v>
       </c>
-      <c r="T27" s="28" t="str">
+      <c r="S27" s="28" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
-      <c r="U27" t="s">
+      <c r="T27" t="s">
         <v>376</v>
+      </c>
+      <c r="V27" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.4</v>
       </c>
       <c r="W27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="X27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15</v>
-      </c>
-      <c r="Y27" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>97</v>
       </c>
-      <c r="AA27" s="28" t="str">
+      <c r="Z27" s="28" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AA27" t="s">
         <v>372</v>
+      </c>
+      <c r="AC27" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.4</v>
       </c>
       <c r="AD27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="AE27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15</v>
-      </c>
-      <c r="AF27" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>97</v>
       </c>
-      <c r="AH27" s="28" t="str">
+      <c r="AG27" s="28" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
-      <c r="AI27" t="s">
+      <c r="AH27" t="s">
         <v>20</v>
       </c>
-      <c r="AJ27" s="37"/>
+      <c r="AI27" s="37"/>
+      <c r="AJ27" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>5.4</v>
+      </c>
       <c r="AK27" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>5.4</v>
-      </c>
-      <c r="AL27" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>8.4</v>
       </c>
-      <c r="AN27" s="28" t="str">
+      <c r="AM27" s="28" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
+      <c r="AN27" t="s">
+        <v>20</v>
+      </c>
       <c r="AO27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP27" t="s">
         <v>289</v>
       </c>
-      <c r="AQ27" s="37">
+      <c r="AP27" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>6.2</v>
+      </c>
+      <c r="AQ27" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>6.2</v>
-      </c>
-      <c r="AR27" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT27" s="28" t="str">
+      <c r="AS27" s="28" t="str">
         <f>'feed pars'!$B30</f>
         <v>palm kernel expeller</v>
       </c>
-      <c r="AU27" t="s">
+      <c r="AT27" t="s">
         <v>369</v>
       </c>
-      <c r="AW27" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV27" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
       <c r="D28" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>90</v>
+        <v>16.971140800000001</v>
       </c>
       <c r="E28" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.971140800000001</v>
+        <v>11.700000000000001</v>
       </c>
       <c r="F28" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>11.700000000000001</v>
+        <v>2.9279999999999999</v>
       </c>
       <c r="G28" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.9279999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H28" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.27</v>
-      </c>
-      <c r="I28" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.56</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28" t="str">
+      <c r="I28" s="28"/>
+      <c r="J28" s="28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
-      <c r="L28" t="s">
+      <c r="K28" t="s">
         <v>19</v>
+      </c>
+      <c r="M28" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>8.5</v>
       </c>
       <c r="N28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>8.5</v>
+        <v>62</v>
       </c>
       <c r="O28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="P28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>86</v>
+        <v>10.7</v>
       </c>
       <c r="Q28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>10.7</v>
-      </c>
-      <c r="R28" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>27</v>
       </c>
-      <c r="T28" s="28" t="str">
+      <c r="S28" s="28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
-      <c r="U28" t="s">
+      <c r="T28" t="s">
         <v>376</v>
+      </c>
+      <c r="V28" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>8.5</v>
       </c>
       <c r="W28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>8.5</v>
+        <v>10.7</v>
       </c>
       <c r="X28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>10.7</v>
-      </c>
-      <c r="Y28" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>27</v>
       </c>
-      <c r="AA28" s="28" t="str">
+      <c r="Z28" s="28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AA28" t="s">
         <v>372</v>
+      </c>
+      <c r="AC28" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>8.5</v>
       </c>
       <c r="AD28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>8.5</v>
+        <v>10.7</v>
       </c>
       <c r="AE28" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>10.7</v>
-      </c>
-      <c r="AF28" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>27</v>
       </c>
-      <c r="AH28" s="28" t="str">
+      <c r="AG28" s="28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
-      <c r="AI28" t="s">
+      <c r="AH28" t="s">
         <v>20</v>
       </c>
-      <c r="AJ28" s="37"/>
+      <c r="AI28" s="37"/>
+      <c r="AJ28" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
+      </c>
       <c r="AK28" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL28" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN28" s="28" t="str">
+      <c r="AM28" s="28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
+      <c r="AN28" t="s">
+        <v>20</v>
+      </c>
       <c r="AO28" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP28" t="s">
         <v>289</v>
+      </c>
+      <c r="AP28" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ28" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR28" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT28" s="28" t="str">
+      <c r="AS28" s="28" t="str">
         <f>'feed pars'!$B31</f>
         <v>luzern meal</v>
       </c>
-      <c r="AU28" t="s">
+      <c r="AT28" t="s">
         <v>369</v>
       </c>
-      <c r="AW28" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV28" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
       <c r="D29" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87</v>
+        <v>18.194124000000002</v>
       </c>
       <c r="E29" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.194124000000002</v>
+        <v>5.8999999999999995</v>
       </c>
       <c r="F29" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>5.8999999999999995</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="G29" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.6399999999999997</v>
+        <v>1.1950000000000001</v>
       </c>
       <c r="H29" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>1.1950000000000001</v>
-      </c>
-      <c r="I29" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.35</v>
       </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28" t="str">
+      <c r="I29" s="28"/>
+      <c r="J29" s="28" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
-      <c r="L29" t="s">
+      <c r="K29" t="s">
         <v>19</v>
+      </c>
+      <c r="M29" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11</v>
       </c>
       <c r="N29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="O29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="P29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>36</v>
+        <v>12.7</v>
       </c>
       <c r="Q29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>12.7</v>
-      </c>
-      <c r="R29" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>45</v>
       </c>
-      <c r="T29" s="28" t="str">
+      <c r="S29" s="28" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
-      <c r="U29" t="s">
+      <c r="T29" t="s">
         <v>376</v>
+      </c>
+      <c r="V29" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11</v>
       </c>
       <c r="W29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="X29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>12.7</v>
-      </c>
-      <c r="Y29" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>45</v>
       </c>
-      <c r="AA29" s="28" t="str">
+      <c r="Z29" s="28" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AA29" t="s">
         <v>372</v>
+      </c>
+      <c r="AC29" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11</v>
       </c>
       <c r="AD29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="AE29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>12.7</v>
-      </c>
-      <c r="AF29" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>45</v>
       </c>
-      <c r="AH29" s="28" t="str">
+      <c r="AG29" s="28" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
-      <c r="AI29" t="s">
+      <c r="AH29" t="s">
         <v>20</v>
       </c>
-      <c r="AJ29" s="37"/>
+      <c r="AI29" s="37"/>
+      <c r="AJ29" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>7.2</v>
+      </c>
       <c r="AK29" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>7.2</v>
-      </c>
-      <c r="AL29" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>10.8</v>
       </c>
-      <c r="AN29" s="28" t="str">
+      <c r="AM29" s="28" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
+      <c r="AN29" t="s">
+        <v>20</v>
+      </c>
       <c r="AO29" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP29" t="s">
         <v>289</v>
       </c>
-      <c r="AQ29" s="37">
+      <c r="AP29" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>7.8</v>
+      </c>
+      <c r="AQ29" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>7.8</v>
-      </c>
-      <c r="AR29" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT29" s="28" t="str">
+      <c r="AS29" s="28" t="str">
         <f>'feed pars'!$B32</f>
         <v>wheat bran</v>
       </c>
-      <c r="AU29" t="s">
+      <c r="AT29" t="s">
         <v>369</v>
       </c>
-      <c r="AW29" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV29" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>7.8160919540229887</v>
       </c>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
       <c r="D30" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87.8</v>
+        <v>18.472360000000002</v>
       </c>
       <c r="E30" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.472360000000002</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="F30" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>3.3000000000000003</v>
+        <v>2.6160000000000001</v>
       </c>
       <c r="G30" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.6160000000000001</v>
+        <v>0.81500000000000006</v>
       </c>
       <c r="H30" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.81500000000000006</v>
-      </c>
-      <c r="I30" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.96</v>
       </c>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28" t="str">
+      <c r="I30" s="28"/>
+      <c r="J30" s="28" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
-      <c r="L30" t="s">
+      <c r="K30" t="s">
         <v>19</v>
       </c>
-      <c r="N30" s="28">
+      <c r="M30" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.3</v>
+      </c>
+      <c r="N30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.3</v>
+        <v>63</v>
       </c>
       <c r="O30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="P30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>98</v>
+        <v>15.627616560000002</v>
       </c>
       <c r="Q30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15.627616560000002</v>
-      </c>
-      <c r="R30" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>27</v>
       </c>
-      <c r="T30" s="28" t="str">
+      <c r="S30" s="28" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
-      <c r="U30" t="s">
+      <c r="T30" t="s">
         <v>376</v>
+      </c>
+      <c r="V30" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="W30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.3</v>
+        <v>15.627616560000002</v>
       </c>
       <c r="X30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15.627616560000002</v>
-      </c>
-      <c r="Y30" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>27</v>
       </c>
-      <c r="AA30" s="28" t="str">
+      <c r="Z30" s="28" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AA30" t="s">
         <v>372</v>
+      </c>
+      <c r="AC30" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="AD30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.3</v>
+        <v>15.627616560000002</v>
       </c>
       <c r="AE30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15.627616560000002</v>
-      </c>
-      <c r="AF30" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>27</v>
       </c>
-      <c r="AH30" s="28" t="str">
+      <c r="AG30" s="28" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
-      <c r="AI30" t="s">
+      <c r="AH30" t="s">
         <v>20</v>
       </c>
-      <c r="AJ30" s="37"/>
+      <c r="AI30" s="37"/>
+      <c r="AJ30" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>8.6999999999999993</v>
+      </c>
       <c r="AK30" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="AL30" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>17.5</v>
       </c>
-      <c r="AN30" s="28" t="str">
+      <c r="AM30" s="28" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
+      <c r="AN30" t="s">
+        <v>20</v>
+      </c>
       <c r="AO30" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP30" t="s">
         <v>289</v>
       </c>
-      <c r="AQ30" s="37">
+      <c r="AP30" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AQ30" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="AR30" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT30" s="28" t="str">
+      <c r="AS30" s="28" t="str">
         <f>'feed pars'!$B33</f>
         <v>wheat bran, fine</v>
       </c>
-      <c r="AU30" t="s">
+      <c r="AT30" t="s">
         <v>369</v>
       </c>
-      <c r="AW30" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV30" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>14.022988505747126</v>
       </c>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
       <c r="D31" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87.6</v>
+        <v>16.845620799999999</v>
       </c>
       <c r="E31" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.845620799999999</v>
+        <v>5</v>
       </c>
       <c r="F31" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>5</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="G31" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>0.41600000000000004</v>
+        <v>0.44</v>
       </c>
       <c r="H31" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.44</v>
-      </c>
-      <c r="I31" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.6</v>
       </c>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28" t="str">
+      <c r="I31" s="28"/>
+      <c r="J31" s="28" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
-      <c r="L31" t="s">
+      <c r="K31" t="s">
         <v>19</v>
+      </c>
+      <c r="M31" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>5.2</v>
       </c>
       <c r="N31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="O31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>32</v>
+        <v>-8</v>
       </c>
       <c r="P31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-8</v>
+        <v>6.2</v>
       </c>
       <c r="Q31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>6.2</v>
-      </c>
-      <c r="R31" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>20</v>
       </c>
-      <c r="T31" s="28" t="str">
+      <c r="S31" s="28" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
-      <c r="U31" t="s">
+      <c r="T31" t="s">
         <v>376</v>
+      </c>
+      <c r="V31" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>5.2</v>
       </c>
       <c r="W31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="X31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>6.2</v>
-      </c>
-      <c r="Y31" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AA31" s="28" t="str">
+      <c r="Z31" s="28" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AA31" t="s">
         <v>372</v>
+      </c>
+      <c r="AC31" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>5.2</v>
       </c>
       <c r="AD31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AE31" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>6.2</v>
-      </c>
-      <c r="AF31" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>20</v>
       </c>
-      <c r="AH31" s="28" t="str">
+      <c r="AG31" s="28" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
-      <c r="AI31" t="s">
+      <c r="AH31" t="s">
         <v>20</v>
       </c>
-      <c r="AJ31" s="37"/>
+      <c r="AI31" s="37"/>
+      <c r="AJ31" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
+      </c>
       <c r="AK31" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL31" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN31" s="28" t="str">
+      <c r="AM31" s="28" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
+      <c r="AN31" t="s">
+        <v>20</v>
+      </c>
       <c r="AO31" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP31" t="s">
         <v>289</v>
+      </c>
+      <c r="AP31" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ31" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR31" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT31" s="28" t="str">
+      <c r="AS31" s="28" t="str">
         <f>'feed pars'!$B34</f>
         <v>oat hulls</v>
       </c>
-      <c r="AU31" t="s">
+      <c r="AT31" t="s">
         <v>369</v>
       </c>
-      <c r="AW31" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV31" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
       <c r="D32" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87.6</v>
+        <v>17.3422616</v>
       </c>
       <c r="E32" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.3422616</v>
+        <v>5.5</v>
       </c>
       <c r="F32" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>5.5</v>
+        <v>1.008</v>
       </c>
       <c r="G32" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.008</v>
+        <v>0.77</v>
       </c>
       <c r="H32" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.77</v>
-      </c>
-      <c r="I32" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
-      <c r="L32" t="s">
+      <c r="K32" t="s">
         <v>19</v>
+      </c>
+      <c r="M32" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>7.2</v>
       </c>
       <c r="N32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>7.2</v>
+        <v>56</v>
       </c>
       <c r="O32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>56</v>
+        <v>-28</v>
       </c>
       <c r="P32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-28</v>
+        <v>8.4</v>
       </c>
       <c r="Q32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>8.4</v>
-      </c>
-      <c r="R32" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>32</v>
       </c>
-      <c r="T32" s="28" t="str">
+      <c r="S32" s="28" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
-      <c r="U32" t="s">
+      <c r="T32" t="s">
         <v>376</v>
+      </c>
+      <c r="V32" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>7.2</v>
       </c>
       <c r="W32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="X32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>8.4</v>
-      </c>
-      <c r="Y32" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>32</v>
       </c>
-      <c r="AA32" s="28" t="str">
+      <c r="Z32" s="28" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AA32" t="s">
         <v>372</v>
+      </c>
+      <c r="AC32" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>7.2</v>
       </c>
       <c r="AD32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AE32" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>8.4</v>
-      </c>
-      <c r="AF32" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>32</v>
       </c>
-      <c r="AH32" s="28" t="str">
+      <c r="AG32" s="28" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
-      <c r="AI32" t="s">
+      <c r="AH32" t="s">
         <v>20</v>
       </c>
-      <c r="AJ32" s="37"/>
+      <c r="AI32" s="37"/>
+      <c r="AJ32" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
+      </c>
       <c r="AK32" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL32" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN32" s="28" t="str">
+      <c r="AM32" s="28" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
+      <c r="AN32" t="s">
+        <v>20</v>
+      </c>
       <c r="AO32" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP32" t="s">
         <v>289</v>
+      </c>
+      <c r="AP32" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ32" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR32" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT32" s="28" t="str">
+      <c r="AS32" s="28" t="str">
         <f>'feed pars'!$B35</f>
         <v>oat bran</v>
       </c>
-      <c r="AU32" t="s">
+      <c r="AT32" t="s">
         <v>369</v>
       </c>
-      <c r="AW32" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV32" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
       <c r="D33" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>87.6</v>
+        <v>18.340564000000001</v>
       </c>
       <c r="E33" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.340564000000001</v>
+        <v>4.5</v>
       </c>
       <c r="F33" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="G33" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.56</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="H33" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="I33" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.6</v>
       </c>
-      <c r="K33" s="28" t="str">
+      <c r="J33" s="28" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
-      <c r="L33" t="s">
+      <c r="K33" t="s">
         <v>19</v>
+      </c>
+      <c r="M33" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11.6</v>
       </c>
       <c r="N33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11.6</v>
+        <v>78</v>
       </c>
       <c r="O33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="P33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>34</v>
+        <v>13.2</v>
       </c>
       <c r="Q33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>13.2</v>
-      </c>
-      <c r="R33" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>40</v>
       </c>
-      <c r="T33" s="28" t="str">
+      <c r="S33" s="28" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
-      <c r="U33" t="s">
+      <c r="T33" t="s">
         <v>376</v>
+      </c>
+      <c r="V33" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11.6</v>
       </c>
       <c r="W33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="X33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>13.2</v>
-      </c>
-      <c r="Y33" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>40</v>
       </c>
-      <c r="AA33" s="28" t="str">
+      <c r="Z33" s="28" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AA33" t="s">
         <v>372</v>
+      </c>
+      <c r="AC33" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11.6</v>
       </c>
       <c r="AD33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="AE33" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>13.2</v>
-      </c>
-      <c r="AF33" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>40</v>
       </c>
-      <c r="AH33" s="28" t="str">
+      <c r="AG33" s="28" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
-      <c r="AI33" t="s">
+      <c r="AH33" t="s">
         <v>20</v>
+      </c>
+      <c r="AJ33" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
       </c>
       <c r="AK33" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL33" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AN33" s="28" t="str">
+      <c r="AM33" s="28" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
+      <c r="AN33" t="s">
+        <v>20</v>
+      </c>
       <c r="AO33" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP33" t="s">
         <v>289</v>
+      </c>
+      <c r="AP33" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ33" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR33" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT33" s="28" t="str">
+      <c r="AS33" s="28" t="str">
         <f>'feed pars'!$B36</f>
         <v>rye bran</v>
       </c>
-      <c r="AU33" t="s">
+      <c r="AT33" t="s">
         <v>369</v>
       </c>
-      <c r="AW33" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV33" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
       <c r="D34" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>90</v>
+        <v>19.659779199999999</v>
       </c>
       <c r="E34" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>19.659779199999999</v>
+        <v>4.05</v>
       </c>
       <c r="F34" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>4.05</v>
+        <v>5.2799999999999994</v>
       </c>
       <c r="G34" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>5.2799999999999994</v>
+        <v>0.88</v>
       </c>
       <c r="H34" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.88</v>
-      </c>
-      <c r="I34" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.165</v>
       </c>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28" t="str">
+      <c r="I34" s="28"/>
+      <c r="J34" s="28" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
-      <c r="L34" t="s">
+      <c r="K34" t="s">
         <v>19</v>
+      </c>
+      <c r="M34" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="N34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.3</v>
+        <v>116</v>
       </c>
       <c r="O34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="P34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>142</v>
+        <v>15.7</v>
       </c>
       <c r="Q34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15.7</v>
-      </c>
-      <c r="R34" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>45</v>
       </c>
-      <c r="T34" s="28" t="str">
+      <c r="S34" s="28" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
-      <c r="U34" t="s">
+      <c r="T34" t="s">
         <v>376</v>
+      </c>
+      <c r="V34" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="W34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="X34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15.7</v>
-      </c>
-      <c r="Y34" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>45</v>
       </c>
-      <c r="AA34" s="28" t="str">
+      <c r="Z34" s="28" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AA34" t="s">
         <v>372</v>
+      </c>
+      <c r="AC34" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.3</v>
       </c>
       <c r="AD34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="AE34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15.7</v>
-      </c>
-      <c r="AF34" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>45</v>
       </c>
-      <c r="AH34" s="28" t="str">
+      <c r="AG34" s="28" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
-      <c r="AI34" t="s">
+      <c r="AH34" t="s">
         <v>20</v>
       </c>
-      <c r="AJ34" s="37"/>
+      <c r="AI34" s="37"/>
+      <c r="AJ34" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>8.1</v>
+      </c>
       <c r="AK34" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>8.1</v>
-      </c>
-      <c r="AL34" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>13.9</v>
       </c>
-      <c r="AN34" s="28" t="str">
+      <c r="AM34" s="28" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
+      <c r="AN34" t="s">
+        <v>20</v>
+      </c>
       <c r="AO34" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP34" t="s">
         <v>289</v>
       </c>
-      <c r="AQ34" s="37">
+      <c r="AP34" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AQ34" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="AR34" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT34" s="28" t="str">
+      <c r="AS34" s="28" t="str">
         <f>'feed pars'!$B37</f>
         <v>wheat distillers grain, dry</v>
       </c>
-      <c r="AU34" t="s">
+      <c r="AT34" t="s">
         <v>369</v>
       </c>
-      <c r="AW34" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV34" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
       <c r="D35" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>11</v>
+        <v>18.8602168</v>
       </c>
       <c r="E35" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>18.8602168</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="F35" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>6.8000000000000007</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="G35" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>4.4800000000000004</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H35" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I35" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
-      <c r="L35" t="s">
+      <c r="K35" t="s">
         <v>19</v>
+      </c>
+      <c r="M35" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v/>
       </c>
       <c r="N35" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
@@ -17349,16 +17211,16 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
         <v/>
       </c>
-      <c r="R35" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
-        <v/>
-      </c>
-      <c r="T35" s="28" t="str">
+      <c r="S35" s="28" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
-      <c r="U35" t="s">
+      <c r="T35" t="s">
         <v>376</v>
+      </c>
+      <c r="V35" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v/>
       </c>
       <c r="W35" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
@@ -17368,16 +17230,16 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
         <v/>
       </c>
-      <c r="Y35" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
-        <v/>
-      </c>
-      <c r="AA35" s="28" t="str">
+      <c r="Z35" s="28" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AA35" t="s">
         <v>372</v>
+      </c>
+      <c r="AC35" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v/>
       </c>
       <c r="AD35" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
@@ -17387,1337 +17249,1297 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
         <v/>
       </c>
-      <c r="AF35" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
-        <v/>
-      </c>
-      <c r="AH35" s="28" t="str">
+      <c r="AG35" s="28" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
-      <c r="AI35" t="s">
+      <c r="AH35" t="s">
         <v>20</v>
       </c>
-      <c r="AJ35" s="37"/>
+      <c r="AI35" s="37"/>
+      <c r="AJ35" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>8.1999999999999993</v>
+      </c>
       <c r="AK35" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="AL35" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>13.017208210412599</v>
       </c>
-      <c r="AN35" s="28" t="str">
+      <c r="AM35" s="28" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
+      <c r="AN35" t="s">
+        <v>20</v>
+      </c>
       <c r="AO35" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP35" t="s">
         <v>289</v>
       </c>
-      <c r="AQ35" s="37">
+      <c r="AP35" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>8.9</v>
+      </c>
+      <c r="AQ35" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>8.9</v>
-      </c>
-      <c r="AR35" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT35" s="28" t="str">
+      <c r="AS35" s="28" t="str">
         <f>'feed pars'!$B38</f>
         <v>wheat distillers grain, wet</v>
       </c>
-      <c r="AU35" t="s">
+      <c r="AT35" t="s">
         <v>369</v>
       </c>
-      <c r="AW35" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV35" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
       <c r="D36" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>90</v>
+        <v>19.848896</v>
       </c>
       <c r="E36" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>19.848896</v>
+        <v>4.3</v>
       </c>
       <c r="F36" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>4.3</v>
+        <v>3.984</v>
       </c>
       <c r="G36" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>3.984</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H36" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I36" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.19500000000000001</v>
       </c>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28" t="str">
+      <c r="I36" s="28"/>
+      <c r="J36" s="28" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
-      <c r="L36" t="s">
+      <c r="K36" t="s">
         <v>19</v>
+      </c>
+      <c r="M36" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>11.6</v>
       </c>
       <c r="N36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>11.6</v>
+        <v>141</v>
       </c>
       <c r="O36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="P36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>20</v>
+        <v>13.6</v>
       </c>
       <c r="Q36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>13.6</v>
-      </c>
-      <c r="R36" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>80</v>
       </c>
-      <c r="T36" s="28" t="str">
+      <c r="S36" s="28" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
-      <c r="U36" t="s">
+      <c r="T36" t="s">
         <v>376</v>
+      </c>
+      <c r="V36" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>11.6</v>
       </c>
       <c r="W36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="X36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>13.6</v>
-      </c>
-      <c r="Y36" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>80</v>
       </c>
-      <c r="AA36" s="28" t="str">
+      <c r="Z36" s="28" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AA36" t="s">
         <v>372</v>
+      </c>
+      <c r="AC36" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>11.6</v>
       </c>
       <c r="AD36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="AE36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>13.6</v>
-      </c>
-      <c r="AF36" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>80</v>
       </c>
-      <c r="AH36" s="28" t="str">
+      <c r="AG36" s="28" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
-      <c r="AI36" t="s">
+      <c r="AH36" t="s">
         <v>20</v>
       </c>
-      <c r="AJ36" s="37"/>
+      <c r="AI36" s="37"/>
+      <c r="AJ36" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>6.6</v>
+      </c>
       <c r="AK36" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>6.6</v>
-      </c>
-      <c r="AL36" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>10.6</v>
       </c>
-      <c r="AN36" s="28" t="str">
+      <c r="AM36" s="28" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
+      <c r="AN36" t="s">
+        <v>20</v>
+      </c>
       <c r="AO36" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP36" t="s">
         <v>289</v>
       </c>
-      <c r="AQ36" s="37">
+      <c r="AP36" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>7.0888888888888877</v>
+      </c>
+      <c r="AQ36" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>7.0888888888888877</v>
-      </c>
-      <c r="AR36" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT36" s="28" t="str">
+      <c r="AS36" s="28" t="str">
         <f>'feed pars'!$B39</f>
         <v>barley brewers grain</v>
       </c>
-      <c r="AU36" t="s">
+      <c r="AT36" t="s">
         <v>369</v>
       </c>
-      <c r="AW36" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV36" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
       <c r="D37" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>89.666666666666671</v>
+        <v>22.900705599999998</v>
       </c>
       <c r="E37" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>22.900705599999998</v>
+        <v>1.95</v>
       </c>
       <c r="F37" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>1.95</v>
+        <v>10.792</v>
       </c>
       <c r="G37" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>10.792</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="H37" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="I37" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.32499999999999996</v>
       </c>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28" t="str">
+      <c r="I37" s="28"/>
+      <c r="J37" s="28" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
-      <c r="L37" t="s">
+      <c r="K37" t="s">
         <v>19</v>
+      </c>
+      <c r="M37" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>16</v>
       </c>
       <c r="N37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>16</v>
+        <v>476</v>
       </c>
       <c r="O37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="P37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>82</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="Q37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>19.600000000000001</v>
-      </c>
-      <c r="R37" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>24</v>
       </c>
-      <c r="T37" s="28" t="str">
+      <c r="S37" s="28" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
-      <c r="U37" t="s">
+      <c r="T37" t="s">
         <v>376</v>
+      </c>
+      <c r="V37" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>16</v>
       </c>
       <c r="W37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>16</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="X37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>19.600000000000001</v>
-      </c>
-      <c r="Y37" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>24</v>
       </c>
-      <c r="AA37" s="28" t="str">
+      <c r="Z37" s="28" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AA37" t="s">
         <v>372</v>
+      </c>
+      <c r="AC37" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>16</v>
       </c>
       <c r="AD37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>16</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="AE37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>19.600000000000001</v>
-      </c>
-      <c r="AF37" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>24</v>
       </c>
-      <c r="AH37" s="28" t="str">
+      <c r="AG37" s="28" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
-      <c r="AI37" t="s">
+      <c r="AH37" t="s">
         <v>20</v>
       </c>
-      <c r="AJ37" s="37"/>
+      <c r="AI37" s="37"/>
+      <c r="AJ37" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>12.9</v>
+      </c>
       <c r="AK37" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>12.9</v>
-      </c>
-      <c r="AL37" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>21.4</v>
       </c>
-      <c r="AN37" s="28" t="str">
+      <c r="AM37" s="28" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
+      <c r="AN37" t="s">
+        <v>20</v>
+      </c>
       <c r="AO37" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP37" t="s">
         <v>289</v>
       </c>
-      <c r="AQ37" s="37">
+      <c r="AP37" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>13.3</v>
+      </c>
+      <c r="AQ37" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>13.3</v>
-      </c>
-      <c r="AR37" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT37" s="28" t="str">
+      <c r="AS37" s="28" t="str">
         <f>'feed pars'!$B40</f>
         <v>maize gluten meal</v>
       </c>
-      <c r="AU37" t="s">
+      <c r="AT37" t="s">
         <v>369</v>
       </c>
-      <c r="AW37" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV37" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>16.321839080459771</v>
       </c>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
       <c r="D38" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>75.5</v>
+        <v>16.1615368</v>
       </c>
       <c r="E38" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.1615368</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="F38" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>11.899999999999999</v>
+        <v>2.2080000000000002</v>
       </c>
       <c r="G38" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.2080000000000002</v>
+        <v>0.03</v>
       </c>
       <c r="H38" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.03</v>
-      </c>
-      <c r="I38" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>3.6500000000000004</v>
       </c>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28" t="str">
+      <c r="I38" s="28"/>
+      <c r="J38" s="28" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
-      <c r="L38" t="s">
+      <c r="K38" t="s">
         <v>19</v>
+      </c>
+      <c r="M38" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>12.4</v>
       </c>
       <c r="N38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>12.4</v>
+        <v>76</v>
       </c>
       <c r="O38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="P38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>3</v>
+        <v>14.1</v>
       </c>
       <c r="Q38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>14.1</v>
-      </c>
-      <c r="R38" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="T38" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="S38" s="28" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
-      <c r="U38" t="s">
+      <c r="T38" t="s">
         <v>376</v>
+      </c>
+      <c r="V38" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>12.4</v>
       </c>
       <c r="W38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="X38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>14.1</v>
-      </c>
-      <c r="Y38" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="AA38" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="28" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AA38" t="s">
         <v>372</v>
+      </c>
+      <c r="AC38" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>12.4</v>
       </c>
       <c r="AD38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="AE38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>14.1</v>
-      </c>
-      <c r="AF38" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="AH38" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="28" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
-      <c r="AI38" t="s">
+      <c r="AH38" t="s">
         <v>20</v>
       </c>
-      <c r="AJ38" s="37"/>
+      <c r="AI38" s="37"/>
+      <c r="AJ38" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>8.6999999999999993</v>
+      </c>
       <c r="AK38" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="AL38" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>13.1</v>
       </c>
-      <c r="AN38" s="28" t="str">
+      <c r="AM38" s="28" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
+      <c r="AN38" t="s">
+        <v>20</v>
+      </c>
       <c r="AO38" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP38" t="s">
         <v>289</v>
       </c>
-      <c r="AQ38" s="37">
+      <c r="AP38" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>9</v>
+      </c>
+      <c r="AQ38" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>9</v>
-      </c>
-      <c r="AR38" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT38" s="28" t="str">
+      <c r="AS38" s="28" t="str">
         <f>'feed pars'!$B41</f>
         <v>sugar beet molasses</v>
       </c>
-      <c r="AU38" t="s">
+      <c r="AT38" t="s">
         <v>369</v>
       </c>
-      <c r="AW38" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV38" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
       <c r="D39" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>89.5</v>
+        <v>17.334312000000001</v>
       </c>
       <c r="E39" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.334312000000001</v>
+        <v>7.1499999999999995</v>
       </c>
       <c r="F39" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>7.1499999999999995</v>
+        <v>1.448</v>
       </c>
       <c r="G39" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.448</v>
+        <v>0.1</v>
       </c>
       <c r="H39" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.1</v>
-      </c>
-      <c r="I39" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.48499999999999999</v>
       </c>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28" t="str">
+      <c r="I39" s="28"/>
+      <c r="J39" s="28" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
-      <c r="L39" t="s">
+      <c r="K39" t="s">
         <v>19</v>
+      </c>
+      <c r="M39" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>12.3</v>
       </c>
       <c r="N39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>12.3</v>
+        <v>107</v>
       </c>
       <c r="O39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>107</v>
+        <v>-96</v>
       </c>
       <c r="P39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-96</v>
+        <v>14.7</v>
       </c>
       <c r="Q39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>14.7</v>
-      </c>
-      <c r="R39" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>32</v>
       </c>
-      <c r="T39" s="28" t="str">
+      <c r="S39" s="28" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
-      <c r="U39" t="s">
+      <c r="T39" t="s">
         <v>376</v>
+      </c>
+      <c r="V39" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>12.3</v>
       </c>
       <c r="W39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>12.3</v>
+        <v>14.7</v>
       </c>
       <c r="X39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>14.7</v>
-      </c>
-      <c r="Y39" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>32</v>
       </c>
-      <c r="AA39" s="28" t="str">
+      <c r="Z39" s="28" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AA39" t="s">
         <v>372</v>
+      </c>
+      <c r="AC39" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>12.3</v>
       </c>
       <c r="AD39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>12.3</v>
+        <v>14.7</v>
       </c>
       <c r="AE39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>14.7</v>
-      </c>
-      <c r="AF39" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>32</v>
       </c>
-      <c r="AH39" s="28" t="str">
+      <c r="AG39" s="28" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
-      <c r="AI39" t="s">
+      <c r="AH39" t="s">
         <v>20</v>
       </c>
-      <c r="AJ39" s="37"/>
+      <c r="AI39" s="37"/>
+      <c r="AJ39" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>6.9</v>
+      </c>
       <c r="AK39" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>6.9</v>
-      </c>
-      <c r="AL39" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>12.2</v>
       </c>
-      <c r="AN39" s="28" t="str">
+      <c r="AM39" s="28" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
+      <c r="AN39" t="s">
+        <v>20</v>
+      </c>
       <c r="AO39" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP39" t="s">
         <v>289</v>
       </c>
-      <c r="AQ39" s="37">
+      <c r="AP39" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>8</v>
+      </c>
+      <c r="AQ39" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>8</v>
-      </c>
-      <c r="AR39" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT39" s="28" t="str">
+      <c r="AS39" s="28" t="str">
         <f>'feed pars'!$B42</f>
         <v>sugar beet pulp</v>
       </c>
-      <c r="AU39" t="s">
+      <c r="AT39" t="s">
         <v>369</v>
       </c>
-      <c r="AW39" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV39" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
       <c r="D40" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>6.25</v>
+        <v>16.464040000000001</v>
       </c>
       <c r="E40" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.464040000000001</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F40" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>9.3000000000000007</v>
+        <v>1.8800000000000001</v>
       </c>
       <c r="G40" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.8800000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H40" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.76</v>
-      </c>
-      <c r="I40" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.355</v>
       </c>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28" t="str">
+      <c r="I40" s="28"/>
+      <c r="J40" s="28" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
-      <c r="L40" t="s">
+      <c r="K40" t="s">
         <v>19</v>
+      </c>
+      <c r="M40" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.6</v>
       </c>
       <c r="N40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.6</v>
+        <v>82</v>
       </c>
       <c r="O40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>82</v>
+        <v>-18</v>
       </c>
       <c r="P40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-18</v>
+        <v>15.1</v>
       </c>
       <c r="Q40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15.1</v>
-      </c>
-      <c r="R40" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>10</v>
       </c>
-      <c r="T40" s="28" t="str">
+      <c r="S40" s="28" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
-      <c r="U40" t="s">
+      <c r="T40" t="s">
         <v>376</v>
+      </c>
+      <c r="V40" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.6</v>
       </c>
       <c r="W40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="X40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15.1</v>
-      </c>
-      <c r="Y40" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AA40" s="28" t="str">
+      <c r="Z40" s="28" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
-      <c r="AB40" t="s">
+      <c r="AA40" t="s">
         <v>372</v>
+      </c>
+      <c r="AC40" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.6</v>
       </c>
       <c r="AD40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="AE40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15.1</v>
-      </c>
-      <c r="AF40" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AH40" s="28" t="str">
+      <c r="AG40" s="28" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
-      <c r="AI40" t="s">
+      <c r="AH40" t="s">
         <v>20</v>
       </c>
-      <c r="AJ40" s="37"/>
+      <c r="AI40" s="37"/>
+      <c r="AJ40" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>12.4</v>
+      </c>
       <c r="AK40" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>12.4</v>
-      </c>
-      <c r="AL40" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>15.205346051464064</v>
       </c>
-      <c r="AN40" s="28" t="str">
+      <c r="AM40" s="28" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
+      <c r="AN40" t="s">
+        <v>20</v>
+      </c>
       <c r="AO40" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP40" t="s">
         <v>289</v>
       </c>
-      <c r="AQ40" s="37">
+      <c r="AP40" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>12.2</v>
+      </c>
+      <c r="AQ40" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>12.2</v>
-      </c>
-      <c r="AR40" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT40" s="28" t="str">
+      <c r="AS40" s="28" t="str">
         <f>'feed pars'!$B43</f>
         <v>whey</v>
       </c>
-      <c r="AU40" t="s">
+      <c r="AT40" t="s">
         <v>369</v>
       </c>
-      <c r="AW40" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV40" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
       <c r="D41" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>97</v>
+        <v>16.975324799999999</v>
       </c>
       <c r="E41" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>16.975324799999999</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>8.6</v>
+        <v>2.048</v>
       </c>
       <c r="G41" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>2.048</v>
+        <v>0.67999999999999994</v>
       </c>
       <c r="H41" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="I41" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.1</v>
       </c>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28" t="str">
+      <c r="I41" s="28"/>
+      <c r="J41" s="28" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
-      <c r="L41" t="s">
+      <c r="K41" t="s">
         <v>19</v>
       </c>
-      <c r="N41" s="28">
+      <c r="M41" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>12.3</v>
+      </c>
+      <c r="N41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>12.3</v>
+        <v>90</v>
       </c>
       <c r="O41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>90</v>
+        <v>-29</v>
       </c>
       <c r="P41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-29</v>
+        <v>15.4048817384</v>
       </c>
       <c r="Q41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>15.4048817384</v>
-      </c>
-      <c r="R41" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>13</v>
       </c>
-      <c r="T41" s="28" t="str">
+      <c r="S41" s="28" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
-      <c r="U41" t="s">
+      <c r="T41" t="s">
         <v>376</v>
+      </c>
+      <c r="V41" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>12.3</v>
       </c>
       <c r="W41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>12.3</v>
+        <v>15.4048817384</v>
       </c>
       <c r="X41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>15.4048817384</v>
-      </c>
-      <c r="Y41" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>13</v>
       </c>
-      <c r="AA41" s="28" t="str">
+      <c r="Z41" s="28" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AA41" t="s">
         <v>372</v>
+      </c>
+      <c r="AC41" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>12.3</v>
       </c>
       <c r="AD41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>12.3</v>
+        <v>15.4048817384</v>
       </c>
       <c r="AE41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>15.4048817384</v>
-      </c>
-      <c r="AF41" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>13</v>
       </c>
-      <c r="AH41" s="28" t="str">
+      <c r="AG41" s="28" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
-      <c r="AI41" t="s">
+      <c r="AH41" t="s">
         <v>20</v>
       </c>
-      <c r="AJ41" s="37"/>
+      <c r="AI41" s="37"/>
+      <c r="AJ41" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>12.4</v>
+      </c>
       <c r="AK41" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>12.4</v>
-      </c>
-      <c r="AL41" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>15.3</v>
       </c>
-      <c r="AN41" s="28" t="str">
+      <c r="AM41" s="28" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
+      <c r="AN41" t="s">
+        <v>20</v>
+      </c>
       <c r="AO41" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP41" t="s">
         <v>289</v>
       </c>
-      <c r="AQ41" s="37">
+      <c r="AP41" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>12.2</v>
+      </c>
+      <c r="AQ41" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>12.2</v>
-      </c>
-      <c r="AR41" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT41" s="28" t="str">
+      <c r="AS41" s="28" t="str">
         <f>'feed pars'!$B44</f>
         <v>whey powder</v>
       </c>
-      <c r="AU41" t="s">
+      <c r="AT41" t="s">
         <v>369</v>
       </c>
-      <c r="AW41" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV41" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
       <c r="D42" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>91</v>
+        <v>23.055932000000002</v>
       </c>
       <c r="E42" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>23.055932000000002</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="F42" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>2.8000000000000003</v>
+        <v>13.48</v>
       </c>
       <c r="G42" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>13.48</v>
+        <v>0.435</v>
       </c>
       <c r="H42" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.435</v>
-      </c>
-      <c r="I42" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>0.81499999999999995</v>
       </c>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28" t="str">
+      <c r="I42" s="28"/>
+      <c r="J42" s="28" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
-      <c r="L42" t="s">
+      <c r="K42" t="s">
         <v>19</v>
+      </c>
+      <c r="M42" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>15.5</v>
       </c>
       <c r="N42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>15.5</v>
+        <v>418</v>
       </c>
       <c r="O42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="P42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>323</v>
+        <v>19.7</v>
       </c>
       <c r="Q42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>19.7</v>
-      </c>
-      <c r="R42" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>33</v>
       </c>
-      <c r="T42" s="28" t="str">
+      <c r="S42" s="28" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
-      <c r="U42" t="s">
+      <c r="T42" t="s">
         <v>376</v>
+      </c>
+      <c r="V42" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>15.5</v>
       </c>
       <c r="W42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>15.5</v>
+        <v>19.7</v>
       </c>
       <c r="X42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>19.7</v>
-      </c>
-      <c r="Y42" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>33</v>
       </c>
-      <c r="AA42" s="28" t="str">
+      <c r="Z42" s="28" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AA42" t="s">
         <v>372</v>
+      </c>
+      <c r="AC42" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>15.5</v>
       </c>
       <c r="AD42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>15.5</v>
+        <v>19.7</v>
       </c>
       <c r="AE42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>19.7</v>
-      </c>
-      <c r="AF42" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>33</v>
       </c>
-      <c r="AH42" s="28" t="str">
+      <c r="AG42" s="28" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
-      <c r="AI42" t="s">
+      <c r="AH42" t="s">
         <v>20</v>
       </c>
-      <c r="AJ42" s="37"/>
+      <c r="AI42" s="37"/>
+      <c r="AJ42" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>11.1</v>
+      </c>
       <c r="AK42" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>11.1</v>
-      </c>
-      <c r="AL42" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>20.8</v>
       </c>
-      <c r="AN42" s="28" t="str">
+      <c r="AM42" s="28" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
+      <c r="AN42" t="s">
+        <v>20</v>
+      </c>
       <c r="AO42" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP42" t="s">
         <v>289</v>
       </c>
-      <c r="AQ42" s="37">
+      <c r="AP42" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>11.3</v>
+      </c>
+      <c r="AQ42" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>11.3</v>
-      </c>
-      <c r="AR42" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT42" s="28" t="str">
+      <c r="AS42" s="28" t="str">
         <f>'feed pars'!$B45</f>
         <v>potatoe protein</v>
       </c>
-      <c r="AU42" t="s">
+      <c r="AT42" t="s">
         <v>369</v>
       </c>
-      <c r="AW42" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AV42" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
       <c r="D43" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>23</v>
+        <v>17.035156000000001</v>
       </c>
       <c r="E43" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>17.035156000000001</v>
+        <v>5.5</v>
       </c>
       <c r="F43" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>5.5</v>
+        <v>1.44</v>
       </c>
       <c r="G43" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>1.44</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="H43" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="I43" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>2.1999999999999997</v>
       </c>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28" t="str">
+      <c r="I43" s="28"/>
+      <c r="J43" s="28" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
-      <c r="L43" s="37" t="s">
+      <c r="K43" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="M43" s="37"/>
-      <c r="N43" s="28">
+      <c r="L43" s="37"/>
+      <c r="M43" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>13.1</v>
+      </c>
+      <c r="N43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>13.1</v>
+        <v>92</v>
       </c>
       <c r="O43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>92</v>
+        <v>-70</v>
       </c>
       <c r="P43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>-70</v>
+        <v>14.9</v>
       </c>
       <c r="Q43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>14.9</v>
-      </c>
-      <c r="R43" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>10</v>
       </c>
-      <c r="S43" s="37"/>
-      <c r="T43" s="28" t="str">
+      <c r="R43" s="37"/>
+      <c r="S43" s="28" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
-      <c r="U43" s="37" t="s">
+      <c r="T43" s="37" t="s">
         <v>376</v>
       </c>
-      <c r="V43" s="37"/>
+      <c r="U43" s="37"/>
+      <c r="V43" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>13.1</v>
+      </c>
       <c r="W43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>13.1</v>
+        <v>14.9</v>
       </c>
       <c r="X43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>14.9</v>
-      </c>
-      <c r="Y43" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>10</v>
       </c>
-      <c r="Z43" s="37"/>
-      <c r="AA43" s="28" t="str">
+      <c r="Y43" s="37"/>
+      <c r="Z43" s="28" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
-      <c r="AB43" s="37" t="s">
+      <c r="AA43" s="37" t="s">
         <v>372</v>
       </c>
-      <c r="AC43" s="37"/>
+      <c r="AB43" s="37"/>
+      <c r="AC43" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>13.1</v>
+      </c>
       <c r="AD43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>13.1</v>
+        <v>14.9</v>
       </c>
       <c r="AE43" s="37">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>14.9</v>
-      </c>
-      <c r="AF43" s="37">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>10</v>
       </c>
-      <c r="AH43" s="28" t="str">
+      <c r="AG43" s="28" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
-      <c r="AI43" s="37" t="s">
+      <c r="AH43" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="AJ43" s="37"/>
+      <c r="AI43" s="37"/>
+      <c r="AJ43" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v/>
+      </c>
       <c r="AK43" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v/>
       </c>
-      <c r="AL43" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v/>
-      </c>
-      <c r="AM43" s="37"/>
-      <c r="AN43" s="28" t="str">
+      <c r="AL43" s="37"/>
+      <c r="AM43" s="28" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
+      <c r="AN43" s="37" t="s">
+        <v>20</v>
+      </c>
       <c r="AO43" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP43" s="37" t="s">
         <v>289</v>
+      </c>
+      <c r="AP43" s="37" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v/>
       </c>
       <c r="AQ43" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
         <v/>
       </c>
-      <c r="AR43" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
-        <v/>
-      </c>
-      <c r="AT43" s="28" t="str">
+      <c r="AS43" s="28" t="str">
         <f>'feed pars'!$B46</f>
         <v>potatoe offals</v>
       </c>
-      <c r="AU43" s="37" t="s">
+      <c r="AT43" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="AV43" s="37"/>
-      <c r="AW43" s="28" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AU43" s="37"/>
+      <c r="AV43" s="28" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
       <c r="D44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>92.05</v>
+        <v>22.254696000000003</v>
       </c>
       <c r="E44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>22.254696000000003</v>
+        <v>13.55</v>
       </c>
       <c r="F44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>13.55</v>
+        <v>12.112000000000002</v>
       </c>
       <c r="G44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v>12.112000000000002</v>
+        <v>2.3499999999999996</v>
       </c>
       <c r="H44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="I44" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
         <v>1.1950000000000001</v>
       </c>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28" t="str">
+      <c r="I44" s="28"/>
+      <c r="J44" s="28" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
-      <c r="L44" s="28" t="s">
+      <c r="K44" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="M44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>14.8</v>
+      </c>
       <c r="N44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v>14.8</v>
+        <v>51</v>
       </c>
       <c r="O44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="P44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
-        <v>154</v>
+        <v>21.750544919999999</v>
       </c>
       <c r="Q44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
-        <v>21.750544919999999</v>
-      </c>
-      <c r="R44" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
         <v>110</v>
       </c>
-      <c r="T44" s="28" t="str">
+      <c r="S44" s="28" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
-      <c r="U44" s="28" t="s">
+      <c r="T44" s="28" t="s">
         <v>376</v>
       </c>
-      <c r="V44" s="28"/>
+      <c r="U44" s="28"/>
+      <c r="V44" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>14.8</v>
+      </c>
       <c r="W44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
-        <v>14.8</v>
+        <v>21.750544919999999</v>
       </c>
       <c r="X44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
-        <v>21.750544919999999</v>
-      </c>
-      <c r="Y44" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
         <v>110</v>
       </c>
-      <c r="AA44" s="28" t="str">
+      <c r="Z44" s="28" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
-      <c r="AB44" s="28" t="s">
+      <c r="AA44" s="28" t="s">
         <v>372</v>
       </c>
-      <c r="AC44" s="28"/>
+      <c r="AB44" s="28"/>
+      <c r="AC44" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>14.8</v>
+      </c>
       <c r="AD44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
-        <v>14.8</v>
+        <v>21.750544919999999</v>
       </c>
       <c r="AE44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
-        <v>21.750544919999999</v>
-      </c>
-      <c r="AF44" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
         <v>110</v>
       </c>
-      <c r="AH44" s="28" t="str">
+      <c r="AG44" s="28" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
-      <c r="AI44" s="28" t="s">
+      <c r="AH44" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="AJ44" s="28"/>
+      <c r="AI44" s="28"/>
+      <c r="AJ44" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>10.8</v>
+      </c>
       <c r="AK44" s="28">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
-        <v>10.8</v>
-      </c>
-      <c r="AL44" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
         <v>19.5</v>
       </c>
-      <c r="AN44" s="28" t="str">
+      <c r="AM44" s="28" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
+      <c r="AN44" s="28" t="s">
+        <v>20</v>
+      </c>
       <c r="AO44" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP44" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="AQ44" s="37">
+      <c r="AP44" s="37">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>10.8</v>
+      </c>
+      <c r="AQ44" s="37" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>10.8</v>
-      </c>
-      <c r="AR44" s="37" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT44" s="28" t="str">
+      <c r="AS44" s="28" t="str">
         <f>'feed pars'!$B47</f>
         <v>fish meal</v>
       </c>
-      <c r="AU44" s="28" t="s">
+      <c r="AT44" s="28" t="s">
         <v>369</v>
       </c>
-      <c r="AV44" s="28"/>
-      <c r="AW44" s="28">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AU44" s="28"/>
+      <c r="AV44" s="28">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v>13.695652173913043</v>
       </c>
     </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" s="36" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
@@ -18726,15 +18548,15 @@
       <c r="C45" s="36"/>
       <c r="D45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),D$1)&lt;&gt;"",D$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),D$1), "")</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="57">
+        <v>100</v>
+      </c>
+      <c r="F45" s="57" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v>100</v>
+        <v/>
       </c>
       <c r="G45" s="57" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
@@ -18744,18 +18566,18 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
         <v/>
       </c>
-      <c r="I45" s="57" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),I$1)&lt;&gt;"",I$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),I$1), "")</f>
-        <v/>
-      </c>
-      <c r="K45" s="57" t="str">
+      <c r="J45" s="57" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
       </c>
-      <c r="L45" s="57" t="s">
+      <c r="K45" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="M45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="57">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
+        <v>0</v>
+      </c>
       <c r="N45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
         <v>0</v>
@@ -18772,18 +18594,18 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),Q$1)&lt;&gt;"",Q$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),Q$1), "")</f>
         <v>0</v>
       </c>
-      <c r="R45" s="57">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),R$1)&lt;&gt;"",R$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),R$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="T45" s="57" t="str">
+      <c r="S45" s="57" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
       </c>
-      <c r="U45" s="57" t="s">
+      <c r="T45" s="57" t="s">
         <v>376</v>
       </c>
-      <c r="V45" s="57"/>
+      <c r="U45" s="57"/>
+      <c r="V45" s="57">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),V$1)&lt;&gt;"",V$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),V$1), "")</f>
+        <v>0</v>
+      </c>
       <c r="W45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),W$1)&lt;&gt;"",W$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),W$1), "")</f>
         <v>0</v>
@@ -18792,18 +18614,18 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),X$1)&lt;&gt;"",X$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),X$1), "")</f>
         <v>0</v>
       </c>
-      <c r="Y45" s="57">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),Y$1)&lt;&gt;"",Y$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),Y$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="AA45" s="57" t="str">
+      <c r="Z45" s="57" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
       </c>
-      <c r="AB45" s="57" t="s">
+      <c r="AA45" s="57" t="s">
         <v>372</v>
       </c>
-      <c r="AC45" s="57"/>
+      <c r="AB45" s="57"/>
+      <c r="AC45" s="57">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AC$1)&lt;&gt;"",AC$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AC$1), "")</f>
+        <v>0</v>
+      </c>
       <c r="AD45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AD$1)&lt;&gt;"",AD$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AD$1), "")</f>
         <v>0</v>
@@ -18812,59 +18634,55 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AE$1)&lt;&gt;"",AE$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AE$1), "")</f>
         <v>0</v>
       </c>
-      <c r="AF45" s="57">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AF$1)&lt;&gt;"",AF$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AF$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="AH45" s="57" t="str">
+      <c r="AG45" s="57" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
       </c>
-      <c r="AI45" s="57" t="s">
+      <c r="AH45" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="AJ45" s="57"/>
+      <c r="AI45" s="57"/>
+      <c r="AJ45" s="57">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AJ$1)&lt;&gt;"",AJ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AJ$1), "")</f>
+        <v>0</v>
+      </c>
       <c r="AK45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AK$1)&lt;&gt;"",AK$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AK$1), "")</f>
         <v>0</v>
       </c>
-      <c r="AL45" s="57">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AL$1)&lt;&gt;"",AL$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AL$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="AN45" s="57" t="str">
+      <c r="AM45" s="57" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
       </c>
+      <c r="AN45" s="57" t="s">
+        <v>20</v>
+      </c>
       <c r="AO45" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP45" s="57" t="s">
         <v>289</v>
       </c>
-      <c r="AQ45" s="36">
+      <c r="AP45" s="36">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="36" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AQ$1)&lt;&gt;"",AQ$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AQ$1), "")</f>
-        <v>0</v>
-      </c>
-      <c r="AR45" s="36" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AR$1)&lt;&gt;"",AR$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AR$1), "")</f>
         <v/>
       </c>
-      <c r="AT45" s="57" t="str">
+      <c r="AS45" s="57" t="str">
         <f>'feed pars'!$B48</f>
         <v>minerals</v>
       </c>
-      <c r="AU45" s="57" t="s">
+      <c r="AT45" s="57" t="s">
         <v>369</v>
       </c>
-      <c r="AV45" s="57"/>
-      <c r="AW45" s="57" t="str">
-        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AW$1)&lt;&gt;"",AW$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AW$1), "")</f>
+      <c r="AU45" s="57"/>
+      <c r="AV45" s="57" t="str">
+        <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="AH46" s="28"/>
+    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AG46" s="28"/>
     </row>
   </sheetData>
   <sortState ref="A54:A96">

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="678">
   <si>
     <t>f_feed</t>
   </si>
@@ -2234,6 +2234,9 @@
   </si>
   <si>
     <t>FeedMgmt-feed_pars.csv</t>
+  </si>
+  <si>
+    <t>Around 4% P seems common in mineral feed</t>
   </si>
 </sst>
 </file>
@@ -2652,7 +2655,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2799,6 +2802,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -12315,9 +12319,18 @@
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="F48" s="82"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="84"/>
+      <c r="F48" s="82">
+        <f t="shared" ref="F48" si="63">AVERAGE(W48,AL48)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="83">
+        <f t="shared" ref="G48" si="64">AVERAGE(X48,AM48)</f>
+        <v>4</v>
+      </c>
+      <c r="H48" s="84">
+        <f t="shared" ref="H48" si="65">AVERAGE(Y48,AN48)</f>
+        <v>0</v>
+      </c>
       <c r="I48" s="85"/>
       <c r="J48" s="85"/>
       <c r="K48" s="20"/>
@@ -12343,15 +12356,27 @@
       <c r="S48" s="88">
         <v>0</v>
       </c>
-      <c r="T48" s="88"/>
-      <c r="U48" s="88"/>
+      <c r="T48" s="88">
+        <v>0</v>
+      </c>
+      <c r="U48" s="88">
+        <v>0</v>
+      </c>
       <c r="V48" s="89">
         <v>1000</v>
       </c>
-      <c r="W48" s="88"/>
-      <c r="X48" s="88"/>
-      <c r="Y48" s="89"/>
-      <c r="Z48" s="78"/>
+      <c r="W48" s="88">
+        <v>0</v>
+      </c>
+      <c r="X48" s="88">
+        <v>4</v>
+      </c>
+      <c r="Y48" s="89">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="118" t="s">
+        <v>677</v>
+      </c>
       <c r="AA48" s="73"/>
       <c r="AB48" s="20"/>
       <c r="AC48" s="86">
@@ -12369,9 +12394,15 @@
       <c r="AG48" s="87">
         <v>0</v>
       </c>
-      <c r="AH48" s="86"/>
-      <c r="AI48" s="87"/>
-      <c r="AJ48" s="88"/>
+      <c r="AH48" s="86">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="87">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="88">
+        <v>0</v>
+      </c>
       <c r="AK48" s="91">
         <v>1000</v>
       </c>
@@ -18554,17 +18585,17 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),E$1)&lt;&gt;"",E$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),E$1), "")</f>
         <v>100</v>
       </c>
-      <c r="F45" s="57" t="str">
+      <c r="F45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),F$1)&lt;&gt;"",F$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),F$1), "")</f>
-        <v/>
-      </c>
-      <c r="G45" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="G45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),G$1)&lt;&gt;"",G$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),G$1), "")</f>
-        <v/>
-      </c>
-      <c r="H45" s="57" t="str">
+        <v>4</v>
+      </c>
+      <c r="H45" s="57">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),H$1)&lt;&gt;"",H$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),H$1), "")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J45" s="57" t="str">
         <f>'feed pars'!$B48</f>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="9" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="horses" sheetId="7" r:id="rId8"/>
     <sheet name="poultry" sheetId="5" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="679">
   <si>
     <t>f_feed</t>
   </si>
@@ -2158,21 +2158,12 @@
     </r>
   </si>
   <si>
-    <t>Hessle &amp; Danielsson (2023)</t>
-  </si>
-  <si>
-    <t>Hessle, A. &amp; Danielsson, R. (2023) Number of cattle required to obtain good ecological status in Swedish grasslands and livestock’s methane emissions. Swedish University of Agricultural Sciences. Department of Animal Environment and Health. Section of Production systems</t>
-  </si>
-  <si>
     <t>Ahlgren, S., Behaderovic, D., Wirsenius, S., Carlsson, A., Hessle, A. Toräng, P., Seeman, A., den Braver, T. &amp;  et al. Kvarnbäck, O. (2022) Miljöpåverkan av svensk nöt- och lammköttsproduktion. RISE</t>
   </si>
   <si>
     <t>Ahlgren et al. (2022)</t>
   </si>
   <si>
-    <t>Suckler cows and all young animals</t>
-  </si>
-  <si>
     <t>Based on 4 weeks grazing for cows with dry period coinciding with grazing period</t>
   </si>
   <si>
@@ -2237,6 +2228,18 @@
   </si>
   <si>
     <t>Around 4% P seems common in mineral feed</t>
+  </si>
+  <si>
+    <t>Hessle, A. &amp; Danielsson, R. (2024). Cattle population required for favorable conservation status of management-dependent semi-natural grasslands and forests, and associated increase in enteric methane emissions. Journal for Nature Conservation, 78, 126571. https://doi.org/10.1016/j.jnc.2024.126571</t>
+  </si>
+  <si>
+    <t>Hessle &amp; Danielsson (2024)</t>
+  </si>
+  <si>
+    <t>calves, suckling</t>
+  </si>
+  <si>
+    <t>same as suckler cows</t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2467,6 +2470,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2655,7 +2665,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2803,6 +2813,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3106,12 +3117,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>652</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -3121,7 +3132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R153"/>
+  <dimension ref="A1:R156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -4292,6 +4303,12 @@
       <c r="A76" t="s">
         <v>19</v>
       </c>
+      <c r="B76" t="s">
+        <v>311</v>
+      </c>
+      <c r="E76" t="s">
+        <v>312</v>
+      </c>
       <c r="H76" t="s">
         <v>314</v>
       </c>
@@ -4302,16 +4319,16 @@
         <v>315</v>
       </c>
       <c r="N76" s="21">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="O76" t="s">
         <v>22</v>
       </c>
       <c r="P76" s="21" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="Q76" t="s">
-        <v>654</v>
+        <v>676</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -4319,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>311</v>
+        <v>600</v>
       </c>
       <c r="E77" t="s">
         <v>312</v>
@@ -4334,21 +4351,25 @@
         <v>315</v>
       </c>
       <c r="N77" s="21">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O77" t="s">
         <v>22</v>
       </c>
-      <c r="P77" s="21" t="s">
-        <v>656</v>
-      </c>
+      <c r="P77" s="21"/>
       <c r="Q77" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>372</v>
+        <v>19</v>
+      </c>
+      <c r="B78" t="s">
+        <v>600</v>
+      </c>
+      <c r="E78" t="s">
+        <v>677</v>
       </c>
       <c r="H78" t="s">
         <v>314</v>
@@ -4359,20 +4380,23 @@
       <c r="M78" t="s">
         <v>315</v>
       </c>
-      <c r="N78" s="21">
-        <v>14.5</v>
+      <c r="N78" s="119">
+        <f>N77</f>
+        <v>100</v>
       </c>
       <c r="O78" t="s">
         <v>22</v>
       </c>
-      <c r="P78" s="3"/>
+      <c r="P78" s="21" t="s">
+        <v>678</v>
+      </c>
       <c r="Q78" t="s">
-        <v>634</v>
+        <v>676</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="H79" t="s">
         <v>314</v>
@@ -4384,25 +4408,19 @@
         <v>315</v>
       </c>
       <c r="N79" s="21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O79" t="s">
         <v>22</v>
       </c>
-      <c r="P79" s="3"/>
+      <c r="P79" s="21"/>
       <c r="Q79" t="s">
-        <v>654</v>
+        <v>676</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>376</v>
-      </c>
-      <c r="D80" t="s">
-        <v>646</v>
-      </c>
-      <c r="E80" t="s">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="H80" t="s">
         <v>314</v>
@@ -4414,199 +4432,222 @@
         <v>315</v>
       </c>
       <c r="N80" s="21">
-        <v>69</v>
+        <v>14.5</v>
       </c>
       <c r="O80" t="s">
         <v>22</v>
       </c>
       <c r="P80" s="3"/>
       <c r="Q80" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N81" s="3"/>
+      <c r="A81" t="s">
+        <v>376</v>
+      </c>
+      <c r="H81" t="s">
+        <v>314</v>
+      </c>
+      <c r="I81" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" t="s">
+        <v>315</v>
+      </c>
+      <c r="N81" s="21">
+        <v>100</v>
+      </c>
+      <c r="O81" t="s">
+        <v>22</v>
+      </c>
       <c r="P81" s="3"/>
+      <c r="Q81" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
+        <v>376</v>
+      </c>
+      <c r="D82" t="s">
+        <v>646</v>
+      </c>
+      <c r="H82" t="s">
+        <v>314</v>
+      </c>
+      <c r="I82" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" t="s">
+        <v>315</v>
+      </c>
+      <c r="N82" s="21">
+        <v>66</v>
+      </c>
+      <c r="O82" t="s">
+        <v>22</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>376</v>
+      </c>
+      <c r="D83" t="s">
+        <v>646</v>
+      </c>
+      <c r="E83" t="s">
+        <v>480</v>
+      </c>
+      <c r="H83" t="s">
+        <v>314</v>
+      </c>
+      <c r="I83" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" t="s">
+        <v>315</v>
+      </c>
+      <c r="N83" s="21">
+        <v>69</v>
+      </c>
+      <c r="O83" t="s">
+        <v>22</v>
+      </c>
+      <c r="P83" s="3"/>
+      <c r="Q83" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N84" s="3"/>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M83" s="6" t="s">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M86" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="N83" s="6">
-        <v>0</v>
-      </c>
-      <c r="O83" s="6" t="s">
+      <c r="N86" s="6">
+        <v>0</v>
+      </c>
+      <c r="O86" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P83" s="6" t="s">
+      <c r="P86" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M84" s="6" t="s">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M87" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="N84" s="6">
-        <v>0</v>
-      </c>
-      <c r="O84" s="6" t="s">
+      <c r="N87" s="6">
+        <v>0</v>
+      </c>
+      <c r="O87" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P84" s="6" t="s">
+      <c r="P87" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>19</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B88" t="s">
         <v>311</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E88" t="s">
         <v>312</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G88" t="s">
         <v>627</v>
       </c>
-      <c r="M85" s="21" t="s">
+      <c r="M88" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="N85" s="21">
+      <c r="N88" s="21">
         <f>(0.8*20+0.2*2)</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="O85" s="21" t="s">
+      <c r="O88" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P85" s="21" t="s">
+      <c r="P88" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="Q88" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>19</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G89" t="s">
         <v>627</v>
       </c>
-      <c r="M86" s="21" t="s">
+      <c r="M89" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="N86" s="21">
+      <c r="N89" s="21">
         <f>(0.6*20+0.4*2)</f>
         <v>12.8</v>
       </c>
-      <c r="O86" s="21" t="s">
+      <c r="O89" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P86" s="21" t="s">
+      <c r="P89" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="Q86" t="s">
+      <c r="Q89" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>376</v>
-      </c>
-      <c r="G87" t="s">
-        <v>627</v>
-      </c>
-      <c r="M87" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="N87" s="21">
-        <v>2</v>
-      </c>
-      <c r="O87" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P87" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>372</v>
-      </c>
-      <c r="G88" t="s">
-        <v>627</v>
-      </c>
-      <c r="M88" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="N88" s="21">
-        <v>2</v>
-      </c>
-      <c r="O88" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P88" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M89" s="21"/>
-      <c r="N89" s="21"/>
-      <c r="O89" s="21"/>
-      <c r="P89" s="21"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>19</v>
-      </c>
-      <c r="B90" t="s">
-        <v>311</v>
-      </c>
-      <c r="E90" t="s">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="G90" t="s">
         <v>627</v>
       </c>
       <c r="M90" s="21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N90" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O90" s="21" t="s">
         <v>22</v>
       </c>
       <c r="P90" s="21" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q90" t="s">
         <v>634</v>
@@ -4614,114 +4655,124 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="G91" t="s">
         <v>627</v>
       </c>
       <c r="M91" s="21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N91" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O91" s="21" t="s">
         <v>22</v>
       </c>
       <c r="P91" s="21" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q91" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="M92" s="21"/>
+      <c r="N92" s="21"/>
+      <c r="O92" s="21"/>
+      <c r="P92" s="21"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>19</v>
       </c>
-      <c r="G92" t="s">
+      <c r="B93" t="s">
+        <v>311</v>
+      </c>
+      <c r="E93" t="s">
+        <v>312</v>
+      </c>
+      <c r="G93" t="s">
         <v>627</v>
       </c>
-      <c r="M92" s="21" t="s">
+      <c r="M93" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="N92" s="21">
+      <c r="N93" s="21">
+        <v>5</v>
+      </c>
+      <c r="O93" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P93" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" t="s">
+        <v>313</v>
+      </c>
+      <c r="G94" t="s">
+        <v>627</v>
+      </c>
+      <c r="M94" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N94" s="21">
+        <v>5</v>
+      </c>
+      <c r="O94" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P94" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" t="s">
+        <v>627</v>
+      </c>
+      <c r="M95" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N95" s="21">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="O92" s="21" t="s">
+      <c r="O95" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P92" s="21" t="s">
+      <c r="P95" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="Q95" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>376</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G96" t="s">
         <v>627</v>
       </c>
-      <c r="M93" s="21" t="s">
+      <c r="M96" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="N93" s="21">
+      <c r="N96" s="21">
         <v>15</v>
-      </c>
-      <c r="O93" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P93" s="21"/>
-      <c r="Q93" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>372</v>
-      </c>
-      <c r="G94" t="s">
-        <v>627</v>
-      </c>
-      <c r="M94" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N94" s="21">
-        <v>15</v>
-      </c>
-      <c r="O94" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P94" s="21"/>
-      <c r="Q94" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M95" s="21"/>
-      <c r="N95" s="21"/>
-      <c r="O95" s="21"/>
-      <c r="P95" s="21"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="22"/>
-      <c r="B96" s="22"/>
-      <c r="E96" s="22"/>
-      <c r="G96" t="s">
-        <v>299</v>
-      </c>
-      <c r="M96" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="N96" s="21">
-        <v>5</v>
       </c>
       <c r="O96" s="21" t="s">
         <v>22</v>
@@ -4732,125 +4783,85 @@
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" s="22" t="str">
-        <f>A90</f>
+      <c r="A97" t="s">
+        <v>372</v>
+      </c>
+      <c r="G97" t="s">
+        <v>627</v>
+      </c>
+      <c r="M97" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N97" s="21">
+        <v>15</v>
+      </c>
+      <c r="O97" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P97" s="21"/>
+      <c r="Q97" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M98" s="21"/>
+      <c r="N98" s="21"/>
+      <c r="O98" s="21"/>
+      <c r="P98" s="21"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="22"/>
+      <c r="B99" s="22"/>
+      <c r="E99" s="22"/>
+      <c r="G99" t="s">
+        <v>299</v>
+      </c>
+      <c r="M99" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="N99" s="21">
+        <v>5</v>
+      </c>
+      <c r="O99" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P99" s="21"/>
+      <c r="Q99" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="22" t="str">
+        <f>A93</f>
         <v>cattle</v>
       </c>
-      <c r="B97" s="22" t="str">
-        <f>B90</f>
+      <c r="B100" s="22" t="str">
+        <f>B93</f>
         <v>dairy</v>
       </c>
-      <c r="E97" s="22" t="str">
-        <f t="shared" ref="E97:E98" si="0">E90</f>
+      <c r="E100" s="22" t="str">
+        <f t="shared" ref="E100:E101" si="0">E93</f>
         <v>cows</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G100" t="s">
         <v>299</v>
       </c>
-      <c r="M97" s="22" t="str">
-        <f t="shared" ref="M97:Q101" si="1">M90</f>
+      <c r="M100" s="22" t="str">
+        <f t="shared" ref="M100:Q104" si="1">M93</f>
         <v>feeding_losses</v>
       </c>
-      <c r="N97" s="22">
+      <c r="N100" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
-      </c>
-      <c r="O97" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P97" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q97" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98" s="22" t="str">
-        <f t="shared" ref="A98:A101" si="2">A91</f>
-        <v>cattle</v>
-      </c>
-      <c r="E98" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>bulls</v>
-      </c>
-      <c r="G98" t="s">
-        <v>299</v>
-      </c>
-      <c r="M98" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N98" s="22">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="O98" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P98" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q98" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>cattle</v>
-      </c>
-      <c r="G99" t="s">
-        <v>299</v>
-      </c>
-      <c r="M99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N99" s="22">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="O99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="Q99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>sheep</v>
-      </c>
-      <c r="G100" t="s">
-        <v>299</v>
-      </c>
-      <c r="M100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N100" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
       </c>
       <c r="O100" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P100" s="22"/>
+      <c r="P100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q100" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
@@ -4858,8 +4869,12 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>horses</v>
+        <f t="shared" ref="A101:A104" si="2">A94</f>
+        <v>cattle</v>
+      </c>
+      <c r="E101" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>bulls</v>
       </c>
       <c r="G101" t="s">
         <v>299</v>
@@ -4870,173 +4885,173 @@
       </c>
       <c r="N101" s="22">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O101" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P101" s="22"/>
+      <c r="P101" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q101" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="22"/>
-      <c r="M102" s="22"/>
-      <c r="N102" s="22"/>
-      <c r="O102" s="22"/>
-      <c r="P102" s="22"/>
-      <c r="Q102" s="22"/>
+      <c r="A102" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>cattle</v>
+      </c>
+      <c r="G102" t="s">
+        <v>299</v>
+      </c>
+      <c r="M102" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N102" s="22">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O102" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P102" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="Q102" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>sheep</v>
+      </c>
       <c r="G103" t="s">
-        <v>628</v>
-      </c>
-      <c r="M103" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="N103" s="21">
-        <v>5</v>
-      </c>
-      <c r="O103" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P103" s="21"/>
-      <c r="Q103" t="s">
-        <v>634</v>
+        <v>299</v>
+      </c>
+      <c r="M103" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N103" s="22">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O103" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P103" s="22"/>
+      <c r="Q103" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="str">
-        <f>A90</f>
+        <f t="shared" si="2"/>
+        <v>horses</v>
+      </c>
+      <c r="G104" t="s">
+        <v>299</v>
+      </c>
+      <c r="M104" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N104" s="22">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O104" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P104" s="22"/>
+      <c r="Q104" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="22"/>
+      <c r="M105" s="22"/>
+      <c r="N105" s="22"/>
+      <c r="O105" s="22"/>
+      <c r="P105" s="22"/>
+      <c r="Q105" s="22"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G106" t="s">
+        <v>628</v>
+      </c>
+      <c r="M106" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="N106" s="21">
+        <v>5</v>
+      </c>
+      <c r="O106" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P106" s="21"/>
+      <c r="Q106" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="22" t="str">
+        <f>A93</f>
         <v>cattle</v>
       </c>
-      <c r="B104" s="22" t="str">
-        <f>B90</f>
+      <c r="B107" s="22" t="str">
+        <f>B93</f>
         <v>dairy</v>
       </c>
-      <c r="E104" s="22" t="str">
-        <f t="shared" ref="E104:E105" si="3">E90</f>
+      <c r="E107" s="22" t="str">
+        <f t="shared" ref="E107:E108" si="3">E93</f>
         <v>cows</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G107" t="s">
         <v>628</v>
       </c>
-      <c r="M104" s="22" t="str">
-        <f t="shared" ref="M104:Q108" si="4">M90</f>
+      <c r="M107" s="22" t="str">
+        <f t="shared" ref="M107:Q111" si="4">M93</f>
         <v>feeding_losses</v>
       </c>
-      <c r="N104" s="22">
+      <c r="N107" s="22">
         <f t="shared" si="4"/>
         <v>5</v>
-      </c>
-      <c r="O104" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P104" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q104" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105" s="22" t="str">
-        <f t="shared" ref="A105:A108" si="5">A91</f>
-        <v>cattle</v>
-      </c>
-      <c r="E105" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
-      </c>
-      <c r="G105" t="s">
-        <v>628</v>
-      </c>
-      <c r="M105" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N105" s="22">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O105" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P105" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q105" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>cattle</v>
-      </c>
-      <c r="G106" t="s">
-        <v>628</v>
-      </c>
-      <c r="M106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N106" s="22">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="O106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="P106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="Q106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>sheep</v>
-      </c>
-      <c r="G107" t="s">
-        <v>628</v>
-      </c>
-      <c r="M107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N107" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
       </c>
       <c r="O107" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P107" s="21"/>
+      <c r="P107" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q107" s="22" t="str">
-        <f t="shared" ref="Q107:Q108" si="6">Q93</f>
+        <f t="shared" si="4"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>horses</v>
+        <f t="shared" ref="A108:A111" si="5">A94</f>
+        <v>cattle</v>
+      </c>
+      <c r="E108" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
       </c>
       <c r="G108" t="s">
         <v>628</v>
@@ -5047,67 +5062,110 @@
       </c>
       <c r="N108" s="22">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O108" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="P108" s="21"/>
+      <c r="P108" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q108" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>cattle</v>
+      </c>
+      <c r="G109" t="s">
+        <v>628</v>
+      </c>
+      <c r="M109" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N109" s="22">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="O109" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P109" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="Q109" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>sheep</v>
+      </c>
+      <c r="G110" t="s">
+        <v>628</v>
+      </c>
+      <c r="M110" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N110" s="22">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="O110" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P110" s="21"/>
+      <c r="Q110" s="22" t="str">
+        <f t="shared" ref="Q110:Q111" si="6">Q96</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>horses</v>
+      </c>
+      <c r="G111" t="s">
+        <v>628</v>
+      </c>
+      <c r="M111" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N111" s="22">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="O111" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="P111" s="21"/>
+      <c r="Q111" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N109" s="3"/>
-      <c r="P109" s="21"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110" s="3"/>
-      <c r="G110" t="s">
-        <v>629</v>
-      </c>
-      <c r="M110" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="N110" s="21"/>
-      <c r="P110" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" s="3"/>
-      <c r="G111" t="s">
-        <v>629</v>
-      </c>
-      <c r="M111" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N111" s="21">
-        <v>2</v>
-      </c>
-      <c r="O111" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P111" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>633</v>
-      </c>
-    </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112" s="3"/>
-      <c r="M112" s="21"/>
-      <c r="N112" s="21"/>
-      <c r="O112" s="21"/>
-      <c r="P112" s="3"/>
+      <c r="N112" s="3"/>
+      <c r="P112" s="21"/>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="G113" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M113" s="21" t="s">
         <v>373</v>
@@ -5120,13 +5178,13 @@
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="G114" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M114" s="21" t="s">
         <v>374</v>
       </c>
       <c r="N114" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O114" s="21" t="s">
         <v>22</v>
@@ -5139,189 +5197,168 @@
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N115" s="3"/>
-      <c r="P115" s="21"/>
+      <c r="A115" s="3"/>
+      <c r="M115" s="21"/>
+      <c r="N115" s="21"/>
+      <c r="O115" s="21"/>
+      <c r="P115" s="3"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="3"/>
+      <c r="G116" t="s">
+        <v>630</v>
+      </c>
+      <c r="M116" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="N116" s="21"/>
+      <c r="P116" s="3" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+      <c r="G117" t="s">
+        <v>630</v>
+      </c>
+      <c r="M117" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="N117" s="21">
+        <v>3</v>
+      </c>
+      <c r="O117" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P117" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N118" s="3"/>
+      <c r="P118" s="21"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
-      <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" s="2"/>
-      <c r="Q116" s="2"/>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>19</v>
-      </c>
-      <c r="N117" s="21"/>
-      <c r="P117" s="21" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="21" t="s">
-        <v>481</v>
-      </c>
-      <c r="N118" s="21">
-        <v>6.7</v>
-      </c>
-      <c r="O118" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="P118" s="3"/>
-      <c r="Q118" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>372</v>
-      </c>
-      <c r="M119" t="s">
-        <v>483</v>
-      </c>
-      <c r="N119" s="21">
-        <v>18</v>
-      </c>
-      <c r="O119" t="s">
-        <v>484</v>
-      </c>
-      <c r="P119" s="3"/>
-      <c r="Q119" t="s">
-        <v>485</v>
-      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2"/>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" s="2"/>
+      <c r="Q119" s="2"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>20</v>
-      </c>
-      <c r="M120" t="s">
-        <v>483</v>
-      </c>
-      <c r="N120" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="O120" t="s">
-        <v>484</v>
-      </c>
-      <c r="P120" s="3"/>
-      <c r="Q120" t="s">
-        <v>485</v>
+        <v>19</v>
+      </c>
+      <c r="N120" s="21"/>
+      <c r="P120" s="21" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>369</v>
-      </c>
-      <c r="M121" t="s">
-        <v>483</v>
+      <c r="A121" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="21" t="s">
+        <v>481</v>
       </c>
       <c r="N121" s="21">
-        <v>0</v>
-      </c>
-      <c r="O121" t="s">
-        <v>484</v>
+        <v>6.7</v>
+      </c>
+      <c r="O121" s="21" t="s">
+        <v>482</v>
       </c>
       <c r="P121" s="3"/>
       <c r="Q121" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>372</v>
+      </c>
+      <c r="M122" t="s">
+        <v>483</v>
+      </c>
+      <c r="N122" s="21">
+        <v>18</v>
+      </c>
+      <c r="O122" t="s">
+        <v>484</v>
+      </c>
+      <c r="P122" s="3"/>
+      <c r="Q122" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N122" s="21"/>
-      <c r="P122" s="3"/>
-    </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>20</v>
+      </c>
       <c r="M123" t="s">
-        <v>597</v>
+        <v>483</v>
       </c>
       <c r="N123" s="21">
-        <v>1</v>
-      </c>
-      <c r="O123" s="21" t="s">
-        <v>598</v>
-      </c>
-      <c r="P123" s="21" t="s">
-        <v>599</v>
-      </c>
-      <c r="Q123" s="21"/>
+        <v>1.5</v>
+      </c>
+      <c r="O123" t="s">
+        <v>484</v>
+      </c>
+      <c r="P123" s="3"/>
+      <c r="Q123" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="M124" t="s">
-        <v>597</v>
+        <v>483</v>
       </c>
       <c r="N124" s="21">
-        <v>1</v>
-      </c>
-      <c r="O124" s="21" t="s">
-        <v>598</v>
-      </c>
-      <c r="P124" s="21"/>
-      <c r="Q124" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="O124" t="s">
+        <v>484</v>
+      </c>
+      <c r="P124" s="3"/>
+      <c r="Q124" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>19</v>
-      </c>
-      <c r="B125" t="s">
-        <v>311</v>
-      </c>
-      <c r="E125" t="s">
-        <v>312</v>
-      </c>
-      <c r="M125" t="s">
-        <v>597</v>
-      </c>
-      <c r="N125" s="21">
-        <v>1</v>
-      </c>
-      <c r="O125" s="21" t="s">
-        <v>598</v>
-      </c>
-      <c r="P125" s="21"/>
-      <c r="Q125" s="21"/>
+      <c r="N125" s="21"/>
+      <c r="P125" s="3"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>19</v>
-      </c>
-      <c r="B126" t="s">
-        <v>311</v>
-      </c>
-      <c r="E126" t="s">
-        <v>313</v>
-      </c>
       <c r="M126" t="s">
         <v>597</v>
       </c>
@@ -5331,19 +5368,15 @@
       <c r="O126" s="21" t="s">
         <v>598</v>
       </c>
-      <c r="P126" s="21"/>
+      <c r="P126" s="21" t="s">
+        <v>599</v>
+      </c>
       <c r="Q126" s="21"/>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>19</v>
       </c>
-      <c r="B127" t="s">
-        <v>600</v>
-      </c>
-      <c r="E127" t="s">
-        <v>313</v>
-      </c>
       <c r="M127" t="s">
         <v>597</v>
       </c>
@@ -5357,102 +5390,97 @@
       <c r="Q127" s="21"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N128" s="3"/>
-      <c r="P128" s="3"/>
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" t="s">
+        <v>311</v>
+      </c>
+      <c r="E128" t="s">
+        <v>312</v>
+      </c>
+      <c r="M128" t="s">
+        <v>597</v>
+      </c>
+      <c r="N128" s="21">
+        <v>1</v>
+      </c>
+      <c r="O128" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="P128" s="21"/>
+      <c r="Q128" s="21"/>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129" s="106" t="s">
-        <v>659</v>
-      </c>
-      <c r="B129" s="106"/>
-      <c r="C129" s="106"/>
-      <c r="D129" s="106"/>
-      <c r="E129" s="107"/>
-      <c r="F129" s="107"/>
-      <c r="G129" s="107"/>
-      <c r="H129" s="107"/>
-      <c r="I129" s="107"/>
-      <c r="J129" s="107"/>
-      <c r="K129" s="107"/>
-      <c r="L129" s="107"/>
-      <c r="M129" s="107"/>
-      <c r="N129" s="107"/>
-      <c r="O129" s="107"/>
-      <c r="P129" s="107" t="s">
+      <c r="A129" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" t="s">
+        <v>311</v>
+      </c>
+      <c r="E129" t="s">
+        <v>313</v>
+      </c>
+      <c r="M129" t="s">
+        <v>597</v>
+      </c>
+      <c r="N129" s="21">
+        <v>1</v>
+      </c>
+      <c r="O129" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="P129" s="21"/>
+      <c r="Q129" s="21"/>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130" t="s">
+        <v>600</v>
+      </c>
+      <c r="E130" t="s">
+        <v>313</v>
+      </c>
+      <c r="M130" t="s">
+        <v>597</v>
+      </c>
+      <c r="N130" s="21">
+        <v>1</v>
+      </c>
+      <c r="O130" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="P130" s="21"/>
+      <c r="Q130" s="21"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N131" s="3"/>
+      <c r="P131" s="3"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132" s="106" t="s">
+        <v>656</v>
+      </c>
+      <c r="B132" s="106"/>
+      <c r="C132" s="106"/>
+      <c r="D132" s="106"/>
+      <c r="E132" s="107"/>
+      <c r="F132" s="107"/>
+      <c r="G132" s="107"/>
+      <c r="H132" s="107"/>
+      <c r="I132" s="107"/>
+      <c r="J132" s="107"/>
+      <c r="K132" s="107"/>
+      <c r="L132" s="107"/>
+      <c r="M132" s="107"/>
+      <c r="N132" s="107"/>
+      <c r="O132" s="107"/>
+      <c r="P132" s="107" t="s">
         <v>291</v>
       </c>
-      <c r="Q129" s="107"/>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="109"/>
-      <c r="B130" s="109"/>
-      <c r="C130" s="109"/>
-      <c r="D130" s="109"/>
-      <c r="E130" s="109"/>
-      <c r="F130" s="109"/>
-      <c r="G130" s="109"/>
-      <c r="H130" s="109"/>
-      <c r="I130" s="109"/>
-      <c r="J130" s="109"/>
-      <c r="K130" s="109"/>
-      <c r="L130" s="110" t="s">
-        <v>612</v>
-      </c>
-      <c r="M130" s="109"/>
-      <c r="N130" s="109"/>
-      <c r="O130" s="109"/>
-      <c r="P130" s="109"/>
-      <c r="Q130" s="109"/>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131" s="109"/>
-      <c r="B131" s="109"/>
-      <c r="C131" s="109"/>
-      <c r="D131" s="109"/>
-      <c r="E131" s="109"/>
-      <c r="F131" s="109"/>
-      <c r="G131" s="109"/>
-      <c r="H131" s="109"/>
-      <c r="I131" s="109"/>
-      <c r="J131" s="109"/>
-      <c r="K131" s="109"/>
-      <c r="L131" s="109"/>
-      <c r="M131" s="109" t="s">
-        <v>370</v>
-      </c>
-      <c r="N131" s="111" t="s">
-        <v>609</v>
-      </c>
-      <c r="O131" s="109" t="s">
-        <v>593</v>
-      </c>
-      <c r="P131" s="112"/>
-      <c r="Q131" s="109"/>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132" s="109"/>
-      <c r="B132" s="109"/>
-      <c r="C132" s="109"/>
-      <c r="D132" s="109"/>
-      <c r="E132" s="109"/>
-      <c r="F132" s="109"/>
-      <c r="G132" s="109"/>
-      <c r="H132" s="109"/>
-      <c r="I132" s="109"/>
-      <c r="J132" s="109"/>
-      <c r="K132" s="109"/>
-      <c r="L132" s="109"/>
-      <c r="M132" s="109" t="s">
-        <v>471</v>
-      </c>
-      <c r="N132" s="111" t="s">
-        <v>609</v>
-      </c>
-      <c r="O132" s="109" t="s">
-        <v>592</v>
-      </c>
-      <c r="P132" s="112"/>
-      <c r="Q132" s="109"/>
+      <c r="Q132" s="107"/>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="109"/>
@@ -5466,13 +5494,11 @@
       <c r="I133" s="109"/>
       <c r="J133" s="109"/>
       <c r="K133" s="109"/>
-      <c r="L133" s="109"/>
-      <c r="M133" s="113" t="s">
-        <v>603</v>
-      </c>
-      <c r="N133" s="111" t="s">
-        <v>609</v>
-      </c>
+      <c r="L133" s="110" t="s">
+        <v>612</v>
+      </c>
+      <c r="M133" s="109"/>
+      <c r="N133" s="109"/>
       <c r="O133" s="109"/>
       <c r="P133" s="109"/>
       <c r="Q133" s="109"/>
@@ -5490,14 +5516,16 @@
       <c r="J134" s="109"/>
       <c r="K134" s="109"/>
       <c r="L134" s="109"/>
-      <c r="M134" s="113" t="s">
-        <v>604</v>
+      <c r="M134" s="109" t="s">
+        <v>370</v>
       </c>
       <c r="N134" s="111" t="s">
         <v>609</v>
       </c>
-      <c r="O134" s="109"/>
-      <c r="P134" s="109"/>
+      <c r="O134" s="109" t="s">
+        <v>593</v>
+      </c>
+      <c r="P134" s="112"/>
       <c r="Q134" s="109"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -5513,14 +5541,16 @@
       <c r="J135" s="109"/>
       <c r="K135" s="109"/>
       <c r="L135" s="109"/>
-      <c r="M135" s="113" t="s">
-        <v>605</v>
+      <c r="M135" s="109" t="s">
+        <v>471</v>
       </c>
       <c r="N135" s="111" t="s">
         <v>609</v>
       </c>
-      <c r="O135" s="109"/>
-      <c r="P135" s="109"/>
+      <c r="O135" s="109" t="s">
+        <v>592</v>
+      </c>
+      <c r="P135" s="112"/>
       <c r="Q135" s="109"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -5537,13 +5567,13 @@
       <c r="K136" s="109"/>
       <c r="L136" s="109"/>
       <c r="M136" s="113" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="N136" s="111" t="s">
         <v>609</v>
       </c>
       <c r="O136" s="109"/>
-      <c r="P136" s="112"/>
+      <c r="P136" s="109"/>
       <c r="Q136" s="109"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -5558,11 +5588,13 @@
       <c r="I137" s="109"/>
       <c r="J137" s="109"/>
       <c r="K137" s="109"/>
-      <c r="L137" s="110" t="s">
-        <v>611</v>
-      </c>
-      <c r="M137" s="109"/>
-      <c r="N137" s="109"/>
+      <c r="L137" s="109"/>
+      <c r="M137" s="113" t="s">
+        <v>604</v>
+      </c>
+      <c r="N137" s="111" t="s">
+        <v>609</v>
+      </c>
       <c r="O137" s="109"/>
       <c r="P137" s="109"/>
       <c r="Q137" s="109"/>
@@ -5580,18 +5612,14 @@
       <c r="J138" s="109"/>
       <c r="K138" s="109"/>
       <c r="L138" s="109"/>
-      <c r="M138" s="109" t="s">
-        <v>17</v>
+      <c r="M138" s="113" t="s">
+        <v>605</v>
       </c>
       <c r="N138" s="111" t="s">
-        <v>610</v>
-      </c>
-      <c r="O138" s="109" t="s">
-        <v>617</v>
-      </c>
-      <c r="P138" s="111" t="s">
-        <v>590</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="O138" s="109"/>
+      <c r="P138" s="109"/>
       <c r="Q138" s="109"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -5607,15 +5635,13 @@
       <c r="J139" s="109"/>
       <c r="K139" s="109"/>
       <c r="L139" s="109"/>
-      <c r="M139" s="109" t="s">
-        <v>583</v>
+      <c r="M139" s="113" t="s">
+        <v>606</v>
       </c>
       <c r="N139" s="111" t="s">
-        <v>610</v>
-      </c>
-      <c r="O139" s="109" t="s">
-        <v>591</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="O139" s="109"/>
       <c r="P139" s="112"/>
       <c r="Q139" s="109"/>
     </row>
@@ -5631,19 +5657,13 @@
       <c r="I140" s="109"/>
       <c r="J140" s="109"/>
       <c r="K140" s="109"/>
-      <c r="L140" s="109"/>
-      <c r="M140" s="109" t="s">
-        <v>472</v>
-      </c>
-      <c r="N140" s="111" t="s">
-        <v>610</v>
-      </c>
-      <c r="O140" s="109" t="s">
-        <v>473</v>
-      </c>
-      <c r="P140" s="111" t="s">
-        <v>474</v>
-      </c>
+      <c r="L140" s="110" t="s">
+        <v>611</v>
+      </c>
+      <c r="M140" s="109"/>
+      <c r="N140" s="109"/>
+      <c r="O140" s="109"/>
+      <c r="P140" s="109"/>
       <c r="Q140" s="109"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -5658,13 +5678,19 @@
       <c r="I141" s="109"/>
       <c r="J141" s="109"/>
       <c r="K141" s="109"/>
-      <c r="L141" s="110" t="s">
-        <v>613</v>
-      </c>
-      <c r="M141" s="109"/>
-      <c r="N141" s="109"/>
-      <c r="O141" s="109"/>
-      <c r="P141" s="109"/>
+      <c r="L141" s="109"/>
+      <c r="M141" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" s="111" t="s">
+        <v>610</v>
+      </c>
+      <c r="O141" s="109" t="s">
+        <v>617</v>
+      </c>
+      <c r="P141" s="111" t="s">
+        <v>590</v>
+      </c>
       <c r="Q141" s="109"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -5681,17 +5707,15 @@
       <c r="K142" s="109"/>
       <c r="L142" s="109"/>
       <c r="M142" s="109" t="s">
-        <v>17</v>
+        <v>583</v>
       </c>
       <c r="N142" s="111" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="O142" s="109" t="s">
-        <v>617</v>
-      </c>
-      <c r="P142" s="111" t="s">
-        <v>590</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="P142" s="112"/>
       <c r="Q142" s="109"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -5708,15 +5732,17 @@
       <c r="K143" s="109"/>
       <c r="L143" s="109"/>
       <c r="M143" s="109" t="s">
-        <v>583</v>
+        <v>472</v>
       </c>
       <c r="N143" s="111" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="O143" s="109" t="s">
-        <v>591</v>
-      </c>
-      <c r="P143" s="112"/>
+        <v>473</v>
+      </c>
+      <c r="P143" s="111" t="s">
+        <v>474</v>
+      </c>
       <c r="Q143" s="109"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -5732,7 +5758,7 @@
       <c r="J144" s="109"/>
       <c r="K144" s="109"/>
       <c r="L144" s="110" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M144" s="109"/>
       <c r="N144" s="109"/>
@@ -5757,7 +5783,7 @@
         <v>17</v>
       </c>
       <c r="N145" s="111" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="O145" s="109" t="s">
         <v>617</v>
@@ -5784,7 +5810,7 @@
         <v>583</v>
       </c>
       <c r="N146" s="111" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="O146" s="109" t="s">
         <v>591</v>
@@ -5805,7 +5831,7 @@
       <c r="J147" s="109"/>
       <c r="K147" s="109"/>
       <c r="L147" s="110" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M147" s="109"/>
       <c r="N147" s="109"/>
@@ -5830,10 +5856,10 @@
         <v>17</v>
       </c>
       <c r="N148" s="111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="O148" s="109" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="P148" s="111" t="s">
         <v>590</v>
@@ -5857,7 +5883,7 @@
         <v>583</v>
       </c>
       <c r="N149" s="111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="O149" s="109" t="s">
         <v>591</v>
@@ -5878,7 +5904,7 @@
       <c r="J150" s="109"/>
       <c r="K150" s="109"/>
       <c r="L150" s="110" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M150" s="109"/>
       <c r="N150" s="109"/>
@@ -5900,23 +5926,96 @@
       <c r="K151" s="109"/>
       <c r="L151" s="109"/>
       <c r="M151" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" s="111" t="s">
+        <v>622</v>
+      </c>
+      <c r="O151" s="109" t="s">
+        <v>618</v>
+      </c>
+      <c r="P151" s="111" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q151" s="109"/>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152" s="109"/>
+      <c r="B152" s="109"/>
+      <c r="C152" s="109"/>
+      <c r="D152" s="109"/>
+      <c r="E152" s="109"/>
+      <c r="F152" s="109"/>
+      <c r="G152" s="109"/>
+      <c r="H152" s="109"/>
+      <c r="I152" s="109"/>
+      <c r="J152" s="109"/>
+      <c r="K152" s="109"/>
+      <c r="L152" s="109"/>
+      <c r="M152" s="109" t="s">
+        <v>583</v>
+      </c>
+      <c r="N152" s="111" t="s">
+        <v>622</v>
+      </c>
+      <c r="O152" s="109" t="s">
+        <v>591</v>
+      </c>
+      <c r="P152" s="112"/>
+      <c r="Q152" s="109"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153" s="109"/>
+      <c r="B153" s="109"/>
+      <c r="C153" s="109"/>
+      <c r="D153" s="109"/>
+      <c r="E153" s="109"/>
+      <c r="F153" s="109"/>
+      <c r="G153" s="109"/>
+      <c r="H153" s="109"/>
+      <c r="I153" s="109"/>
+      <c r="J153" s="109"/>
+      <c r="K153" s="109"/>
+      <c r="L153" s="110" t="s">
+        <v>616</v>
+      </c>
+      <c r="M153" s="109"/>
+      <c r="N153" s="109"/>
+      <c r="O153" s="109"/>
+      <c r="P153" s="109"/>
+      <c r="Q153" s="109"/>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154" s="109"/>
+      <c r="B154" s="109"/>
+      <c r="C154" s="109"/>
+      <c r="D154" s="109"/>
+      <c r="E154" s="109"/>
+      <c r="F154" s="109"/>
+      <c r="G154" s="109"/>
+      <c r="H154" s="109"/>
+      <c r="I154" s="109"/>
+      <c r="J154" s="109"/>
+      <c r="K154" s="109"/>
+      <c r="L154" s="109"/>
+      <c r="M154" s="109" t="s">
         <v>608</v>
       </c>
-      <c r="N151" s="111" t="s">
+      <c r="N154" s="111" t="s">
         <v>623</v>
       </c>
-      <c r="O151" s="109" t="s">
+      <c r="O154" s="109" t="s">
         <v>619</v>
       </c>
-      <c r="P151" s="111"/>
-      <c r="Q151" s="109"/>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M153" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="N153" s="108" t="s">
-        <v>676</v>
+      <c r="P154" s="111"/>
+      <c r="Q154" s="109"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M156" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="N156" s="108" t="s">
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -7810,7 +7909,7 @@
       </c>
       <c r="AO16" s="77"/>
       <c r="AP16" s="74" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="AQ16" t="s">
         <v>465</v>
@@ -12375,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="118" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AA48" s="73"/>
       <c r="AB48" s="20"/>
@@ -12430,7 +12529,7 @@
       <c r="J50" s="65"/>
       <c r="K50" s="66"/>
       <c r="O50" s="115" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="51" spans="4:19" x14ac:dyDescent="0.25">
@@ -12454,7 +12553,7 @@
         <v>29</v>
       </c>
       <c r="R51" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="S51" t="s">
         <v>41</v>
@@ -12504,7 +12603,7 @@
       <c r="J53" s="36"/>
       <c r="K53" s="39"/>
       <c r="O53" s="115" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="54" spans="4:19" x14ac:dyDescent="0.25">
@@ -12695,19 +12794,19 @@
         <v>15</v>
       </c>
       <c r="D2" s="36" t="s">
+        <v>660</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>661</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>662</v>
+      </c>
+      <c r="G2" s="36" t="s">
         <v>663</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="H2" s="36" t="s">
         <v>664</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>665</v>
-      </c>
-      <c r="G2" s="36" t="s">
-        <v>666</v>
-      </c>
-      <c r="H2" s="36" t="s">
-        <v>667</v>
       </c>
       <c r="I2" s="37"/>
       <c r="J2" s="36" t="s">
@@ -12720,19 +12819,19 @@
         <v>15</v>
       </c>
       <c r="M2" s="36" t="s">
+        <v>665</v>
+      </c>
+      <c r="N2" s="36" t="s">
+        <v>666</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>667</v>
+      </c>
+      <c r="P2" s="36" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q2" s="36" t="s">
         <v>668</v>
-      </c>
-      <c r="N2" s="36" t="s">
-        <v>669</v>
-      </c>
-      <c r="O2" s="36" t="s">
-        <v>670</v>
-      </c>
-      <c r="P2" s="36" t="s">
-        <v>673</v>
-      </c>
-      <c r="Q2" s="36" t="s">
-        <v>671</v>
       </c>
       <c r="S2" s="36" t="s">
         <v>0</v>
@@ -12744,13 +12843,13 @@
         <v>15</v>
       </c>
       <c r="V2" s="36" t="s">
+        <v>665</v>
+      </c>
+      <c r="W2" s="36" t="s">
+        <v>670</v>
+      </c>
+      <c r="X2" s="36" t="s">
         <v>668</v>
-      </c>
-      <c r="W2" s="36" t="s">
-        <v>673</v>
-      </c>
-      <c r="X2" s="36" t="s">
-        <v>671</v>
       </c>
       <c r="Z2" s="36" t="s">
         <v>0</v>
@@ -12762,13 +12861,13 @@
         <v>15</v>
       </c>
       <c r="AC2" s="36" t="s">
+        <v>665</v>
+      </c>
+      <c r="AD2" s="36" t="s">
+        <v>670</v>
+      </c>
+      <c r="AE2" s="36" t="s">
         <v>668</v>
-      </c>
-      <c r="AD2" s="36" t="s">
-        <v>673</v>
-      </c>
-      <c r="AE2" s="36" t="s">
-        <v>671</v>
       </c>
       <c r="AG2" s="36" t="s">
         <v>0</v>
@@ -12780,10 +12879,10 @@
         <v>15</v>
       </c>
       <c r="AJ2" s="36" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="AK2" s="36" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="AM2" s="36" t="s">
         <v>0</v>
@@ -12795,10 +12894,10 @@
         <v>15</v>
       </c>
       <c r="AP2" s="36" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="AQ2" s="36" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="AS2" s="36" t="s">
         <v>0</v>
@@ -12810,7 +12909,7 @@
         <v>15</v>
       </c>
       <c r="AV2" s="101" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.25">

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="681">
   <si>
     <t>Statistics Netherlands (2012) Standardised calculation methods for animal manure and nutrients. Standard data 1990–2008</t>
   </si>
@@ -2267,9 +2267,6 @@
   </si>
   <si>
     <t>organic</t>
-  </si>
-  <si>
-    <t>&lt;-- BORDE INTE BEHÖVAS!</t>
   </si>
   <si>
     <t>No domestic organic sugar production</t>
@@ -3138,7 +3135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R175"/>
+  <dimension ref="A1:R173"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" style="1" customWidth="1"/>
@@ -4294,20 +4291,18 @@
       <c r="H75"/>
       <c r="I75"/>
       <c r="J75" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N75" s="10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O75" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P75" s="10" t="s">
-        <v>680</v>
-      </c>
+      <c r="P75" s="10"/>
       <c r="Q75"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -4315,8 +4310,18 @@
       <c r="G76"/>
       <c r="H76"/>
       <c r="I76"/>
-      <c r="J76"/>
-      <c r="N76" s="10"/>
+      <c r="J76" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N76" s="10">
+        <v>42</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P76" s="10"/>
       <c r="Q76"/>
     </row>
@@ -4325,14 +4330,14 @@
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
-      <c r="J77" t="s">
-        <v>60</v>
+      <c r="J77" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N77" s="10">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O77" s="1" t="s">
         <v>82</v>
@@ -4346,13 +4351,13 @@
       <c r="H78"/>
       <c r="I78"/>
       <c r="J78" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N78" s="10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>82</v>
@@ -4366,7 +4371,7 @@
       <c r="H79"/>
       <c r="I79"/>
       <c r="J79" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>88</v>
@@ -4386,7 +4391,7 @@
       <c r="H80"/>
       <c r="I80"/>
       <c r="J80" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>88</v>
@@ -4406,7 +4411,7 @@
       <c r="H81"/>
       <c r="I81"/>
       <c r="J81" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>88</v>
@@ -4426,7 +4431,7 @@
       <c r="H82"/>
       <c r="I82"/>
       <c r="J82" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>88</v>
@@ -4441,38 +4446,22 @@
       <c r="Q82"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
-      <c r="I83"/>
-      <c r="J83" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N83" s="10">
-        <v>0</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N83" s="10"/>
       <c r="P83" s="10"/>
       <c r="Q83"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
-      <c r="J84" s="1" t="s">
-        <v>76</v>
+      <c r="C84" t="s">
+        <v>679</v>
+      </c>
+      <c r="J84" t="s">
+        <v>60</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N84" s="10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>82</v>
@@ -4481,22 +4470,35 @@
       <c r="Q84"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N85" s="10"/>
+      <c r="C85" t="s">
+        <v>679</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N85" s="10">
+        <v>4</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P85" s="10"/>
-      <c r="Q85"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>679</v>
       </c>
       <c r="J86" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N86" s="10">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>82</v>
@@ -4508,45 +4510,46 @@
       <c r="C87" t="s">
         <v>679</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>54</v>
+      <c r="J87" t="s">
+        <v>70</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N87" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P87" s="10"/>
+      <c r="P87" s="10" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>679</v>
       </c>
       <c r="J88" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N88" s="10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P88" s="10"/>
-      <c r="Q88"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>679</v>
       </c>
-      <c r="J89" t="s">
-        <v>70</v>
+      <c r="J89" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>88</v>
@@ -4557,80 +4560,104 @@
       <c r="O89" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P89" s="10" t="s">
-        <v>681</v>
-      </c>
+      <c r="P89" s="10"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C90" t="s">
-        <v>679</v>
-      </c>
-      <c r="J90" t="s">
-        <v>71</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N90" s="10">
-        <v>0</v>
-      </c>
-      <c r="O90" s="1" t="s">
+      <c r="N90" s="10"/>
+      <c r="P90" s="10"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N93" s="12">
+        <v>28</v>
+      </c>
+      <c r="O93" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P90" s="10"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C91" t="s">
-        <v>679</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N91" s="10">
-        <v>0</v>
-      </c>
-      <c r="O91" s="1" t="s">
+      <c r="P93" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N94" s="12">
+        <v>100</v>
+      </c>
+      <c r="O94" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P91" s="10"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N92" s="10"/>
-      <c r="P92" s="10"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
+      <c r="P94" s="12"/>
+      <c r="Q94" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>95</v>
@@ -4641,14 +4668,15 @@
       <c r="M95" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N95" s="12">
-        <v>28</v>
+      <c r="N95" s="14">
+        <f>N94</f>
+        <v>100</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P95" s="12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="Q95" s="1" t="s">
         <v>98</v>
@@ -4658,12 +4686,6 @@
       <c r="A96" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="H96" s="1" t="s">
         <v>95</v>
       </c>
@@ -4674,7 +4696,7 @@
         <v>96</v>
       </c>
       <c r="N96" s="12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>82</v>
@@ -4686,13 +4708,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>95</v>
@@ -4703,23 +4719,20 @@
       <c r="M97" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N97" s="14">
-        <f>N96</f>
-        <v>100</v>
+      <c r="N97" s="12">
+        <v>14.5</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P97" s="12" t="s">
-        <v>101</v>
-      </c>
+      <c r="P97" s="10"/>
       <c r="Q97" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>95</v>
@@ -4731,19 +4744,22 @@
         <v>96</v>
       </c>
       <c r="N98" s="12">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P98" s="12"/>
+      <c r="P98" s="10"/>
       <c r="Q98" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>95</v>
@@ -4755,20 +4771,26 @@
         <v>96</v>
       </c>
       <c r="N99" s="12">
-        <v>14.5</v>
+        <v>66</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P99" s="10"/>
       <c r="Q99" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="D100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="H100" s="1" t="s">
         <v>95</v>
       </c>
@@ -4779,7 +4801,7 @@
         <v>96</v>
       </c>
       <c r="N100" s="12">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>82</v>
@@ -4790,124 +4812,115 @@
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M101" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N101" s="12">
-        <v>66</v>
-      </c>
-      <c r="O101" s="1" t="s">
+      <c r="N101" s="10"/>
+      <c r="P101" s="10"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M103" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="N103" s="6">
+        <v>0</v>
+      </c>
+      <c r="O103" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P101" s="10"/>
-      <c r="Q101" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N102" s="12">
-        <v>69</v>
-      </c>
-      <c r="O102" s="1" t="s">
+      <c r="P103" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M104" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="N104" s="6">
+        <v>0</v>
+      </c>
+      <c r="O104" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P102" s="10"/>
-      <c r="Q102" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N103" s="10"/>
-      <c r="P103" s="10"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
+      <c r="P104" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M105" s="6" t="s">
+      <c r="A105" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M105" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="N105" s="6">
-        <v>0</v>
-      </c>
-      <c r="O105" s="6" t="s">
+      <c r="N105" s="12">
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O105" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P105" s="6" t="s">
-        <v>25</v>
+      <c r="P105" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q105" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M106" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="N106" s="6">
-        <v>0</v>
-      </c>
-      <c r="O106" s="6" t="s">
+      <c r="A106" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M106" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N106" s="12">
+        <f>(0.6*20+0.4*2)</f>
+        <v>12.8</v>
+      </c>
+      <c r="O106" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P106" s="6" t="s">
-        <v>25</v>
+      <c r="P106" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q106" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>111</v>
@@ -4916,14 +4929,13 @@
         <v>109</v>
       </c>
       <c r="N107" s="12">
-        <f>(0.8*20+0.2*2)</f>
-        <v>16.399999999999999</v>
+        <v>2</v>
       </c>
       <c r="O107" s="12" t="s">
         <v>82</v>
       </c>
       <c r="P107" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q107" s="1" t="s">
         <v>103</v>
@@ -4931,7 +4943,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>111</v>
@@ -4940,81 +4952,83 @@
         <v>109</v>
       </c>
       <c r="N108" s="12">
-        <f>(0.6*20+0.4*2)</f>
-        <v>12.8</v>
+        <v>2</v>
       </c>
       <c r="O108" s="12" t="s">
         <v>82</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q108" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M109" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N109" s="12">
-        <v>2</v>
-      </c>
-      <c r="O109" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P109" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q109" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="M109" s="12"/>
+      <c r="N109" s="12"/>
+      <c r="O109" s="12"/>
+      <c r="P109" s="12"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>111</v>
       </c>
       <c r="M110" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N110" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O110" s="12" t="s">
         <v>82</v>
       </c>
       <c r="P110" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q110" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M111" s="12"/>
-      <c r="N111" s="12"/>
-      <c r="O111" s="12"/>
-      <c r="P111" s="12"/>
+      <c r="A111" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M111" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N111" s="12">
+        <v>5</v>
+      </c>
+      <c r="O111" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P111" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="G112" s="1" t="s">
         <v>111</v>
       </c>
@@ -5022,13 +5036,14 @@
         <v>110</v>
       </c>
       <c r="N112" s="12">
-        <v>5</v>
+        <f>0.9*5+0.1*15</f>
+        <v>6</v>
       </c>
       <c r="O112" s="12" t="s">
         <v>82</v>
       </c>
       <c r="P112" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q112" s="1" t="s">
         <v>103</v>
@@ -5036,10 +5051,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>111</v>
@@ -5048,21 +5060,19 @@
         <v>110</v>
       </c>
       <c r="N113" s="12">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O113" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P113" s="12" t="s">
-        <v>115</v>
-      </c>
+      <c r="P113" s="12"/>
       <c r="Q113" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>111</v>
@@ -5071,52 +5081,34 @@
         <v>110</v>
       </c>
       <c r="N114" s="12">
-        <f>0.9*5+0.1*15</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O114" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P114" s="12" t="s">
-        <v>117</v>
-      </c>
+      <c r="P114" s="12"/>
       <c r="Q114" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M115" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N115" s="12">
-        <v>15</v>
-      </c>
-      <c r="O115" s="12" t="s">
-        <v>82</v>
-      </c>
+      <c r="M115" s="12"/>
+      <c r="N115" s="12"/>
+      <c r="O115" s="12"/>
       <c r="P115" s="12"/>
-      <c r="Q115" s="1" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="A116" s="15"/>
+      <c r="B116" s="15"/>
+      <c r="E116" s="15"/>
       <c r="G116" s="1" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="M116" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N116" s="12">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O116" s="12" t="s">
         <v>82</v>
@@ -5127,30 +5119,73 @@
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
+      <c r="A117" s="15" t="str">
+        <f>A110</f>
+        <v>cattle</v>
+      </c>
+      <c r="B117" s="15" t="str">
+        <f>B110</f>
+        <v>dairy</v>
+      </c>
+      <c r="E117" s="15" t="str">
+        <f>E110</f>
+        <v>cows</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M117" s="15" t="str">
+        <f t="shared" ref="M117:Q119" si="0">M110</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N117" s="15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O117" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>%</v>
+      </c>
+      <c r="P117" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q117" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" s="15"/>
-      <c r="B118" s="15"/>
-      <c r="E118" s="15"/>
+      <c r="A118" s="15" t="str">
+        <f>A111</f>
+        <v>cattle</v>
+      </c>
+      <c r="E118" s="15" t="str">
+        <f>E111</f>
+        <v>bulls</v>
+      </c>
       <c r="G118" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M118" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N118" s="12">
+      <c r="M118" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N118" s="15">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O118" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P118" s="12"/>
-      <c r="Q118" s="1" t="s">
-        <v>103</v>
+      <c r="O118" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>%</v>
+      </c>
+      <c r="P118" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q118" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -5158,24 +5193,16 @@
         <f>A112</f>
         <v>cattle</v>
       </c>
-      <c r="B119" s="15" t="str">
-        <f>B112</f>
-        <v>dairy</v>
-      </c>
-      <c r="E119" s="15" t="str">
-        <f>E112</f>
-        <v>cows</v>
-      </c>
       <c r="G119" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M119" s="15" t="str">
-        <f t="shared" ref="M119:Q121" si="0">M112</f>
+        <f t="shared" si="0"/>
         <v>feeding_losses</v>
       </c>
       <c r="N119" s="15">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O119" s="15" t="str">
         <f t="shared" si="0"/>
@@ -5183,7 +5210,7 @@
       </c>
       <c r="P119" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>No feeding on pasture</v>
+        <v>10% feeding on pasture</v>
       </c>
       <c r="Q119" s="15" t="str">
         <f t="shared" si="0"/>
@@ -5193,141 +5220,149 @@
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="15" t="str">
         <f>A113</f>
-        <v>cattle</v>
-      </c>
-      <c r="E120" s="15" t="str">
-        <f>E113</f>
-        <v>bulls</v>
+        <v>sheep</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M120" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M120:O121" si="1">M113</f>
         <v>feeding_losses</v>
       </c>
       <c r="N120" s="15">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="O120" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P120" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>No feeding on pasture</v>
-      </c>
+      <c r="P120" s="15"/>
       <c r="Q120" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>Q113</f>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="15" t="str">
         <f>A114</f>
-        <v>cattle</v>
+        <v>horses</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M121" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>feeding_losses</v>
       </c>
       <c r="N121" s="15">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O121" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>%</v>
-      </c>
-      <c r="P121" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="Q121" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" s="15" t="str">
-        <f>A115</f>
-        <v>sheep</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M122" s="15" t="str">
-        <f t="shared" ref="M122:O123" si="1">M115</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N122" s="15">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="O122" s="15" t="str">
+      <c r="O121" s="15" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
+      <c r="P121" s="15"/>
+      <c r="Q121" s="15" t="str">
+        <f>Q114</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" s="15"/>
+      <c r="M122" s="15"/>
+      <c r="N122" s="15"/>
+      <c r="O122" s="15"/>
       <c r="P122" s="15"/>
-      <c r="Q122" s="15" t="str">
-        <f>Q115</f>
+      <c r="Q122" s="15"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G123" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M123" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N123" s="12">
+        <v>5</v>
+      </c>
+      <c r="O123" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" s="15" t="str">
+        <f>A110</f>
+        <v>cattle</v>
+      </c>
+      <c r="B124" s="15" t="str">
+        <f>B110</f>
+        <v>dairy</v>
+      </c>
+      <c r="E124" s="15" t="str">
+        <f>E110</f>
+        <v>cows</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M124" s="15" t="str">
+        <f t="shared" ref="M124:Q126" si="2">M110</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N124" s="15">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="O124" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>%</v>
+      </c>
+      <c r="P124" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q124" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123" s="15" t="str">
-        <f>A116</f>
-        <v>horses</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M123" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N123" s="15">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="O123" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="P123" s="15"/>
-      <c r="Q123" s="15" t="str">
-        <f>Q116</f>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124" s="15"/>
-      <c r="M124" s="15"/>
-      <c r="N124" s="15"/>
-      <c r="O124" s="15"/>
-      <c r="P124" s="15"/>
-      <c r="Q124" s="15"/>
-    </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" s="15" t="str">
+        <f>A111</f>
+        <v>cattle</v>
+      </c>
+      <c r="E125" s="15" t="str">
+        <f>E111</f>
+        <v>bulls</v>
+      </c>
       <c r="G125" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M125" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N125" s="12">
+      <c r="M125" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N125" s="15">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="O125" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P125" s="12"/>
-      <c r="Q125" s="1" t="s">
-        <v>103</v>
+      <c r="O125" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>%</v>
+      </c>
+      <c r="P125" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="Q125" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -5335,24 +5370,16 @@
         <f>A112</f>
         <v>cattle</v>
       </c>
-      <c r="B126" s="15" t="str">
-        <f>B112</f>
-        <v>dairy</v>
-      </c>
-      <c r="E126" s="15" t="str">
-        <f>E112</f>
-        <v>cows</v>
-      </c>
       <c r="G126" s="1" t="s">
         <v>118</v>
       </c>
       <c r="M126" s="15" t="str">
-        <f t="shared" ref="M126:Q128" si="2">M112</f>
+        <f t="shared" si="2"/>
         <v>feeding_losses</v>
       </c>
       <c r="N126" s="15">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O126" s="15" t="str">
         <f t="shared" si="2"/>
@@ -5360,7 +5387,7 @@
       </c>
       <c r="P126" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>No feeding on pasture</v>
+        <v>10% feeding on pasture</v>
       </c>
       <c r="Q126" s="15" t="str">
         <f t="shared" si="2"/>
@@ -5370,268 +5397,242 @@
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="15" t="str">
         <f>A113</f>
-        <v>cattle</v>
-      </c>
-      <c r="E127" s="15" t="str">
-        <f>E113</f>
-        <v>bulls</v>
+        <v>sheep</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>118</v>
       </c>
       <c r="M127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M127:O128" si="3">M113</f>
         <v>feeding_losses</v>
       </c>
       <c r="N127" s="15">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="O127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>%</v>
       </c>
-      <c r="P127" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>No feeding on pasture</v>
-      </c>
+      <c r="P127" s="12"/>
       <c r="Q127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>Q113</f>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="15" t="str">
         <f>A114</f>
-        <v>cattle</v>
+        <v>horses</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>118</v>
       </c>
       <c r="M128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>feeding_losses</v>
       </c>
       <c r="N128" s="15">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="O128" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>%</v>
-      </c>
-      <c r="P128" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="Q128" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129" s="15" t="str">
-        <f>A115</f>
-        <v>sheep</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M129" s="15" t="str">
-        <f t="shared" ref="M129:O130" si="3">M115</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N129" s="15">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="O129" s="15" t="str">
+      <c r="O128" s="15" t="str">
         <f t="shared" si="3"/>
         <v>%</v>
       </c>
+      <c r="P128" s="12"/>
+      <c r="Q128" s="15" t="str">
+        <f>Q114</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N129" s="10"/>
       <c r="P129" s="12"/>
-      <c r="Q129" s="15" t="str">
-        <f>Q115</f>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="15" t="str">
-        <f>A116</f>
-        <v>horses</v>
-      </c>
+      <c r="A130" s="10"/>
       <c r="G130" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M130" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N130" s="15">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="O130" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>%</v>
-      </c>
-      <c r="P130" s="12"/>
-      <c r="Q130" s="15" t="str">
-        <f>Q116</f>
-        <v>Cederberg &amp; Henriksson (2020)</v>
+        <v>119</v>
+      </c>
+      <c r="M130" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N130" s="12"/>
+      <c r="P130" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N131" s="10"/>
-      <c r="P131" s="12"/>
+      <c r="A131" s="10"/>
+      <c r="G131" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M131" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N131" s="12">
+        <v>2</v>
+      </c>
+      <c r="O131" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P131" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q131" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="10"/>
-      <c r="G132" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M132" s="12" t="s">
-        <v>109</v>
-      </c>
+      <c r="M132" s="12"/>
       <c r="N132" s="12"/>
-      <c r="P132" s="10" t="s">
-        <v>120</v>
-      </c>
+      <c r="O132" s="12"/>
+      <c r="P132" s="10"/>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="10"/>
       <c r="G133" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M133" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N133" s="12">
-        <v>2</v>
-      </c>
-      <c r="O133" s="12" t="s">
-        <v>82</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N133" s="12"/>
       <c r="P133" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q133" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="10"/>
-      <c r="M134" s="12"/>
-      <c r="N134" s="12"/>
-      <c r="O134" s="12"/>
-      <c r="P134" s="10"/>
+      <c r="G134" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M134" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N134" s="12">
+        <v>3</v>
+      </c>
+      <c r="O134" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P134" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q134" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135" s="10"/>
-      <c r="G135" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M135" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N135" s="12"/>
-      <c r="P135" s="10" t="s">
-        <v>120</v>
-      </c>
+      <c r="N135" s="10"/>
+      <c r="P135" s="12"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136" s="10"/>
-      <c r="G136" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M136" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N136" s="12">
-        <v>3</v>
-      </c>
-      <c r="O136" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P136" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q136" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="A136" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+      <c r="L136" s="4"/>
+      <c r="M136" s="4"/>
+      <c r="N136" s="4"/>
+      <c r="O136" s="4"/>
+      <c r="P136" s="4"/>
+      <c r="Q136" s="4"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N137" s="10"/>
-      <c r="P137" s="12"/>
+      <c r="A137" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N137" s="12"/>
+      <c r="P137" s="12" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B138" s="3"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
-      <c r="L138" s="4"/>
-      <c r="M138" s="4"/>
-      <c r="N138" s="4"/>
-      <c r="O138" s="4"/>
-      <c r="P138" s="4"/>
-      <c r="Q138" s="4"/>
+      <c r="A138" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B138" s="10"/>
+      <c r="C138" s="10"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10"/>
+      <c r="H138" s="10"/>
+      <c r="I138" s="10"/>
+      <c r="J138" s="10"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="10"/>
+      <c r="M138" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="N138" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="O138" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="P138" s="10"/>
+      <c r="Q138" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N139" s="12"/>
-      <c r="P139" s="12" t="s">
-        <v>125</v>
+        <v>102</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N139" s="12">
+        <v>18</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P139" s="10"/>
+      <c r="Q139" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B140" s="10"/>
-      <c r="C140" s="10"/>
-      <c r="D140" s="10"/>
-      <c r="E140" s="10"/>
-      <c r="F140" s="10"/>
-      <c r="G140" s="10"/>
-      <c r="H140" s="10"/>
-      <c r="I140" s="10"/>
-      <c r="J140" s="10"/>
-      <c r="K140" s="10"/>
-      <c r="L140" s="10"/>
-      <c r="M140" s="12" t="s">
-        <v>126</v>
+      <c r="A140" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="N140" s="12">
-        <v>6.7</v>
-      </c>
-      <c r="O140" s="12" t="s">
-        <v>127</v>
+        <v>1.5</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="P140" s="10"/>
       <c r="Q140" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>129</v>
       </c>
       <c r="N141" s="12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
         <v>130</v>
@@ -5642,46 +5643,50 @@
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M142" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N142" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="O142" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="N142" s="12"/>
       <c r="P142" s="10"/>
-      <c r="Q142" s="1" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="M143" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N143" s="12">
-        <v>0</v>
-      </c>
-      <c r="O143" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="P143" s="10"/>
-      <c r="Q143" s="1" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O143" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="P143" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q143" s="12"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N144" s="12"/>
-      <c r="P144" s="10"/>
+      <c r="A144" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M144" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N144" s="12">
+        <v>1</v>
+      </c>
+      <c r="O144" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="P144" s="12"/>
+      <c r="Q144" s="12"/>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="M145" s="1" t="s">
         <v>132</v>
       </c>
@@ -5691,15 +5696,19 @@
       <c r="O145" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="P145" s="12" t="s">
-        <v>134</v>
-      </c>
+      <c r="P145" s="12"/>
       <c r="Q145" s="12"/>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="B146" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="M146" s="1" t="s">
         <v>132</v>
       </c>
@@ -5717,10 +5726,10 @@
         <v>92</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>132</v>
@@ -5735,75 +5744,77 @@
       <c r="Q147" s="12"/>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N148" s="12">
-        <v>1</v>
-      </c>
-      <c r="O148" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="P148" s="12"/>
-      <c r="Q148" s="12"/>
+      <c r="N148" s="10"/>
+      <c r="P148" s="10"/>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M149" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N149" s="12">
-        <v>1</v>
-      </c>
-      <c r="O149" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="P149" s="12"/>
-      <c r="Q149" s="12"/>
+      <c r="A149" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B149" s="16"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="17"/>
+      <c r="G149" s="17"/>
+      <c r="H149" s="17"/>
+      <c r="I149" s="17"/>
+      <c r="J149" s="17"/>
+      <c r="K149" s="17"/>
+      <c r="L149" s="17"/>
+      <c r="M149" s="17"/>
+      <c r="N149" s="17"/>
+      <c r="O149" s="17"/>
+      <c r="P149" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q149" s="17"/>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N150" s="10"/>
-      <c r="P150" s="10"/>
+      <c r="A150" s="18"/>
+      <c r="B150" s="18"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="18"/>
+      <c r="F150" s="18"/>
+      <c r="G150" s="18"/>
+      <c r="H150" s="18"/>
+      <c r="I150" s="18"/>
+      <c r="J150" s="18"/>
+      <c r="K150" s="18"/>
+      <c r="L150" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="M150" s="18"/>
+      <c r="N150" s="18"/>
+      <c r="O150" s="18"/>
+      <c r="P150" s="18"/>
+      <c r="Q150" s="18"/>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A151" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="17"/>
-      <c r="F151" s="17"/>
-      <c r="G151" s="17"/>
-      <c r="H151" s="17"/>
-      <c r="I151" s="17"/>
-      <c r="J151" s="17"/>
-      <c r="K151" s="17"/>
-      <c r="L151" s="17"/>
-      <c r="M151" s="17"/>
-      <c r="N151" s="17"/>
-      <c r="O151" s="17"/>
-      <c r="P151" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q151" s="17"/>
+      <c r="A151" s="18"/>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="18"/>
+      <c r="G151" s="18"/>
+      <c r="H151" s="18"/>
+      <c r="I151" s="18"/>
+      <c r="J151" s="18"/>
+      <c r="K151" s="18"/>
+      <c r="L151" s="18"/>
+      <c r="M151" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="N151" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="O151" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="P151" s="21"/>
+      <c r="Q151" s="18"/>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
@@ -5817,13 +5828,17 @@
       <c r="I152" s="18"/>
       <c r="J152" s="18"/>
       <c r="K152" s="18"/>
-      <c r="L152" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="M152" s="18"/>
-      <c r="N152" s="18"/>
-      <c r="O152" s="18"/>
-      <c r="P152" s="18"/>
+      <c r="L152" s="18"/>
+      <c r="M152" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="N152" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="O152" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="P152" s="21"/>
       <c r="Q152" s="18"/>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -5839,16 +5854,14 @@
       <c r="J153" s="18"/>
       <c r="K153" s="18"/>
       <c r="L153" s="18"/>
-      <c r="M153" s="18" t="s">
-        <v>138</v>
+      <c r="M153" s="22" t="s">
+        <v>143</v>
       </c>
       <c r="N153" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="O153" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="P153" s="21"/>
+      <c r="O153" s="18"/>
+      <c r="P153" s="18"/>
       <c r="Q153" s="18"/>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -5864,16 +5877,14 @@
       <c r="J154" s="18"/>
       <c r="K154" s="18"/>
       <c r="L154" s="18"/>
-      <c r="M154" s="18" t="s">
-        <v>141</v>
+      <c r="M154" s="22" t="s">
+        <v>144</v>
       </c>
       <c r="N154" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="O154" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="P154" s="21"/>
+      <c r="O154" s="18"/>
+      <c r="P154" s="18"/>
       <c r="Q154" s="18"/>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -5890,7 +5901,7 @@
       <c r="K155" s="18"/>
       <c r="L155" s="18"/>
       <c r="M155" s="22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N155" s="20" t="s">
         <v>139</v>
@@ -5913,13 +5924,13 @@
       <c r="K156" s="18"/>
       <c r="L156" s="18"/>
       <c r="M156" s="22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N156" s="20" t="s">
         <v>139</v>
       </c>
       <c r="O156" s="18"/>
-      <c r="P156" s="18"/>
+      <c r="P156" s="21"/>
       <c r="Q156" s="18"/>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -5934,13 +5945,11 @@
       <c r="I157" s="18"/>
       <c r="J157" s="18"/>
       <c r="K157" s="18"/>
-      <c r="L157" s="18"/>
-      <c r="M157" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="N157" s="20" t="s">
-        <v>139</v>
-      </c>
+      <c r="L157" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="M157" s="18"/>
+      <c r="N157" s="18"/>
       <c r="O157" s="18"/>
       <c r="P157" s="18"/>
       <c r="Q157" s="18"/>
@@ -5958,14 +5967,18 @@
       <c r="J158" s="18"/>
       <c r="K158" s="18"/>
       <c r="L158" s="18"/>
-      <c r="M158" s="22" t="s">
-        <v>146</v>
+      <c r="M158" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="N158" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="O158" s="18"/>
-      <c r="P158" s="21"/>
+        <v>149</v>
+      </c>
+      <c r="O158" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="P158" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="Q158" s="18"/>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -5980,13 +5993,17 @@
       <c r="I159" s="18"/>
       <c r="J159" s="18"/>
       <c r="K159" s="18"/>
-      <c r="L159" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="M159" s="18"/>
-      <c r="N159" s="18"/>
-      <c r="O159" s="18"/>
-      <c r="P159" s="18"/>
+      <c r="L159" s="18"/>
+      <c r="M159" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N159" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="O159" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P159" s="21"/>
       <c r="Q159" s="18"/>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -6003,16 +6020,16 @@
       <c r="K160" s="18"/>
       <c r="L160" s="18"/>
       <c r="M160" s="18" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N160" s="20" t="s">
         <v>149</v>
       </c>
       <c r="O160" s="18" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P160" s="20" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="Q160" s="18"/>
     </row>
@@ -6028,17 +6045,13 @@
       <c r="I161" s="18"/>
       <c r="J161" s="18"/>
       <c r="K161" s="18"/>
-      <c r="L161" s="18"/>
-      <c r="M161" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="N161" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="O161" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P161" s="21"/>
+      <c r="L161" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="M161" s="18"/>
+      <c r="N161" s="18"/>
+      <c r="O161" s="18"/>
+      <c r="P161" s="18"/>
       <c r="Q161" s="18"/>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -6055,16 +6068,16 @@
       <c r="K162" s="18"/>
       <c r="L162" s="18"/>
       <c r="M162" s="18" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="N162" s="20" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="O162" s="18" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P162" s="20" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="Q162" s="18"/>
     </row>
@@ -6080,13 +6093,17 @@
       <c r="I163" s="18"/>
       <c r="J163" s="18"/>
       <c r="K163" s="18"/>
-      <c r="L163" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="M163" s="18"/>
-      <c r="N163" s="18"/>
-      <c r="O163" s="18"/>
-      <c r="P163" s="18"/>
+      <c r="L163" s="18"/>
+      <c r="M163" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N163" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="O163" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P163" s="21"/>
       <c r="Q163" s="18"/>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -6101,19 +6118,13 @@
       <c r="I164" s="18"/>
       <c r="J164" s="18"/>
       <c r="K164" s="18"/>
-      <c r="L164" s="18"/>
-      <c r="M164" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="N164" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="O164" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="P164" s="20" t="s">
-        <v>151</v>
-      </c>
+      <c r="L164" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="M164" s="18"/>
+      <c r="N164" s="18"/>
+      <c r="O164" s="18"/>
+      <c r="P164" s="18"/>
       <c r="Q164" s="18"/>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -6130,15 +6141,17 @@
       <c r="K165" s="18"/>
       <c r="L165" s="18"/>
       <c r="M165" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N165" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O165" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P165" s="21"/>
+        <v>150</v>
+      </c>
+      <c r="P165" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="Q165" s="18"/>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -6153,13 +6166,17 @@
       <c r="I166" s="18"/>
       <c r="J166" s="18"/>
       <c r="K166" s="18"/>
-      <c r="L166" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="M166" s="18"/>
-      <c r="N166" s="18"/>
-      <c r="O166" s="18"/>
-      <c r="P166" s="18"/>
+      <c r="L166" s="18"/>
+      <c r="M166" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N166" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="O166" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P166" s="21"/>
       <c r="Q166" s="18"/>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -6174,19 +6191,13 @@
       <c r="I167" s="18"/>
       <c r="J167" s="18"/>
       <c r="K167" s="18"/>
-      <c r="L167" s="18"/>
-      <c r="M167" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="N167" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="O167" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="P167" s="20" t="s">
-        <v>151</v>
-      </c>
+      <c r="L167" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="M167" s="18"/>
+      <c r="N167" s="18"/>
+      <c r="O167" s="18"/>
+      <c r="P167" s="18"/>
       <c r="Q167" s="18"/>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -6203,15 +6214,17 @@
       <c r="K168" s="18"/>
       <c r="L168" s="18"/>
       <c r="M168" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N168" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O168" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P168" s="21"/>
+        <v>163</v>
+      </c>
+      <c r="P168" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="Q168" s="18"/>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -6226,13 +6239,17 @@
       <c r="I169" s="18"/>
       <c r="J169" s="18"/>
       <c r="K169" s="18"/>
-      <c r="L169" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="M169" s="18"/>
-      <c r="N169" s="18"/>
-      <c r="O169" s="18"/>
-      <c r="P169" s="18"/>
+      <c r="L169" s="18"/>
+      <c r="M169" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N169" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="O169" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P169" s="21"/>
       <c r="Q169" s="18"/>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -6247,19 +6264,13 @@
       <c r="I170" s="18"/>
       <c r="J170" s="18"/>
       <c r="K170" s="18"/>
-      <c r="L170" s="18"/>
-      <c r="M170" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="N170" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="O170" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="P170" s="20" t="s">
-        <v>151</v>
-      </c>
+      <c r="L170" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="M170" s="18"/>
+      <c r="N170" s="18"/>
+      <c r="O170" s="18"/>
+      <c r="P170" s="18"/>
       <c r="Q170" s="18"/>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -6276,80 +6287,34 @@
       <c r="K171" s="18"/>
       <c r="L171" s="18"/>
       <c r="M171" s="18" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="N171" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O171" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P171" s="21"/>
+        <v>167</v>
+      </c>
+      <c r="P171" s="20"/>
       <c r="Q171" s="18"/>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A172" s="18"/>
-      <c r="B172" s="18"/>
-      <c r="C172" s="18"/>
-      <c r="D172" s="18"/>
-      <c r="E172" s="18"/>
-      <c r="F172" s="18"/>
-      <c r="G172" s="18"/>
-      <c r="H172" s="18"/>
-      <c r="I172" s="18"/>
-      <c r="J172" s="18"/>
-      <c r="K172" s="18"/>
-      <c r="L172" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="M172" s="18"/>
-      <c r="N172" s="18"/>
-      <c r="O172" s="18"/>
-      <c r="P172" s="18"/>
-      <c r="Q172" s="18"/>
-    </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A173" s="18"/>
-      <c r="B173" s="18"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="18"/>
-      <c r="E173" s="18"/>
-      <c r="F173" s="18"/>
-      <c r="G173" s="18"/>
-      <c r="H173" s="18"/>
-      <c r="I173" s="18"/>
-      <c r="J173" s="18"/>
-      <c r="K173" s="18"/>
-      <c r="L173" s="18"/>
-      <c r="M173" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="N173" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="O173" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="P173" s="20"/>
-      <c r="Q173" s="18"/>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F175"/>
-      <c r="G175"/>
-      <c r="H175"/>
-      <c r="I175"/>
-      <c r="J175"/>
-      <c r="K175"/>
-      <c r="L175"/>
-      <c r="M175" s="1" t="s">
+      <c r="F173"/>
+      <c r="G173"/>
+      <c r="H173"/>
+      <c r="I173"/>
+      <c r="J173"/>
+      <c r="K173"/>
+      <c r="L173"/>
+      <c r="M173" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N175" s="12" t="s">
+      <c r="N173" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="O175"/>
-      <c r="P175"/>
-      <c r="Q175"/>
+      <c r="O173"/>
+      <c r="P173"/>
+      <c r="Q173"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -22,7 +22,7 @@
     <sheet name="horses" sheetId="8" r:id="rId8"/>
     <sheet name="poultry" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="681">
   <si>
     <t>Statistics Netherlands (2012) Standardised calculation methods for animal manure and nutrients. Standard data 1990–2008</t>
   </si>
@@ -3135,7 +3135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R173"/>
+  <dimension ref="A1:R175"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" style="1" customWidth="1"/>
@@ -3708,7 +3708,7 @@
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F33" s="1" t="s">
         <v>61</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>1.1389521640091116</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F34" s="1" t="s">
         <v>62</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>1.1415525114155252</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F35" s="1" t="s">
         <v>64</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>1.1415525114155252</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F36" s="1" t="s">
         <v>65</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>1.1415525114155252</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F37" s="1" t="s">
         <v>66</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F38" s="1" t="s">
         <v>68</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F39" s="1" t="s">
         <v>69</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F40" s="1" t="s">
         <v>70</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>1.3245033112582782</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F41" s="1" t="s">
         <v>71</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>1.1173184357541899</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F42" s="1" t="s">
         <v>72</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F43" s="1" t="s">
         <v>73</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F44" s="1" t="s">
         <v>74</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F45" s="1" t="s">
         <v>75</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>4.3478260869565215</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F46" s="1" t="s">
         <v>76</v>
       </c>
@@ -3918,92 +3918,93 @@
         <v>1.0863661053775122</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N47" s="9"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+    <row r="47" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="F47" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" s="9">
+        <f>1/INDEX('feed pars'!C$6:C$47/100,MATCH(F47,'feed pars'!B$6:B$47,0))</f>
+        <v>1.1152416356877324</v>
+      </c>
+    </row>
+    <row r="48" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="N48" s="9"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N48" s="9"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F49" s="1" t="s">
+      <c r="N49" s="9"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N49" s="9">
+      <c r="N50" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N50" s="9"/>
-    </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="N51" s="9"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-    </row>
-    <row r="52" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+    </row>
+    <row r="53" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M53" s="6" t="s">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M54" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="N53" s="6">
-        <v>0</v>
-      </c>
-      <c r="O53" s="6" t="s">
+      <c r="N54" s="6">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P53" s="6" t="s">
+      <c r="P54" s="6" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I54" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="N54" s="10">
-        <v>95</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I55" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>81</v>
@@ -4017,7 +4018,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I56" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>81</v>
@@ -4030,26 +4031,22 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="I57" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="10">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P57" s="10"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>36</v>
@@ -4067,10 +4064,10 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>81</v>
@@ -4085,7 +4082,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>35</v>
@@ -4103,10 +4100,10 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>81</v>
@@ -4121,7 +4118,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>37</v>
@@ -4138,34 +4135,37 @@
       <c r="P62" s="10"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N63" s="10"/>
+      <c r="A63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N63" s="10">
+        <v>30</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P63" s="10"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
-        <v>85</v>
-      </c>
       <c r="N64" s="10"/>
       <c r="P64" s="10"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I65" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="N65" s="10">
-        <v>5</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="A65" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="N65" s="10"/>
       <c r="P65" s="10"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I66" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>86</v>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I67" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>86</v>
@@ -4194,130 +4194,125 @@
       <c r="P67" s="10"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N68" s="10"/>
+      <c r="I68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N68" s="10">
+        <v>5</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P68" s="10"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+      <c r="N69" s="10"/>
+      <c r="P69" s="10"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M70" s="6" t="s">
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M71" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="N70" s="6">
+      <c r="N71" s="6">
         <v>100</v>
       </c>
-      <c r="O70" s="6" t="s">
+      <c r="O71" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P70" s="6" t="s">
+      <c r="P71" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N71" s="12">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P71" s="6"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I72" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="N72" s="10">
-        <v>0</v>
-      </c>
-      <c r="O72" s="1" t="s">
+      <c r="N72" s="12">
+        <v>0</v>
+      </c>
+      <c r="O72" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P72" s="10" t="s">
-        <v>89</v>
-      </c>
+      <c r="P72" s="6"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I73" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N73" s="10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P73" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I74" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N74" s="10">
+        <v>50</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P74" s="10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N74" s="10"/>
-      <c r="P74" s="10"/>
-    </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75" t="s">
-        <v>60</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N75" s="10">
-        <v>80</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N75" s="10"/>
       <c r="P75" s="10"/>
-      <c r="Q75"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F76"/>
       <c r="G76"/>
       <c r="H76"/>
       <c r="I76"/>
-      <c r="J76" s="1" t="s">
-        <v>46</v>
+      <c r="J76" t="s">
+        <v>60</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N76" s="10">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="O76" s="1" t="s">
         <v>82</v>
@@ -4331,13 +4326,13 @@
       <c r="H77"/>
       <c r="I77"/>
       <c r="J77" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N77" s="10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O77" s="1" t="s">
         <v>82</v>
@@ -4351,7 +4346,7 @@
       <c r="H78"/>
       <c r="I78"/>
       <c r="J78" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>88</v>
@@ -4371,7 +4366,7 @@
       <c r="H79"/>
       <c r="I79"/>
       <c r="J79" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>88</v>
@@ -4391,7 +4386,7 @@
       <c r="H80"/>
       <c r="I80"/>
       <c r="J80" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>88</v>
@@ -4411,7 +4406,7 @@
       <c r="H81"/>
       <c r="I81"/>
       <c r="J81" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>88</v>
@@ -4431,7 +4426,7 @@
       <c r="H82"/>
       <c r="I82"/>
       <c r="J82" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>88</v>
@@ -4446,22 +4441,34 @@
       <c r="Q82"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N83" s="10"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N83" s="10">
+        <v>0</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P83" s="10"/>
       <c r="Q83"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C84" t="s">
-        <v>679</v>
-      </c>
-      <c r="J84" t="s">
-        <v>60</v>
+      <c r="J84" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N84" s="10">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>82</v>
@@ -4470,35 +4477,22 @@
       <c r="Q84"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C85" t="s">
-        <v>679</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N85" s="10">
-        <v>4</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N85" s="10"/>
       <c r="P85" s="10"/>
+      <c r="Q85"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>679</v>
       </c>
       <c r="J86" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N86" s="10">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>82</v>
@@ -4510,46 +4504,45 @@
       <c r="C87" t="s">
         <v>679</v>
       </c>
-      <c r="J87" t="s">
-        <v>70</v>
+      <c r="J87" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N87" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P87" s="10" t="s">
-        <v>680</v>
-      </c>
+      <c r="P87" s="10"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>679</v>
       </c>
       <c r="J88" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>88</v>
       </c>
       <c r="N88" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P88" s="10"/>
+      <c r="Q88"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>679</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>74</v>
+      <c r="J89" t="s">
+        <v>70</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>88</v>
@@ -4560,104 +4553,80 @@
       <c r="O89" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P89" s="10"/>
+      <c r="P89" s="10" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N90" s="10"/>
+      <c r="C90" t="s">
+        <v>679</v>
+      </c>
+      <c r="J90" t="s">
+        <v>71</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N90" s="10">
+        <v>0</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P90" s="10"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+      <c r="C91" t="s">
+        <v>679</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N91" s="10">
+        <v>0</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P91" s="10"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N92" s="10"/>
+      <c r="P92" s="10"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N93" s="12">
-        <v>28</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="P93" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q93" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N94" s="12">
-        <v>100</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="P94" s="12"/>
-      <c r="Q94" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>95</v>
@@ -4668,15 +4637,14 @@
       <c r="M95" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N95" s="14">
-        <f>N94</f>
-        <v>100</v>
+      <c r="N95" s="12">
+        <v>28</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P95" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="Q95" s="1" t="s">
         <v>98</v>
@@ -4686,6 +4654,12 @@
       <c r="A96" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="B96" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="H96" s="1" t="s">
         <v>95</v>
       </c>
@@ -4696,7 +4670,7 @@
         <v>96</v>
       </c>
       <c r="N96" s="12">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>82</v>
@@ -4708,7 +4682,13 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>95</v>
@@ -4719,20 +4699,23 @@
       <c r="M97" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N97" s="12">
-        <v>14.5</v>
+      <c r="N97" s="14">
+        <f>N96</f>
+        <v>100</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P97" s="10"/>
+      <c r="P97" s="12" t="s">
+        <v>101</v>
+      </c>
       <c r="Q97" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>95</v>
@@ -4744,22 +4727,19 @@
         <v>96</v>
       </c>
       <c r="N98" s="12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P98" s="10"/>
+      <c r="P98" s="12"/>
       <c r="Q98" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>95</v>
@@ -4771,26 +4751,20 @@
         <v>96</v>
       </c>
       <c r="N99" s="12">
-        <v>66</v>
+        <v>14.5</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>82</v>
       </c>
       <c r="P99" s="10"/>
       <c r="Q99" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H100" s="1" t="s">
         <v>95</v>
       </c>
@@ -4801,7 +4775,7 @@
         <v>96</v>
       </c>
       <c r="N100" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>82</v>
@@ -4812,223 +4786,231 @@
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N101" s="10"/>
+      <c r="A101" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N101" s="12">
+        <v>66</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="P101" s="10"/>
+      <c r="Q101" s="1" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N102" s="12">
+        <v>69</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P102" s="10"/>
+      <c r="Q102" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N103" s="10"/>
+      <c r="P103" s="10"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M103" s="6" t="s">
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M105" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="N103" s="6">
-        <v>0</v>
-      </c>
-      <c r="O103" s="6" t="s">
+      <c r="N105" s="6">
+        <v>0</v>
+      </c>
+      <c r="O105" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P103" s="6" t="s">
+      <c r="P105" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M104" s="6" t="s">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M106" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="N104" s="6">
-        <v>0</v>
-      </c>
-      <c r="O104" s="6" t="s">
+      <c r="N106" s="6">
+        <v>0</v>
+      </c>
+      <c r="O106" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P104" s="6" t="s">
+      <c r="P106" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M105" s="12" t="s">
+      <c r="M107" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="N105" s="12">
+      <c r="N107" s="12">
         <f>(0.8*20+0.2*2)</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="O105" s="12" t="s">
+      <c r="O107" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P105" s="12" t="s">
+      <c r="P107" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="Q105" s="1" t="s">
+      <c r="Q107" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="G108" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M106" s="12" t="s">
+      <c r="M108" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="N106" s="12">
+      <c r="N108" s="12">
         <f>(0.6*20+0.4*2)</f>
         <v>12.8</v>
       </c>
-      <c r="O106" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P106" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q106" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M107" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N107" s="12">
-        <v>2</v>
-      </c>
-      <c r="O107" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P107" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q107" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M108" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N108" s="12">
-        <v>2</v>
-      </c>
       <c r="O108" s="12" t="s">
         <v>82</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q108" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M109" s="12"/>
-      <c r="N109" s="12"/>
-      <c r="O109" s="12"/>
-      <c r="P109" s="12"/>
+      <c r="A109" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M109" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N109" s="12">
+        <v>2</v>
+      </c>
+      <c r="O109" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P109" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>111</v>
       </c>
       <c r="M110" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N110" s="12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O110" s="12" t="s">
         <v>82</v>
       </c>
       <c r="P110" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q110" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M111" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N111" s="12">
-        <v>5</v>
-      </c>
-      <c r="O111" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P111" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q111" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="M111" s="12"/>
+      <c r="N111" s="12"/>
+      <c r="O111" s="12"/>
+      <c r="P111" s="12"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="B112" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="G112" s="1" t="s">
         <v>111</v>
       </c>
@@ -5036,79 +5018,101 @@
         <v>110</v>
       </c>
       <c r="N112" s="12">
+        <v>5</v>
+      </c>
+      <c r="O112" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P112" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M113" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N113" s="12">
+        <v>5</v>
+      </c>
+      <c r="O113" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P113" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M114" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N114" s="12">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="O112" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P112" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q112" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M113" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N113" s="12">
-        <v>15</v>
-      </c>
-      <c r="O113" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P113" s="12"/>
-      <c r="Q113" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M114" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N114" s="12">
-        <v>15</v>
-      </c>
       <c r="O114" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P114" s="12"/>
+      <c r="P114" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="Q114" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M115" s="12"/>
-      <c r="N115" s="12"/>
-      <c r="O115" s="12"/>
+      <c r="A115" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M115" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N115" s="12">
+        <v>15</v>
+      </c>
+      <c r="O115" s="12" t="s">
+        <v>82</v>
+      </c>
       <c r="P115" s="12"/>
+      <c r="Q115" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="15"/>
-      <c r="B116" s="15"/>
-      <c r="E116" s="15"/>
+      <c r="A116" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="G116" s="1" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="M116" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N116" s="12">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O116" s="12" t="s">
         <v>82</v>
@@ -5119,73 +5123,30 @@
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117" s="15" t="str">
-        <f>A110</f>
-        <v>cattle</v>
-      </c>
-      <c r="B117" s="15" t="str">
-        <f>B110</f>
-        <v>dairy</v>
-      </c>
-      <c r="E117" s="15" t="str">
-        <f>E110</f>
-        <v>cows</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M117" s="15" t="str">
-        <f t="shared" ref="M117:Q119" si="0">M110</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N117" s="15">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O117" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>%</v>
-      </c>
-      <c r="P117" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q117" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
+      <c r="M117" s="12"/>
+      <c r="N117" s="12"/>
+      <c r="O117" s="12"/>
+      <c r="P117" s="12"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="str">
-        <f>A111</f>
-        <v>cattle</v>
-      </c>
-      <c r="E118" s="15" t="str">
-        <f>E111</f>
-        <v>bulls</v>
-      </c>
+      <c r="A118" s="15"/>
+      <c r="B118" s="15"/>
+      <c r="E118" s="15"/>
       <c r="G118" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M118" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N118" s="15">
-        <f t="shared" si="0"/>
+      <c r="M118" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N118" s="12">
         <v>5</v>
       </c>
-      <c r="O118" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>%</v>
-      </c>
-      <c r="P118" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q118" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
+      <c r="O118" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P118" s="12"/>
+      <c r="Q118" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -5193,16 +5154,24 @@
         <f>A112</f>
         <v>cattle</v>
       </c>
+      <c r="B119" s="15" t="str">
+        <f>B112</f>
+        <v>dairy</v>
+      </c>
+      <c r="E119" s="15" t="str">
+        <f>E112</f>
+        <v>cows</v>
+      </c>
       <c r="G119" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M119" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M119:Q121" si="0">M112</f>
         <v>feeding_losses</v>
       </c>
       <c r="N119" s="15">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O119" s="15" t="str">
         <f t="shared" si="0"/>
@@ -5210,7 +5179,7 @@
       </c>
       <c r="P119" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="Q119" s="15" t="str">
         <f t="shared" si="0"/>
@@ -5220,149 +5189,141 @@
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="15" t="str">
         <f>A113</f>
-        <v>sheep</v>
+        <v>cattle</v>
+      </c>
+      <c r="E120" s="15" t="str">
+        <f>E113</f>
+        <v>bulls</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M120" s="15" t="str">
-        <f t="shared" ref="M120:O121" si="1">M113</f>
+        <f t="shared" si="0"/>
         <v>feeding_losses</v>
       </c>
       <c r="N120" s="15">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="O120" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>%</v>
       </c>
-      <c r="P120" s="15"/>
+      <c r="P120" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q120" s="15" t="str">
-        <f>Q113</f>
+        <f t="shared" si="0"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="15" t="str">
         <f>A114</f>
-        <v>horses</v>
+        <v>cattle</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M121" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N121" s="15">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="O121" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>%</v>
+      </c>
+      <c r="P121" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="Q121" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" s="15" t="str">
+        <f>A115</f>
+        <v>sheep</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M122" s="15" t="str">
+        <f t="shared" ref="M122:O123" si="1">M115</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N122" s="15">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O122" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="P122" s="15"/>
+      <c r="Q122" s="15" t="str">
+        <f>Q115</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" s="15" t="str">
+        <f>A116</f>
+        <v>horses</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M123" s="15" t="str">
         <f t="shared" si="1"/>
         <v>feeding_losses</v>
       </c>
-      <c r="N121" s="15">
+      <c r="N123" s="15">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="O121" s="15" t="str">
+      <c r="O123" s="15" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="P121" s="15"/>
-      <c r="Q121" s="15" t="str">
-        <f>Q114</f>
+      <c r="P123" s="15"/>
+      <c r="Q123" s="15" t="str">
+        <f>Q116</f>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" s="15"/>
-      <c r="M122" s="15"/>
-      <c r="N122" s="15"/>
-      <c r="O122" s="15"/>
-      <c r="P122" s="15"/>
-      <c r="Q122" s="15"/>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G123" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M123" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N123" s="12">
-        <v>5</v>
-      </c>
-      <c r="O123" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124" s="15" t="str">
-        <f>A110</f>
-        <v>cattle</v>
-      </c>
-      <c r="B124" s="15" t="str">
-        <f>B110</f>
-        <v>dairy</v>
-      </c>
-      <c r="E124" s="15" t="str">
-        <f>E110</f>
-        <v>cows</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M124" s="15" t="str">
-        <f t="shared" ref="M124:Q126" si="2">M110</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N124" s="15">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O124" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>%</v>
-      </c>
-      <c r="P124" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q124" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
-      </c>
+      <c r="A124" s="15"/>
+      <c r="M124" s="15"/>
+      <c r="N124" s="15"/>
+      <c r="O124" s="15"/>
+      <c r="P124" s="15"/>
+      <c r="Q124" s="15"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125" s="15" t="str">
-        <f>A111</f>
-        <v>cattle</v>
-      </c>
-      <c r="E125" s="15" t="str">
-        <f>E111</f>
-        <v>bulls</v>
-      </c>
       <c r="G125" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M125" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N125" s="15">
-        <f t="shared" si="2"/>
+      <c r="M125" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N125" s="12">
         <v>5</v>
       </c>
-      <c r="O125" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>%</v>
-      </c>
-      <c r="P125" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q125" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
+      <c r="O125" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P125" s="12"/>
+      <c r="Q125" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -5370,16 +5331,24 @@
         <f>A112</f>
         <v>cattle</v>
       </c>
+      <c r="B126" s="15" t="str">
+        <f>B112</f>
+        <v>dairy</v>
+      </c>
+      <c r="E126" s="15" t="str">
+        <f>E112</f>
+        <v>cows</v>
+      </c>
       <c r="G126" s="1" t="s">
         <v>118</v>
       </c>
       <c r="M126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M126:Q128" si="2">M112</f>
         <v>feeding_losses</v>
       </c>
       <c r="N126" s="15">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O126" s="15" t="str">
         <f t="shared" si="2"/>
@@ -5387,7 +5356,7 @@
       </c>
       <c r="P126" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="Q126" s="15" t="str">
         <f t="shared" si="2"/>
@@ -5397,242 +5366,268 @@
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="15" t="str">
         <f>A113</f>
-        <v>sheep</v>
+        <v>cattle</v>
+      </c>
+      <c r="E127" s="15" t="str">
+        <f>E113</f>
+        <v>bulls</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>118</v>
       </c>
       <c r="M127" s="15" t="str">
-        <f t="shared" ref="M127:O128" si="3">M113</f>
+        <f t="shared" si="2"/>
         <v>feeding_losses</v>
       </c>
       <c r="N127" s="15">
-        <f t="shared" si="3"/>
-        <v>15</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="O127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>%</v>
       </c>
-      <c r="P127" s="12"/>
+      <c r="P127" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="Q127" s="15" t="str">
-        <f>Q113</f>
+        <f t="shared" si="2"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="15" t="str">
         <f>A114</f>
-        <v>horses</v>
+        <v>cattle</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>118</v>
       </c>
       <c r="M128" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N128" s="15">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="O128" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>%</v>
+      </c>
+      <c r="P128" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="Q128" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129" s="15" t="str">
+        <f>A115</f>
+        <v>sheep</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M129" s="15" t="str">
+        <f t="shared" ref="M129:O130" si="3">M115</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N129" s="15">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="O129" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>%</v>
+      </c>
+      <c r="P129" s="12"/>
+      <c r="Q129" s="15" t="str">
+        <f>Q115</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" s="15" t="str">
+        <f>A116</f>
+        <v>horses</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M130" s="15" t="str">
         <f t="shared" si="3"/>
         <v>feeding_losses</v>
       </c>
-      <c r="N128" s="15">
+      <c r="N130" s="15">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="O128" s="15" t="str">
+      <c r="O130" s="15" t="str">
         <f t="shared" si="3"/>
         <v>%</v>
       </c>
-      <c r="P128" s="12"/>
-      <c r="Q128" s="15" t="str">
-        <f>Q114</f>
+      <c r="P130" s="12"/>
+      <c r="Q130" s="15" t="str">
+        <f>Q116</f>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N129" s="10"/>
-      <c r="P129" s="12"/>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="10"/>
-      <c r="G130" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M130" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N130" s="12"/>
-      <c r="P130" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131" s="10"/>
-      <c r="G131" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M131" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N131" s="12">
-        <v>2</v>
-      </c>
-      <c r="O131" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P131" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q131" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="N131" s="10"/>
+      <c r="P131" s="12"/>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="10"/>
-      <c r="M132" s="12"/>
+      <c r="G132" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M132" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="N132" s="12"/>
-      <c r="O132" s="12"/>
-      <c r="P132" s="10"/>
+      <c r="P132" s="10" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="10"/>
       <c r="G133" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M133" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N133" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="N133" s="12">
+        <v>2</v>
+      </c>
+      <c r="O133" s="12" t="s">
+        <v>82</v>
+      </c>
       <c r="P133" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="Q133" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="10"/>
-      <c r="G134" s="1" t="s">
+      <c r="M134" s="12"/>
+      <c r="N134" s="12"/>
+      <c r="O134" s="12"/>
+      <c r="P134" s="10"/>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135" s="10"/>
+      <c r="G135" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="M134" s="12" t="s">
+      <c r="M135" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N135" s="12"/>
+      <c r="P135" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136" s="10"/>
+      <c r="G136" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M136" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="N134" s="12">
+      <c r="N136" s="12">
         <v>3</v>
       </c>
-      <c r="O134" s="12" t="s">
+      <c r="O136" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P134" s="10" t="s">
+      <c r="P136" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="Q134" s="1" t="s">
+      <c r="Q136" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N135" s="10"/>
-      <c r="P135" s="12"/>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N137" s="10"/>
+      <c r="P137" s="12"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B136" s="3"/>
-      <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="4"/>
-      <c r="L136" s="4"/>
-      <c r="M136" s="4"/>
-      <c r="N136" s="4"/>
-      <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-      <c r="Q136" s="4"/>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N137" s="12"/>
-      <c r="P137" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B138" s="10"/>
-      <c r="C138" s="10"/>
-      <c r="D138" s="10"/>
-      <c r="E138" s="10"/>
-      <c r="F138" s="10"/>
-      <c r="G138" s="10"/>
-      <c r="H138" s="10"/>
-      <c r="I138" s="10"/>
-      <c r="J138" s="10"/>
-      <c r="K138" s="10"/>
-      <c r="L138" s="10"/>
-      <c r="M138" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="N138" s="12">
-        <v>6.7</v>
-      </c>
-      <c r="O138" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="P138" s="10"/>
-      <c r="Q138" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+      <c r="L138" s="4"/>
+      <c r="M138" s="4"/>
+      <c r="N138" s="4"/>
+      <c r="O138" s="4"/>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="4"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N139" s="12">
-        <v>18</v>
-      </c>
-      <c r="O139" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="P139" s="10"/>
-      <c r="Q139" s="1" t="s">
-        <v>131</v>
+        <v>92</v>
+      </c>
+      <c r="N139" s="12"/>
+      <c r="P139" s="12" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M140" s="1" t="s">
-        <v>129</v>
+      <c r="A140" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B140" s="10"/>
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
+      <c r="G140" s="10"/>
+      <c r="H140" s="10"/>
+      <c r="I140" s="10"/>
+      <c r="J140" s="10"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="10"/>
+      <c r="M140" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="N140" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="O140" s="1" t="s">
-        <v>130</v>
+        <v>6.7</v>
+      </c>
+      <c r="O140" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="P140" s="10"/>
       <c r="Q140" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>129</v>
       </c>
       <c r="N141" s="12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O141" s="1" t="s">
         <v>130</v>
@@ -5643,50 +5638,46 @@
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N142" s="12"/>
+      <c r="A142" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M142" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N142" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="P142" s="10"/>
+      <c r="Q142" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="M143" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="N143" s="12">
-        <v>1</v>
-      </c>
-      <c r="O143" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="P143" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q143" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="O143" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P143" s="10"/>
+      <c r="Q143" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M144" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N144" s="12">
-        <v>1</v>
-      </c>
-      <c r="O144" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="P144" s="12"/>
-      <c r="Q144" s="12"/>
+      <c r="N144" s="12"/>
+      <c r="P144" s="10"/>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="M145" s="1" t="s">
         <v>132</v>
       </c>
@@ -5696,19 +5687,15 @@
       <c r="O145" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="P145" s="12"/>
+      <c r="P145" s="12" t="s">
+        <v>134</v>
+      </c>
       <c r="Q145" s="12"/>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="M146" s="1" t="s">
         <v>132</v>
       </c>
@@ -5726,10 +5713,10 @@
         <v>92</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>132</v>
@@ -5744,77 +5731,75 @@
       <c r="Q147" s="12"/>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N148" s="10"/>
-      <c r="P148" s="10"/>
+      <c r="A148" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N148" s="12">
+        <v>1</v>
+      </c>
+      <c r="O148" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="P148" s="12"/>
+      <c r="Q148" s="12"/>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N149" s="12">
+        <v>1</v>
+      </c>
+      <c r="O149" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="P149" s="12"/>
+      <c r="Q149" s="12"/>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N150" s="10"/>
+      <c r="P150" s="10"/>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B149" s="16"/>
-      <c r="C149" s="16"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="17"/>
-      <c r="H149" s="17"/>
-      <c r="I149" s="17"/>
-      <c r="J149" s="17"/>
-      <c r="K149" s="17"/>
-      <c r="L149" s="17"/>
-      <c r="M149" s="17"/>
-      <c r="N149" s="17"/>
-      <c r="O149" s="17"/>
-      <c r="P149" s="17" t="s">
+      <c r="B151" s="16"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="17"/>
+      <c r="F151" s="17"/>
+      <c r="G151" s="17"/>
+      <c r="H151" s="17"/>
+      <c r="I151" s="17"/>
+      <c r="J151" s="17"/>
+      <c r="K151" s="17"/>
+      <c r="L151" s="17"/>
+      <c r="M151" s="17"/>
+      <c r="N151" s="17"/>
+      <c r="O151" s="17"/>
+      <c r="P151" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="Q149" s="17"/>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A150" s="18"/>
-      <c r="B150" s="18"/>
-      <c r="C150" s="18"/>
-      <c r="D150" s="18"/>
-      <c r="E150" s="18"/>
-      <c r="F150" s="18"/>
-      <c r="G150" s="18"/>
-      <c r="H150" s="18"/>
-      <c r="I150" s="18"/>
-      <c r="J150" s="18"/>
-      <c r="K150" s="18"/>
-      <c r="L150" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="M150" s="18"/>
-      <c r="N150" s="18"/>
-      <c r="O150" s="18"/>
-      <c r="P150" s="18"/>
-      <c r="Q150" s="18"/>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A151" s="18"/>
-      <c r="B151" s="18"/>
-      <c r="C151" s="18"/>
-      <c r="D151" s="18"/>
-      <c r="E151" s="18"/>
-      <c r="F151" s="18"/>
-      <c r="G151" s="18"/>
-      <c r="H151" s="18"/>
-      <c r="I151" s="18"/>
-      <c r="J151" s="18"/>
-      <c r="K151" s="18"/>
-      <c r="L151" s="18"/>
-      <c r="M151" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="N151" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="O151" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="P151" s="21"/>
-      <c r="Q151" s="18"/>
+      <c r="Q151" s="17"/>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
@@ -5828,17 +5813,13 @@
       <c r="I152" s="18"/>
       <c r="J152" s="18"/>
       <c r="K152" s="18"/>
-      <c r="L152" s="18"/>
-      <c r="M152" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="N152" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="O152" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="P152" s="21"/>
+      <c r="L152" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="M152" s="18"/>
+      <c r="N152" s="18"/>
+      <c r="O152" s="18"/>
+      <c r="P152" s="18"/>
       <c r="Q152" s="18"/>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -5854,14 +5835,16 @@
       <c r="J153" s="18"/>
       <c r="K153" s="18"/>
       <c r="L153" s="18"/>
-      <c r="M153" s="22" t="s">
-        <v>143</v>
+      <c r="M153" s="18" t="s">
+        <v>138</v>
       </c>
       <c r="N153" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="O153" s="18"/>
-      <c r="P153" s="18"/>
+      <c r="O153" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="P153" s="21"/>
       <c r="Q153" s="18"/>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -5877,14 +5860,16 @@
       <c r="J154" s="18"/>
       <c r="K154" s="18"/>
       <c r="L154" s="18"/>
-      <c r="M154" s="22" t="s">
-        <v>144</v>
+      <c r="M154" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="N154" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="O154" s="18"/>
-      <c r="P154" s="18"/>
+      <c r="O154" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="P154" s="21"/>
       <c r="Q154" s="18"/>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -5901,7 +5886,7 @@
       <c r="K155" s="18"/>
       <c r="L155" s="18"/>
       <c r="M155" s="22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N155" s="20" t="s">
         <v>139</v>
@@ -5924,13 +5909,13 @@
       <c r="K156" s="18"/>
       <c r="L156" s="18"/>
       <c r="M156" s="22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N156" s="20" t="s">
         <v>139</v>
       </c>
       <c r="O156" s="18"/>
-      <c r="P156" s="21"/>
+      <c r="P156" s="18"/>
       <c r="Q156" s="18"/>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -5945,11 +5930,13 @@
       <c r="I157" s="18"/>
       <c r="J157" s="18"/>
       <c r="K157" s="18"/>
-      <c r="L157" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="M157" s="18"/>
-      <c r="N157" s="18"/>
+      <c r="L157" s="18"/>
+      <c r="M157" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="N157" s="20" t="s">
+        <v>139</v>
+      </c>
       <c r="O157" s="18"/>
       <c r="P157" s="18"/>
       <c r="Q157" s="18"/>
@@ -5967,18 +5954,14 @@
       <c r="J158" s="18"/>
       <c r="K158" s="18"/>
       <c r="L158" s="18"/>
-      <c r="M158" s="18" t="s">
-        <v>148</v>
+      <c r="M158" s="22" t="s">
+        <v>146</v>
       </c>
       <c r="N158" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="O158" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="P158" s="20" t="s">
-        <v>151</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O158" s="18"/>
+      <c r="P158" s="21"/>
       <c r="Q158" s="18"/>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -5993,17 +5976,13 @@
       <c r="I159" s="18"/>
       <c r="J159" s="18"/>
       <c r="K159" s="18"/>
-      <c r="L159" s="18"/>
-      <c r="M159" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="N159" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="O159" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P159" s="21"/>
+      <c r="L159" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="M159" s="18"/>
+      <c r="N159" s="18"/>
+      <c r="O159" s="18"/>
+      <c r="P159" s="18"/>
       <c r="Q159" s="18"/>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -6020,16 +5999,16 @@
       <c r="K160" s="18"/>
       <c r="L160" s="18"/>
       <c r="M160" s="18" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="N160" s="20" t="s">
         <v>149</v>
       </c>
       <c r="O160" s="18" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P160" s="20" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="Q160" s="18"/>
     </row>
@@ -6045,13 +6024,17 @@
       <c r="I161" s="18"/>
       <c r="J161" s="18"/>
       <c r="K161" s="18"/>
-      <c r="L161" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="M161" s="18"/>
-      <c r="N161" s="18"/>
-      <c r="O161" s="18"/>
-      <c r="P161" s="18"/>
+      <c r="L161" s="18"/>
+      <c r="M161" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N161" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="O161" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P161" s="21"/>
       <c r="Q161" s="18"/>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -6068,16 +6051,16 @@
       <c r="K162" s="18"/>
       <c r="L162" s="18"/>
       <c r="M162" s="18" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N162" s="20" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="O162" s="18" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P162" s="20" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="Q162" s="18"/>
     </row>
@@ -6093,17 +6076,13 @@
       <c r="I163" s="18"/>
       <c r="J163" s="18"/>
       <c r="K163" s="18"/>
-      <c r="L163" s="18"/>
-      <c r="M163" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="N163" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="O163" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P163" s="21"/>
+      <c r="L163" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="M163" s="18"/>
+      <c r="N163" s="18"/>
+      <c r="O163" s="18"/>
+      <c r="P163" s="18"/>
       <c r="Q163" s="18"/>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -6118,13 +6097,19 @@
       <c r="I164" s="18"/>
       <c r="J164" s="18"/>
       <c r="K164" s="18"/>
-      <c r="L164" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="M164" s="18"/>
-      <c r="N164" s="18"/>
-      <c r="O164" s="18"/>
-      <c r="P164" s="18"/>
+      <c r="L164" s="18"/>
+      <c r="M164" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="N164" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="O164" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="P164" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="Q164" s="18"/>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -6141,17 +6126,15 @@
       <c r="K165" s="18"/>
       <c r="L165" s="18"/>
       <c r="M165" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N165" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O165" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="P165" s="20" t="s">
-        <v>151</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="P165" s="21"/>
       <c r="Q165" s="18"/>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -6166,17 +6149,13 @@
       <c r="I166" s="18"/>
       <c r="J166" s="18"/>
       <c r="K166" s="18"/>
-      <c r="L166" s="18"/>
-      <c r="M166" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="N166" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="O166" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P166" s="21"/>
+      <c r="L166" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="M166" s="18"/>
+      <c r="N166" s="18"/>
+      <c r="O166" s="18"/>
+      <c r="P166" s="18"/>
       <c r="Q166" s="18"/>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -6191,13 +6170,19 @@
       <c r="I167" s="18"/>
       <c r="J167" s="18"/>
       <c r="K167" s="18"/>
-      <c r="L167" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="M167" s="18"/>
-      <c r="N167" s="18"/>
-      <c r="O167" s="18"/>
-      <c r="P167" s="18"/>
+      <c r="L167" s="18"/>
+      <c r="M167" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="N167" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="O167" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="P167" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="Q167" s="18"/>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -6214,17 +6199,15 @@
       <c r="K168" s="18"/>
       <c r="L168" s="18"/>
       <c r="M168" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N168" s="20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O168" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="P168" s="20" t="s">
-        <v>151</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="P168" s="21"/>
       <c r="Q168" s="18"/>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -6239,17 +6222,13 @@
       <c r="I169" s="18"/>
       <c r="J169" s="18"/>
       <c r="K169" s="18"/>
-      <c r="L169" s="18"/>
-      <c r="M169" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="N169" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="O169" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="P169" s="21"/>
+      <c r="L169" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="M169" s="18"/>
+      <c r="N169" s="18"/>
+      <c r="O169" s="18"/>
+      <c r="P169" s="18"/>
       <c r="Q169" s="18"/>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -6264,13 +6243,19 @@
       <c r="I170" s="18"/>
       <c r="J170" s="18"/>
       <c r="K170" s="18"/>
-      <c r="L170" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="M170" s="18"/>
-      <c r="N170" s="18"/>
-      <c r="O170" s="18"/>
-      <c r="P170" s="18"/>
+      <c r="L170" s="18"/>
+      <c r="M170" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="N170" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="O170" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="P170" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="Q170" s="18"/>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -6287,34 +6272,80 @@
       <c r="K171" s="18"/>
       <c r="L171" s="18"/>
       <c r="M171" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N171" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="O171" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P171" s="21"/>
+      <c r="Q171" s="18"/>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172" s="18"/>
+      <c r="B172" s="18"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="18"/>
+      <c r="E172" s="18"/>
+      <c r="F172" s="18"/>
+      <c r="G172" s="18"/>
+      <c r="H172" s="18"/>
+      <c r="I172" s="18"/>
+      <c r="J172" s="18"/>
+      <c r="K172" s="18"/>
+      <c r="L172" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="M172" s="18"/>
+      <c r="N172" s="18"/>
+      <c r="O172" s="18"/>
+      <c r="P172" s="18"/>
+      <c r="Q172" s="18"/>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A173" s="18"/>
+      <c r="B173" s="18"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="18"/>
+      <c r="E173" s="18"/>
+      <c r="F173" s="18"/>
+      <c r="G173" s="18"/>
+      <c r="H173" s="18"/>
+      <c r="I173" s="18"/>
+      <c r="J173" s="18"/>
+      <c r="K173" s="18"/>
+      <c r="L173" s="18"/>
+      <c r="M173" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="N171" s="20" t="s">
+      <c r="N173" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="O171" s="18" t="s">
+      <c r="O173" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="P171" s="20"/>
-      <c r="Q171" s="18"/>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F173"/>
-      <c r="G173"/>
-      <c r="H173"/>
-      <c r="I173"/>
-      <c r="J173"/>
-      <c r="K173"/>
-      <c r="L173"/>
-      <c r="M173" s="1" t="s">
+      <c r="P173" s="20"/>
+      <c r="Q173" s="18"/>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F175"/>
+      <c r="G175"/>
+      <c r="H175"/>
+      <c r="I175"/>
+      <c r="J175"/>
+      <c r="K175"/>
+      <c r="L175"/>
+      <c r="M175" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N173" s="12" t="s">
+      <c r="N175" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="O173"/>
-      <c r="P173"/>
-      <c r="Q173"/>
+      <c r="O175"/>
+      <c r="P175"/>
+      <c r="Q175"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="1" r:id="rId1"/>
@@ -838,12 +838,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>https://www.feedipedia.org/node/500, https://www.feedipedia.org/node/432</t>
-  </si>
-  <si>
-    <t>https://www.feedipedia.org/node/13883</t>
-  </si>
-  <si>
     <t>%DM accrding to harvest stat</t>
   </si>
   <si>
@@ -2270,6 +2264,12 @@
   </si>
   <si>
     <t>No domestic organic sugar production</t>
+  </si>
+  <si>
+    <t>https://www.feedipedia.org/node/13883, https://grovfoderverktyget.se/?p=31159</t>
+  </si>
+  <si>
+    <t>https://www.feedipedia.org/node/500, https://www.feedipedia.org/node/432, https://grovfoderverktyget.se/?p=31151</t>
   </si>
 </sst>
 </file>
@@ -3920,10 +3920,10 @@
     </row>
     <row r="47" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F47" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>24</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="J84" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>88</v>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J86" t="s">
         <v>60</v>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>54</v>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J88" t="s">
         <v>67</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J89" t="s">
         <v>70</v>
@@ -4554,12 +4554,12 @@
         <v>82</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J90" t="s">
         <v>71</v>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>74</v>
@@ -7050,8 +7050,13 @@
         <f>(8.3+8.7)/2</f>
         <v>8.5</v>
       </c>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
+      <c r="O8" s="55">
+        <v>61</v>
+      </c>
+      <c r="P8" s="67">
+        <f>P9</f>
+        <v>-19</v>
+      </c>
       <c r="Q8" s="55">
         <f>AVERAGE('ruminants, roughage'!H23:H24)</f>
         <v>10.75</v>
@@ -7086,7 +7091,7 @@
         <v>2.35</v>
       </c>
       <c r="Z8" s="51" t="s">
-        <v>203</v>
+        <v>680</v>
       </c>
       <c r="AA8" s="1" t="s">
         <v>202</v>
@@ -7253,8 +7258,12 @@
       <c r="N10" s="42">
         <v>11</v>
       </c>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
+      <c r="O10" s="42">
+        <v>84</v>
+      </c>
+      <c r="P10" s="42">
+        <v>-44</v>
+      </c>
       <c r="Q10" s="42">
         <f>AVERAGE('ruminants, roughage'!H25:H26)</f>
         <v>12.3</v>
@@ -7288,7 +7297,7 @@
         <v>1.03</v>
       </c>
       <c r="Z10" s="51" t="s">
-        <v>204</v>
+        <v>679</v>
       </c>
       <c r="AA10" s="23" t="s">
         <v>202</v>
@@ -7445,7 +7454,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="I12" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K12" s="28">
         <f>MATCH($B12,ruminants!$A$3:$A$120,0)</f>
@@ -7565,7 +7574,7 @@
       </c>
       <c r="AO12" s="13"/>
       <c r="AP12" s="64" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AQ12" s="1" t="s">
         <v>202</v>
@@ -7612,7 +7621,7 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="28">
@@ -7733,7 +7742,7 @@
       </c>
       <c r="AO13" s="13"/>
       <c r="AP13" s="64" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AQ13" s="1" t="s">
         <v>202</v>
@@ -7780,7 +7789,7 @@
         <v>0.54</v>
       </c>
       <c r="I14" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="28">
@@ -7901,7 +7910,7 @@
       </c>
       <c r="AO14" s="13"/>
       <c r="AP14" s="64" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AQ14" s="1" t="s">
         <v>202</v>
@@ -7948,7 +7957,7 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="I15" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="28">
@@ -8069,7 +8078,7 @@
       </c>
       <c r="AO15" s="13"/>
       <c r="AP15" s="64" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AQ15" s="1" t="s">
         <v>202</v>
@@ -8116,7 +8125,7 @@
         <v>0.55499999999999994</v>
       </c>
       <c r="I16" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="28">
@@ -8237,7 +8246,7 @@
       </c>
       <c r="AO16" s="13"/>
       <c r="AP16" s="64" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AQ16" s="1" t="s">
         <v>202</v>
@@ -8284,7 +8293,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="I17" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="28">
@@ -8403,7 +8412,7 @@
       </c>
       <c r="AO17" s="13"/>
       <c r="AP17" s="64" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AQ17" s="1" t="s">
         <v>202</v>
@@ -8450,7 +8459,7 @@
         <v>1.155</v>
       </c>
       <c r="I18" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="28">
@@ -8568,7 +8577,7 @@
       </c>
       <c r="AO18" s="13"/>
       <c r="AP18" s="64" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AQ18" s="1" t="s">
         <v>202</v>
@@ -8615,7 +8624,7 @@
         <v>1.375</v>
       </c>
       <c r="I19" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="28"/>
@@ -8670,7 +8679,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="Z19" s="51" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AA19" s="62"/>
       <c r="AB19" s="28">
@@ -8726,7 +8735,7 @@
       </c>
       <c r="AO19" s="13"/>
       <c r="AP19" s="64" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AQ19" s="1" t="s">
         <v>202</v>
@@ -8764,7 +8773,7 @@
         <v>0.90999999999999992</v>
       </c>
       <c r="I20" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="28">
@@ -8882,7 +8891,7 @@
       </c>
       <c r="AO20" s="13"/>
       <c r="AP20" s="64" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AQ20" s="1" t="s">
         <v>202</v>
@@ -8893,7 +8902,7 @@
         <v>16.8</v>
       </c>
       <c r="AU20" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="2:47" x14ac:dyDescent="0.25">
@@ -8925,7 +8934,7 @@
         <v>0.89500000000000002</v>
       </c>
       <c r="I21" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="28">
@@ -9043,7 +9052,7 @@
       </c>
       <c r="AO21" s="13"/>
       <c r="AP21" s="64" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AQ21" s="1" t="s">
         <v>202</v>
@@ -9131,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="51" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AA22" s="62"/>
       <c r="AB22" s="28">
@@ -9187,7 +9196,7 @@
       </c>
       <c r="AO22" s="13"/>
       <c r="AP22" s="64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AQ22" s="1" t="s">
         <v>202</v>
@@ -9435,7 +9444,7 @@
         <v>16</v>
       </c>
       <c r="AU24" s="23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="2:47" x14ac:dyDescent="0.25">
@@ -9583,7 +9592,7 @@
       </c>
       <c r="AO25" s="13"/>
       <c r="AP25" s="64" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AQ25" s="1" t="s">
         <v>202</v>
@@ -9683,7 +9692,7 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="Z26" s="51" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AA26" s="62"/>
       <c r="AB26" s="28">
@@ -9739,7 +9748,7 @@
       </c>
       <c r="AO26" s="13"/>
       <c r="AP26" s="64" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AQ26" s="1" t="s">
         <v>202</v>
@@ -9893,7 +9902,7 @@
       </c>
       <c r="AO27" s="13"/>
       <c r="AP27" s="64" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AQ27" s="1" t="s">
         <v>202</v>
@@ -10205,7 +10214,7 @@
       </c>
       <c r="AO29" s="13"/>
       <c r="AP29" s="64" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AQ29" s="1" t="s">
         <v>202</v>
@@ -10216,7 +10225,7 @@
         <v>8.6</v>
       </c>
       <c r="AU29" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:47" x14ac:dyDescent="0.25">
@@ -10450,7 +10459,7 @@
         <v>2.56</v>
       </c>
       <c r="Z31" s="51" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AA31" s="62"/>
       <c r="AB31" s="28"/>
@@ -10620,7 +10629,7 @@
       </c>
       <c r="AO32" s="13"/>
       <c r="AP32" s="64" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AQ32" s="1" t="s">
         <v>202</v>
@@ -10718,7 +10727,7 @@
         <v>0.62</v>
       </c>
       <c r="Z33" s="23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AA33" s="62"/>
       <c r="AB33" s="28">
@@ -10774,7 +10783,7 @@
       </c>
       <c r="AO33" s="13"/>
       <c r="AP33" s="64" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AQ33" s="1" t="s">
         <v>202</v>
@@ -11264,7 +11273,7 @@
       </c>
       <c r="AO37" s="13"/>
       <c r="AP37" s="64" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AQ37" s="1" t="s">
         <v>202</v>
@@ -11517,10 +11526,10 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AO39" s="51" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AP39" s="64" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AQ39" s="1" t="s">
         <v>202</v>
@@ -11531,7 +11540,7 @@
     </row>
     <row r="40" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C40" s="46">
         <f>AVERAGE(AC40,L40,AS40)</f>
@@ -11674,7 +11683,7 @@
       </c>
       <c r="AO40" s="51"/>
       <c r="AP40" s="64" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AQ40" s="1" t="s">
         <v>202</v>
@@ -11837,7 +11846,7 @@
       </c>
       <c r="AO41" s="13"/>
       <c r="AP41" s="64" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AQ41" s="1" t="s">
         <v>202</v>
@@ -11991,7 +12000,7 @@
       </c>
       <c r="AO42" s="13"/>
       <c r="AP42" s="64" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AQ42" s="1" t="s">
         <v>202</v>
@@ -12235,7 +12244,7 @@
         <v>2.1</v>
       </c>
       <c r="Z44" s="51" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA44" s="62"/>
       <c r="AB44" s="28">
@@ -12291,7 +12300,7 @@
       </c>
       <c r="AO44" s="13"/>
       <c r="AP44" s="64" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AQ44" s="1" t="s">
         <v>202</v>
@@ -12445,7 +12454,7 @@
       </c>
       <c r="AO45" s="13"/>
       <c r="AP45" s="64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AQ45" s="1" t="s">
         <v>202</v>
@@ -12655,7 +12664,7 @@
         <v>1.1900000000000002</v>
       </c>
       <c r="Z47" s="51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AA47" s="62"/>
       <c r="AB47" s="28">
@@ -12712,7 +12721,7 @@
       </c>
       <c r="AO47" s="13"/>
       <c r="AP47" s="64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AQ47" s="1" t="s">
         <v>202</v>
@@ -12732,7 +12741,7 @@
     </row>
     <row r="48" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B48" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C48" s="73">
         <f t="shared" si="24"/>
@@ -12802,7 +12811,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AA48" s="62"/>
       <c r="AB48" s="5"/>
@@ -12847,7 +12856,7 @@
     </row>
     <row r="50" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D50" s="87" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E50" s="88"/>
       <c r="F50" s="89"/>
@@ -12857,12 +12866,12 @@
       <c r="J50" s="89"/>
       <c r="K50" s="90"/>
       <c r="O50" s="91" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D51" s="39" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E51" s="52"/>
       <c r="F51" s="52"/>
@@ -12881,7 +12890,7 @@
         <v>46</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>59</v>
@@ -12889,7 +12898,7 @@
     </row>
     <row r="52" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D52" s="92" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="52"/>
@@ -12921,7 +12930,7 @@
     </row>
     <row r="53" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D53" s="95" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E53" s="96"/>
       <c r="F53" s="97"/>
@@ -12931,7 +12940,7 @@
       <c r="J53" s="97"/>
       <c r="K53" s="98"/>
       <c r="O53" s="91" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="4:19" x14ac:dyDescent="0.25">
@@ -12959,7 +12968,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1"/>
-    <hyperlink ref="Z10" r:id="rId2"/>
+    <hyperlink ref="Z10" r:id="rId2" display="https://www.feedipedia.org/node/13883"/>
     <hyperlink ref="AP12" r:id="rId3"/>
     <hyperlink ref="AP13" r:id="rId4"/>
     <hyperlink ref="AP14" r:id="rId5"/>
@@ -13014,7 +13023,7 @@
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -13034,7 +13043,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -13054,7 +13063,7 @@
         <v>17</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
@@ -13068,7 +13077,7 @@
         <v>17</v>
       </c>
       <c r="Z1" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
@@ -13082,7 +13091,7 @@
         <v>17</v>
       </c>
       <c r="AG1" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4"/>
@@ -13093,7 +13102,7 @@
         <v>29</v>
       </c>
       <c r="AM1" s="27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
@@ -13102,7 +13111,7 @@
       </c>
       <c r="AQ1" s="4"/>
       <c r="AS1" s="27" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -13121,19 +13130,19 @@
         <v>8</v>
       </c>
       <c r="D2" s="97" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="97" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="97" t="s">
         <v>251</v>
       </c>
-      <c r="E2" s="97" t="s">
+      <c r="G2" s="97" t="s">
         <v>252</v>
       </c>
-      <c r="F2" s="97" t="s">
+      <c r="H2" s="97" t="s">
         <v>253</v>
-      </c>
-      <c r="G2" s="97" t="s">
-        <v>254</v>
-      </c>
-      <c r="H2" s="97" t="s">
-        <v>255</v>
       </c>
       <c r="I2" s="52"/>
       <c r="J2" s="97" t="s">
@@ -13146,19 +13155,19 @@
         <v>8</v>
       </c>
       <c r="M2" s="97" t="s">
+        <v>254</v>
+      </c>
+      <c r="N2" s="97" t="s">
+        <v>255</v>
+      </c>
+      <c r="O2" s="97" t="s">
         <v>256</v>
       </c>
-      <c r="N2" s="97" t="s">
+      <c r="P2" s="97" t="s">
         <v>257</v>
       </c>
-      <c r="O2" s="97" t="s">
+      <c r="Q2" s="97" t="s">
         <v>258</v>
-      </c>
-      <c r="P2" s="97" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q2" s="97" t="s">
-        <v>260</v>
       </c>
       <c r="S2" s="97" t="s">
         <v>9</v>
@@ -13170,13 +13179,13 @@
         <v>8</v>
       </c>
       <c r="V2" s="97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="W2" s="97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="X2" s="97" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z2" s="97" t="s">
         <v>9</v>
@@ -13188,13 +13197,13 @@
         <v>8</v>
       </c>
       <c r="AC2" s="97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AD2" s="97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AE2" s="97" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG2" s="97" t="s">
         <v>9</v>
@@ -13206,10 +13215,10 @@
         <v>8</v>
       </c>
       <c r="AJ2" s="97" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AK2" s="97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM2" s="97" t="s">
         <v>9</v>
@@ -13221,10 +13230,10 @@
         <v>8</v>
       </c>
       <c r="AP2" s="97" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AQ2" s="97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AS2" s="97" t="s">
         <v>9</v>
@@ -13236,7 +13245,7 @@
         <v>8</v>
       </c>
       <c r="AV2" s="99" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.25">
@@ -13353,7 +13362,7 @@
         <v>83</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP3" s="89" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A3,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -13489,7 +13498,7 @@
         <v>83</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP4" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A4,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -13548,13 +13557,13 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
         <v>8.5</v>
       </c>
-      <c r="N5" s="52" t="str">
+      <c r="N5" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v/>
-      </c>
-      <c r="O5" s="52" t="str">
+        <v>61</v>
+      </c>
+      <c r="O5" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v/>
+        <v>-19</v>
       </c>
       <c r="P5" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
@@ -13625,7 +13634,7 @@
         <v>83</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP5" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A5,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -13761,7 +13770,7 @@
         <v>83</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP6" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A6,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -13820,13 +13829,13 @@
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),M$1)&lt;&gt;"",M$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),M$1), "")</f>
         <v>11</v>
       </c>
-      <c r="N7" s="52" t="str">
+      <c r="N7" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),N$1)&lt;&gt;"",N$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),N$1), "")</f>
-        <v/>
-      </c>
-      <c r="O7" s="52" t="str">
+        <v>84</v>
+      </c>
+      <c r="O7" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),O$1)&lt;&gt;"",O$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),O$1), "")</f>
-        <v/>
+        <v>-44</v>
       </c>
       <c r="P7" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),P$1)&lt;&gt;"",P$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),P$1), "")</f>
@@ -13897,7 +13906,7 @@
         <v>83</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP7" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A7,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14033,7 +14042,7 @@
         <v>83</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP8" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A8,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14170,7 +14179,7 @@
         <v>83</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP9" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A9,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14307,7 +14316,7 @@
         <v>83</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP10" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A10,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14444,7 +14453,7 @@
         <v>83</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP11" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A11,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14581,7 +14590,7 @@
         <v>83</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP12" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A12,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14718,7 +14727,7 @@
         <v>83</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP13" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A13,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14855,7 +14864,7 @@
         <v>83</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP14" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A14,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -14992,7 +15001,7 @@
         <v>83</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP15" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A15,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15129,7 +15138,7 @@
         <v>83</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP16" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A16,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15266,7 +15275,7 @@
         <v>83</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP17" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A17,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15403,7 +15412,7 @@
         <v>83</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP18" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A18,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15540,7 +15549,7 @@
         <v>83</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP19" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A19,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15677,7 +15686,7 @@
         <v>83</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP20" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A20,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15814,7 +15823,7 @@
         <v>83</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP21" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A21,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -15951,7 +15960,7 @@
         <v>83</v>
       </c>
       <c r="AO22" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP22" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A22,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16088,7 +16097,7 @@
         <v>83</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP23" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A23,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16225,7 +16234,7 @@
         <v>83</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP24" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A24,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16362,7 +16371,7 @@
         <v>83</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP25" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16499,7 +16508,7 @@
         <v>83</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP26" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A26,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16636,7 +16645,7 @@
         <v>83</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP27" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A27,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16773,7 +16782,7 @@
         <v>83</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP28" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A28,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -16910,7 +16919,7 @@
         <v>83</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP29" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A29,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17047,7 +17056,7 @@
         <v>83</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP30" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A30,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17184,7 +17193,7 @@
         <v>83</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP31" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A31,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17321,7 +17330,7 @@
         <v>83</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP32" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A32,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17456,7 +17465,7 @@
         <v>83</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP33" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A33,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17593,7 +17602,7 @@
         <v>83</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP34" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A34,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17730,7 +17739,7 @@
         <v>83</v>
       </c>
       <c r="AO35" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP35" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A35,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -17867,7 +17876,7 @@
         <v>83</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP36" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A36,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18004,7 +18013,7 @@
         <v>83</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP37" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A37,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18141,7 +18150,7 @@
         <v>83</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP38" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A38,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18278,7 +18287,7 @@
         <v>83</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP39" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A39,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18415,7 +18424,7 @@
         <v>83</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP40" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A40,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18552,7 +18561,7 @@
         <v>83</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP41" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A41,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18689,7 +18698,7 @@
         <v>83</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP42" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A42,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18832,7 +18841,7 @@
         <v>83</v>
       </c>
       <c r="AO43" s="52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP43" s="52" t="str">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A43,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -18973,7 +18982,7 @@
         <v>83</v>
       </c>
       <c r="AO44" s="42" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP44" s="52">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A44,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -19115,7 +19124,7 @@
         <v>83</v>
       </c>
       <c r="AO45" s="101" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP45" s="97">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AP$1)&lt;&gt;"",AP$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A45,'feed pars'!$B$6:$B$48,0),AP$1), "")</f>
@@ -19277,13 +19286,13 @@
         <v>178</v>
       </c>
       <c r="B2" s="103" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="103" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="103" t="s">
         <v>264</v>
-      </c>
-      <c r="C2" s="103" t="s">
-        <v>265</v>
-      </c>
-      <c r="D2" s="103" t="s">
-        <v>266</v>
       </c>
       <c r="E2" s="103" t="s">
         <v>197</v>
@@ -19292,109 +19301,109 @@
         <v>198</v>
       </c>
       <c r="G2" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="103" t="s">
+        <v>266</v>
+      </c>
+      <c r="I2" s="103" t="s">
         <v>267</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="J2" s="103" t="s">
         <v>268</v>
       </c>
-      <c r="I2" s="103" t="s">
+      <c r="K2" s="103" t="s">
         <v>269</v>
       </c>
-      <c r="J2" s="103" t="s">
+      <c r="L2" s="103" t="s">
         <v>270</v>
       </c>
-      <c r="K2" s="103" t="s">
+      <c r="M2" s="103" t="s">
         <v>271</v>
       </c>
-      <c r="L2" s="103" t="s">
+      <c r="N2" s="103" t="s">
         <v>272</v>
       </c>
-      <c r="M2" s="103" t="s">
+      <c r="O2" s="103" t="s">
         <v>273</v>
       </c>
-      <c r="N2" s="103" t="s">
+      <c r="P2" s="103" t="s">
         <v>274</v>
       </c>
-      <c r="O2" s="103" t="s">
+      <c r="Q2" s="103" t="s">
         <v>275</v>
       </c>
-      <c r="P2" s="103" t="s">
+      <c r="R2" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="Q2" s="103" t="s">
+      <c r="S2" s="103" t="s">
         <v>277</v>
       </c>
-      <c r="R2" s="103" t="s">
+      <c r="T2" s="103" t="s">
         <v>278</v>
       </c>
-      <c r="S2" s="103" t="s">
+      <c r="U2" s="103" t="s">
         <v>279</v>
       </c>
-      <c r="T2" s="103" t="s">
+      <c r="V2" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="U2" s="103" t="s">
+      <c r="W2" s="103" t="s">
         <v>281</v>
       </c>
-      <c r="V2" s="103" t="s">
+      <c r="X2" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="W2" s="103" t="s">
+      <c r="Y2" s="103" t="s">
         <v>283</v>
       </c>
-      <c r="X2" s="103" t="s">
+      <c r="Z2" s="103" t="s">
         <v>284</v>
       </c>
-      <c r="Y2" s="103" t="s">
+      <c r="AA2" s="103" t="s">
         <v>285</v>
       </c>
-      <c r="Z2" s="103" t="s">
+      <c r="AB2" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="AA2" s="103" t="s">
+      <c r="AC2" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="AB2" s="103" t="s">
+      <c r="AD2" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="AC2" s="103" t="s">
+      <c r="AE2" s="103" t="s">
         <v>289</v>
       </c>
-      <c r="AD2" s="103" t="s">
+      <c r="AF2" s="103" t="s">
         <v>290</v>
       </c>
-      <c r="AE2" s="103" t="s">
+      <c r="AG2" s="103" t="s">
         <v>291</v>
       </c>
-      <c r="AF2" s="103" t="s">
+      <c r="AH2" s="103" t="s">
         <v>292</v>
       </c>
-      <c r="AG2" s="103" t="s">
+      <c r="AI2" s="103" t="s">
         <v>293</v>
       </c>
-      <c r="AH2" s="103" t="s">
+      <c r="AJ2" s="103" t="s">
         <v>294</v>
       </c>
-      <c r="AI2" s="103" t="s">
+      <c r="AK2" s="103" t="s">
         <v>295</v>
       </c>
-      <c r="AJ2" s="103" t="s">
+      <c r="AL2" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="AK2" s="103" t="s">
+      <c r="AM2" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="AL2" s="103" t="s">
+      <c r="AN2" s="103" t="s">
         <v>298</v>
       </c>
-      <c r="AM2" s="103" t="s">
+      <c r="AO2" s="103" t="s">
         <v>299</v>
-      </c>
-      <c r="AN2" s="103" t="s">
-        <v>300</v>
-      </c>
-      <c r="AO2" s="103" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
@@ -19405,7 +19414,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="105" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D3" s="106">
         <v>11</v>
@@ -19507,7 +19516,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="108" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D4" s="109">
         <v>28</v>
@@ -19616,7 +19625,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="105" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D5" s="106">
         <v>90</v>
@@ -19727,7 +19736,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="108" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" s="109">
         <v>89</v>
@@ -19849,7 +19858,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="105" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D7" s="106">
         <v>8.1</v>
@@ -19959,7 +19968,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="108" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" s="109">
         <v>100</v>
@@ -20084,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="105" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" s="106">
         <v>92</v>
@@ -20206,7 +20215,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="108" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D10" s="109">
         <v>100</v>
@@ -20328,7 +20337,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="105" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D11" s="106">
         <v>90</v>
@@ -20450,7 +20459,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="108" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D12" s="109">
         <v>91</v>
@@ -20571,7 +20580,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="105" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D13" s="106">
         <v>87</v>
@@ -20693,7 +20702,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D14" s="109">
         <v>87</v>
@@ -20802,7 +20811,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="105" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D15" s="106">
         <v>87</v>
@@ -20927,7 +20936,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="108" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D16" s="109">
         <v>91</v>
@@ -21049,7 +21058,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D17" s="106">
         <v>90</v>
@@ -21171,7 +21180,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="108" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D18" s="109">
         <v>89</v>
@@ -21293,7 +21302,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="105" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D19" s="106">
         <v>91</v>
@@ -21415,7 +21424,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="108" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D20" s="109">
         <v>99.5</v>
@@ -21540,7 +21549,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D21" s="106">
         <v>87</v>
@@ -21662,7 +21671,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="108" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D22" s="109">
         <v>88</v>
@@ -21784,7 +21793,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="105" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D23" s="106">
         <v>88</v>
@@ -21903,13 +21912,13 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B24" s="107">
         <v>22</v>
       </c>
       <c r="C24" s="108" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D24" s="109">
         <v>90</v>
@@ -22034,7 +22043,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="105" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D25" s="106">
         <v>76</v>
@@ -22156,7 +22165,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="108" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D26" s="109">
         <v>74</v>
@@ -22278,7 +22287,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="105" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D27" s="106">
         <v>99.5</v>
@@ -22400,7 +22409,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="108" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D28" s="109">
         <v>88</v>
@@ -22522,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D29" s="106">
         <v>100</v>
@@ -22647,7 +22656,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="108" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D30" s="109">
         <v>100</v>
@@ -22772,7 +22781,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="105" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D31" s="106">
         <v>91</v>
@@ -22890,7 +22899,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D32" s="109">
         <v>16.5</v>
@@ -23007,7 +23016,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="105" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D33" s="106">
         <v>92</v>
@@ -23127,7 +23136,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="108" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D34" s="109">
         <v>18</v>
@@ -23238,7 +23247,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="105" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D35" s="106">
         <v>92</v>
@@ -23361,7 +23370,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="108" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D36" s="109">
         <v>89</v>
@@ -23481,7 +23490,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="105" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D37" s="106">
         <v>89</v>
@@ -23606,7 +23615,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="108" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D38" s="109">
         <v>89</v>
@@ -23728,7 +23737,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="105" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D39" s="106">
         <v>87</v>
@@ -23853,7 +23862,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="108" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D40" s="109">
         <v>87</v>
@@ -23978,7 +23987,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="105" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D41" s="106">
         <v>87</v>
@@ -24098,7 +24107,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="108" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D42" s="109">
         <v>100</v>
@@ -24220,7 +24229,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="105" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D43" s="106">
         <v>95</v>
@@ -24342,7 +24351,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="108" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D44" s="109">
         <v>88</v>
@@ -24461,7 +24470,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="105" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D45" s="106">
         <v>88</v>
@@ -24583,7 +24592,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D46" s="109">
         <v>88</v>
@@ -24708,7 +24717,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="105" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D47" s="106">
         <v>87</v>
@@ -24831,7 +24840,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="108" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D48" s="109">
         <v>90</v>
@@ -24953,7 +24962,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="105" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D49" s="106">
         <v>87</v>
@@ -25075,7 +25084,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="108" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D50" s="109">
         <v>99</v>
@@ -25197,7 +25206,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="105" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D51" s="106">
         <v>99</v>
@@ -25320,7 +25329,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="108" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D52" s="109">
         <v>5.5</v>
@@ -25442,7 +25451,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="105" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D53" s="106">
         <v>98</v>
@@ -25567,7 +25576,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="108" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D54" s="109">
         <v>97</v>
@@ -25692,7 +25701,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="105" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D55" s="106">
         <v>87</v>
@@ -25817,7 +25826,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="108" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D56" s="109">
         <v>88</v>
@@ -25942,7 +25951,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="105" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D57" s="106">
         <v>87</v>
@@ -26067,7 +26076,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="108" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D58" s="109">
         <v>87</v>
@@ -26190,7 +26199,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="105" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D59" s="106">
         <v>87</v>
@@ -26312,7 +26321,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="108" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D60" s="109">
         <v>12</v>
@@ -26594,16 +26603,16 @@
         <v>178</v>
       </c>
       <c r="B2" s="103" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="103" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="103" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="103" t="s">
-        <v>265</v>
-      </c>
-      <c r="D2" s="103" t="s">
-        <v>266</v>
-      </c>
       <c r="E2" s="103" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F2" s="103" t="s">
         <v>189</v>
@@ -26612,85 +26621,85 @@
         <v>190</v>
       </c>
       <c r="H2" s="103" t="s">
+        <v>359</v>
+      </c>
+      <c r="I2" s="103" t="s">
+        <v>360</v>
+      </c>
+      <c r="J2" s="103" t="s">
         <v>361</v>
       </c>
-      <c r="I2" s="103" t="s">
-        <v>362</v>
-      </c>
-      <c r="J2" s="103" t="s">
-        <v>363</v>
-      </c>
       <c r="K2" s="103" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L2" s="103" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M2" s="103" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N2" s="103" t="s">
         <v>195</v>
       </c>
       <c r="O2" s="103" t="s">
+        <v>362</v>
+      </c>
+      <c r="P2" s="103" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q2" s="103" t="s">
         <v>364</v>
       </c>
-      <c r="P2" s="103" t="s">
+      <c r="R2" s="103" t="s">
         <v>365</v>
       </c>
-      <c r="Q2" s="103" t="s">
+      <c r="S2" s="103" t="s">
         <v>366</v>
       </c>
-      <c r="R2" s="103" t="s">
+      <c r="T2" s="103" t="s">
         <v>367</v>
       </c>
-      <c r="S2" s="103" t="s">
+      <c r="U2" s="103" t="s">
         <v>368</v>
       </c>
-      <c r="T2" s="103" t="s">
+      <c r="V2" s="103" t="s">
         <v>369</v>
       </c>
-      <c r="U2" s="103" t="s">
+      <c r="W2" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="X2" s="103" t="s">
         <v>370</v>
       </c>
-      <c r="V2" s="103" t="s">
+      <c r="Y2" s="103" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z2" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA2" s="103" t="s">
         <v>371</v>
       </c>
-      <c r="W2" s="103" t="s">
-        <v>274</v>
-      </c>
-      <c r="X2" s="103" t="s">
+      <c r="AB2" s="103" t="s">
+        <v>289</v>
+      </c>
+      <c r="AC2" s="103" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD2" s="103" t="s">
+        <v>291</v>
+      </c>
+      <c r="AE2" s="103" t="s">
+        <v>292</v>
+      </c>
+      <c r="AF2" s="103" t="s">
+        <v>293</v>
+      </c>
+      <c r="AG2" s="103" t="s">
         <v>372</v>
       </c>
-      <c r="Y2" s="103" t="s">
-        <v>273</v>
-      </c>
-      <c r="Z2" s="103" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA2" s="103" t="s">
-        <v>373</v>
-      </c>
-      <c r="AB2" s="103" t="s">
-        <v>291</v>
-      </c>
-      <c r="AC2" s="103" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD2" s="103" t="s">
+      <c r="AH2" s="103" t="s">
         <v>293</v>
-      </c>
-      <c r="AE2" s="103" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF2" s="103" t="s">
-        <v>295</v>
-      </c>
-      <c r="AG2" s="103" t="s">
-        <v>374</v>
-      </c>
-      <c r="AH2" s="103" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
@@ -26698,7 +26707,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="106" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D3" s="106">
         <v>50</v>
@@ -26769,7 +26778,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D4" s="109">
         <v>85</v>
@@ -26840,7 +26849,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="106" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D5" s="106">
         <v>90</v>
@@ -26919,7 +26928,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D6" s="109">
         <v>90</v>
@@ -26990,7 +26999,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="106" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D7" s="106">
         <v>84</v>
@@ -27085,7 +27094,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" s="109">
         <v>14</v>
@@ -27174,7 +27183,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="106" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D9" s="106">
         <v>85</v>
@@ -27245,7 +27254,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D10" s="109">
         <v>92</v>
@@ -27332,7 +27341,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="106" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D11" s="106">
         <v>92</v>
@@ -27431,7 +27440,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D12" s="109">
         <v>92</v>
@@ -27514,7 +27523,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="106" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D13" s="106">
         <v>92</v>
@@ -27597,7 +27606,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D14" s="109">
         <v>90</v>
@@ -27692,7 +27701,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="106" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D15" s="106">
         <v>90</v>
@@ -27783,7 +27792,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D16" s="109">
         <v>99</v>
@@ -27862,7 +27871,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="106" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D17" s="106">
         <v>12</v>
@@ -27955,7 +27964,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D18" s="109">
         <v>90</v>
@@ -28030,7 +28039,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D19" s="106">
         <v>15</v>
@@ -28119,7 +28128,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D20" s="109">
         <v>16</v>
@@ -28210,7 +28219,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D21" s="106">
         <v>90</v>
@@ -28301,7 +28310,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D22" s="109">
         <v>89</v>
@@ -28392,7 +28401,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="106" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D23" s="106">
         <v>80</v>
@@ -28486,7 +28495,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D24" s="109">
         <v>85</v>
@@ -28585,7 +28594,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="106" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D25" s="106">
         <v>59</v>
@@ -28678,7 +28687,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="109" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D26" s="109">
         <v>74</v>
@@ -28761,7 +28770,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="106" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D27" s="106">
         <v>93</v>
@@ -28832,7 +28841,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D28" s="109">
         <v>37</v>
@@ -28924,7 +28933,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="106" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D29" s="106">
         <v>87</v>
@@ -29006,7 +29015,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="109" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D30" s="109">
         <v>85</v>
@@ -29110,7 +29119,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="106" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D31" s="106">
         <v>87</v>
@@ -29197,7 +29206,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="109" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D32" s="109">
         <v>87</v>
@@ -29288,7 +29297,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D33" s="106">
         <v>50</v>
@@ -29359,7 +29368,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="109" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D34" s="109">
         <v>82</v>
@@ -29446,7 +29455,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="106" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D35" s="106">
         <v>90</v>
@@ -29533,7 +29542,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D36" s="109">
         <v>88</v>
@@ -29624,7 +29633,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="106" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D37" s="106">
         <v>94</v>
@@ -29721,7 +29730,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="109" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D38" s="109">
         <v>92</v>
@@ -29814,7 +29823,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="106" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D39" s="106">
         <v>7</v>
@@ -29904,7 +29913,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="109" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D40" s="109">
         <v>90</v>
@@ -30001,7 +30010,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="106" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D41" s="106">
         <v>90</v>
@@ -30092,7 +30101,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="109" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D42" s="109">
         <v>37</v>
@@ -30189,7 +30198,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="106" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D43" s="106">
         <v>87</v>
@@ -30271,7 +30280,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="109" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D44" s="109">
         <v>87</v>
@@ -30372,7 +30381,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="106" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D45" s="106">
         <v>86</v>
@@ -30469,7 +30478,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="109" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D46" s="109">
         <v>12</v>
@@ -30567,7 +30576,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="106" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D47" s="106">
         <v>93</v>
@@ -30660,7 +30669,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="109" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D48" s="109">
         <v>90</v>
@@ -30755,7 +30764,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="106" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D49" s="106">
         <v>90</v>
@@ -30848,7 +30857,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="109" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D50" s="109">
         <v>87</v>
@@ -30941,7 +30950,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="106" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D51" s="106">
         <v>13</v>
@@ -31027,13 +31036,13 @@
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B52" s="107">
         <v>50</v>
       </c>
       <c r="C52" s="109" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D52" s="109">
         <v>92</v>
@@ -31135,7 +31144,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="106" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D53" s="106">
         <v>22</v>
@@ -31226,7 +31235,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D54" s="109">
         <v>32</v>
@@ -31326,7 +31335,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="106" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D55" s="106">
         <v>48</v>
@@ -31417,7 +31426,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="109" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D56" s="109">
         <v>87</v>
@@ -31514,7 +31523,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="106" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D57" s="106">
         <v>13</v>
@@ -31611,7 +31620,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="109" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D58" s="109">
         <v>8</v>
@@ -31705,7 +31714,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="106" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D59" s="106">
         <v>7</v>
@@ -31800,7 +31809,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="109" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D60" s="109">
         <v>6</v>
@@ -31895,7 +31904,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="106" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D61" s="106">
         <v>12</v>
@@ -31993,7 +32002,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="109" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D62" s="109">
         <v>91</v>
@@ -32088,7 +32097,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="106" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D63" s="106">
         <v>91</v>
@@ -32181,7 +32190,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="109" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D64" s="109">
         <v>6</v>
@@ -32271,7 +32280,7 @@
         <v>63</v>
       </c>
       <c r="C65" s="106" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D65" s="106">
         <v>23</v>
@@ -32370,7 +32379,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="109" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D66" s="109">
         <v>14</v>
@@ -32462,7 +32471,7 @@
         <v>65</v>
       </c>
       <c r="C67" s="106" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D67" s="106">
         <v>90</v>
@@ -32554,7 +32563,7 @@
         <v>66</v>
       </c>
       <c r="C68" s="109" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D68" s="109">
         <v>94</v>
@@ -32651,7 +32660,7 @@
         <v>67</v>
       </c>
       <c r="C69" s="106" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D69" s="106">
         <v>94</v>
@@ -32750,7 +32759,7 @@
         <v>68</v>
       </c>
       <c r="C70" s="109" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D70" s="109">
         <v>21</v>
@@ -32827,7 +32836,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="106" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D71" s="106">
         <v>90</v>
@@ -32929,7 +32938,7 @@
         <v>70</v>
       </c>
       <c r="C72" s="109" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D72" s="109">
         <v>90</v>
@@ -33031,7 +33040,7 @@
         <v>71</v>
       </c>
       <c r="C73" s="106" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D73" s="106">
         <v>93</v>
@@ -33130,7 +33139,7 @@
         <v>72</v>
       </c>
       <c r="C74" s="109" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D74" s="109">
         <v>35</v>
@@ -33211,7 +33220,7 @@
         <v>73</v>
       </c>
       <c r="C75" s="106" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D75" s="106">
         <v>89</v>
@@ -33304,7 +33313,7 @@
         <v>74</v>
       </c>
       <c r="C76" s="109" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D76" s="109">
         <v>87</v>
@@ -33399,7 +33408,7 @@
         <v>75</v>
       </c>
       <c r="C77" s="106" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D77" s="106">
         <v>9</v>
@@ -33493,7 +33502,7 @@
         <v>76</v>
       </c>
       <c r="C78" s="109" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D78" s="109">
         <v>87</v>
@@ -33587,7 +33596,7 @@
         <v>77</v>
       </c>
       <c r="C79" s="106" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D79" s="106">
         <v>87</v>
@@ -33685,7 +33694,7 @@
         <v>78</v>
       </c>
       <c r="C80" s="109" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D80" s="109">
         <v>87</v>
@@ -33782,7 +33791,7 @@
         <v>79</v>
       </c>
       <c r="C81" s="106" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D81" s="106">
         <v>78</v>
@@ -33869,7 +33878,7 @@
         <v>80</v>
       </c>
       <c r="C82" s="109" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D82" s="109">
         <v>93</v>
@@ -33940,7 +33949,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="106" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D83" s="106">
         <v>90</v>
@@ -34027,7 +34036,7 @@
         <v>82</v>
       </c>
       <c r="C84" s="109" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D84" s="109">
         <v>94</v>
@@ -34098,7 +34107,7 @@
         <v>83</v>
       </c>
       <c r="C85" s="106" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D85" s="106">
         <v>90</v>
@@ -34185,7 +34194,7 @@
         <v>84</v>
       </c>
       <c r="C86" s="109" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D86" s="109">
         <v>90</v>
@@ -34268,7 +34277,7 @@
         <v>85</v>
       </c>
       <c r="C87" s="106" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D87" s="106">
         <v>24</v>
@@ -34357,7 +34366,7 @@
         <v>86</v>
       </c>
       <c r="C88" s="109" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D88" s="109">
         <v>14</v>
@@ -34442,7 +34451,7 @@
         <v>87</v>
       </c>
       <c r="C89" s="106" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D89" s="106">
         <v>27</v>
@@ -34538,7 +34547,7 @@
         <v>88</v>
       </c>
       <c r="C90" s="109" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D90" s="109">
         <v>75</v>
@@ -34623,7 +34632,7 @@
         <v>89</v>
       </c>
       <c r="C91" s="106" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D91" s="106">
         <v>19</v>
@@ -34708,7 +34717,7 @@
         <v>90</v>
       </c>
       <c r="C92" s="109" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D92" s="109">
         <v>91</v>
@@ -34808,7 +34817,7 @@
         <v>91</v>
       </c>
       <c r="C93" s="106" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D93" s="106">
         <v>90</v>
@@ -34904,7 +34913,7 @@
         <v>92</v>
       </c>
       <c r="C94" s="109" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D94" s="109">
         <v>87</v>
@@ -35000,7 +35009,7 @@
         <v>93</v>
       </c>
       <c r="C95" s="106" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D95" s="106">
         <v>87</v>
@@ -35097,7 +35106,7 @@
         <v>94</v>
       </c>
       <c r="C96" s="109" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D96" s="109">
         <v>87</v>
@@ -35184,7 +35193,7 @@
         <v>95</v>
       </c>
       <c r="C97" s="106" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D97" s="106">
         <v>92</v>
@@ -35277,7 +35286,7 @@
         <v>96</v>
       </c>
       <c r="C98" s="109" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D98" s="109">
         <v>92</v>
@@ -35372,7 +35381,7 @@
         <v>97</v>
       </c>
       <c r="C99" s="106" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D99" s="106">
         <v>93</v>
@@ -35463,7 +35472,7 @@
         <v>98</v>
       </c>
       <c r="C100" s="109" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D100" s="109">
         <v>92</v>
@@ -35559,7 +35568,7 @@
         <v>99</v>
       </c>
       <c r="C101" s="106" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D101" s="106">
         <v>92</v>
@@ -35654,7 +35663,7 @@
         <v>100</v>
       </c>
       <c r="C102" s="109" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D102" s="109">
         <v>87</v>
@@ -35745,7 +35754,7 @@
         <v>101</v>
       </c>
       <c r="C103" s="106" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D103" s="106">
         <v>50</v>
@@ -35824,7 +35833,7 @@
         <v>102</v>
       </c>
       <c r="C104" s="109" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D104" s="109">
         <v>88</v>
@@ -35917,7 +35926,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="106" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D105" s="106">
         <v>50</v>
@@ -36002,7 +36011,7 @@
         <v>104</v>
       </c>
       <c r="C106" s="109" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D106" s="109">
         <v>89</v>
@@ -36073,7 +36082,7 @@
         <v>105</v>
       </c>
       <c r="C107" s="106" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D107" s="106">
         <v>98</v>
@@ -36154,7 +36163,7 @@
         <v>106</v>
       </c>
       <c r="C108" s="109" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D108" s="109">
         <v>93</v>
@@ -36221,7 +36230,7 @@
         <v>107</v>
       </c>
       <c r="C109" s="106" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D109" s="106">
         <v>90</v>
@@ -36292,7 +36301,7 @@
         <v>108</v>
       </c>
       <c r="C110" s="109" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D110" s="109">
         <v>85</v>
@@ -36366,7 +36375,7 @@
         <v>109</v>
       </c>
       <c r="C111" s="106" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D111" s="106">
         <v>90</v>
@@ -36459,7 +36468,7 @@
         <v>110</v>
       </c>
       <c r="C112" s="109" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D112" s="109">
         <v>87</v>
@@ -36549,7 +36558,7 @@
         <v>111</v>
       </c>
       <c r="C113" s="106" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D113" s="106">
         <v>87</v>
@@ -36649,7 +36658,7 @@
         <v>112</v>
       </c>
       <c r="C114" s="109" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D114" s="109">
         <v>87</v>
@@ -36748,7 +36757,7 @@
         <v>113</v>
       </c>
       <c r="C115" s="106" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D115" s="106">
         <v>87</v>
@@ -36827,7 +36836,7 @@
         <v>114</v>
       </c>
       <c r="C116" s="109" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D116" s="109">
         <v>19</v>
@@ -36925,7 +36934,7 @@
         <v>115</v>
       </c>
       <c r="C117" s="106" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D117" s="106">
         <v>87</v>
@@ -37024,7 +37033,7 @@
         <v>116</v>
       </c>
       <c r="C118" s="109" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D118" s="109">
         <v>31</v>
@@ -37107,7 +37116,7 @@
         <v>117</v>
       </c>
       <c r="C119" s="106" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D119" s="106">
         <v>31</v>
@@ -37190,7 +37199,7 @@
         <v>118</v>
       </c>
       <c r="C120" s="109" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D120" s="109">
         <v>18</v>
@@ -37288,13 +37297,13 @@
   <sheetData>
     <row r="2" spans="2:31" ht="57.75" x14ac:dyDescent="0.25">
       <c r="B2" s="103" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C2" s="103" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D2" s="103" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E2" s="103" t="s">
         <v>189</v>
@@ -37303,70 +37312,70 @@
         <v>190</v>
       </c>
       <c r="G2" s="103" t="s">
+        <v>491</v>
+      </c>
+      <c r="H2" s="103" t="s">
+        <v>492</v>
+      </c>
+      <c r="I2" s="103" t="s">
         <v>493</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="J2" s="103" t="s">
         <v>494</v>
       </c>
-      <c r="I2" s="103" t="s">
+      <c r="K2" s="103" t="s">
         <v>495</v>
       </c>
-      <c r="J2" s="103" t="s">
+      <c r="L2" s="103" t="s">
         <v>496</v>
       </c>
-      <c r="K2" s="103" t="s">
+      <c r="M2" s="103" t="s">
         <v>497</v>
       </c>
-      <c r="L2" s="103" t="s">
+      <c r="N2" s="103" t="s">
         <v>498</v>
       </c>
-      <c r="M2" s="103" t="s">
+      <c r="O2" s="103" t="s">
         <v>499</v>
       </c>
-      <c r="N2" s="103" t="s">
+      <c r="P2" s="103" t="s">
         <v>500</v>
       </c>
-      <c r="O2" s="103" t="s">
+      <c r="Q2" s="103" t="s">
         <v>501</v>
       </c>
-      <c r="P2" s="103" t="s">
+      <c r="R2" s="103" t="s">
         <v>502</v>
       </c>
-      <c r="Q2" s="103" t="s">
+      <c r="S2" s="103" t="s">
         <v>503</v>
       </c>
-      <c r="R2" s="103" t="s">
+      <c r="T2" s="103" t="s">
         <v>504</v>
       </c>
-      <c r="S2" s="103" t="s">
+      <c r="U2" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="V2" s="103" t="s">
         <v>505</v>
       </c>
-      <c r="T2" s="103" t="s">
-        <v>506</v>
-      </c>
-      <c r="U2" s="103" t="s">
-        <v>271</v>
-      </c>
-      <c r="V2" s="103" t="s">
-        <v>507</v>
-      </c>
       <c r="W2" s="103" t="s">
+        <v>289</v>
+      </c>
+      <c r="X2" s="103" t="s">
+        <v>290</v>
+      </c>
+      <c r="Y2" s="103" t="s">
         <v>291</v>
       </c>
-      <c r="X2" s="103" t="s">
+      <c r="Z2" s="103" t="s">
         <v>292</v>
       </c>
-      <c r="Y2" s="103" t="s">
+      <c r="AA2" s="103" t="s">
         <v>293</v>
       </c>
-      <c r="Z2" s="103" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA2" s="103" t="s">
-        <v>295</v>
-      </c>
       <c r="AB2" s="103" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.25">
@@ -37374,7 +37383,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="110" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D3" s="106">
         <v>9.4</v>
@@ -37443,7 +37452,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D4" s="109">
         <v>9.4</v>
@@ -37512,7 +37521,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="110" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D5" s="106">
         <v>6.1</v>
@@ -37581,7 +37590,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="111" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D6" s="109">
         <v>9.4</v>
@@ -37650,7 +37659,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="110" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D7" s="106">
         <v>10.5</v>
@@ -37719,7 +37728,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D8" s="109">
         <v>11.1</v>
@@ -37788,7 +37797,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="110" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D9" s="106">
         <v>11</v>
@@ -37862,7 +37871,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="111" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D10" s="109">
         <v>10.1</v>
@@ -37934,7 +37943,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="110" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D11" s="106">
         <v>9.5</v>
@@ -38002,7 +38011,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="111" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D12" s="109">
         <v>10.5</v>
@@ -38078,7 +38087,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="110" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D13" s="106">
         <v>10.8</v>
@@ -38152,7 +38161,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="111" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D14" s="109">
         <v>11.5</v>
@@ -38226,7 +38235,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="110" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D15" s="106">
         <v>9.8000000000000007</v>
@@ -38313,7 +38322,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="111" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D16" s="109">
         <v>9.8000000000000007</v>
@@ -38400,7 +38409,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="110" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D17" s="106">
         <v>9.3000000000000007</v>
@@ -38485,7 +38494,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="111" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D18" s="109">
         <v>9.3000000000000007</v>
@@ -38570,7 +38579,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="110" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D19" s="106">
         <v>10.199999999999999</v>
@@ -38655,7 +38664,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="111" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D20" s="109">
         <v>10.199999999999999</v>
@@ -38740,7 +38749,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="110" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D21" s="106">
         <v>10.9</v>
@@ -38823,7 +38832,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="111" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D22" s="109">
         <v>11.7</v>
@@ -38904,7 +38913,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="110" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D23" s="106">
         <v>8</v>
@@ -38983,7 +38992,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="111" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D24" s="109">
         <v>9.1999999999999993</v>
@@ -39066,7 +39075,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="110" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D25" s="106">
         <v>10.1</v>
@@ -39149,7 +39158,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="111" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D26" s="109">
         <v>10.3</v>
@@ -39232,7 +39241,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="110" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D27" s="106">
         <v>10.3</v>
@@ -39315,7 +39324,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="111" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D28" s="109">
         <v>10.1</v>
@@ -39396,7 +39405,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="110" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D29" s="106">
         <v>10.199999999999999</v>
@@ -39477,7 +39486,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="111" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D30" s="109">
         <v>10.1</v>
@@ -39558,7 +39567,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="110" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D31" s="106">
         <v>10.199999999999999</v>
@@ -39641,7 +39650,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="111" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D32" s="109">
         <v>9.9</v>
@@ -39722,7 +39731,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="110" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D33" s="106">
         <v>9.1</v>
@@ -39803,7 +39812,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="111" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D34" s="109">
         <v>9.3000000000000007</v>
@@ -39884,7 +39893,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="110" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D35" s="106">
         <v>9.1999999999999993</v>
@@ -39965,7 +39974,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="111" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D36" s="109">
         <v>9.4</v>
@@ -40038,7 +40047,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="110" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D37" s="106">
         <v>10.199999999999999</v>
@@ -40125,7 +40134,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="111" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D38" s="109">
         <v>10.199999999999999</v>
@@ -40212,7 +40221,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="110" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D39" s="106">
         <v>9.8000000000000007</v>
@@ -40297,7 +40306,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="111" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D40" s="109">
         <v>9.8000000000000007</v>
@@ -40382,7 +40391,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="110" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D41" s="106">
         <v>10.7</v>
@@ -40467,7 +40476,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="111" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D42" s="109">
         <v>10.7</v>
@@ -40552,7 +40561,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="110" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D43" s="106">
         <v>9.9</v>
@@ -40637,7 +40646,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="111" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D44" s="109">
         <v>9.9</v>
@@ -40722,7 +40731,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="110" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D45" s="106">
         <v>9.5</v>
@@ -40807,7 +40816,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="111" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D46" s="109">
         <v>9.3000000000000007</v>
@@ -40892,7 +40901,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="110" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D47" s="106">
         <v>10.4</v>
@@ -40977,7 +40986,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="111" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D48" s="109">
         <v>10.4</v>
@@ -41062,7 +41071,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="110" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D49" s="106">
         <v>10.199999999999999</v>
@@ -41149,7 +41158,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="111" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D50" s="109">
         <v>10.199999999999999</v>
@@ -41236,7 +41245,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="110" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D51" s="106">
         <v>9.5</v>
@@ -41321,7 +41330,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="111" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D52" s="109">
         <v>9.5</v>
@@ -41406,7 +41415,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="110" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D53" s="106">
         <v>11</v>
@@ -41491,7 +41500,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="111" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D54" s="109">
         <v>11</v>
@@ -41576,7 +41585,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="110" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D55" s="106">
         <v>10.6</v>
@@ -41661,7 +41670,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="111" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D56" s="109">
         <v>10.6</v>
@@ -41746,7 +41755,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="110" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D57" s="106">
         <v>10.199999999999999</v>
@@ -41831,7 +41840,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="111" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D58" s="109">
         <v>10.199999999999999</v>
@@ -41916,7 +41925,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="110" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D59" s="106">
         <v>11</v>
@@ -42001,7 +42010,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="111" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D60" s="109">
         <v>11</v>
@@ -42086,7 +42095,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="110" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D61" s="106">
         <v>10.5</v>
@@ -42183,43 +42192,43 @@
         <v>178</v>
       </c>
       <c r="B2" s="103" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C2" s="103" t="s">
+        <v>565</v>
+      </c>
+      <c r="D2" s="103" t="s">
+        <v>566</v>
+      </c>
+      <c r="E2" s="103" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="103" t="s">
+      <c r="F2" s="103" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="103" t="s">
+      <c r="G2" s="103" t="s">
         <v>569</v>
       </c>
-      <c r="F2" s="103" t="s">
+      <c r="H2" s="103" t="s">
         <v>570</v>
       </c>
-      <c r="G2" s="103" t="s">
+      <c r="I2" s="103" t="s">
         <v>571</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="J2" s="103" t="s">
         <v>572</v>
       </c>
-      <c r="I2" s="103" t="s">
+      <c r="K2" s="103" t="s">
         <v>573</v>
       </c>
-      <c r="J2" s="103" t="s">
+      <c r="L2" s="103" t="s">
         <v>574</v>
       </c>
-      <c r="K2" s="103" t="s">
+      <c r="M2" s="103" t="s">
         <v>575</v>
       </c>
-      <c r="L2" s="103" t="s">
+      <c r="N2" s="103" t="s">
         <v>576</v>
-      </c>
-      <c r="M2" s="103" t="s">
-        <v>577</v>
-      </c>
-      <c r="N2" s="103" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -42227,7 +42236,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="106" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D3" s="106">
         <v>50</v>
@@ -42266,7 +42275,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D4" s="109">
         <v>85</v>
@@ -42305,7 +42314,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="106" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D5" s="106">
         <v>90</v>
@@ -42346,7 +42355,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D6" s="109">
         <v>90</v>
@@ -42387,7 +42396,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="106" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D7" s="106">
         <v>90</v>
@@ -42428,7 +42437,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D8" s="109">
         <v>90</v>
@@ -42469,7 +42478,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="106" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D9" s="106">
         <v>8</v>
@@ -42510,7 +42519,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D10" s="109">
         <v>91</v>
@@ -42551,7 +42560,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="106" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D11" s="106">
         <v>94</v>
@@ -42592,7 +42601,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D12" s="109">
         <v>91</v>
@@ -42633,7 +42642,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="106" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D13" s="106">
         <v>90</v>
@@ -42674,7 +42683,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D14" s="109">
         <v>87</v>
@@ -42713,7 +42722,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="106" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D15" s="106">
         <v>87</v>
@@ -42754,7 +42763,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D16" s="109">
         <v>87</v>
@@ -42795,7 +42804,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="106" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D17" s="106">
         <v>82</v>
@@ -42834,7 +42843,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D18" s="109">
         <v>87</v>
@@ -42869,7 +42878,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D19" s="106">
         <v>87</v>
@@ -42910,7 +42919,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D20" s="109">
         <v>93</v>
@@ -42951,7 +42960,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D21" s="106">
         <v>90</v>
@@ -42992,7 +43001,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D22" s="109">
         <v>87</v>
@@ -43033,7 +43042,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="106" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D23" s="106">
         <v>87</v>
@@ -43074,7 +43083,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D24" s="109">
         <v>92</v>
@@ -43115,7 +43124,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="106" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D25" s="106">
         <v>9</v>
@@ -43156,7 +43165,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="109" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D26" s="109">
         <v>12</v>
@@ -43197,7 +43206,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="106" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D27" s="106">
         <v>91</v>
@@ -43238,7 +43247,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="109" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D28" s="109">
         <v>90</v>
@@ -43279,7 +43288,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="106" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D29" s="106">
         <v>94</v>
@@ -43320,7 +43329,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="109" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D30" s="109">
         <v>94</v>
@@ -43361,7 +43370,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="106" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D31" s="106">
         <v>93</v>
@@ -43402,7 +43411,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="109" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D32" s="109">
         <v>87</v>
@@ -43443,7 +43452,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D33" s="106">
         <v>89</v>
@@ -43484,7 +43493,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="109" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D34" s="109">
         <v>87</v>
@@ -43525,7 +43534,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="106" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D35" s="106">
         <v>87</v>
@@ -43566,7 +43575,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D36" s="109">
         <v>87</v>
@@ -43607,7 +43616,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="106" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D37" s="106">
         <v>78</v>
@@ -43648,7 +43657,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="109" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D38" s="109">
         <v>75</v>
@@ -43689,7 +43698,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="106" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D39" s="106">
         <v>91</v>
@@ -43730,7 +43739,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="109" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D40" s="109">
         <v>90</v>
@@ -43771,7 +43780,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="106" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D41" s="106">
         <v>87</v>
@@ -43812,7 +43821,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="109" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D42" s="109">
         <v>87</v>
@@ -43853,7 +43862,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="106" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D43" s="106">
         <v>92</v>
@@ -43894,7 +43903,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="109" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D44" s="109">
         <v>92</v>
@@ -43935,7 +43944,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="106" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D45" s="106">
         <v>87</v>
@@ -43976,7 +43985,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="109" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D46" s="109">
         <v>90</v>
@@ -44017,7 +44026,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="106" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D47" s="106">
         <v>90</v>
@@ -44058,7 +44067,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="109" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D48" s="109">
         <v>88</v>
@@ -44099,7 +44108,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="106" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D49" s="106">
         <v>89</v>
@@ -44138,7 +44147,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="109" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D50" s="109">
         <v>100</v>
@@ -44179,7 +44188,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="106" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D51" s="106">
         <v>87</v>
@@ -44220,7 +44229,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="109" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D52" s="109">
         <v>87</v>
@@ -44261,7 +44270,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="106" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D53" s="106">
         <v>87</v>
@@ -44302,7 +44311,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="109" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D54" s="109">
         <v>87</v>
@@ -44341,7 +44350,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="106" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D55" s="106">
         <v>87</v>
@@ -44382,7 +44391,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="109" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D56" s="109">
         <v>87</v>
@@ -44494,64 +44503,64 @@
         <v>178</v>
       </c>
       <c r="B2" s="103" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C2" s="103" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D2" s="103" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E2" s="103" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F2" s="103" t="s">
+        <v>628</v>
+      </c>
+      <c r="G2" s="103" t="s">
+        <v>629</v>
+      </c>
+      <c r="H2" s="103" t="s">
         <v>630</v>
       </c>
-      <c r="G2" s="103" t="s">
+      <c r="I2" s="103" t="s">
         <v>631</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="J2" s="103" t="s">
         <v>632</v>
       </c>
-      <c r="I2" s="103" t="s">
+      <c r="K2" s="103" t="s">
         <v>633</v>
       </c>
-      <c r="J2" s="103" t="s">
+      <c r="L2" s="103" t="s">
+        <v>271</v>
+      </c>
+      <c r="M2" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="N2" s="103" t="s">
+        <v>268</v>
+      </c>
+      <c r="O2" s="103" t="s">
+        <v>289</v>
+      </c>
+      <c r="P2" s="103" t="s">
         <v>634</v>
       </c>
-      <c r="K2" s="103" t="s">
+      <c r="Q2" s="103" t="s">
         <v>635</v>
       </c>
-      <c r="L2" s="103" t="s">
-        <v>273</v>
-      </c>
-      <c r="M2" s="103" t="s">
-        <v>274</v>
-      </c>
-      <c r="N2" s="103" t="s">
-        <v>270</v>
-      </c>
-      <c r="O2" s="103" t="s">
-        <v>291</v>
-      </c>
-      <c r="P2" s="103" t="s">
+      <c r="R2" s="103" t="s">
+        <v>292</v>
+      </c>
+      <c r="S2" s="103" t="s">
+        <v>293</v>
+      </c>
+      <c r="T2" s="103" t="s">
         <v>636</v>
       </c>
-      <c r="Q2" s="103" t="s">
+      <c r="U2" s="103" t="s">
         <v>637</v>
-      </c>
-      <c r="R2" s="103" t="s">
-        <v>294</v>
-      </c>
-      <c r="S2" s="103" t="s">
-        <v>295</v>
-      </c>
-      <c r="T2" s="103" t="s">
-        <v>638</v>
-      </c>
-      <c r="U2" s="103" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -44562,7 +44571,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="106" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D3" s="106">
         <v>99</v>
@@ -44624,7 +44633,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D4" s="109">
         <v>99</v>
@@ -44686,7 +44695,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="106" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D5" s="106">
         <v>100</v>
@@ -44748,7 +44757,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D6" s="109">
         <v>100</v>
@@ -44810,7 +44819,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="106" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D7" s="106">
         <v>100</v>
@@ -44875,7 +44884,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D8" s="109">
         <v>92</v>
@@ -44937,7 +44946,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="106" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D9" s="106">
         <v>92</v>
@@ -44999,7 +45008,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D10" s="109">
         <v>92</v>
@@ -45061,7 +45070,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="106" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D11" s="106">
         <v>100</v>
@@ -45126,7 +45135,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D12" s="109">
         <v>87</v>
@@ -45188,7 +45197,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="106" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D13" s="106">
         <v>87</v>
@@ -45250,7 +45259,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D14" s="109">
         <v>87</v>
@@ -45312,7 +45321,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="106" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D15" s="106">
         <v>87</v>
@@ -45374,7 +45383,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="109" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D16" s="109">
         <v>87</v>
@@ -45436,7 +45445,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="106" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D17" s="106">
         <v>100</v>
@@ -45501,7 +45510,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D18" s="109">
         <v>87</v>
@@ -45563,7 +45572,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D19" s="106">
         <v>87</v>
@@ -45625,7 +45634,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D20" s="109">
         <v>87</v>
@@ -45687,7 +45696,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D21" s="106">
         <v>95</v>
@@ -45749,7 +45758,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D22" s="109">
         <v>93</v>
@@ -45811,7 +45820,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="106" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D23" s="106">
         <v>93</v>
@@ -45873,7 +45882,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D24" s="109">
         <v>90</v>
@@ -45935,7 +45944,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="106" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D25" s="106">
         <v>100</v>
@@ -46000,7 +46009,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="109" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D26" s="109">
         <v>87</v>
@@ -46059,13 +46068,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B27" s="104">
         <v>25</v>
       </c>
       <c r="C27" s="106" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D27" s="106">
         <v>87</v>
@@ -46127,7 +46136,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="109" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D28" s="109">
         <v>100</v>
@@ -46189,7 +46198,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="106" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D29" s="106">
         <v>100</v>
@@ -46254,7 +46263,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="109" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D30" s="109">
         <v>90</v>
@@ -46319,7 +46328,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="106" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D31" s="106">
         <v>90</v>
@@ -46384,7 +46393,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="109" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D32" s="109">
         <v>87</v>
@@ -46449,7 +46458,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D33" s="106">
         <v>89</v>
@@ -46511,7 +46520,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="109" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D34" s="109">
         <v>99</v>
@@ -46576,7 +46585,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="106" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D35" s="106">
         <v>87</v>
@@ -46638,7 +46647,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D36" s="109">
         <v>99</v>
@@ -46703,7 +46712,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="106" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D37" s="106">
         <v>87</v>
@@ -46768,7 +46777,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="109" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D38" s="109">
         <v>87</v>
@@ -46830,7 +46839,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="106" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D39" s="106">
         <v>87</v>
@@ -46895,7 +46904,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="109" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D40" s="109">
         <v>87</v>
@@ -46960,7 +46969,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="106" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D41" s="106">
         <v>87</v>

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="horses" sheetId="8" r:id="rId8"/>
     <sheet name="poultry" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="682">
   <si>
     <t>Statistics Netherlands (2012) Standardised calculation methods for animal manure and nutrients. Standard data 1990–2008</t>
   </si>
@@ -2270,6 +2270,9 @@
   </si>
   <si>
     <t>https://www.feedipedia.org/node/500, https://www.feedipedia.org/node/432, https://grovfoderverktyget.se/?p=31151</t>
+  </si>
+  <si>
+    <t>https://www.feedipedia.org/node/12502</t>
   </si>
 </sst>
 </file>
@@ -2697,7 +2700,7 @@
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -2841,6 +2844,7 @@
     <xf numFmtId="1" fontId="29" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -10067,7 +10071,12 @@
       <c r="AP28" s="64"/>
       <c r="AR28" s="28"/>
       <c r="AS28" s="39"/>
-      <c r="AT28" s="65"/>
+      <c r="AT28" s="65">
+        <v>10.5</v>
+      </c>
+      <c r="AU28" s="115" t="s">
+        <v>681</v>
+      </c>
     </row>
     <row r="29" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
@@ -13003,10 +13012,11 @@
     <hyperlink ref="Z47" r:id="rId34"/>
     <hyperlink ref="AP47" r:id="rId35"/>
     <hyperlink ref="D52" r:id="rId36"/>
+    <hyperlink ref="AU28" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId37"/>
+  <legacyDrawing r:id="rId38"/>
 </worksheet>
 </file>
 
@@ -13019,6 +13029,7 @@
     <col min="2" max="3" width="10.140625" style="1" customWidth="1"/>
     <col min="4" max="9" width="12.28515625" style="1" customWidth="1"/>
     <col min="10" max="24" width="8.85546875" style="1" customWidth="1"/>
+    <col min="45" max="45" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -16388,9 +16399,9 @@
       <c r="AT25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AV25" s="42" t="str">
+      <c r="AV25" s="42">
         <f>IF(AND(INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AV$1)&lt;&gt;"",AV$1&lt;&gt;""), INDEX('feed pars'!$C$6:$AT$48,MATCH($A25,'feed pars'!$B$6:$B$48,0),AV$1), "")</f>
-        <v/>
+        <v>10.5</v>
       </c>
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.25">

--- a/data/default/FeedMgmt.xlsx
+++ b/data/default/FeedMgmt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D1DBCA-15B1-4B74-9490-01EE36603292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19BF084-01D8-48DC-B211-7CE17313D69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="14265" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="2100" windowWidth="13710" windowHeight="8700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="1" r:id="rId1"/>
@@ -157,8 +157,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="667">
   <si>
     <t>Statistics Netherlands (2012) Standardised calculation methods for animal manure and nutrients. Standard data 1990–2008</t>
   </si>
@@ -2234,6 +2256,12 @@
   </si>
   <si>
     <t>https://doi.org/10.1080/09064702.2021.1993319</t>
+  </si>
+  <si>
+    <t>0.38 kg oil + 0.60 kg meal per kg rapeseed</t>
+  </si>
+  <si>
+    <t>See DemandAndConversions</t>
   </si>
 </sst>
 </file>
@@ -3126,7 +3154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q156"/>
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -3134,7 +3162,7 @@
     <col min="9" max="9" width="19.5703125" customWidth="1"/>
     <col min="10" max="11" width="20.140625" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" customWidth="1"/>
     <col min="14" max="14" width="25.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" customWidth="1"/>
     <col min="16" max="16" width="38.140625" customWidth="1"/>
@@ -3232,32 +3260,29 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="M4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F5,'feed pars'!B$6:B$49,0))</f>
-        <v>1</v>
-      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
         <v>28</v>
@@ -3272,7 +3297,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" t="s">
         <v>28</v>
@@ -3287,7 +3312,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
         <v>28</v>
@@ -3302,10 +3327,10 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M9" t="s">
         <v>24</v>
@@ -3317,54 +3342,54 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>653</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M10" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F10,'feed pars'!B$6:B$49,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>34</v>
+        <v>653</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M11" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F11,'feed pars'!B$6:B$49,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
         <v>24</v>
       </c>
       <c r="N12" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F12,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1627906976744187</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M13" t="s">
         <v>24</v>
@@ -3376,10 +3401,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
         <v>24</v>
@@ -3391,10 +3416,10 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M15" t="s">
         <v>24</v>
@@ -3406,10 +3431,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M16" t="s">
         <v>24</v>
@@ -3419,12 +3444,12 @@
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M17" t="s">
         <v>24</v>
@@ -3434,24 +3459,24 @@
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M18" t="s">
         <v>24</v>
       </c>
       <c r="N18" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F18,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1764705882352942</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.1627906976744187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
-        <v>655</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
         <v>41</v>
@@ -3460,71 +3485,69 @@
         <v>24</v>
       </c>
       <c r="N19" s="8">
-        <f>N18/0.2</f>
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F19,'feed pars'!B$6:B$49,0))</f>
+        <v>1.1764705882352942</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>655</v>
+      </c>
+      <c r="I20" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" s="8">
+        <f>N19/0.2</f>
         <v>5.8823529411764701</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P20" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F20" s="9" t="s">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F21" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9" t="s">
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="N20" s="8"/>
-      <c r="P20" s="9" t="s">
+      <c r="N21" s="8"/>
+      <c r="P21" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F21" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
         <v>42</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I22" t="s">
         <v>42</v>
-      </c>
-      <c r="M21" t="s">
-        <v>24</v>
-      </c>
-      <c r="N21" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F21,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1764705882352942</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" t="s">
-        <v>43</v>
       </c>
       <c r="M22" t="s">
         <v>24</v>
       </c>
       <c r="N22" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F22,'feed pars'!B$6:B$49,0))</f>
-        <v>1.0989010989010988</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.1764705882352942</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M23" t="s">
         <v>24</v>
@@ -3534,176 +3557,181 @@
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F24" s="9" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N24" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F24,'feed pars'!B$6:B$49,0))</f>
+        <v>1.0989010989010988</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F25" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9" t="s">
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9" t="s">
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="10">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F24,'feed pars'!B$6:B$49,0))*1/0.38</f>
+      <c r="N25" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F25,'feed pars'!B$6:B$49,0))*1/0.38</f>
         <v>2.6315789473684212</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F25" s="9" t="s">
+      <c r="P25" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F26" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" s="8"/>
-      <c r="P25" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F26" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
       <c r="M26" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N26" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F26,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1494252873563218</v>
-      </c>
-      <c r="O26" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="N26" s="8" cm="1">
+        <f t="array" ref="N26">1/_xlfn.SINGLE(INDEX('feed pars'!C$6:C$49/100,MATCH(F26,'feed pars'!B$6:B$49,0)))*1/0.6</f>
+        <v>1.6666666666666667</v>
+      </c>
       <c r="P26" s="9"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="11"/>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F27" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="8"/>
+      <c r="M27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F27,'feed pars'!B$6:B$49,0))</f>
+        <v>1.1494252873563218</v>
+      </c>
       <c r="O27" s="11"/>
       <c r="P27" s="9"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F28" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="9"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
         <v>51</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J29" t="s">
         <v>51</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M29" t="s">
         <v>24</v>
       </c>
-      <c r="N28" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F28,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N29" s="10">
+      <c r="N29" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F29,'feed pars'!B$6:B$49,0))</f>
         <v>1.1428571428571428</v>
       </c>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9" t="s">
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" s="10">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F30,'feed pars'!B$6:B$49,0))</f>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F30" t="s">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
         <v>46</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J31" t="s">
         <v>46</v>
-      </c>
-      <c r="M30" t="s">
-        <v>24</v>
-      </c>
-      <c r="N30" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F30,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1173184357541899</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-      <c r="J31" t="s">
-        <v>54</v>
       </c>
       <c r="M31" t="s">
         <v>24</v>
       </c>
       <c r="N31" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F31,'feed pars'!B$6:B$49,0))</f>
-        <v>1.0928961748633879</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.1173184357541899</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M32" t="s">
         <v>24</v>
       </c>
       <c r="N32" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F32,'feed pars'!B$6:B$49,0))</f>
-        <v>1.0989010989010988</v>
+        <v>1.0928961748633879</v>
       </c>
     </row>
     <row r="33" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M33" t="s">
         <v>24</v>
@@ -3714,47 +3742,47 @@
       </c>
     </row>
     <row r="34" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F34" s="9" t="s">
+      <c r="F34" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F34,'feed pars'!B$6:B$49,0))</f>
+        <v>1.0989010989010988</v>
+      </c>
+    </row>
+    <row r="35" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F35" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9" t="s">
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9" t="s">
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N34" s="10">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F34,'feed pars'!B$6:B$49,0))</f>
+      <c r="N35" s="10">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F35,'feed pars'!B$6:B$49,0))</f>
         <v>1.1111111111111112</v>
       </c>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9" t="s">
+      <c r="O35" s="9"/>
+      <c r="P35" s="9" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" t="s">
-        <v>60</v>
-      </c>
-      <c r="M35" t="s">
-        <v>24</v>
-      </c>
-      <c r="N35" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F35,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1494252873563218</v>
       </c>
     </row>
     <row r="36" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J36" t="s">
         <v>60</v>
@@ -3764,27 +3792,27 @@
       </c>
       <c r="N36" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F36,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1389521640091116</v>
+        <v>1.1494252873563218</v>
       </c>
     </row>
     <row r="37" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M37" t="s">
         <v>24</v>
       </c>
       <c r="N37" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F37,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1415525114155252</v>
+        <v>1.1389521640091116</v>
       </c>
     </row>
     <row r="38" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J38" t="s">
         <v>63</v>
@@ -3799,10 +3827,10 @@
     </row>
     <row r="39" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J39" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M39" t="s">
         <v>24</v>
@@ -3814,22 +3842,22 @@
     </row>
     <row r="40" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J40" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M40" t="s">
         <v>24</v>
       </c>
       <c r="N40" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F40,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1111111111111112</v>
+        <v>1.1415525114155252</v>
       </c>
     </row>
     <row r="41" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J41" t="s">
         <v>67</v>
@@ -3838,73 +3866,73 @@
         <v>24</v>
       </c>
       <c r="N41" s="8">
-        <f>N40</f>
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F41,'feed pars'!B$6:B$49,0))</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="42" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M42" t="s">
         <v>24</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="8">
+        <f>N41</f>
+        <v>1.1111111111111112</v>
+      </c>
+    </row>
+    <row r="43" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
+        <v>69</v>
+      </c>
+      <c r="J43" t="s">
+        <v>69</v>
+      </c>
+      <c r="M43" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" s="10">
         <f>1/0.25</f>
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F43" t="s">
-        <v>70</v>
-      </c>
-      <c r="J43" t="s">
-        <v>70</v>
-      </c>
-      <c r="M43" t="s">
-        <v>24</v>
-      </c>
-      <c r="N43" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F43,'feed pars'!B$6:B$49,0))</f>
-        <v>1.3245033112582782</v>
-      </c>
-    </row>
     <row r="44" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M44" t="s">
         <v>24</v>
       </c>
       <c r="N44" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F44,'feed pars'!B$6:B$49,0))</f>
-        <v>1.1173184357541899</v>
+        <v>1.3245033112582782</v>
       </c>
     </row>
     <row r="45" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M45" t="s">
         <v>24</v>
       </c>
       <c r="N45" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F45,'feed pars'!B$6:B$49,0))</f>
-        <v>16</v>
+        <v>1.1173184357541899</v>
       </c>
     </row>
     <row r="46" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J46" t="s">
         <v>72</v>
@@ -3912,171 +3940,172 @@
       <c r="M46" t="s">
         <v>24</v>
       </c>
-      <c r="N46" s="10">
-        <f>N45</f>
+      <c r="N46" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F46,'feed pars'!B$6:B$49,0))</f>
         <v>16</v>
       </c>
     </row>
     <row r="47" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J47" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M47" t="s">
         <v>24</v>
       </c>
-      <c r="N47" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F47,'feed pars'!B$6:B$49,0))</f>
-        <v>1.0989010989010988</v>
+      <c r="N47" s="10">
+        <f>N46</f>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M48" t="s">
         <v>24</v>
       </c>
       <c r="N48" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F48,'feed pars'!B$6:B$49,0))</f>
-        <v>4.3478260869565215</v>
+        <v>1.0989010989010988</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M49" t="s">
         <v>24</v>
       </c>
       <c r="N49" s="8">
         <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F49,'feed pars'!B$6:B$49,0))</f>
-        <v>1.0863661053775122</v>
+        <v>4.3478260869565215</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F50" t="s">
-        <v>658</v>
+        <v>76</v>
       </c>
       <c r="J50" t="s">
-        <v>659</v>
+        <v>76</v>
       </c>
       <c r="M50" t="s">
         <v>24</v>
       </c>
-      <c r="N50" s="10">
-        <v>1</v>
+      <c r="N50" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F50,'feed pars'!B$6:B$49,0))</f>
+        <v>1.0863661053775122</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F51" t="s">
-        <v>193</v>
+        <v>658</v>
       </c>
       <c r="J51" t="s">
-        <v>193</v>
+        <v>659</v>
       </c>
       <c r="M51" t="s">
         <v>24</v>
       </c>
-      <c r="N51" s="8">
-        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F51,'feed pars'!B$6:B$49,0))</f>
+      <c r="N51" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F52" t="s">
+        <v>193</v>
+      </c>
+      <c r="J52" t="s">
+        <v>193</v>
+      </c>
+      <c r="M52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" s="8">
+        <f>1/INDEX('feed pars'!C$6:C$49/100,MATCH(F52,'feed pars'!B$6:B$49,0))</f>
         <v>1.1152416356877324</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N52" s="8"/>
-    </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="N53" s="8"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N53" s="8"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F54" t="s">
+      <c r="N54" s="8"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F55" t="s">
         <v>78</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K55" t="s">
         <v>78</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M55" t="s">
         <v>24</v>
       </c>
-      <c r="N54" s="8">
+      <c r="N55" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N55" s="8"/>
-    </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="N56" s="8"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M58" s="5" t="s">
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M59" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="N58" s="5">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5" t="s">
+      <c r="N59" s="5">
+        <v>0</v>
+      </c>
+      <c r="O59" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P58" s="5" t="s">
+      <c r="P59" s="5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I59" t="s">
-        <v>28</v>
-      </c>
-      <c r="M59" t="s">
-        <v>81</v>
-      </c>
-      <c r="N59" s="9">
-        <v>95</v>
-      </c>
-      <c r="O59" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I60" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M60" t="s">
         <v>81</v>
@@ -4090,7 +4119,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M61" t="s">
         <v>81</v>
@@ -4103,26 +4132,22 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>83</v>
-      </c>
       <c r="I62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M62" t="s">
         <v>81</v>
       </c>
       <c r="N62" s="9">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="O62" t="s">
         <v>82</v>
       </c>
-      <c r="P62" s="9"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I63" t="s">
         <v>36</v>
@@ -4140,10 +4165,10 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I64" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M64" t="s">
         <v>81</v>
@@ -4158,7 +4183,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I65" t="s">
         <v>35</v>
@@ -4176,10 +4201,10 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I66" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M66" t="s">
         <v>81</v>
@@ -4194,7 +4219,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I67" t="s">
         <v>37</v>
@@ -4211,34 +4236,37 @@
       <c r="P67" s="9"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N68" s="9"/>
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="I68" t="s">
+        <v>37</v>
+      </c>
+      <c r="M68" t="s">
+        <v>81</v>
+      </c>
+      <c r="N68" s="9">
+        <v>30</v>
+      </c>
+      <c r="O68" t="s">
+        <v>82</v>
+      </c>
       <c r="P68" s="9"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="N69" s="9"/>
       <c r="P69" s="9"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I70" t="s">
-        <v>28</v>
-      </c>
-      <c r="M70" t="s">
-        <v>86</v>
-      </c>
-      <c r="N70" s="9">
-        <v>5</v>
-      </c>
-      <c r="O70" t="s">
-        <v>82</v>
-      </c>
+      <c r="A70" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="N70" s="9"/>
       <c r="P70" s="9"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I71" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M71" t="s">
         <v>86</v>
@@ -4253,7 +4281,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M72" t="s">
         <v>86</v>
@@ -4267,121 +4295,121 @@
       <c r="P72" s="9"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N73" s="9"/>
+      <c r="I73" t="s">
+        <v>34</v>
+      </c>
+      <c r="M73" t="s">
+        <v>86</v>
+      </c>
+      <c r="N73" s="9">
+        <v>5</v>
+      </c>
+      <c r="O73" t="s">
+        <v>82</v>
+      </c>
       <c r="P73" s="9"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+      <c r="N74" s="9"/>
+      <c r="P74" s="9"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M75" s="5" t="s">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M76" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N75" s="5">
+      <c r="N76" s="5">
         <v>100</v>
       </c>
-      <c r="O75" s="5" t="s">
+      <c r="O76" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P75" s="5" t="s">
+      <c r="P76" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I76" t="s">
-        <v>49</v>
-      </c>
-      <c r="M76" t="s">
-        <v>88</v>
-      </c>
-      <c r="N76" s="11">
-        <v>0</v>
-      </c>
-      <c r="O76" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P76" s="5"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I77" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M77" t="s">
         <v>88</v>
       </c>
-      <c r="N77" s="9">
-        <v>0</v>
-      </c>
-      <c r="O77" t="s">
+      <c r="N77" s="11">
+        <v>0</v>
+      </c>
+      <c r="O77" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="P77" s="9" t="s">
-        <v>89</v>
-      </c>
+      <c r="P77" s="5"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I78" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M78" t="s">
         <v>88</v>
       </c>
       <c r="N78" s="9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O78" t="s">
         <v>82</v>
       </c>
       <c r="P78" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I79" t="s">
+        <v>40</v>
+      </c>
+      <c r="M79" t="s">
+        <v>88</v>
+      </c>
+      <c r="N79" s="9">
+        <v>50</v>
+      </c>
+      <c r="O79" t="s">
+        <v>82</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N79" s="9"/>
-      <c r="P79" s="9"/>
-    </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J80" t="s">
-        <v>60</v>
-      </c>
-      <c r="M80" t="s">
-        <v>88</v>
-      </c>
-      <c r="N80" s="9">
-        <v>80</v>
-      </c>
-      <c r="O80" t="s">
-        <v>82</v>
-      </c>
+      <c r="N80" s="9"/>
       <c r="P80" s="9"/>
     </row>
     <row r="81" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J81" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="M81" t="s">
         <v>88</v>
       </c>
       <c r="N81" s="9">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="O81" t="s">
         <v>82</v>
@@ -4390,13 +4418,13 @@
     </row>
     <row r="82" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J82" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M82" t="s">
         <v>88</v>
       </c>
       <c r="N82" s="9">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O82" t="s">
         <v>82</v>
@@ -4405,7 +4433,7 @@
     </row>
     <row r="83" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M83" t="s">
         <v>88</v>
@@ -4420,7 +4448,7 @@
     </row>
     <row r="84" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J84" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M84" t="s">
         <v>88</v>
@@ -4435,7 +4463,7 @@
     </row>
     <row r="85" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M85" t="s">
         <v>88</v>
@@ -4450,7 +4478,7 @@
     </row>
     <row r="86" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M86" t="s">
         <v>88</v>
@@ -4465,7 +4493,7 @@
     </row>
     <row r="87" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J87" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M87" t="s">
         <v>88</v>
@@ -4480,7 +4508,7 @@
     </row>
     <row r="88" spans="3:16" x14ac:dyDescent="0.25">
       <c r="J88" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="M88" t="s">
         <v>88</v>
@@ -4494,25 +4522,22 @@
       <c r="P88" s="9"/>
     </row>
     <row r="89" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="N89" s="9"/>
+      <c r="J89" t="s">
+        <v>193</v>
+      </c>
+      <c r="M89" t="s">
+        <v>88</v>
+      </c>
+      <c r="N89" s="9">
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
+        <v>82</v>
+      </c>
       <c r="P89" s="9"/>
     </row>
     <row r="90" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C90" t="s">
-        <v>644</v>
-      </c>
-      <c r="J90" t="s">
-        <v>60</v>
-      </c>
-      <c r="M90" t="s">
-        <v>88</v>
-      </c>
-      <c r="N90" s="9">
-        <v>85</v>
-      </c>
-      <c r="O90" t="s">
-        <v>82</v>
-      </c>
+      <c r="N90" s="9"/>
       <c r="P90" s="9"/>
     </row>
     <row r="91" spans="3:16" x14ac:dyDescent="0.25">
@@ -4520,13 +4545,13 @@
         <v>644</v>
       </c>
       <c r="J91" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M91" t="s">
         <v>88</v>
       </c>
       <c r="N91" s="9">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="O91" t="s">
         <v>82</v>
@@ -4538,13 +4563,13 @@
         <v>644</v>
       </c>
       <c r="J92" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M92" t="s">
         <v>88</v>
       </c>
       <c r="N92" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O92" t="s">
         <v>82</v>
@@ -4556,27 +4581,25 @@
         <v>644</v>
       </c>
       <c r="J93" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M93" t="s">
         <v>88</v>
       </c>
       <c r="N93" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O93" t="s">
         <v>82</v>
       </c>
-      <c r="P93" s="9" t="s">
-        <v>645</v>
-      </c>
+      <c r="P93" s="9"/>
     </row>
     <row r="94" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
         <v>644</v>
       </c>
       <c r="J94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M94" t="s">
         <v>88</v>
@@ -4587,14 +4610,16 @@
       <c r="O94" t="s">
         <v>82</v>
       </c>
-      <c r="P94" s="9"/>
+      <c r="P94" s="9" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="95" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>644</v>
       </c>
       <c r="J95" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M95" t="s">
         <v>88</v>
@@ -4608,68 +4633,54 @@
       <c r="P95" s="9"/>
     </row>
     <row r="96" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="N96" s="9"/>
+      <c r="C96" t="s">
+        <v>644</v>
+      </c>
+      <c r="J96" t="s">
+        <v>74</v>
+      </c>
+      <c r="M96" t="s">
+        <v>88</v>
+      </c>
+      <c r="N96" s="9">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
+        <v>82</v>
+      </c>
       <c r="P96" s="9"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+      <c r="N97" s="9"/>
+      <c r="P97" s="9"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3"/>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3"/>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>92</v>
-      </c>
-      <c r="B99" t="s">
-        <v>93</v>
-      </c>
-      <c r="E99" t="s">
-        <v>94</v>
-      </c>
-      <c r="H99" t="s">
-        <v>95</v>
-      </c>
-      <c r="I99" t="s">
-        <v>34</v>
-      </c>
-      <c r="M99" t="s">
-        <v>96</v>
-      </c>
-      <c r="N99" s="11">
-        <v>28</v>
-      </c>
-      <c r="O99" t="s">
-        <v>82</v>
-      </c>
-      <c r="P99" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>98</v>
-      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>92</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E100" t="s">
         <v>94</v>
@@ -4684,12 +4695,14 @@
         <v>96</v>
       </c>
       <c r="N100" s="11">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="O100" t="s">
         <v>82</v>
       </c>
-      <c r="P100" s="11"/>
+      <c r="P100" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="Q100" t="s">
         <v>98</v>
       </c>
@@ -4702,7 +4715,7 @@
         <v>99</v>
       </c>
       <c r="E101" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H101" t="s">
         <v>95</v>
@@ -4713,16 +4726,13 @@
       <c r="M101" t="s">
         <v>96</v>
       </c>
-      <c r="N101" s="13">
-        <f>N100</f>
+      <c r="N101" s="11">
         <v>100</v>
       </c>
       <c r="O101" t="s">
         <v>82</v>
       </c>
-      <c r="P101" s="11" t="s">
-        <v>101</v>
-      </c>
+      <c r="P101" s="11"/>
       <c r="Q101" t="s">
         <v>98</v>
       </c>
@@ -4731,6 +4741,12 @@
       <c r="A102" t="s">
         <v>92</v>
       </c>
+      <c r="B102" t="s">
+        <v>99</v>
+      </c>
+      <c r="E102" t="s">
+        <v>100</v>
+      </c>
       <c r="H102" t="s">
         <v>95</v>
       </c>
@@ -4740,20 +4756,23 @@
       <c r="M102" t="s">
         <v>96</v>
       </c>
-      <c r="N102" s="11">
-        <v>80</v>
+      <c r="N102" s="13">
+        <f>N101</f>
+        <v>100</v>
       </c>
       <c r="O102" t="s">
         <v>82</v>
       </c>
-      <c r="P102" s="11"/>
+      <c r="P102" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="Q102" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H103" t="s">
         <v>95</v>
@@ -4765,19 +4784,19 @@
         <v>96</v>
       </c>
       <c r="N103" s="11">
-        <v>14.5</v>
+        <v>80</v>
       </c>
       <c r="O103" t="s">
         <v>82</v>
       </c>
-      <c r="P103" s="9"/>
+      <c r="P103" s="11"/>
       <c r="Q103" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H104" t="s">
         <v>95</v>
@@ -4789,23 +4808,20 @@
         <v>96</v>
       </c>
       <c r="N104" s="11">
-        <v>100</v>
+        <v>14.5</v>
       </c>
       <c r="O104" t="s">
         <v>82</v>
       </c>
       <c r="P104" s="9"/>
       <c r="Q104" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
-      <c r="D105" t="s">
-        <v>106</v>
-      </c>
       <c r="H105" t="s">
         <v>95</v>
       </c>
@@ -4816,7 +4832,7 @@
         <v>96</v>
       </c>
       <c r="N105" s="11">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="O105" t="s">
         <v>82</v>
@@ -4833,9 +4849,6 @@
       <c r="D106" t="s">
         <v>106</v>
       </c>
-      <c r="E106" t="s">
-        <v>107</v>
-      </c>
       <c r="H106" t="s">
         <v>95</v>
       </c>
@@ -4846,7 +4859,7 @@
         <v>96</v>
       </c>
       <c r="N106" s="11">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O106" t="s">
         <v>82</v>
@@ -4857,47 +4870,63 @@
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N107" s="9"/>
+      <c r="A107" t="s">
+        <v>104</v>
+      </c>
+      <c r="D107" t="s">
+        <v>106</v>
+      </c>
+      <c r="E107" t="s">
+        <v>107</v>
+      </c>
+      <c r="H107" t="s">
+        <v>95</v>
+      </c>
+      <c r="I107" t="s">
+        <v>34</v>
+      </c>
+      <c r="M107" t="s">
+        <v>96</v>
+      </c>
+      <c r="N107" s="11">
+        <v>69</v>
+      </c>
+      <c r="O107" t="s">
+        <v>82</v>
+      </c>
       <c r="P107" s="9"/>
+      <c r="Q107" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+      <c r="N108" s="9"/>
+      <c r="P108" s="9"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3"/>
-      <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
-      <c r="L108" s="3"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="3"/>
-      <c r="O108" s="3"/>
-      <c r="P108" s="3"/>
-      <c r="Q108" s="3"/>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M109" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="N109" s="5">
-        <v>0</v>
-      </c>
-      <c r="O109" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="P109" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M110" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N110" s="5">
         <v>0</v>
@@ -4910,39 +4939,29 @@
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>92</v>
-      </c>
-      <c r="B111" t="s">
-        <v>93</v>
-      </c>
-      <c r="E111" t="s">
-        <v>94</v>
-      </c>
-      <c r="G111" t="s">
-        <v>111</v>
-      </c>
-      <c r="M111" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N111" s="11">
-        <f>(0.8*20+0.2*2)</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="O111" s="11" t="s">
+      <c r="M111" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="N111" s="5">
+        <v>0</v>
+      </c>
+      <c r="O111" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P111" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>103</v>
+      <c r="P111" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>92</v>
       </c>
+      <c r="B112" t="s">
+        <v>93</v>
+      </c>
+      <c r="E112" t="s">
+        <v>94</v>
+      </c>
       <c r="G112" t="s">
         <v>111</v>
       </c>
@@ -4950,37 +4969,38 @@
         <v>109</v>
       </c>
       <c r="N112" s="11">
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O112" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P112" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>92</v>
+      </c>
+      <c r="G113" t="s">
+        <v>111</v>
+      </c>
+      <c r="M113" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N113" s="11">
         <f>(0.6*20+0.4*2)</f>
         <v>12.8</v>
       </c>
-      <c r="O112" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P112" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>104</v>
-      </c>
-      <c r="G113" t="s">
-        <v>111</v>
-      </c>
-      <c r="M113" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N113" s="11">
-        <v>2</v>
-      </c>
       <c r="O113" s="11" t="s">
         <v>82</v>
       </c>
       <c r="P113" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q113" t="s">
         <v>103</v>
@@ -4988,7 +5008,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G114" t="s">
         <v>111</v>
@@ -5010,46 +5030,43 @@
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M115" s="11"/>
-      <c r="N115" s="11"/>
-      <c r="O115" s="11"/>
-      <c r="P115" s="11"/>
+      <c r="A115" t="s">
+        <v>102</v>
+      </c>
+      <c r="G115" t="s">
+        <v>111</v>
+      </c>
+      <c r="M115" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N115" s="11">
+        <v>2</v>
+      </c>
+      <c r="O115" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P115" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>92</v>
-      </c>
-      <c r="B116" t="s">
-        <v>93</v>
-      </c>
-      <c r="E116" t="s">
-        <v>94</v>
-      </c>
-      <c r="G116" t="s">
-        <v>111</v>
-      </c>
-      <c r="M116" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="N116" s="11">
-        <v>5</v>
-      </c>
-      <c r="O116" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P116" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>103</v>
-      </c>
+      <c r="M116" s="11"/>
+      <c r="N116" s="11"/>
+      <c r="O116" s="11"/>
+      <c r="P116" s="11"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>92</v>
       </c>
+      <c r="B117" t="s">
+        <v>93</v>
+      </c>
       <c r="E117" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="G117" t="s">
         <v>111</v>
@@ -5074,6 +5091,9 @@
       <c r="A118" t="s">
         <v>92</v>
       </c>
+      <c r="E118" t="s">
+        <v>116</v>
+      </c>
       <c r="G118" t="s">
         <v>111</v>
       </c>
@@ -5081,43 +5101,45 @@
         <v>110</v>
       </c>
       <c r="N118" s="11">
+        <v>5</v>
+      </c>
+      <c r="O118" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P118" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>92</v>
+      </c>
+      <c r="G119" t="s">
+        <v>111</v>
+      </c>
+      <c r="M119" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N119" s="11">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="O118" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P118" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>104</v>
-      </c>
-      <c r="G119" t="s">
-        <v>111</v>
-      </c>
-      <c r="M119" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="N119" s="11">
-        <v>15</v>
-      </c>
       <c r="O119" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="P119" s="11"/>
+      <c r="P119" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="Q119" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G120" t="s">
         <v>111</v>
@@ -5137,67 +5159,51 @@
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M121" s="11"/>
-      <c r="N121" s="11"/>
-      <c r="O121" s="11"/>
+      <c r="A121" t="s">
+        <v>102</v>
+      </c>
+      <c r="G121" t="s">
+        <v>111</v>
+      </c>
+      <c r="M121" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N121" s="11">
+        <v>15</v>
+      </c>
+      <c r="O121" s="11" t="s">
+        <v>82</v>
+      </c>
       <c r="P121" s="11"/>
+      <c r="Q121" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" s="14"/>
-      <c r="B122" s="14"/>
-      <c r="E122" s="14"/>
-      <c r="G122" t="s">
-        <v>30</v>
-      </c>
-      <c r="M122" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N122" s="11">
-        <v>5</v>
-      </c>
-      <c r="O122" s="11" t="s">
-        <v>82</v>
-      </c>
+      <c r="M122" s="11"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="11"/>
       <c r="P122" s="11"/>
-      <c r="Q122" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123" s="14" t="str">
-        <f>A116</f>
-        <v>cattle</v>
-      </c>
-      <c r="B123" s="14" t="str">
-        <f>B116</f>
-        <v>dairy</v>
-      </c>
-      <c r="E123" s="14" t="str">
-        <f>E116</f>
-        <v>cows</v>
-      </c>
+      <c r="A123" s="14"/>
+      <c r="B123" s="14"/>
+      <c r="E123" s="14"/>
       <c r="G123" t="s">
         <v>30</v>
       </c>
-      <c r="M123" s="14" t="str">
-        <f t="shared" ref="M123:Q125" si="0">M116</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N123" s="14">
-        <f t="shared" si="0"/>
+      <c r="M123" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N123" s="11">
         <v>5</v>
       </c>
-      <c r="O123" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>%</v>
-      </c>
-      <c r="P123" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q123" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
+      <c r="O123" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P123" s="11"/>
+      <c r="Q123" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -5205,15 +5211,19 @@
         <f>A117</f>
         <v>cattle</v>
       </c>
+      <c r="B124" s="14" t="str">
+        <f>B117</f>
+        <v>dairy</v>
+      </c>
       <c r="E124" s="14" t="str">
         <f>E117</f>
-        <v>bulls</v>
+        <v>cows</v>
       </c>
       <c r="G124" t="s">
         <v>30</v>
       </c>
       <c r="M124" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M124:Q126" si="0">M117</f>
         <v>feeding_losses</v>
       </c>
       <c r="N124" s="14">
@@ -5238,6 +5248,10 @@
         <f>A118</f>
         <v>cattle</v>
       </c>
+      <c r="E125" s="14" t="str">
+        <f>E118</f>
+        <v>bulls</v>
+      </c>
       <c r="G125" t="s">
         <v>30</v>
       </c>
@@ -5247,7 +5261,7 @@
       </c>
       <c r="N125" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O125" s="14" t="str">
         <f t="shared" si="0"/>
@@ -5255,7 +5269,7 @@
       </c>
       <c r="P125" s="14" t="str">
         <f t="shared" si="0"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="Q125" s="14" t="str">
         <f t="shared" si="0"/>
@@ -5265,39 +5279,42 @@
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="str">
         <f>A119</f>
-        <v>sheep</v>
+        <v>cattle</v>
       </c>
       <c r="G126" t="s">
         <v>30</v>
       </c>
       <c r="M126" s="14" t="str">
-        <f t="shared" ref="M126:O127" si="1">M119</f>
+        <f t="shared" si="0"/>
         <v>feeding_losses</v>
       </c>
       <c r="N126" s="14">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="O126" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>%</v>
       </c>
-      <c r="P126" s="14"/>
+      <c r="P126" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>10% feeding on pasture</v>
+      </c>
       <c r="Q126" s="14" t="str">
-        <f>Q119</f>
+        <f t="shared" si="0"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="str">
         <f>A120</f>
-        <v>horses</v>
+        <v>sheep</v>
       </c>
       <c r="G127" t="s">
         <v>30</v>
       </c>
       <c r="M127" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M127:O128" si="1">M120</f>
         <v>feeding_losses</v>
       </c>
       <c r="N127" s="14">
@@ -5315,66 +5332,55 @@
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="14"/>
-      <c r="M128" s="14"/>
-      <c r="N128" s="14"/>
-      <c r="O128" s="14"/>
+      <c r="A128" s="14" t="str">
+        <f>A121</f>
+        <v>horses</v>
+      </c>
+      <c r="G128" t="s">
+        <v>30</v>
+      </c>
+      <c r="M128" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N128" s="14">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O128" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
       <c r="P128" s="14"/>
-      <c r="Q128" s="14"/>
+      <c r="Q128" s="14" t="str">
+        <f>Q121</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G129" t="s">
-        <v>118</v>
-      </c>
-      <c r="M129" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N129" s="11">
-        <v>5</v>
-      </c>
-      <c r="O129" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P129" s="11"/>
-      <c r="Q129" t="s">
-        <v>103</v>
-      </c>
+      <c r="A129" s="14"/>
+      <c r="M129" s="14"/>
+      <c r="N129" s="14"/>
+      <c r="O129" s="14"/>
+      <c r="P129" s="14"/>
+      <c r="Q129" s="14"/>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="str">
-        <f>A116</f>
-        <v>cattle</v>
-      </c>
-      <c r="B130" s="14" t="str">
-        <f>B116</f>
-        <v>dairy</v>
-      </c>
-      <c r="E130" s="14" t="str">
-        <f>E116</f>
-        <v>cows</v>
-      </c>
       <c r="G130" t="s">
         <v>118</v>
       </c>
-      <c r="M130" s="14" t="str">
-        <f t="shared" ref="M130:Q132" si="2">M116</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="N130" s="14">
-        <f t="shared" si="2"/>
+      <c r="M130" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N130" s="11">
         <v>5</v>
       </c>
-      <c r="O130" s="14" t="str">
-        <f t="shared" si="2"/>
-        <v>%</v>
-      </c>
-      <c r="P130" s="14" t="str">
-        <f t="shared" si="2"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="Q130" s="14" t="str">
-        <f t="shared" si="2"/>
-        <v>Cederberg &amp; Henriksson (2020)</v>
+      <c r="O130" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P130" s="11"/>
+      <c r="Q130" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -5382,15 +5388,19 @@
         <f>A117</f>
         <v>cattle</v>
       </c>
+      <c r="B131" s="14" t="str">
+        <f>B117</f>
+        <v>dairy</v>
+      </c>
       <c r="E131" s="14" t="str">
         <f>E117</f>
-        <v>bulls</v>
+        <v>cows</v>
       </c>
       <c r="G131" t="s">
         <v>118</v>
       </c>
       <c r="M131" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M131:Q133" si="2">M117</f>
         <v>feeding_losses</v>
       </c>
       <c r="N131" s="14">
@@ -5415,6 +5425,10 @@
         <f>A118</f>
         <v>cattle</v>
       </c>
+      <c r="E132" s="14" t="str">
+        <f>E118</f>
+        <v>bulls</v>
+      </c>
       <c r="G132" t="s">
         <v>118</v>
       </c>
@@ -5424,7 +5438,7 @@
       </c>
       <c r="N132" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O132" s="14" t="str">
         <f t="shared" si="2"/>
@@ -5432,7 +5446,7 @@
       </c>
       <c r="P132" s="14" t="str">
         <f t="shared" si="2"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="Q132" s="14" t="str">
         <f t="shared" si="2"/>
@@ -5442,39 +5456,42 @@
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="str">
         <f>A119</f>
-        <v>sheep</v>
+        <v>cattle</v>
       </c>
       <c r="G133" t="s">
         <v>118</v>
       </c>
       <c r="M133" s="14" t="str">
-        <f t="shared" ref="M133:O134" si="3">M119</f>
+        <f t="shared" si="2"/>
         <v>feeding_losses</v>
       </c>
       <c r="N133" s="14">
-        <f t="shared" si="3"/>
-        <v>15</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="O133" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>%</v>
       </c>
-      <c r="P133" s="11"/>
+      <c r="P133" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>10% feeding on pasture</v>
+      </c>
       <c r="Q133" s="14" t="str">
-        <f>Q119</f>
+        <f t="shared" si="2"/>
         <v>Cederberg &amp; Henriksson (2020)</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="str">
         <f>A120</f>
-        <v>horses</v>
+        <v>sheep</v>
       </c>
       <c r="G134" t="s">
         <v>118</v>
       </c>
       <c r="M134" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="M134:O135" si="3">M120</f>
         <v>feeding_losses</v>
       </c>
       <c r="N134" s="14">
@@ -5492,21 +5509,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N135" s="9"/>
+      <c r="A135" s="14" t="str">
+        <f>A121</f>
+        <v>horses</v>
+      </c>
+      <c r="G135" t="s">
+        <v>118</v>
+      </c>
+      <c r="M135" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="N135" s="14">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="O135" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v>%</v>
+      </c>
       <c r="P135" s="11"/>
+      <c r="Q135" s="14" t="str">
+        <f>Q121</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136" s="9"/>
-      <c r="G136" t="s">
-        <v>119</v>
-      </c>
-      <c r="M136" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N136" s="11"/>
-      <c r="P136" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="N136" s="9"/>
+      <c r="P136" s="11"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="9"/>
@@ -5514,40 +5544,40 @@
         <v>119</v>
       </c>
       <c r="M137" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="N137" s="11">
-        <v>2</v>
-      </c>
-      <c r="O137" s="11" t="s">
-        <v>82</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N137" s="11"/>
       <c r="P137" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="9"/>
-      <c r="M138" s="11"/>
-      <c r="N138" s="11"/>
-      <c r="O138" s="11"/>
-      <c r="P138" s="9"/>
+      <c r="G138" t="s">
+        <v>119</v>
+      </c>
+      <c r="M138" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N138" s="11">
+        <v>2</v>
+      </c>
+      <c r="O138" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P138" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="9"/>
-      <c r="G139" t="s">
-        <v>123</v>
-      </c>
-      <c r="M139" s="11" t="s">
-        <v>109</v>
-      </c>
+      <c r="M139" s="11"/>
       <c r="N139" s="11"/>
-      <c r="P139" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="O139" s="11"/>
+      <c r="P139" s="9"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="9"/>
@@ -5555,111 +5585,106 @@
         <v>123</v>
       </c>
       <c r="M140" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N140" s="11"/>
+      <c r="P140" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141" s="9"/>
+      <c r="G141" t="s">
+        <v>123</v>
+      </c>
+      <c r="M141" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="N140" s="11">
+      <c r="N141" s="11">
         <v>3</v>
       </c>
-      <c r="O140" s="11" t="s">
+      <c r="O141" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="P140" s="9" t="s">
+      <c r="P141" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="Q140" t="s">
+      <c r="Q141" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N141" s="9"/>
-      <c r="P141" s="11"/>
-    </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
+      <c r="N142" s="9"/>
+      <c r="P142" s="11"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
-      <c r="I142" s="3"/>
-      <c r="J142" s="3"/>
-      <c r="K142" s="3"/>
-      <c r="L142" s="3"/>
-      <c r="M142" s="3"/>
-      <c r="N142" s="3"/>
-      <c r="O142" s="3"/>
-      <c r="P142" s="3"/>
-      <c r="Q142" s="3"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
+      <c r="P143" s="3"/>
+      <c r="Q143" s="3"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>92</v>
       </c>
-      <c r="N143" s="11"/>
-      <c r="P143" s="11" t="s">
+      <c r="N144" s="11"/>
+      <c r="P144" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144" s="11" t="s">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="9"/>
-      <c r="J144" s="9"/>
-      <c r="K144" s="9"/>
-      <c r="L144" s="9"/>
-      <c r="M144" s="11" t="s">
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9"/>
+      <c r="E145" s="9"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="9"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="9"/>
+      <c r="K145" s="9"/>
+      <c r="L145" s="9"/>
+      <c r="M145" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="N144" s="11">
+      <c r="N145" s="11">
         <v>6.7</v>
       </c>
-      <c r="O144" s="11" t="s">
+      <c r="O145" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="P144" s="9"/>
-      <c r="Q144" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>102</v>
-      </c>
-      <c r="M145" t="s">
-        <v>129</v>
-      </c>
-      <c r="N145" s="11">
-        <v>18</v>
-      </c>
-      <c r="O145" t="s">
-        <v>130</v>
       </c>
       <c r="P145" s="9"/>
       <c r="Q145" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="M146" t="s">
         <v>129</v>
       </c>
       <c r="N146" s="11">
-        <v>1.5</v>
+        <v>18</v>
       </c>
       <c r="O146" t="s">
         <v>130</v>
@@ -5671,13 +5696,13 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M147" t="s">
         <v>129</v>
       </c>
       <c r="N147" s="11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O147" t="s">
         <v>130</v>
@@ -5688,28 +5713,28 @@
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N148" s="11"/>
+      <c r="A148" t="s">
+        <v>84</v>
+      </c>
+      <c r="M148" t="s">
+        <v>129</v>
+      </c>
+      <c r="N148" s="11">
+        <v>0</v>
+      </c>
+      <c r="O148" t="s">
+        <v>130</v>
+      </c>
       <c r="P148" s="9"/>
+      <c r="Q148" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M149" t="s">
-        <v>132</v>
-      </c>
-      <c r="N149" s="11">
-        <v>1</v>
-      </c>
-      <c r="O149" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="P149" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q149" s="11"/>
+      <c r="N149" s="11"/>
+      <c r="P149" s="9"/>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>92</v>
-      </c>
       <c r="M150" t="s">
         <v>132</v>
       </c>
@@ -5719,19 +5744,15 @@
       <c r="O150" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="P150" s="11"/>
+      <c r="P150" s="11" t="s">
+        <v>134</v>
+      </c>
       <c r="Q150" s="11"/>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>92</v>
       </c>
-      <c r="B151" t="s">
-        <v>93</v>
-      </c>
-      <c r="E151" t="s">
-        <v>94</v>
-      </c>
       <c r="M151" t="s">
         <v>132</v>
       </c>
@@ -5752,7 +5773,7 @@
         <v>93</v>
       </c>
       <c r="E152" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="M152" t="s">
         <v>132</v>
@@ -5771,7 +5792,7 @@
         <v>92</v>
       </c>
       <c r="B153" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E153" t="s">
         <v>116</v>
@@ -5789,38 +5810,60 @@
       <c r="Q153" s="11"/>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N154" s="9"/>
-      <c r="P154" s="9"/>
+      <c r="A154" t="s">
+        <v>92</v>
+      </c>
+      <c r="B154" t="s">
+        <v>99</v>
+      </c>
+      <c r="E154" t="s">
+        <v>116</v>
+      </c>
+      <c r="M154" t="s">
+        <v>132</v>
+      </c>
+      <c r="N154" s="11">
+        <v>1</v>
+      </c>
+      <c r="O154" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="P154" s="11"/>
+      <c r="Q154" s="11"/>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A155" s="2" t="s">
+      <c r="N155" s="9"/>
+      <c r="P155" s="9"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="3"/>
-      <c r="F155" s="3"/>
-      <c r="G155" s="3"/>
-      <c r="H155" s="3"/>
-      <c r="I155" s="3"/>
-      <c r="J155" s="3"/>
-      <c r="K155" s="3"/>
-      <c r="L155" s="3"/>
-      <c r="M155" s="3"/>
-      <c r="N155" s="3"/>
-      <c r="O155" s="3"/>
-      <c r="P155" s="3"/>
-      <c r="Q155" s="3"/>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M156" t="s">
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="3"/>
+      <c r="K156" s="3"/>
+      <c r="L156" s="3"/>
+      <c r="M156" s="3"/>
+      <c r="N156" s="3"/>
+      <c r="O156" s="3"/>
+      <c r="P156" s="3"/>
+      <c r="Q156" s="3"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M157" t="s">
         <v>135</v>
       </c>
-      <c r="N156" s="11" t="s">
+      <c r="N157" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="P156" t="s">
+      <c r="P157" t="s">
         <v>648</v>
       </c>
     </row>
